--- a/CONSOLIDADO DASHBOARD VILLA.xlsx
+++ b/CONSOLIDADO DASHBOARD VILLA.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30117"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FCHAVEZC\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FCHAVEZC\Desktop\KPIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{733DB302-AA71-442D-9F67-D36D3347FCA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1418DAF3-2709-4340-867E-49C37996D66C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CONSOLIDADO" sheetId="1" r:id="rId1"/>
     <sheet name="RESUMEN" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CONSOLIDADO!$A$1:$M$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CONSOLIDADO!$A$1:$M$100</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="987" uniqueCount="379">
   <si>
     <t>ID</t>
   </si>
@@ -916,13 +916,274 @@
   </si>
   <si>
     <t>Alta/Crítica</t>
+  </si>
+  <si>
+    <t>27/05/2026</t>
+  </si>
+  <si>
+    <t>Ingreso 2</t>
+  </si>
+  <si>
+    <t>Chapa de mampara malograda.</t>
+  </si>
+  <si>
+    <t>20:10</t>
+  </si>
+  <si>
+    <t>Baño discapacitados 1er piso</t>
+  </si>
+  <si>
+    <t>Filtración de agua en tubería.</t>
+  </si>
+  <si>
+    <t>21:07</t>
+  </si>
+  <si>
+    <t>Escaleras junto ascensor</t>
+  </si>
+  <si>
+    <t>Luces apagadas en 2do y 3er piso.</t>
+  </si>
+  <si>
+    <t>07:08</t>
+  </si>
+  <si>
+    <t>Microbiología 308 y 310</t>
+  </si>
+  <si>
+    <t>Sin gas en mecheros de laboratorio.</t>
+  </si>
+  <si>
+    <t>06:55</t>
+  </si>
+  <si>
+    <t>Anatomía Animal 101</t>
+  </si>
+  <si>
+    <t>Puerta laboratorio</t>
+  </si>
+  <si>
+    <t>Chapa atascada.</t>
+  </si>
+  <si>
+    <t>07:26</t>
+  </si>
+  <si>
+    <t>Bromatología A212</t>
+  </si>
+  <si>
+    <t>Señalética caída.</t>
+  </si>
+  <si>
+    <t>11:01</t>
+  </si>
+  <si>
+    <t>Laboratorio O302</t>
+  </si>
+  <si>
+    <t>Goteo persistente de agua.</t>
+  </si>
+  <si>
+    <t>10:47</t>
+  </si>
+  <si>
+    <t>Anatomía Patológica 102</t>
+  </si>
+  <si>
+    <t>13:39</t>
+  </si>
+  <si>
+    <t>Biología O309</t>
+  </si>
+  <si>
+    <t>Filtración de agua en techo.</t>
+  </si>
+  <si>
+    <t>14:33</t>
+  </si>
+  <si>
+    <t>Corte de energía en laboratorio.</t>
+  </si>
+  <si>
+    <t>Fisiología 2-304</t>
+  </si>
+  <si>
+    <t>EQUIPO</t>
+  </si>
+  <si>
+    <t>Botón de encendido averiado.</t>
+  </si>
+  <si>
+    <t>16:32</t>
+  </si>
+  <si>
+    <t>BIO5 PA-305</t>
+  </si>
+  <si>
+    <t>INFRAESTRUCTURA</t>
+  </si>
+  <si>
+    <t>Lámina metálica levantada en acceso.</t>
+  </si>
+  <si>
+    <t>Fisiología 4</t>
+  </si>
+  <si>
+    <t>Pestillo trabado de puerta.</t>
+  </si>
+  <si>
+    <t>07:27</t>
+  </si>
+  <si>
+    <t>O307</t>
+  </si>
+  <si>
+    <t>Tomacorrientes salidos.</t>
+  </si>
+  <si>
+    <t>14:01</t>
+  </si>
+  <si>
+    <t>O202</t>
+  </si>
+  <si>
+    <t>Aula</t>
+  </si>
+  <si>
+    <t>Sin energía en punto de docente.</t>
+  </si>
+  <si>
+    <t>28/05/2026</t>
+  </si>
+  <si>
+    <t>08:06</t>
+  </si>
+  <si>
+    <t>Revisión solicitada en laboratorio 310.</t>
+  </si>
+  <si>
+    <t>09:38</t>
+  </si>
+  <si>
+    <t>A302</t>
+  </si>
+  <si>
+    <t>Ing. Agroforestal</t>
+  </si>
+  <si>
+    <t>Problema en lavadero.</t>
+  </si>
+  <si>
+    <t>11:58</t>
+  </si>
+  <si>
+    <t>B5 PA</t>
+  </si>
+  <si>
+    <t>Riel de puerta pendiente de reparación.</t>
+  </si>
+  <si>
+    <t>12:29</t>
+  </si>
+  <si>
+    <t>N103</t>
+  </si>
+  <si>
+    <t>Biología Molecular</t>
+  </si>
+  <si>
+    <t>Goteo de agua en lavadero.</t>
+  </si>
+  <si>
+    <t>En atención</t>
+  </si>
+  <si>
+    <t>A208</t>
+  </si>
+  <si>
+    <t>Física</t>
+  </si>
+  <si>
+    <t>08:04</t>
+  </si>
+  <si>
+    <t>Tópico</t>
+  </si>
+  <si>
+    <t>Silla de ruedas con tuercas salidas.</t>
+  </si>
+  <si>
+    <t>09:25</t>
+  </si>
+  <si>
+    <t>Ducha varones</t>
+  </si>
+  <si>
+    <t>Dispensador de jabón sin tapa ni envase.</t>
+  </si>
+  <si>
+    <t>K109</t>
+  </si>
+  <si>
+    <t>Baldosa caída sobre mesa docente.</t>
+  </si>
+  <si>
+    <t>10:57</t>
+  </si>
+  <si>
+    <t>SSHH varones 3er piso</t>
+  </si>
+  <si>
+    <t>Brazo hidráulico y manija dañados.</t>
+  </si>
+  <si>
+    <t>13:19</t>
+  </si>
+  <si>
+    <t>Lavadero doctores</t>
+  </si>
+  <si>
+    <t>Caño con fuga de agua.</t>
+  </si>
+  <si>
+    <t>13:36</t>
+  </si>
+  <si>
+    <t>Cuarto limpieza 2do piso</t>
+  </si>
+  <si>
+    <t>Chapa malograda.</t>
+  </si>
+  <si>
+    <t>15:39</t>
+  </si>
+  <si>
+    <t>N311</t>
+  </si>
+  <si>
+    <t>Puerta caída, no cierra correctamente.</t>
+  </si>
+  <si>
+    <t>18:13</t>
+  </si>
+  <si>
+    <t>Sin iluminación en postes.</t>
+  </si>
+  <si>
+    <t>18:37</t>
+  </si>
+  <si>
+    <t>Pasadizo aulas nuevas</t>
+  </si>
+  <si>
+    <t>Luces apagadas en 1er piso.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -943,7 +1204,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -980,6 +1241,12 @@
         <fgColor rgb="FFEAECEE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -993,7 +1260,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1013,6 +1280,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1183,8 +1453,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E19CD508-BA72-43CC-BAB7-D3462941A1CF}" name="REGISTRO_DIARIO" displayName="REGISTRO_DIARIO" ref="A1:M71" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13">
-  <autoFilter ref="A1:M71" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E19CD508-BA72-43CC-BAB7-D3462941A1CF}" name="REGISTRO_DIARIO" displayName="REGISTRO_DIARIO" ref="A1:M100" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13">
+  <autoFilter ref="A1:M100" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{0DFF22FF-ED84-4682-B2E8-267202A4B0B6}" name="ID" dataDxfId="12"/>
     <tableColumn id="2" xr3:uid="{FD595907-4AC6-4B7B-B329-232CB92A82EF}" name="Fecha" dataDxfId="11"/>
@@ -1489,8 +1759,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M72"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
+  <dimension ref="A1:M100"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1502,11 +1772,11 @@
     <col min="9" max="9" width="14" customWidth="1"/>
     <col min="10" max="10" width="16" customWidth="1"/>
     <col min="11" max="11" width="36" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" customWidth="1"/>
+    <col min="12" max="12" width="14.44140625" customWidth="1"/>
     <col min="13" max="13" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1547,12 +1817,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="15.75">
+    <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="15">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -1593,7 +1863,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="15">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -1628,7 +1898,7 @@
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
     </row>
-    <row r="5" spans="1:13" ht="15">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>3</v>
       </c>
@@ -1669,7 +1939,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="15">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>4</v>
       </c>
@@ -1710,7 +1980,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="30.75">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
         <v>5</v>
       </c>
@@ -1749,7 +2019,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="15">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>6</v>
       </c>
@@ -1790,7 +2060,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="15">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>7</v>
       </c>
@@ -1829,7 +2099,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="15">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>8</v>
       </c>
@@ -1868,7 +2138,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="15">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
         <v>9</v>
       </c>
@@ -1905,7 +2175,7 @@
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
     </row>
-    <row r="12" spans="1:13" ht="15">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="4">
         <v>10</v>
       </c>
@@ -1944,7 +2214,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="15">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>11</v>
       </c>
@@ -1981,7 +2251,7 @@
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
     </row>
-    <row r="14" spans="1:13" ht="15">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
         <v>12</v>
       </c>
@@ -2018,7 +2288,7 @@
       <c r="L14" s="5"/>
       <c r="M14" s="5"/>
     </row>
-    <row r="15" spans="1:13" ht="15">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>13</v>
       </c>
@@ -2055,7 +2325,7 @@
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
     </row>
-    <row r="16" spans="1:13" ht="15">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
         <v>14</v>
       </c>
@@ -2094,7 +2364,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="15">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>15</v>
       </c>
@@ -2131,7 +2401,7 @@
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
     </row>
-    <row r="18" spans="1:13" ht="15">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>16</v>
       </c>
@@ -2172,7 +2442,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="15">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>17</v>
       </c>
@@ -2211,7 +2481,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="15">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>18</v>
       </c>
@@ -2252,7 +2522,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="15">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>19</v>
       </c>
@@ -2289,7 +2559,7 @@
       <c r="L21" s="3"/>
       <c r="M21" s="3"/>
     </row>
-    <row r="22" spans="1:13" ht="15">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>20</v>
       </c>
@@ -2326,7 +2596,7 @@
       <c r="L22" s="3"/>
       <c r="M22" s="3"/>
     </row>
-    <row r="23" spans="1:13" ht="15">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>21</v>
       </c>
@@ -2365,7 +2635,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="15">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>22</v>
       </c>
@@ -2406,7 +2676,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="15">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>23</v>
       </c>
@@ -2447,7 +2717,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="15">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>24</v>
       </c>
@@ -2482,7 +2752,7 @@
       <c r="L26" s="3"/>
       <c r="M26" s="3"/>
     </row>
-    <row r="27" spans="1:13" ht="15">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <v>25</v>
       </c>
@@ -2519,7 +2789,7 @@
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
     </row>
-    <row r="28" spans="1:13" ht="15">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <v>26</v>
       </c>
@@ -2556,7 +2826,7 @@
       <c r="L28" s="3"/>
       <c r="M28" s="3"/>
     </row>
-    <row r="29" spans="1:13" ht="15">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <v>27</v>
       </c>
@@ -2593,7 +2863,7 @@
       <c r="L29" s="3"/>
       <c r="M29" s="3"/>
     </row>
-    <row r="30" spans="1:13" ht="15">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <v>28</v>
       </c>
@@ -2630,7 +2900,7 @@
       <c r="L30" s="3"/>
       <c r="M30" s="3"/>
     </row>
-    <row r="31" spans="1:13" ht="15">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" s="5">
         <v>29</v>
       </c>
@@ -2665,12 +2935,12 @@
       <c r="L31" s="5"/>
       <c r="M31" s="5"/>
     </row>
-    <row r="32" spans="1:13" ht="15.75">
+    <row r="32" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="33" spans="1:13" ht="15">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>30</v>
       </c>
@@ -2709,7 +2979,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="34" spans="1:13" ht="15">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
         <v>31</v>
       </c>
@@ -2744,7 +3014,7 @@
       <c r="L34" s="3"/>
       <c r="M34" s="3"/>
     </row>
-    <row r="35" spans="1:13" ht="15">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
         <v>32</v>
       </c>
@@ -2781,7 +3051,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="36" spans="1:13" ht="15">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
         <v>33</v>
       </c>
@@ -2818,7 +3088,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="37" spans="1:13" ht="15">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
         <v>34</v>
       </c>
@@ -2857,7 +3127,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="15">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
         <v>35</v>
       </c>
@@ -2892,7 +3162,7 @@
       <c r="L38" s="3"/>
       <c r="M38" s="3"/>
     </row>
-    <row r="39" spans="1:13" ht="15">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
         <v>36</v>
       </c>
@@ -2929,7 +3199,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="40" spans="1:13" ht="15">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
         <v>37</v>
       </c>
@@ -2966,7 +3236,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="41" spans="1:13" ht="15">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
         <v>38</v>
       </c>
@@ -3001,7 +3271,7 @@
       <c r="L41" s="3"/>
       <c r="M41" s="3"/>
     </row>
-    <row r="42" spans="1:13" ht="15">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
         <v>39</v>
       </c>
@@ -3036,7 +3306,7 @@
       <c r="L42" s="3"/>
       <c r="M42" s="3"/>
     </row>
-    <row r="43" spans="1:13" ht="15">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
         <v>40</v>
       </c>
@@ -3073,7 +3343,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="44" spans="1:13" ht="15">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" s="4">
         <v>41</v>
       </c>
@@ -3110,7 +3380,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="45" spans="1:13" ht="30.75">
+    <row r="45" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
         <v>42</v>
       </c>
@@ -3145,7 +3415,7 @@
       <c r="L45" s="3"/>
       <c r="M45" s="3"/>
     </row>
-    <row r="46" spans="1:13" ht="15">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
         <v>43</v>
       </c>
@@ -3182,7 +3452,7 @@
       <c r="L46" s="3"/>
       <c r="M46" s="3"/>
     </row>
-    <row r="47" spans="1:13" ht="15">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
         <v>44</v>
       </c>
@@ -3221,7 +3491,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="48" spans="1:13" ht="15">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
         <v>45</v>
       </c>
@@ -3258,7 +3528,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="49" spans="1:13" ht="15">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
         <v>46</v>
       </c>
@@ -3297,7 +3567,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="50" spans="1:13" ht="30.75">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
         <v>47</v>
       </c>
@@ -3332,7 +3602,7 @@
       <c r="L50" s="3"/>
       <c r="M50" s="3"/>
     </row>
-    <row r="51" spans="1:13" ht="15">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
         <v>48</v>
       </c>
@@ -3367,7 +3637,7 @@
       <c r="L51" s="3"/>
       <c r="M51" s="3"/>
     </row>
-    <row r="52" spans="1:13" ht="30.75">
+    <row r="52" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A52" s="4">
         <v>49</v>
       </c>
@@ -3406,7 +3676,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="53" spans="1:13" ht="15">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
         <v>50</v>
       </c>
@@ -3441,7 +3711,7 @@
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
     </row>
-    <row r="54" spans="1:13" ht="30.75">
+    <row r="54" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A54" s="5">
         <v>51</v>
       </c>
@@ -3478,7 +3748,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="55" spans="1:13" ht="15">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A55" s="3">
         <v>52</v>
       </c>
@@ -3513,7 +3783,7 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
     </row>
-    <row r="56" spans="1:13" ht="15">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A56" s="3">
         <v>53</v>
       </c>
@@ -3552,7 +3822,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="57" spans="1:13" ht="15">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A57" s="3">
         <v>54</v>
       </c>
@@ -3591,7 +3861,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="58" spans="1:13" ht="15">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A58" s="3">
         <v>55</v>
       </c>
@@ -3628,7 +3898,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="59" spans="1:13" ht="15">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A59" s="3">
         <v>56</v>
       </c>
@@ -3665,7 +3935,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="60" spans="1:13" ht="15">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A60" s="3">
         <v>57</v>
       </c>
@@ -3702,7 +3972,7 @@
       <c r="L60" s="3"/>
       <c r="M60" s="3"/>
     </row>
-    <row r="61" spans="1:13" ht="15">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A61" s="3">
         <v>58</v>
       </c>
@@ -3741,7 +4011,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="62" spans="1:13" ht="15">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A62" s="3">
         <v>59</v>
       </c>
@@ -3778,7 +4048,7 @@
       <c r="L62" s="3"/>
       <c r="M62" s="3"/>
     </row>
-    <row r="63" spans="1:13" ht="15">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
         <v>60</v>
       </c>
@@ -3819,7 +4089,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="64" spans="1:13" ht="15">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A64" s="3">
         <v>61</v>
       </c>
@@ -3854,7 +4124,7 @@
       <c r="L64" s="3"/>
       <c r="M64" s="3"/>
     </row>
-    <row r="65" spans="1:13" ht="15">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A65" s="3">
         <v>62</v>
       </c>
@@ -3891,7 +4161,7 @@
       <c r="L65" s="3"/>
       <c r="M65" s="3"/>
     </row>
-    <row r="66" spans="1:13" ht="30.75">
+    <row r="66" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
         <v>63</v>
       </c>
@@ -3932,7 +4202,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="67" spans="1:13" ht="15">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A67" s="3">
         <v>64</v>
       </c>
@@ -3967,7 +4237,7 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
     </row>
-    <row r="68" spans="1:13" ht="15">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A68" s="3">
         <v>65</v>
       </c>
@@ -4004,7 +4274,7 @@
       <c r="L68" s="3"/>
       <c r="M68" s="3"/>
     </row>
-    <row r="69" spans="1:13" ht="15">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A69" s="3">
         <v>66</v>
       </c>
@@ -4041,7 +4311,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="70" spans="1:13" ht="15">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
         <v>67</v>
       </c>
@@ -4082,7 +4352,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="71" spans="1:13" ht="30.75">
+    <row r="71" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A71" s="3">
         <v>68</v>
       </c>
@@ -4119,7 +4389,1021 @@
       <c r="L71" s="3"/>
       <c r="M71" s="3"/>
     </row>
-    <row r="72" spans="1:13" ht="15"/>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A72" s="8">
+        <v>69</v>
+      </c>
+      <c r="B72" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="D72" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E72" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="F72" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="G72" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="H72" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="I72" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="J72" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="K72" s="8"/>
+      <c r="L72" s="8"/>
+      <c r="M72" s="8"/>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A73" s="8">
+        <v>70</v>
+      </c>
+      <c r="B73" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="C73" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="D73" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E73" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="F73" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="G73" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="H73" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="I73" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="J73" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="K73" s="8"/>
+      <c r="L73" s="8"/>
+      <c r="M73" s="8"/>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A74" s="8">
+        <v>71</v>
+      </c>
+      <c r="B74" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="D74" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E74" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F74" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="G74" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="H74" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="I74" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="J74" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="K74" s="8"/>
+      <c r="L74" s="8"/>
+      <c r="M74" s="8"/>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A75" s="8">
+        <v>72</v>
+      </c>
+      <c r="B75" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="C75" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="D75" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E75" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="F75" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="G75" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="H75" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="I75" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="J75" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="K75" s="8"/>
+      <c r="L75" s="8"/>
+      <c r="M75" s="8"/>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A76" s="8">
+        <v>73</v>
+      </c>
+      <c r="B76" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="C76" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="D76" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E76" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="F76" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="G76" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="H76" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="I76" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="J76" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="K76" s="8"/>
+      <c r="L76" s="8"/>
+      <c r="M76" s="8"/>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A77" s="8">
+        <v>74</v>
+      </c>
+      <c r="B77" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="C77" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="D77" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E77" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="F77" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="G77" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H77" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="I77" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="J77" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="K77" s="8"/>
+      <c r="L77" s="8"/>
+      <c r="M77" s="8"/>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A78" s="8">
+        <v>75</v>
+      </c>
+      <c r="B78" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="C78" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="D78" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E78" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="F78" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="G78" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="H78" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="I78" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="J78" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="K78" s="8"/>
+      <c r="L78" s="8"/>
+      <c r="M78" s="8"/>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A79" s="8">
+        <v>76</v>
+      </c>
+      <c r="B79" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="C79" s="8" t="s">
+        <v>314</v>
+      </c>
+      <c r="D79" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E79" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="F79" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="G79" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="H79" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="I79" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="J79" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="K79" s="8"/>
+      <c r="L79" s="8"/>
+      <c r="M79" s="8"/>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A80" s="8">
+        <v>77</v>
+      </c>
+      <c r="B80" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="C80" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="D80" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E80" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="F80" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="G80" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="H80" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="I80" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="J80" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="K80" s="8"/>
+      <c r="L80" s="8"/>
+      <c r="M80" s="8"/>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A81" s="8">
+        <v>78</v>
+      </c>
+      <c r="B81" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="C81" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="D81" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E81" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="F81" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="G81" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="H81" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="I81" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="J81" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="K81" s="8"/>
+      <c r="L81" s="8"/>
+      <c r="M81" s="8"/>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A82" s="8">
+        <v>79</v>
+      </c>
+      <c r="B82" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="C82" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="D82" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E82" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="F82" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="G82" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="H82" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="I82" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="J82" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="K82" s="8"/>
+      <c r="L82" s="8"/>
+      <c r="M82" s="8"/>
+    </row>
+    <row r="83" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A83" s="8">
+        <v>80</v>
+      </c>
+      <c r="B83" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="C83" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="D83" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E83" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="F83" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="G83" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="H83" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="I83" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="J83" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="K83" s="8"/>
+      <c r="L83" s="8"/>
+      <c r="M83" s="8"/>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A84" s="8">
+        <v>81</v>
+      </c>
+      <c r="B84" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="C84" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="D84" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E84" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="F84" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="G84" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="H84" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="I84" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="J84" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="K84" s="8"/>
+      <c r="L84" s="8"/>
+      <c r="M84" s="8"/>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A85" s="8">
+        <v>82</v>
+      </c>
+      <c r="B85" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="C85" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="D85" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E85" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="F85" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="G85" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="H85" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="I85" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="J85" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="K85" s="8"/>
+      <c r="L85" s="8"/>
+      <c r="M85" s="8"/>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A86" s="8">
+        <v>83</v>
+      </c>
+      <c r="B86" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="C86" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="D86" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E86" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="F86" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="G86" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="H86" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="I86" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="J86" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="K86" s="8"/>
+      <c r="L86" s="8"/>
+      <c r="M86" s="8"/>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A87" s="8">
+        <v>84</v>
+      </c>
+      <c r="B87" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="C87" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="D87" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E87" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F87" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="G87" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H87" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="I87" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="J87" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="K87" s="8"/>
+      <c r="L87" s="8"/>
+      <c r="M87" s="8"/>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A88" s="8">
+        <v>85</v>
+      </c>
+      <c r="B88" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="C88" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="D88" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E88" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="F88" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="G88" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="H88" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="I88" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="J88" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="K88" s="8"/>
+      <c r="L88" s="8"/>
+      <c r="M88" s="8"/>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A89" s="8">
+        <v>86</v>
+      </c>
+      <c r="B89" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="C89" s="8" t="s">
+        <v>344</v>
+      </c>
+      <c r="D89" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E89" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="F89" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="G89" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="H89" s="8" t="s">
+        <v>346</v>
+      </c>
+      <c r="I89" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="J89" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="K89" s="8"/>
+      <c r="L89" s="8"/>
+      <c r="M89" s="8"/>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A90" s="8">
+        <v>87</v>
+      </c>
+      <c r="B90" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="C90" s="8" t="s">
+        <v>347</v>
+      </c>
+      <c r="D90" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E90" s="8" t="s">
+        <v>348</v>
+      </c>
+      <c r="F90" s="8" t="s">
+        <v>349</v>
+      </c>
+      <c r="G90" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="H90" s="8" t="s">
+        <v>350</v>
+      </c>
+      <c r="I90" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="J90" s="8" t="s">
+        <v>351</v>
+      </c>
+      <c r="K90" s="8"/>
+      <c r="L90" s="8"/>
+      <c r="M90" s="8"/>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A91" s="8">
+        <v>88</v>
+      </c>
+      <c r="B91" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="C91" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="D91" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E91" s="8" t="s">
+        <v>352</v>
+      </c>
+      <c r="F91" s="8" t="s">
+        <v>353</v>
+      </c>
+      <c r="G91" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H91" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="I91" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="J91" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="K91" s="8"/>
+      <c r="L91" s="8"/>
+      <c r="M91" s="8"/>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A92" s="8">
+        <v>89</v>
+      </c>
+      <c r="B92" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="C92" s="8" t="s">
+        <v>354</v>
+      </c>
+      <c r="D92" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E92" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="F92" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="G92" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H92" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="I92" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="J92" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="K92" s="8"/>
+      <c r="L92" s="8"/>
+      <c r="M92" s="8"/>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A93" s="8">
+        <v>90</v>
+      </c>
+      <c r="B93" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="C93" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="D93" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E93" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="F93" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="G93" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="H93" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="I93" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="J93" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="K93" s="8"/>
+      <c r="L93" s="8"/>
+      <c r="M93" s="8"/>
+    </row>
+    <row r="94" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A94" s="8">
+        <v>91</v>
+      </c>
+      <c r="B94" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="C94" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="D94" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E94" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="F94" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="G94" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="H94" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="I94" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="J94" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="K94" s="8"/>
+      <c r="L94" s="8"/>
+      <c r="M94" s="8"/>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A95" s="8">
+        <v>92</v>
+      </c>
+      <c r="B95" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="C95" s="8" t="s">
+        <v>362</v>
+      </c>
+      <c r="D95" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E95" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F95" s="8" t="s">
+        <v>363</v>
+      </c>
+      <c r="G95" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="H95" s="8" t="s">
+        <v>364</v>
+      </c>
+      <c r="I95" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="J95" s="8" t="s">
+        <v>351</v>
+      </c>
+      <c r="K95" s="8"/>
+      <c r="L95" s="8"/>
+      <c r="M95" s="8"/>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A96" s="8">
+        <v>93</v>
+      </c>
+      <c r="B96" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="C96" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="D96" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E96" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="F96" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="G96" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="H96" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="I96" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="J96" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="K96" s="8"/>
+      <c r="L96" s="8"/>
+      <c r="M96" s="8"/>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A97" s="8">
+        <v>94</v>
+      </c>
+      <c r="B97" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="C97" s="8" t="s">
+        <v>368</v>
+      </c>
+      <c r="D97" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E97" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F97" s="8" t="s">
+        <v>369</v>
+      </c>
+      <c r="G97" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="H97" s="8" t="s">
+        <v>370</v>
+      </c>
+      <c r="I97" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="J97" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="K97" s="8"/>
+      <c r="L97" s="8"/>
+      <c r="M97" s="8"/>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A98" s="8">
+        <v>95</v>
+      </c>
+      <c r="B98" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="C98" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="D98" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E98" s="8" t="s">
+        <v>372</v>
+      </c>
+      <c r="F98" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="G98" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="H98" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="I98" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="J98" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="K98" s="8"/>
+      <c r="L98" s="8"/>
+      <c r="M98" s="8"/>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A99" s="8">
+        <v>96</v>
+      </c>
+      <c r="B99" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="C99" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="D99" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E99" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="F99" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="G99" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="H99" s="8" t="s">
+        <v>375</v>
+      </c>
+      <c r="I99" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="J99" s="8" t="s">
+        <v>351</v>
+      </c>
+      <c r="K99" s="8"/>
+      <c r="L99" s="8"/>
+      <c r="M99" s="8"/>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A100" s="8">
+        <v>97</v>
+      </c>
+      <c r="B100" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="C100" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="D100" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E100" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F100" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="G100" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="H100" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="I100" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="J100" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="K100" s="8"/>
+      <c r="L100" s="8"/>
+      <c r="M100" s="8"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -4131,7 +5415,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -4141,7 +5425,7 @@
     <col min="6" max="6" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -4161,7 +5445,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -4181,7 +5465,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>134</v>
       </c>
@@ -4493,6 +5777,31 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="f1757aba-7c56-4df5-87be-16e23bbe4ed8" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="08db9a84-ec2d-4a5a-811e-d3601eed0ad4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_dlc_DocId xmlns="f1757aba-7c56-4df5-87be-16e23bbe4ed8">MZ43R4M2M7CF-139809376-3915696</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="f1757aba-7c56-4df5-87be-16e23bbe4ed8">
+      <Url>https://grupoeducad.sharepoint.com/sites/fs-ucsur/_layouts/15/DocIdRedir.aspx?ID=MZ43R4M2M7CF-139809376-3915696</Url>
+      <Description>MZ43R4M2M7CF-139809376-3915696</Description>
+    </_dlc_DocIdUrl>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
   <Receiver>
@@ -4542,43 +5851,48 @@
 </spe:Receivers>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="f1757aba-7c56-4df5-87be-16e23bbe4ed8" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="08db9a84-ec2d-4a5a-811e-d3601eed0ad4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_dlc_DocId xmlns="f1757aba-7c56-4df5-87be-16e23bbe4ed8">MZ43R4M2M7CF-139809376-3915696</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="f1757aba-7c56-4df5-87be-16e23bbe4ed8">
-      <Url>https://grupoeducad.sharepoint.com/sites/fs-ucsur/_layouts/15/DocIdRedir.aspx?ID=MZ43R4M2M7CF-139809376-3915696</Url>
-      <Description>MZ43R4M2M7CF-139809376-3915696</Description>
-    </_dlc_DocIdUrl>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1912D125-5B41-4C39-9570-81A8B20345D3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1912D125-5B41-4C39-9570-81A8B20345D3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="f1757aba-7c56-4df5-87be-16e23bbe4ed8"/>
+    <ds:schemaRef ds:uri="08db9a84-ec2d-4a5a-811e-d3601eed0ad4"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20F437A9-C9B8-4439-AE05-95D86B5341E9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62B0FC80-0856-4EF7-88D7-08AE3DAFCCCE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="f1757aba-7c56-4df5-87be-16e23bbe4ed8"/>
+    <ds:schemaRef ds:uri="08db9a84-ec2d-4a5a-811e-d3601eed0ad4"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B9F25F23-8111-4B47-AB5D-AFE100C1109F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B9F25F23-8111-4B47-AB5D-AFE100C1109F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62B0FC80-0856-4EF7-88D7-08AE3DAFCCCE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20F437A9-C9B8-4439-AE05-95D86B5341E9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/CONSOLIDADO DASHBOARD VILLA.xlsx
+++ b/CONSOLIDADO DASHBOARD VILLA.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1418DAF3-2709-4340-867E-49C37996D66C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CONSOLIDADO" sheetId="1" r:id="rId1"/>
@@ -5491,6 +5491,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="f1757aba-7c56-4df5-87be-16e23bbe4ed8" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="08db9a84-ec2d-4a5a-811e-d3601eed0ad4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_dlc_DocId xmlns="f1757aba-7c56-4df5-87be-16e23bbe4ed8">MZ43R4M2M7CF-139809376-3915696</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="f1757aba-7c56-4df5-87be-16e23bbe4ed8">
+      <Url>https://grupoeducad.sharepoint.com/sites/fs-ucsur/_layouts/15/DocIdRedir.aspx?ID=MZ43R4M2M7CF-139809376-3915696</Url>
+      <Description>MZ43R4M2M7CF-139809376-3915696</Description>
+    </_dlc_DocIdUrl>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100D7500CB0E7AC8047B9E59392F2D722FC" ma:contentTypeVersion="447" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="89580b0bb16e9dafb55400b1304f38cd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f1757aba-7c56-4df5-87be-16e23bbe4ed8" xmlns:ns3="08db9a84-ec2d-4a5a-811e-d3601eed0ad4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="20837f56299e62693d34fc82a8c955a7" ns2:_="" ns3:_="">
     <xsd:import namespace="f1757aba-7c56-4df5-87be-16e23bbe4ed8"/>
@@ -5776,31 +5801,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="f1757aba-7c56-4df5-87be-16e23bbe4ed8" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="08db9a84-ec2d-4a5a-811e-d3601eed0ad4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_dlc_DocId xmlns="f1757aba-7c56-4df5-87be-16e23bbe4ed8">MZ43R4M2M7CF-139809376-3915696</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="f1757aba-7c56-4df5-87be-16e23bbe4ed8">
-      <Url>https://grupoeducad.sharepoint.com/sites/fs-ucsur/_layouts/15/DocIdRedir.aspx?ID=MZ43R4M2M7CF-139809376-3915696</Url>
-      <Description>MZ43R4M2M7CF-139809376-3915696</Description>
-    </_dlc_DocIdUrl>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
@@ -5852,6 +5852,25 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B9F25F23-8111-4B47-AB5D-AFE100C1109F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62B0FC80-0856-4EF7-88D7-08AE3DAFCCCE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="f1757aba-7c56-4df5-87be-16e23bbe4ed8"/>
+    <ds:schemaRef ds:uri="08db9a84-ec2d-4a5a-811e-d3601eed0ad4"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1912D125-5B41-4C39-9570-81A8B20345D3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5870,25 +5889,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62B0FC80-0856-4EF7-88D7-08AE3DAFCCCE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="f1757aba-7c56-4df5-87be-16e23bbe4ed8"/>
-    <ds:schemaRef ds:uri="08db9a84-ec2d-4a5a-811e-d3601eed0ad4"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B9F25F23-8111-4B47-AB5D-AFE100C1109F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20F437A9-C9B8-4439-AE05-95D86B5341E9}">
   <ds:schemaRefs>

--- a/CONSOLIDADO DASHBOARD VILLA.xlsx
+++ b/CONSOLIDADO DASHBOARD VILLA.xlsx
@@ -8,33 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FCHAVEZC\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F280AEA-B5A4-4E67-9034-BE4D5E9ED4E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E64C2F91-E512-432E-9588-8E19FC76BECC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CONSOLIDADO" sheetId="1" r:id="rId1"/>
     <sheet name="RESUMEN" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3253" uniqueCount="940">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3314" uniqueCount="941">
   <si>
     <t>ID</t>
   </si>
@@ -2286,9 +2273,6 @@
     <t>Se informa filtración de agua en techo en dirección del aula 308.</t>
   </si>
   <si>
-    <t xml:space="preserve">se repite  </t>
-  </si>
-  <si>
     <t>SSHH docentes varones 3er piso</t>
   </si>
   <si>
@@ -2853,7 +2837,13 @@
     <t>solucionado por proveedor H&amp;E</t>
   </si>
   <si>
-    <t>Jose rodas, Angel Ytaco y luis Matos</t>
+    <t>MYT</t>
+  </si>
+  <si>
+    <t>4/0672026</t>
+  </si>
+  <si>
+    <t>nO APLICA</t>
   </si>
 </sst>
 </file>
@@ -2943,7 +2933,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -3001,17 +2991,8 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -3030,6 +3011,12 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3676,7 +3663,7 @@
           <bgColor rgb="FFB7F0E5"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <fill>
@@ -4133,7 +4120,7 @@
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="2" max="2" width="14" style="13" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" style="19" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" style="19" hidden="1" customWidth="1"/>
     <col min="4" max="4" width="14.85546875" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="26" customWidth="1"/>
     <col min="6" max="6" width="29.28515625" customWidth="1"/>
@@ -4141,7 +4128,7 @@
     <col min="8" max="8" width="70" customWidth="1"/>
     <col min="9" max="10" width="12.5703125" customWidth="1"/>
     <col min="11" max="11" width="54.28515625" customWidth="1"/>
-    <col min="12" max="12" width="22.28515625" customWidth="1"/>
+    <col min="12" max="12" width="22.28515625" style="29" customWidth="1"/>
     <col min="13" max="13" width="42" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4220,7 +4207,7 @@
       <c r="K2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L2" s="25" t="s">
+      <c r="L2" s="22" t="s">
         <v>13</v>
       </c>
       <c r="M2" s="1" t="s">
@@ -4261,7 +4248,7 @@
       <c r="K3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L3" s="26">
+      <c r="L3" s="23">
         <v>46168</v>
       </c>
       <c r="M3" s="2" t="s">
@@ -4302,7 +4289,7 @@
       <c r="K4" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="L4" s="25" t="s">
+      <c r="L4" s="22" t="s">
         <v>13</v>
       </c>
       <c r="M4" s="1" t="s">
@@ -4343,7 +4330,7 @@
       <c r="K5" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="L5" s="25" t="s">
+      <c r="L5" s="22" t="s">
         <v>13</v>
       </c>
       <c r="M5" s="1" t="s">
@@ -4384,7 +4371,7 @@
       <c r="K6" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L6" s="25" t="s">
+      <c r="L6" s="22" t="s">
         <v>13</v>
       </c>
       <c r="M6" s="3" t="s">
@@ -4425,7 +4412,7 @@
       <c r="K7" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="L7" s="25" t="s">
+      <c r="L7" s="22" t="s">
         <v>13</v>
       </c>
       <c r="M7" s="1" t="s">
@@ -4466,7 +4453,7 @@
       <c r="K8" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="L8" s="25" t="s">
+      <c r="L8" s="22" t="s">
         <v>13</v>
       </c>
       <c r="M8" s="2" t="s">
@@ -4507,7 +4494,7 @@
       <c r="K9" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="L9" s="25" t="s">
+      <c r="L9" s="22" t="s">
         <v>13</v>
       </c>
       <c r="M9" s="2" t="s">
@@ -4548,7 +4535,7 @@
       <c r="K10" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="L10" s="11" t="s">
+      <c r="L10" s="28" t="s">
         <v>13</v>
       </c>
       <c r="M10" s="3"/>
@@ -4587,7 +4574,7 @@
       <c r="K11" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="L11" s="25" t="s">
+      <c r="L11" s="22" t="s">
         <v>13</v>
       </c>
       <c r="M11" s="3" t="s">
@@ -4628,7 +4615,7 @@
       <c r="K12" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L12" s="25" t="s">
+      <c r="L12" s="22" t="s">
         <v>13</v>
       </c>
       <c r="M12" s="2"/>
@@ -4667,7 +4654,7 @@
       <c r="K13" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L13" s="23">
+      <c r="L13" s="21">
         <v>46168</v>
       </c>
       <c r="M13" s="4"/>
@@ -4706,7 +4693,7 @@
       <c r="K14" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="L14" s="23">
+      <c r="L14" s="21">
         <v>46168</v>
       </c>
       <c r="M14" s="2"/>
@@ -4745,7 +4732,7 @@
       <c r="K15" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="L15" s="23">
+      <c r="L15" s="21">
         <v>46168</v>
       </c>
       <c r="M15" s="3" t="s">
@@ -4786,7 +4773,7 @@
       <c r="K16" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="L16" s="23">
+      <c r="L16" s="21">
         <v>46168</v>
       </c>
       <c r="M16" s="2"/>
@@ -4825,7 +4812,7 @@
       <c r="K17" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="L17" s="23">
+      <c r="L17" s="21">
         <v>46168</v>
       </c>
       <c r="M17" s="1" t="s">
@@ -4866,7 +4853,7 @@
       <c r="K18" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="L18" s="23">
+      <c r="L18" s="21">
         <v>46168</v>
       </c>
       <c r="M18" s="2" t="s">
@@ -4907,7 +4894,7 @@
       <c r="K19" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L19" s="25" t="s">
+      <c r="L19" s="22" t="s">
         <v>13</v>
       </c>
       <c r="M19" s="1" t="s">
@@ -4948,7 +4935,7 @@
       <c r="K20" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="L20" s="23">
+      <c r="L20" s="21">
         <v>46168</v>
       </c>
       <c r="M20" s="2"/>
@@ -4987,7 +4974,7 @@
       <c r="K21" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L21" s="23">
+      <c r="L21" s="21">
         <v>46168</v>
       </c>
       <c r="M21" s="2"/>
@@ -5026,7 +5013,7 @@
       <c r="K22" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L22" s="25" t="s">
+      <c r="L22" s="22" t="s">
         <v>13</v>
       </c>
       <c r="M22" s="2" t="s">
@@ -5067,7 +5054,7 @@
       <c r="K23" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L23" s="25" t="s">
+      <c r="L23" s="22" t="s">
         <v>13</v>
       </c>
       <c r="M23" s="1" t="s">
@@ -5108,7 +5095,7 @@
       <c r="K24" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L24" s="25" t="s">
+      <c r="L24" s="22" t="s">
         <v>13</v>
       </c>
       <c r="M24" s="1" t="s">
@@ -5147,7 +5134,7 @@
         <v>65</v>
       </c>
       <c r="K25" s="2"/>
-      <c r="L25" s="2"/>
+      <c r="L25" s="25"/>
       <c r="M25" s="2"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
@@ -5184,7 +5171,7 @@
       <c r="K26" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="L26" s="23">
+      <c r="L26" s="21">
         <v>46168</v>
       </c>
       <c r="M26" s="2"/>
@@ -5223,7 +5210,7 @@
       <c r="K27" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="L27" s="25" t="s">
+      <c r="L27" s="22" t="s">
         <v>13</v>
       </c>
       <c r="M27" s="2"/>
@@ -5262,7 +5249,7 @@
       <c r="K28" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L28" s="25" t="s">
+      <c r="L28" s="22" t="s">
         <v>13</v>
       </c>
       <c r="M28" s="2"/>
@@ -5301,7 +5288,7 @@
       <c r="K29" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="L29" s="10" t="s">
+      <c r="L29" s="25" t="s">
         <v>13</v>
       </c>
       <c r="M29" s="2"/>
@@ -5338,9 +5325,9 @@
         <v>21</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>922</v>
-      </c>
-      <c r="L30" s="25" t="s">
+        <v>921</v>
+      </c>
+      <c r="L30" s="22" t="s">
         <v>13</v>
       </c>
       <c r="M30" s="4" t="s">
@@ -5381,7 +5368,7 @@
       <c r="K31" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="L31" s="27">
+      <c r="L31" s="24">
         <v>46199</v>
       </c>
       <c r="M31" s="4" t="s">
@@ -5422,7 +5409,7 @@
       <c r="K32" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="L32" s="26">
+      <c r="L32" s="23">
         <v>46177</v>
       </c>
       <c r="M32" s="2"/>
@@ -5459,9 +5446,9 @@
         <v>21</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>923</v>
-      </c>
-      <c r="L33" s="26">
+        <v>922</v>
+      </c>
+      <c r="L33" s="23">
         <v>46168</v>
       </c>
       <c r="M33" s="2" t="s">
@@ -5500,9 +5487,9 @@
         <v>21</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>923</v>
-      </c>
-      <c r="L34" s="26">
+        <v>922</v>
+      </c>
+      <c r="L34" s="23">
         <v>46168</v>
       </c>
       <c r="M34" s="2" t="s">
@@ -5541,9 +5528,9 @@
         <v>21</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>923</v>
-      </c>
-      <c r="L35" s="26">
+        <v>922</v>
+      </c>
+      <c r="L35" s="23">
         <v>46168</v>
       </c>
       <c r="M35" s="2" t="s">
@@ -5584,7 +5571,7 @@
       <c r="K36" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L36" s="26">
+      <c r="L36" s="23">
         <v>46174</v>
       </c>
       <c r="M36" s="2"/>
@@ -5621,9 +5608,9 @@
         <v>21</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>924</v>
-      </c>
-      <c r="L37" s="28"/>
+        <v>923</v>
+      </c>
+      <c r="L37" s="25"/>
       <c r="M37" s="2" t="s">
         <v>161</v>
       </c>
@@ -5660,9 +5647,9 @@
         <v>21</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>925</v>
-      </c>
-      <c r="L38" s="26">
+        <v>924</v>
+      </c>
+      <c r="L38" s="23">
         <v>46168</v>
       </c>
       <c r="M38" s="2" t="s">
@@ -5703,7 +5690,7 @@
       <c r="K39" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L39" s="26">
+      <c r="L39" s="23">
         <v>46168</v>
       </c>
       <c r="M39" s="2"/>
@@ -5742,7 +5729,7 @@
       <c r="K40" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="L40" s="26">
+      <c r="L40" s="23">
         <v>46168</v>
       </c>
       <c r="M40" s="2"/>
@@ -5779,9 +5766,9 @@
         <v>21</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>924</v>
-      </c>
-      <c r="L41" s="28"/>
+        <v>923</v>
+      </c>
+      <c r="L41" s="25"/>
       <c r="M41" s="2" t="s">
         <v>161</v>
       </c>
@@ -5820,7 +5807,7 @@
       <c r="K42" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="L42" s="26">
+      <c r="L42" s="23">
         <v>46168</v>
       </c>
       <c r="M42" s="3"/>
@@ -5857,7 +5844,7 @@
         <v>65</v>
       </c>
       <c r="K43" s="2"/>
-      <c r="L43" s="2"/>
+      <c r="L43" s="25"/>
       <c r="M43" s="2"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
@@ -5892,9 +5879,9 @@
         <v>65</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>932</v>
-      </c>
-      <c r="L44" s="2"/>
+        <v>931</v>
+      </c>
+      <c r="L44" s="25"/>
       <c r="M44" s="2"/>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
@@ -5931,7 +5918,7 @@
       <c r="K45" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L45" s="26">
+      <c r="L45" s="23">
         <v>46168</v>
       </c>
       <c r="M45" s="2" t="s">
@@ -5970,9 +5957,9 @@
         <v>21</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>933</v>
-      </c>
-      <c r="L46" s="21">
+        <v>932</v>
+      </c>
+      <c r="L46" s="23">
         <v>46175</v>
       </c>
       <c r="M46" s="2" t="s">
@@ -6013,7 +6000,7 @@
       <c r="K47" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L47" s="26">
+      <c r="L47" s="23">
         <v>46168</v>
       </c>
       <c r="M47" s="2" t="s">
@@ -6054,7 +6041,7 @@
       <c r="K48" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="L48" s="2"/>
+      <c r="L48" s="25"/>
       <c r="M48" s="2"/>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
@@ -6089,9 +6076,9 @@
         <v>21</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>934</v>
-      </c>
-      <c r="L49" s="21">
+        <v>933</v>
+      </c>
+      <c r="L49" s="23">
         <v>46175</v>
       </c>
       <c r="M49" s="2"/>
@@ -6130,7 +6117,7 @@
       <c r="K50" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L50" s="26">
+      <c r="L50" s="23">
         <v>46168</v>
       </c>
       <c r="M50" s="3" t="s">
@@ -6171,7 +6158,7 @@
       <c r="K51" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="L51" s="26">
+      <c r="L51" s="23">
         <v>46168</v>
       </c>
       <c r="M51" s="2"/>
@@ -6208,7 +6195,7 @@
         <v>21</v>
       </c>
       <c r="K52" s="4" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="L52" s="24">
         <v>46168</v>
@@ -6251,7 +6238,7 @@
       <c r="K53" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L53" s="26">
+      <c r="L53" s="23">
         <v>46168</v>
       </c>
       <c r="M53" s="2"/>
@@ -6290,7 +6277,7 @@
       <c r="K54" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="L54" s="26">
+      <c r="L54" s="23">
         <v>46168</v>
       </c>
       <c r="M54" s="2" t="s">
@@ -6331,7 +6318,7 @@
       <c r="K55" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L55" s="26">
+      <c r="L55" s="23">
         <v>46168</v>
       </c>
       <c r="M55" s="2" t="s">
@@ -6372,7 +6359,7 @@
       <c r="K56" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L56" s="26">
+      <c r="L56" s="23">
         <v>46168</v>
       </c>
       <c r="M56" s="2" t="s">
@@ -6413,7 +6400,7 @@
       <c r="K57" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L57" s="26">
+      <c r="L57" s="23">
         <v>46168</v>
       </c>
       <c r="M57" s="2" t="s">
@@ -6454,7 +6441,7 @@
       <c r="K58" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L58" s="26">
+      <c r="L58" s="23">
         <v>46168</v>
       </c>
       <c r="M58" s="2"/>
@@ -6493,7 +6480,7 @@
       <c r="K59" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="L59" s="2"/>
+      <c r="L59" s="25"/>
       <c r="M59" s="2" t="s">
         <v>247</v>
       </c>
@@ -6532,7 +6519,7 @@
       <c r="K60" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="L60" s="21">
+      <c r="L60" s="23">
         <v>46199</v>
       </c>
       <c r="M60" s="2"/>
@@ -6571,7 +6558,7 @@
       <c r="K61" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="L61" s="1" t="s">
+      <c r="L61" s="22" t="s">
         <v>132</v>
       </c>
       <c r="M61" s="1" t="s">
@@ -6612,7 +6599,7 @@
       <c r="K62" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="L62" s="26">
+      <c r="L62" s="23">
         <v>46168</v>
       </c>
       <c r="M62" s="2"/>
@@ -6651,7 +6638,7 @@
       <c r="K63" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="L63" s="26">
+      <c r="L63" s="23">
         <v>46168</v>
       </c>
       <c r="M63" s="2"/>
@@ -6690,7 +6677,7 @@
       <c r="K64" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L64" s="26">
+      <c r="L64" s="23">
         <v>46168</v>
       </c>
       <c r="M64" s="1" t="s">
@@ -6731,7 +6718,7 @@
       <c r="K65" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="L65" s="26">
+      <c r="L65" s="23">
         <v>46168</v>
       </c>
       <c r="M65" s="2"/>
@@ -6770,7 +6757,7 @@
       <c r="K66" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L66" s="26">
+      <c r="L66" s="23">
         <v>46168</v>
       </c>
       <c r="M66" s="2"/>
@@ -6807,7 +6794,7 @@
         <v>21</v>
       </c>
       <c r="K67" s="2"/>
-      <c r="L67" s="26">
+      <c r="L67" s="23">
         <v>46168</v>
       </c>
       <c r="M67" s="2" t="s">
@@ -6848,7 +6835,7 @@
       <c r="K68" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="L68" s="26">
+      <c r="L68" s="23">
         <v>46168</v>
       </c>
       <c r="M68" s="1" t="s">
@@ -6889,7 +6876,7 @@
       <c r="K69" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L69" s="26">
+      <c r="L69" s="23">
         <v>46168</v>
       </c>
       <c r="M69" s="2"/>
@@ -6926,9 +6913,9 @@
         <v>21</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>926</v>
-      </c>
-      <c r="L70" s="26">
+        <v>925</v>
+      </c>
+      <c r="L70" s="23">
         <v>46168</v>
       </c>
       <c r="M70" s="1"/>
@@ -6965,7 +6952,7 @@
         <v>21</v>
       </c>
       <c r="K71" s="1"/>
-      <c r="L71" s="25" t="s">
+      <c r="L71" s="22" t="s">
         <v>291</v>
       </c>
       <c r="M71" s="1" t="s">
@@ -7006,7 +6993,7 @@
       <c r="K72" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="L72" s="23">
+      <c r="L72" s="21">
         <v>46169</v>
       </c>
       <c r="M72" s="1" t="s">
@@ -7047,7 +7034,7 @@
       <c r="K73" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L73" s="25" t="s">
+      <c r="L73" s="22" t="s">
         <v>301</v>
       </c>
       <c r="M73" s="1" t="s">
@@ -7088,7 +7075,7 @@
       <c r="K74" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="L74" s="23">
+      <c r="L74" s="21">
         <v>46169</v>
       </c>
       <c r="M74" s="1"/>
@@ -7127,7 +7114,7 @@
       <c r="K75" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L75" s="23">
+      <c r="L75" s="21">
         <v>46169</v>
       </c>
       <c r="M75" s="1"/>
@@ -7164,9 +7151,9 @@
         <v>21</v>
       </c>
       <c r="K76" s="1" t="s">
-        <v>927</v>
-      </c>
-      <c r="L76" s="23">
+        <v>926</v>
+      </c>
+      <c r="L76" s="21">
         <v>46169</v>
       </c>
       <c r="M76" s="1" t="s">
@@ -7205,9 +7192,9 @@
         <v>21</v>
       </c>
       <c r="K77" s="1" t="s">
-        <v>927</v>
-      </c>
-      <c r="L77" s="23">
+        <v>926</v>
+      </c>
+      <c r="L77" s="21">
         <v>46169</v>
       </c>
       <c r="M77" s="1" t="s">
@@ -7246,9 +7233,9 @@
         <v>65</v>
       </c>
       <c r="K78" s="1" t="s">
-        <v>935</v>
-      </c>
-      <c r="L78" s="1"/>
+        <v>934</v>
+      </c>
+      <c r="L78" s="22"/>
       <c r="M78" s="1"/>
     </row>
     <row r="79" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7283,9 +7270,9 @@
         <v>21</v>
       </c>
       <c r="K79" s="1" t="s">
-        <v>927</v>
-      </c>
-      <c r="L79" s="23">
+        <v>926</v>
+      </c>
+      <c r="L79" s="21">
         <v>46169</v>
       </c>
       <c r="M79" s="1" t="s">
@@ -7324,7 +7311,7 @@
         <v>65</v>
       </c>
       <c r="K80" s="1"/>
-      <c r="L80" s="1"/>
+      <c r="L80" s="22"/>
       <c r="M80" s="1" t="s">
         <v>326</v>
       </c>
@@ -7361,7 +7348,7 @@
         <v>65</v>
       </c>
       <c r="K81" s="1"/>
-      <c r="L81" s="1"/>
+      <c r="L81" s="22"/>
       <c r="M81" s="1" t="s">
         <v>326</v>
       </c>
@@ -7400,7 +7387,7 @@
       <c r="K82" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="L82" s="23">
+      <c r="L82" s="21">
         <v>46169</v>
       </c>
       <c r="M82" s="1"/>
@@ -7439,7 +7426,7 @@
       <c r="K83" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="L83" s="23">
+      <c r="L83" s="21">
         <v>46169</v>
       </c>
       <c r="M83" s="1"/>
@@ -7476,7 +7463,7 @@
         <v>65</v>
       </c>
       <c r="K84" s="1"/>
-      <c r="L84" s="1"/>
+      <c r="L84" s="22"/>
       <c r="M84" s="1"/>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.25">
@@ -7511,7 +7498,7 @@
         <v>65</v>
       </c>
       <c r="K85" s="1"/>
-      <c r="L85" s="1"/>
+      <c r="L85" s="22"/>
       <c r="M85" s="1"/>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.25">
@@ -7548,7 +7535,7 @@
       <c r="K86" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="L86" s="23">
+      <c r="L86" s="21">
         <v>46169</v>
       </c>
       <c r="M86" s="1"/>
@@ -7585,7 +7572,7 @@
         <v>65</v>
       </c>
       <c r="K87" s="1"/>
-      <c r="L87" s="1"/>
+      <c r="L87" s="22"/>
       <c r="M87" s="1"/>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.25">
@@ -7622,7 +7609,7 @@
       <c r="K88" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L88" s="23">
+      <c r="L88" s="21">
         <v>46169</v>
       </c>
       <c r="M88" s="1"/>
@@ -7661,7 +7648,7 @@
       <c r="K89" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="L89" s="23">
+      <c r="L89" s="21">
         <v>46169</v>
       </c>
       <c r="M89" s="1"/>
@@ -7700,7 +7687,7 @@
       <c r="K90" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L90" s="23">
+      <c r="L90" s="21">
         <v>46169</v>
       </c>
       <c r="M90" s="1"/>
@@ -7736,10 +7723,10 @@
       <c r="J91" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="K91" s="29" t="s">
-        <v>929</v>
-      </c>
-      <c r="L91" s="22">
+      <c r="K91" s="26" t="s">
+        <v>928</v>
+      </c>
+      <c r="L91" s="21">
         <v>46169</v>
       </c>
       <c r="M91" s="1"/>
@@ -7778,7 +7765,7 @@
       <c r="K92" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L92" s="23">
+      <c r="L92" s="21">
         <v>46169</v>
       </c>
       <c r="M92" s="1" t="s">
@@ -7819,7 +7806,7 @@
       <c r="K93" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L93" s="23">
+      <c r="L93" s="21">
         <v>46169</v>
       </c>
       <c r="M93" s="1" t="s">
@@ -7860,7 +7847,7 @@
       <c r="K94" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="L94" s="23">
+      <c r="L94" s="21">
         <v>46169</v>
       </c>
       <c r="M94" s="1"/>
@@ -7899,7 +7886,7 @@
       <c r="K95" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L95" s="23">
+      <c r="L95" s="21">
         <v>46169</v>
       </c>
       <c r="M95" s="1"/>
@@ -7938,7 +7925,7 @@
       <c r="K96" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L96" s="23">
+      <c r="L96" s="21">
         <v>46169</v>
       </c>
       <c r="M96" s="1"/>
@@ -7975,9 +7962,9 @@
         <v>65</v>
       </c>
       <c r="K97" s="1" t="s">
-        <v>935</v>
-      </c>
-      <c r="L97" s="1"/>
+        <v>934</v>
+      </c>
+      <c r="L97" s="22"/>
       <c r="M97" s="1"/>
     </row>
     <row r="98" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -8012,9 +7999,9 @@
         <v>65</v>
       </c>
       <c r="K98" s="1" t="s">
-        <v>935</v>
-      </c>
-      <c r="L98" s="1"/>
+        <v>934</v>
+      </c>
+      <c r="L98" s="22"/>
       <c r="M98" s="1"/>
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.25">
@@ -8051,7 +8038,7 @@
       <c r="K99" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L99" s="25" t="s">
+      <c r="L99" s="22" t="s">
         <v>285</v>
       </c>
       <c r="M99" s="1" t="s">
@@ -8092,7 +8079,7 @@
       <c r="K100" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L100" s="25" t="s">
+      <c r="L100" s="22" t="s">
         <v>285</v>
       </c>
       <c r="M100" s="1"/>
@@ -8131,7 +8118,7 @@
       <c r="K101" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L101" s="25" t="s">
+      <c r="L101" s="22" t="s">
         <v>285</v>
       </c>
       <c r="M101" s="1"/>
@@ -8170,7 +8157,7 @@
       <c r="K102" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="L102" s="1"/>
+      <c r="L102" s="22"/>
       <c r="M102" s="1"/>
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.25">
@@ -8207,7 +8194,7 @@
       <c r="K103" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L103" s="25" t="s">
+      <c r="L103" s="22" t="s">
         <v>301</v>
       </c>
       <c r="M103" s="1"/>
@@ -8244,7 +8231,7 @@
         <v>21</v>
       </c>
       <c r="K104" s="1"/>
-      <c r="L104" s="25" t="s">
+      <c r="L104" s="22" t="s">
         <v>285</v>
       </c>
       <c r="M104" s="1" t="s">
@@ -8285,7 +8272,7 @@
       <c r="K105" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="L105" s="25" t="s">
+      <c r="L105" s="22" t="s">
         <v>285</v>
       </c>
       <c r="M105" s="1"/>
@@ -8324,7 +8311,7 @@
       <c r="K106" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L106" s="25" t="s">
+      <c r="L106" s="22" t="s">
         <v>285</v>
       </c>
       <c r="M106" s="1"/>
@@ -8363,7 +8350,7 @@
       <c r="K107" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L107" s="25" t="s">
+      <c r="L107" s="22" t="s">
         <v>285</v>
       </c>
       <c r="M107" s="1"/>
@@ -8402,7 +8389,7 @@
       <c r="K108" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L108" s="25" t="s">
+      <c r="L108" s="22" t="s">
         <v>285</v>
       </c>
       <c r="M108" s="1" t="s">
@@ -8443,7 +8430,7 @@
       <c r="K109" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="L109" s="25" t="s">
+      <c r="L109" s="22" t="s">
         <v>285</v>
       </c>
       <c r="M109" s="1"/>
@@ -8480,9 +8467,9 @@
         <v>21</v>
       </c>
       <c r="K110" s="1" t="s">
-        <v>931</v>
-      </c>
-      <c r="L110" s="22">
+        <v>930</v>
+      </c>
+      <c r="L110" s="21">
         <v>46175</v>
       </c>
       <c r="M110" s="1"/>
@@ -8518,10 +8505,10 @@
       <c r="J111" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="K111" s="29" t="s">
-        <v>929</v>
-      </c>
-      <c r="L111" s="22">
+      <c r="K111" s="26" t="s">
+        <v>928</v>
+      </c>
+      <c r="L111" s="21">
         <v>46170</v>
       </c>
       <c r="M111" s="1"/>
@@ -8558,7 +8545,7 @@
         <v>65</v>
       </c>
       <c r="K112" s="20"/>
-      <c r="L112" s="1"/>
+      <c r="L112" s="22"/>
       <c r="M112" s="1" t="s">
         <v>417</v>
       </c>
@@ -8595,7 +8582,7 @@
         <v>21</v>
       </c>
       <c r="K113" s="1"/>
-      <c r="L113" s="25" t="s">
+      <c r="L113" s="22" t="s">
         <v>291</v>
       </c>
       <c r="M113" s="1"/>
@@ -8632,7 +8619,7 @@
         <v>65</v>
       </c>
       <c r="K114" s="1"/>
-      <c r="L114" s="1"/>
+      <c r="L114" s="22"/>
       <c r="M114" s="1" t="s">
         <v>421</v>
       </c>
@@ -8669,9 +8656,9 @@
         <v>21</v>
       </c>
       <c r="K115" s="1" t="s">
-        <v>931</v>
-      </c>
-      <c r="L115" s="22">
+        <v>930</v>
+      </c>
+      <c r="L115" s="21">
         <v>46175</v>
       </c>
       <c r="M115" s="1"/>
@@ -8708,9 +8695,9 @@
         <v>21</v>
       </c>
       <c r="K116" s="4" t="s">
-        <v>922</v>
-      </c>
-      <c r="L116" s="25" t="s">
+        <v>921</v>
+      </c>
+      <c r="L116" s="22" t="s">
         <v>291</v>
       </c>
       <c r="M116" s="1" t="s">
@@ -8751,7 +8738,7 @@
       <c r="K117" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="L117" s="25" t="s">
+      <c r="L117" s="22" t="s">
         <v>291</v>
       </c>
       <c r="M117" s="1"/>
@@ -8790,7 +8777,7 @@
       <c r="K118" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L118" s="25" t="s">
+      <c r="L118" s="22" t="s">
         <v>291</v>
       </c>
       <c r="M118" s="1"/>
@@ -8827,9 +8814,9 @@
         <v>65</v>
       </c>
       <c r="K119" s="1" t="s">
-        <v>935</v>
-      </c>
-      <c r="L119" s="1"/>
+        <v>934</v>
+      </c>
+      <c r="L119" s="22"/>
       <c r="M119" s="1"/>
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.25">
@@ -8866,7 +8853,7 @@
       <c r="K120" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L120" s="25" t="s">
+      <c r="L120" s="22" t="s">
         <v>291</v>
       </c>
       <c r="M120" s="1"/>
@@ -8905,7 +8892,7 @@
       <c r="K121" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="L121" s="25" t="s">
+      <c r="L121" s="22" t="s">
         <v>291</v>
       </c>
       <c r="M121" s="1"/>
@@ -8944,7 +8931,7 @@
       <c r="K122" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="L122" s="25" t="s">
+      <c r="L122" s="22" t="s">
         <v>291</v>
       </c>
       <c r="M122" s="1"/>
@@ -8983,7 +8970,7 @@
       <c r="K123" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="L123" s="25" t="s">
+      <c r="L123" s="22" t="s">
         <v>291</v>
       </c>
       <c r="M123" s="1"/>
@@ -9020,9 +9007,9 @@
         <v>65</v>
       </c>
       <c r="K124" s="1" t="s">
-        <v>935</v>
-      </c>
-      <c r="L124" s="1"/>
+        <v>934</v>
+      </c>
+      <c r="L124" s="22"/>
       <c r="M124" s="1"/>
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.25">
@@ -9059,7 +9046,7 @@
       <c r="K125" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L125" s="25" t="s">
+      <c r="L125" s="22" t="s">
         <v>291</v>
       </c>
       <c r="M125" s="1"/>
@@ -9096,9 +9083,9 @@
         <v>21</v>
       </c>
       <c r="K126" s="1" t="s">
-        <v>927</v>
-      </c>
-      <c r="L126" s="22">
+        <v>926</v>
+      </c>
+      <c r="L126" s="21">
         <v>46170</v>
       </c>
       <c r="M126" s="1"/>
@@ -9134,10 +9121,10 @@
       <c r="J127" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="K127" s="29" t="s">
-        <v>929</v>
-      </c>
-      <c r="L127" s="22">
+      <c r="K127" s="26" t="s">
+        <v>928</v>
+      </c>
+      <c r="L127" s="21">
         <v>46170</v>
       </c>
       <c r="M127" s="1"/>
@@ -9176,7 +9163,7 @@
       <c r="K128" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="L128" s="22">
+      <c r="L128" s="21">
         <v>46172</v>
       </c>
       <c r="M128" s="1"/>
@@ -9212,10 +9199,10 @@
       <c r="J129" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="K129" s="29" t="s">
-        <v>929</v>
-      </c>
-      <c r="L129" s="22">
+      <c r="K129" s="26" t="s">
+        <v>928</v>
+      </c>
+      <c r="L129" s="21">
         <v>46170</v>
       </c>
       <c r="M129" s="1" t="s">
@@ -9256,7 +9243,7 @@
       <c r="K130" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="L130" s="25" t="s">
+      <c r="L130" s="22" t="s">
         <v>291</v>
       </c>
       <c r="M130" s="1"/>
@@ -9295,7 +9282,7 @@
       <c r="K131" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L131" s="25" t="s">
+      <c r="L131" s="22" t="s">
         <v>291</v>
       </c>
       <c r="M131" s="1"/>
@@ -9334,7 +9321,7 @@
       <c r="K132" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L132" s="25" t="s">
+      <c r="L132" s="22" t="s">
         <v>301</v>
       </c>
       <c r="M132" s="1"/>
@@ -9373,7 +9360,7 @@
       <c r="K133" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="L133" s="25" t="s">
+      <c r="L133" s="22" t="s">
         <v>291</v>
       </c>
       <c r="M133" s="1"/>
@@ -9412,7 +9399,7 @@
       <c r="K134" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="L134" s="25" t="s">
+      <c r="L134" s="22" t="s">
         <v>291</v>
       </c>
       <c r="M134" s="1"/>
@@ -9451,7 +9438,7 @@
       <c r="K135" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L135" s="25" t="s">
+      <c r="L135" s="22" t="s">
         <v>291</v>
       </c>
       <c r="M135" s="1" t="s">
@@ -9492,7 +9479,7 @@
       <c r="K136" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="L136" s="25" t="s">
+      <c r="L136" s="22" t="s">
         <v>488</v>
       </c>
       <c r="M136" s="1"/>
@@ -9531,7 +9518,7 @@
       <c r="K137" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L137" s="25" t="s">
+      <c r="L137" s="22" t="s">
         <v>488</v>
       </c>
       <c r="M137" s="1"/>
@@ -9570,7 +9557,7 @@
       <c r="K138" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L138" s="25" t="s">
+      <c r="L138" s="22" t="s">
         <v>301</v>
       </c>
       <c r="M138" s="1"/>
@@ -9609,7 +9596,7 @@
       <c r="K139" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="L139" s="25" t="s">
+      <c r="L139" s="22" t="s">
         <v>488</v>
       </c>
       <c r="M139" s="1"/>
@@ -9648,7 +9635,7 @@
       <c r="K140" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L140" s="25" t="s">
+      <c r="L140" s="22" t="s">
         <v>301</v>
       </c>
       <c r="M140" s="1"/>
@@ -9687,7 +9674,7 @@
       <c r="K141" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L141" s="25" t="s">
+      <c r="L141" s="22" t="s">
         <v>301</v>
       </c>
       <c r="M141" s="1"/>
@@ -9726,7 +9713,7 @@
       <c r="K142" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L142" s="25" t="s">
+      <c r="L142" s="22" t="s">
         <v>301</v>
       </c>
       <c r="M142" s="1" t="s">
@@ -9767,7 +9754,7 @@
       <c r="K143" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="L143" s="23">
+      <c r="L143" s="21">
         <v>46202</v>
       </c>
       <c r="M143" s="1"/>
@@ -9806,7 +9793,7 @@
       <c r="K144" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L144" s="23">
+      <c r="L144" s="21">
         <v>46202</v>
       </c>
       <c r="M144" s="1"/>
@@ -9843,7 +9830,7 @@
         <v>65</v>
       </c>
       <c r="K145" s="1"/>
-      <c r="L145" s="1"/>
+      <c r="L145" s="22"/>
       <c r="M145" s="1"/>
     </row>
     <row r="146" spans="1:13" x14ac:dyDescent="0.25">
@@ -9878,9 +9865,9 @@
         <v>21</v>
       </c>
       <c r="K146" s="2" t="s">
-        <v>937</v>
-      </c>
-      <c r="L146" s="22">
+        <v>936</v>
+      </c>
+      <c r="L146" s="21">
         <v>46176</v>
       </c>
       <c r="M146" s="1"/>
@@ -9917,7 +9904,7 @@
         <v>65</v>
       </c>
       <c r="K147" s="1"/>
-      <c r="L147" s="1"/>
+      <c r="L147" s="22"/>
       <c r="M147" s="1"/>
     </row>
     <row r="148" spans="1:13" x14ac:dyDescent="0.25">
@@ -9954,7 +9941,7 @@
       <c r="K148" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L148" s="25" t="s">
+      <c r="L148" s="22" t="s">
         <v>301</v>
       </c>
       <c r="M148" s="1"/>
@@ -9993,7 +9980,7 @@
       <c r="K149" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L149" s="25" t="s">
+      <c r="L149" s="22" t="s">
         <v>301</v>
       </c>
       <c r="M149" s="1"/>
@@ -10032,7 +10019,7 @@
       <c r="K150" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L150" s="25" t="s">
+      <c r="L150" s="22" t="s">
         <v>301</v>
       </c>
       <c r="M150" s="1"/>
@@ -10069,7 +10056,7 @@
         <v>65</v>
       </c>
       <c r="K151" s="1"/>
-      <c r="L151" s="1"/>
+      <c r="L151" s="22"/>
       <c r="M151" s="1"/>
     </row>
     <row r="152" spans="1:13" x14ac:dyDescent="0.25">
@@ -10106,7 +10093,7 @@
       <c r="K152" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L152" s="25"/>
+      <c r="L152" s="22"/>
       <c r="M152" s="1" t="s">
         <v>428</v>
       </c>
@@ -10145,7 +10132,7 @@
       <c r="K153" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L153" s="22">
+      <c r="L153" s="21">
         <v>46146</v>
       </c>
       <c r="M153" s="1"/>
@@ -10184,7 +10171,7 @@
       <c r="K154" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="L154" s="22">
+      <c r="L154" s="21">
         <v>46146</v>
       </c>
       <c r="M154" s="1"/>
@@ -10223,7 +10210,7 @@
       <c r="K155" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L155" s="25" t="s">
+      <c r="L155" s="22" t="s">
         <v>301</v>
       </c>
       <c r="M155" s="1"/>
@@ -10260,7 +10247,7 @@
         <v>65</v>
       </c>
       <c r="K156" s="1"/>
-      <c r="L156" s="1"/>
+      <c r="L156" s="22"/>
       <c r="M156" s="1"/>
     </row>
     <row r="157" spans="1:13" x14ac:dyDescent="0.25">
@@ -10295,7 +10282,7 @@
         <v>65</v>
       </c>
       <c r="K157" s="1"/>
-      <c r="L157" s="1"/>
+      <c r="L157" s="22"/>
       <c r="M157" s="1"/>
     </row>
     <row r="158" spans="1:13" x14ac:dyDescent="0.25">
@@ -10332,7 +10319,7 @@
       <c r="K158" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L158" s="25" t="s">
+      <c r="L158" s="22" t="s">
         <v>301</v>
       </c>
       <c r="M158" s="1"/>
@@ -10369,7 +10356,7 @@
         <v>65</v>
       </c>
       <c r="K159" s="1"/>
-      <c r="L159" s="1"/>
+      <c r="L159" s="22"/>
       <c r="M159" s="1"/>
     </row>
     <row r="160" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -10406,7 +10393,7 @@
       <c r="K160" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="L160" s="22">
+      <c r="L160" s="21">
         <v>46171</v>
       </c>
       <c r="M160" s="1"/>
@@ -10445,7 +10432,7 @@
       <c r="K161" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="L161" s="22">
+      <c r="L161" s="21">
         <v>46146</v>
       </c>
       <c r="M161" s="1"/>
@@ -10482,9 +10469,9 @@
         <v>21</v>
       </c>
       <c r="K162" s="1" t="s">
-        <v>938</v>
-      </c>
-      <c r="L162" s="22">
+        <v>937</v>
+      </c>
+      <c r="L162" s="21">
         <v>46175</v>
       </c>
       <c r="M162" s="1"/>
@@ -10523,7 +10510,7 @@
       <c r="K163" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="L163" s="22">
+      <c r="L163" s="21">
         <v>46172</v>
       </c>
       <c r="M163" s="1"/>
@@ -10562,7 +10549,7 @@
       <c r="K164" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L164" s="25" t="s">
+      <c r="L164" s="22" t="s">
         <v>301</v>
       </c>
       <c r="M164" s="1"/>
@@ -10601,7 +10588,7 @@
       <c r="K165" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="L165" s="22">
+      <c r="L165" s="21">
         <v>46171</v>
       </c>
       <c r="M165" s="1"/>
@@ -10638,7 +10625,7 @@
         <v>65</v>
       </c>
       <c r="K166" s="1"/>
-      <c r="L166" s="1"/>
+      <c r="L166" s="22"/>
       <c r="M166" s="1"/>
     </row>
     <row r="167" spans="1:13" x14ac:dyDescent="0.25">
@@ -10675,7 +10662,7 @@
       <c r="K167" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L167" s="25" t="s">
+      <c r="L167" s="22" t="s">
         <v>301</v>
       </c>
       <c r="M167" s="1" t="s">
@@ -10711,10 +10698,14 @@
         <v>20</v>
       </c>
       <c r="J168" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K168" s="1"/>
-      <c r="L168" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="K168" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L168" s="21">
+        <v>46177</v>
+      </c>
       <c r="M168" s="1"/>
     </row>
     <row r="169" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -10746,10 +10737,14 @@
         <v>20</v>
       </c>
       <c r="J169" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K169" s="1"/>
-      <c r="L169" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="K169" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L169" s="21">
+        <v>46177</v>
+      </c>
       <c r="M169" s="1"/>
     </row>
     <row r="170" spans="1:13" x14ac:dyDescent="0.25">
@@ -10781,10 +10776,14 @@
         <v>39</v>
       </c>
       <c r="J170" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K170" s="1"/>
-      <c r="L170" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="K170" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L170" s="21">
+        <v>46177</v>
+      </c>
       <c r="M170" s="1"/>
     </row>
     <row r="171" spans="1:13" x14ac:dyDescent="0.25">
@@ -10816,10 +10815,14 @@
         <v>20</v>
       </c>
       <c r="J171" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K171" s="1"/>
-      <c r="L171" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="K171" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L171" s="21">
+        <v>46177</v>
+      </c>
       <c r="M171" s="1"/>
     </row>
     <row r="172" spans="1:13" x14ac:dyDescent="0.25">
@@ -10851,10 +10854,14 @@
         <v>39</v>
       </c>
       <c r="J172" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K172" s="1"/>
-      <c r="L172" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="K172" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L172" s="21">
+        <v>46177</v>
+      </c>
       <c r="M172" s="1"/>
     </row>
     <row r="173" spans="1:13" x14ac:dyDescent="0.25">
@@ -10886,10 +10893,14 @@
         <v>20</v>
       </c>
       <c r="J173" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K173" s="1"/>
-      <c r="L173" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="K173" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L173" s="21">
+        <v>46177</v>
+      </c>
       <c r="M173" s="1"/>
     </row>
     <row r="174" spans="1:13" x14ac:dyDescent="0.25">
@@ -10924,7 +10935,7 @@
         <v>65</v>
       </c>
       <c r="K174" s="1"/>
-      <c r="L174" s="1"/>
+      <c r="L174" s="22"/>
       <c r="M174" s="1"/>
     </row>
     <row r="175" spans="1:13" x14ac:dyDescent="0.25">
@@ -10961,7 +10972,7 @@
       <c r="K175" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="L175" s="25" t="s">
+      <c r="L175" s="22" t="s">
         <v>573</v>
       </c>
       <c r="M175" s="1"/>
@@ -11000,7 +11011,7 @@
       <c r="K176" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="L176" s="25" t="s">
+      <c r="L176" s="22" t="s">
         <v>573</v>
       </c>
       <c r="M176" s="1"/>
@@ -11037,7 +11048,7 @@
         <v>65</v>
       </c>
       <c r="K177" s="1"/>
-      <c r="L177" s="1"/>
+      <c r="L177" s="22"/>
       <c r="M177" s="1"/>
     </row>
     <row r="178" spans="1:13" x14ac:dyDescent="0.25">
@@ -11072,7 +11083,7 @@
         <v>65</v>
       </c>
       <c r="K178" s="1"/>
-      <c r="L178" s="1"/>
+      <c r="L178" s="22"/>
       <c r="M178" s="1"/>
     </row>
     <row r="179" spans="1:13" x14ac:dyDescent="0.25">
@@ -11107,7 +11118,7 @@
         <v>65</v>
       </c>
       <c r="K179" s="1"/>
-      <c r="L179" s="1"/>
+      <c r="L179" s="22"/>
       <c r="M179" s="1"/>
     </row>
     <row r="180" spans="1:13" x14ac:dyDescent="0.25">
@@ -11139,10 +11150,14 @@
         <v>20</v>
       </c>
       <c r="J180" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K180" s="1"/>
-      <c r="L180" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="K180" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L180" s="21">
+        <v>46177</v>
+      </c>
       <c r="M180" s="1"/>
     </row>
     <row r="181" spans="1:13" x14ac:dyDescent="0.25">
@@ -11174,10 +11189,14 @@
         <v>20</v>
       </c>
       <c r="J181" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K181" s="1"/>
-      <c r="L181" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="K181" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L181" s="21">
+        <v>46177</v>
+      </c>
       <c r="M181" s="1"/>
     </row>
     <row r="182" spans="1:13" x14ac:dyDescent="0.25">
@@ -11209,10 +11228,14 @@
         <v>39</v>
       </c>
       <c r="J182" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K182" s="1"/>
-      <c r="L182" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="K182" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L182" s="21">
+        <v>46177</v>
+      </c>
       <c r="M182" s="1"/>
     </row>
     <row r="183" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -11247,7 +11270,7 @@
         <v>65</v>
       </c>
       <c r="K183" s="1"/>
-      <c r="L183" s="1"/>
+      <c r="L183" s="22"/>
       <c r="M183" s="1"/>
     </row>
     <row r="184" spans="1:13" x14ac:dyDescent="0.25">
@@ -11279,10 +11302,14 @@
         <v>20</v>
       </c>
       <c r="J184" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K184" s="1"/>
-      <c r="L184" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="K184" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L184" s="21">
+        <v>46177</v>
+      </c>
       <c r="M184" s="1"/>
     </row>
     <row r="185" spans="1:13" x14ac:dyDescent="0.25">
@@ -11314,11 +11341,17 @@
         <v>20</v>
       </c>
       <c r="J185" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K185" s="1"/>
-      <c r="L185" s="1"/>
-      <c r="M185" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="K185" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L185" s="21">
+        <v>46178</v>
+      </c>
+      <c r="M185" s="1" t="s">
+        <v>938</v>
+      </c>
     </row>
     <row r="186" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A186" s="1">
@@ -11349,10 +11382,14 @@
         <v>39</v>
       </c>
       <c r="J186" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K186" s="1"/>
-      <c r="L186" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="K186" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="L186" s="22" t="s">
+        <v>939</v>
+      </c>
       <c r="M186" s="1"/>
     </row>
     <row r="187" spans="1:13" x14ac:dyDescent="0.25">
@@ -11384,11 +11421,17 @@
         <v>20</v>
       </c>
       <c r="J187" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K187" s="1"/>
-      <c r="L187" s="1"/>
-      <c r="M187" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="K187" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="L187" s="21">
+        <v>46178</v>
+      </c>
+      <c r="M187" s="1" t="s">
+        <v>428</v>
+      </c>
     </row>
     <row r="188" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A188" s="1">
@@ -11419,11 +11462,17 @@
         <v>39</v>
       </c>
       <c r="J188" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K188" s="1"/>
-      <c r="L188" s="1"/>
-      <c r="M188" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="K188" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="L188" s="21">
+        <v>46178</v>
+      </c>
+      <c r="M188" s="1" t="s">
+        <v>428</v>
+      </c>
     </row>
     <row r="189" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A189" s="1">
@@ -11457,7 +11506,7 @@
         <v>65</v>
       </c>
       <c r="K189" s="1"/>
-      <c r="L189" s="1"/>
+      <c r="L189" s="22"/>
       <c r="M189" s="1"/>
     </row>
     <row r="190" spans="1:13" x14ac:dyDescent="0.25">
@@ -11489,10 +11538,14 @@
         <v>20</v>
       </c>
       <c r="J190" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K190" s="1"/>
-      <c r="L190" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="K190" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L190" s="22" t="s">
+        <v>939</v>
+      </c>
       <c r="M190" s="1"/>
     </row>
     <row r="191" spans="1:13" x14ac:dyDescent="0.25">
@@ -11524,10 +11577,14 @@
         <v>20</v>
       </c>
       <c r="J191" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K191" s="1"/>
-      <c r="L191" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="K191" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L191" s="21">
+        <v>46178</v>
+      </c>
       <c r="M191" s="1"/>
     </row>
     <row r="192" spans="1:13" x14ac:dyDescent="0.25">
@@ -11559,10 +11616,14 @@
         <v>39</v>
       </c>
       <c r="J192" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K192" s="1"/>
-      <c r="L192" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="K192" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="L192" s="22" t="s">
+        <v>939</v>
+      </c>
       <c r="M192" s="1"/>
     </row>
     <row r="193" spans="1:13" x14ac:dyDescent="0.25">
@@ -11594,10 +11655,14 @@
         <v>39</v>
       </c>
       <c r="J193" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K193" s="1"/>
-      <c r="L193" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="K193" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L193" s="21">
+        <v>46177</v>
+      </c>
       <c r="M193" s="1"/>
     </row>
     <row r="194" spans="1:13" x14ac:dyDescent="0.25">
@@ -11632,7 +11697,7 @@
         <v>65</v>
       </c>
       <c r="K194" s="1"/>
-      <c r="L194" s="1"/>
+      <c r="L194" s="22"/>
       <c r="M194" s="1"/>
     </row>
     <row r="195" spans="1:13" x14ac:dyDescent="0.25">
@@ -11669,7 +11734,7 @@
       <c r="K195" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="L195" s="25" t="s">
+      <c r="L195" s="22" t="s">
         <v>573</v>
       </c>
       <c r="M195" s="1"/>
@@ -11706,7 +11771,7 @@
         <v>65</v>
       </c>
       <c r="K196" s="1"/>
-      <c r="L196" s="1"/>
+      <c r="L196" s="22"/>
       <c r="M196" s="1"/>
     </row>
     <row r="197" spans="1:13" x14ac:dyDescent="0.25">
@@ -11738,10 +11803,14 @@
         <v>20</v>
       </c>
       <c r="J197" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K197" s="1"/>
-      <c r="L197" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="K197" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L197" s="21">
+        <v>46176</v>
+      </c>
       <c r="M197" s="1"/>
     </row>
     <row r="198" spans="1:13" x14ac:dyDescent="0.25">
@@ -11776,7 +11845,7 @@
         <v>21</v>
       </c>
       <c r="K198" s="1"/>
-      <c r="L198" s="25" t="s">
+      <c r="L198" s="22" t="s">
         <v>573</v>
       </c>
       <c r="M198" s="1"/>
@@ -11815,7 +11884,7 @@
       <c r="K199" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="L199" s="25" t="s">
+      <c r="L199" s="22" t="s">
         <v>573</v>
       </c>
       <c r="M199" s="1"/>
@@ -11854,7 +11923,7 @@
       <c r="K200" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="L200" s="25" t="s">
+      <c r="L200" s="22" t="s">
         <v>573</v>
       </c>
       <c r="M200" s="1"/>
@@ -11888,11 +11957,17 @@
         <v>64</v>
       </c>
       <c r="J201" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K201" s="1"/>
-      <c r="L201" s="1"/>
-      <c r="M201" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="K201" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L201" s="21">
+        <v>46176</v>
+      </c>
+      <c r="M201" s="1" t="s">
+        <v>428</v>
+      </c>
     </row>
     <row r="202" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A202" s="1">
@@ -11928,7 +12003,7 @@
       <c r="K202" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L202" s="25" t="s">
+      <c r="L202" s="22" t="s">
         <v>573</v>
       </c>
       <c r="M202" s="1" t="s">
@@ -11969,7 +12044,7 @@
       <c r="K203" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L203" s="25" t="s">
+      <c r="L203" s="22" t="s">
         <v>488</v>
       </c>
       <c r="M203" s="1"/>
@@ -12008,7 +12083,7 @@
       <c r="K204" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="L204" s="25" t="s">
+      <c r="L204" s="22" t="s">
         <v>573</v>
       </c>
       <c r="M204" s="1"/>
@@ -12042,10 +12117,14 @@
         <v>20</v>
       </c>
       <c r="J205" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K205" s="1"/>
-      <c r="L205" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="K205" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L205" s="21">
+        <v>46176</v>
+      </c>
       <c r="M205" s="1"/>
     </row>
     <row r="206" spans="1:13" x14ac:dyDescent="0.25">
@@ -12077,10 +12156,14 @@
         <v>39</v>
       </c>
       <c r="J206" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K206" s="1"/>
-      <c r="L206" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="K206" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L206" s="21">
+        <v>46176</v>
+      </c>
       <c r="M206" s="1"/>
     </row>
     <row r="207" spans="1:13" x14ac:dyDescent="0.25">
@@ -12112,10 +12195,14 @@
         <v>20</v>
       </c>
       <c r="J207" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K207" s="1"/>
-      <c r="L207" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="K207" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="L207" s="21">
+        <v>46177</v>
+      </c>
       <c r="M207" s="1"/>
     </row>
     <row r="208" spans="1:13" x14ac:dyDescent="0.25">
@@ -12147,10 +12234,14 @@
         <v>20</v>
       </c>
       <c r="J208" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K208" s="1"/>
-      <c r="L208" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="K208" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L208" s="21">
+        <v>46177</v>
+      </c>
       <c r="M208" s="1"/>
     </row>
     <row r="209" spans="1:13" x14ac:dyDescent="0.25">
@@ -12182,10 +12273,14 @@
         <v>20</v>
       </c>
       <c r="J209" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K209" s="1"/>
-      <c r="L209" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="K209" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L209" s="21">
+        <v>46175</v>
+      </c>
       <c r="M209" s="1"/>
     </row>
     <row r="210" spans="1:13" x14ac:dyDescent="0.25">
@@ -12217,10 +12312,14 @@
         <v>39</v>
       </c>
       <c r="J210" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K210" s="1"/>
-      <c r="L210" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="K210" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="L210" s="21">
+        <v>46176</v>
+      </c>
       <c r="M210" s="1"/>
     </row>
     <row r="211" spans="1:13" x14ac:dyDescent="0.25">
@@ -12252,10 +12351,14 @@
         <v>64</v>
       </c>
       <c r="J211" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K211" s="1"/>
-      <c r="L211" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="K211" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L211" s="21">
+        <v>46175</v>
+      </c>
       <c r="M211" s="1"/>
     </row>
     <row r="212" spans="1:13" x14ac:dyDescent="0.25">
@@ -12290,7 +12393,7 @@
         <v>65</v>
       </c>
       <c r="K212" s="1"/>
-      <c r="L212" s="1"/>
+      <c r="L212" s="22"/>
       <c r="M212" s="1"/>
     </row>
     <row r="213" spans="1:13" x14ac:dyDescent="0.25">
@@ -12322,11 +12425,17 @@
         <v>39</v>
       </c>
       <c r="J213" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K213" s="1"/>
-      <c r="L213" s="1"/>
-      <c r="M213" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="K213" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="L213" s="21">
+        <v>46173</v>
+      </c>
+      <c r="M213" s="1" t="s">
+        <v>428</v>
+      </c>
     </row>
     <row r="214" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A214" s="1">
@@ -12357,10 +12466,14 @@
         <v>20</v>
       </c>
       <c r="J214" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K214" s="1"/>
-      <c r="L214" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="K214" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L214" s="21">
+        <v>46177</v>
+      </c>
       <c r="M214" s="1"/>
     </row>
     <row r="215" spans="1:13" x14ac:dyDescent="0.25">
@@ -12392,10 +12505,14 @@
         <v>20</v>
       </c>
       <c r="J215" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K215" s="1"/>
-      <c r="L215" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="K215" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="L215" s="21">
+        <v>46174</v>
+      </c>
       <c r="M215" s="1"/>
     </row>
     <row r="216" spans="1:13" x14ac:dyDescent="0.25">
@@ -12427,10 +12544,14 @@
         <v>20</v>
       </c>
       <c r="J216" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K216" s="1"/>
-      <c r="L216" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="K216" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L216" s="21">
+        <v>46177</v>
+      </c>
       <c r="M216" s="1"/>
     </row>
     <row r="217" spans="1:13" x14ac:dyDescent="0.25">
@@ -12462,10 +12583,14 @@
         <v>39</v>
       </c>
       <c r="J217" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K217" s="1"/>
-      <c r="L217" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="K217" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L217" s="21">
+        <v>46176</v>
+      </c>
       <c r="M217" s="1"/>
     </row>
     <row r="218" spans="1:13" x14ac:dyDescent="0.25">
@@ -12497,10 +12622,14 @@
         <v>39</v>
       </c>
       <c r="J218" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K218" s="1"/>
-      <c r="L218" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="K218" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L218" s="21">
+        <v>46174</v>
+      </c>
       <c r="M218" s="1"/>
     </row>
     <row r="219" spans="1:13" x14ac:dyDescent="0.25">
@@ -12532,11 +12661,17 @@
         <v>39</v>
       </c>
       <c r="J219" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K219" s="1"/>
-      <c r="L219" s="1"/>
-      <c r="M219" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="K219" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="L219" s="21">
+        <v>46174</v>
+      </c>
+      <c r="M219" s="1" t="s">
+        <v>940</v>
+      </c>
     </row>
     <row r="220" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A220" s="1">
@@ -12567,10 +12702,14 @@
         <v>20</v>
       </c>
       <c r="J220" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K220" s="1"/>
-      <c r="L220" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="K220" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L220" s="21">
+        <v>46174</v>
+      </c>
       <c r="M220" s="1"/>
     </row>
     <row r="221" spans="1:13" x14ac:dyDescent="0.25">
@@ -12602,10 +12741,14 @@
         <v>20</v>
       </c>
       <c r="J221" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K221" s="1"/>
-      <c r="L221" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="K221" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L221" s="21">
+        <v>46175</v>
+      </c>
       <c r="M221" s="1"/>
     </row>
     <row r="222" spans="1:13" x14ac:dyDescent="0.25">
@@ -12637,12 +12780,12 @@
         <v>20</v>
       </c>
       <c r="J222" s="1" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="K222" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="L222" s="22">
+      <c r="L222" s="21">
         <v>46175</v>
       </c>
       <c r="M222" s="1"/>
@@ -12681,7 +12824,7 @@
       <c r="K223" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="L223" s="22">
+      <c r="L223" s="21">
         <v>46175</v>
       </c>
       <c r="M223" s="1"/>
@@ -12715,10 +12858,14 @@
         <v>20</v>
       </c>
       <c r="J224" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K224" s="1"/>
-      <c r="L224" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="K224" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="L224" s="21">
+        <v>46176</v>
+      </c>
       <c r="M224" s="1"/>
     </row>
     <row r="225" spans="1:13" x14ac:dyDescent="0.25">
@@ -12750,10 +12897,14 @@
         <v>20</v>
       </c>
       <c r="J225" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K225" s="1"/>
-      <c r="L225" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="K225" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L225" s="21">
+        <v>46176</v>
+      </c>
       <c r="M225" s="1"/>
     </row>
     <row r="226" spans="1:13" x14ac:dyDescent="0.25">
@@ -12785,10 +12936,14 @@
         <v>20</v>
       </c>
       <c r="J226" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K226" s="1"/>
-      <c r="L226" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="K226" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L226" s="21">
+        <v>46176</v>
+      </c>
       <c r="M226" s="1"/>
     </row>
     <row r="227" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -12820,10 +12975,14 @@
         <v>39</v>
       </c>
       <c r="J227" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K227" s="1"/>
-      <c r="L227" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="K227" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L227" s="21">
+        <v>46176</v>
+      </c>
       <c r="M227" s="1"/>
     </row>
     <row r="228" spans="1:13" x14ac:dyDescent="0.25">
@@ -12855,10 +13014,14 @@
         <v>39</v>
       </c>
       <c r="J228" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K228" s="1"/>
-      <c r="L228" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="K228" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L228" s="21">
+        <v>46176</v>
+      </c>
       <c r="M228" s="1"/>
     </row>
     <row r="229" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -12890,10 +13053,14 @@
         <v>20</v>
       </c>
       <c r="J229" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K229" s="1"/>
-      <c r="L229" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="K229" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L229" s="21">
+        <v>46176</v>
+      </c>
       <c r="M229" s="1"/>
     </row>
     <row r="230" spans="1:13" x14ac:dyDescent="0.25">
@@ -12927,10 +13094,8 @@
       <c r="J230" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="K230" s="1" t="s">
-        <v>935</v>
-      </c>
-      <c r="L230" s="1"/>
+      <c r="K230" s="1"/>
+      <c r="L230" s="21"/>
       <c r="M230" s="1"/>
     </row>
     <row r="231" spans="1:13" x14ac:dyDescent="0.25">
@@ -12962,10 +13127,14 @@
         <v>20</v>
       </c>
       <c r="J231" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K231" s="1"/>
-      <c r="L231" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="K231" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="L231" s="21">
+        <v>46178</v>
+      </c>
       <c r="M231" s="1"/>
     </row>
     <row r="232" spans="1:13" x14ac:dyDescent="0.25">
@@ -12997,10 +13166,14 @@
         <v>39</v>
       </c>
       <c r="J232" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K232" s="1"/>
-      <c r="L232" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="K232" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L232" s="21">
+        <v>46177</v>
+      </c>
       <c r="M232" s="1"/>
     </row>
     <row r="233" spans="1:13" x14ac:dyDescent="0.25">
@@ -13032,10 +13205,14 @@
         <v>20</v>
       </c>
       <c r="J233" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K233" s="1"/>
-      <c r="L233" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="K233" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L233" s="21">
+        <v>46177</v>
+      </c>
       <c r="M233" s="1"/>
     </row>
     <row r="234" spans="1:13" x14ac:dyDescent="0.25">
@@ -13067,10 +13244,14 @@
         <v>39</v>
       </c>
       <c r="J234" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K234" s="1"/>
-      <c r="L234" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="K234" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L234" s="21">
+        <v>46177</v>
+      </c>
       <c r="M234" s="1"/>
     </row>
     <row r="235" spans="1:13" x14ac:dyDescent="0.25">
@@ -13102,10 +13283,14 @@
         <v>20</v>
       </c>
       <c r="J235" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K235" s="1"/>
-      <c r="L235" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="K235" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L235" s="21">
+        <v>46177</v>
+      </c>
       <c r="M235" s="1"/>
     </row>
     <row r="236" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -13142,7 +13327,7 @@
       <c r="K236" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L236" s="25" t="s">
+      <c r="L236" s="22" t="s">
         <v>488</v>
       </c>
       <c r="M236" s="1" t="s">
@@ -13183,7 +13368,7 @@
       <c r="K237" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="L237" s="22">
+      <c r="L237" s="21">
         <v>46174</v>
       </c>
       <c r="M237" s="1"/>
@@ -13222,7 +13407,7 @@
       <c r="K238" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="L238" s="25" t="s">
+      <c r="L238" s="22" t="s">
         <v>488</v>
       </c>
       <c r="M238" s="1"/>
@@ -13256,11 +13441,17 @@
         <v>20</v>
       </c>
       <c r="J239" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K239" s="1"/>
-      <c r="L239" s="1"/>
-      <c r="M239" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="K239" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L239" s="21">
+        <v>46177</v>
+      </c>
+      <c r="M239" s="1" t="s">
+        <v>428</v>
+      </c>
     </row>
     <row r="240" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A240" s="1">
@@ -13291,10 +13482,14 @@
         <v>20</v>
       </c>
       <c r="J240" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K240" s="1"/>
-      <c r="L240" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="K240" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L240" s="21">
+        <v>46177</v>
+      </c>
       <c r="M240" s="1"/>
     </row>
     <row r="241" spans="1:13" x14ac:dyDescent="0.25">
@@ -13331,7 +13526,7 @@
       <c r="K241" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L241" s="25" t="s">
+      <c r="L241" s="22" t="s">
         <v>488</v>
       </c>
       <c r="M241" s="1"/>
@@ -13368,7 +13563,7 @@
         <v>65</v>
       </c>
       <c r="K242" s="1"/>
-      <c r="L242" s="1"/>
+      <c r="L242" s="22"/>
       <c r="M242" s="1"/>
     </row>
     <row r="243" spans="1:13" x14ac:dyDescent="0.25">
@@ -13405,7 +13600,7 @@
       <c r="K243" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L243" s="25" t="s">
+      <c r="L243" s="22" t="s">
         <v>488</v>
       </c>
       <c r="M243" s="1"/>
@@ -13444,7 +13639,7 @@
       <c r="K244" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="L244" s="25" t="s">
+      <c r="L244" s="22" t="s">
         <v>488</v>
       </c>
       <c r="M244" s="1"/>
@@ -13483,7 +13678,7 @@
       <c r="K245" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="L245" s="25" t="s">
+      <c r="L245" s="22" t="s">
         <v>488</v>
       </c>
       <c r="M245" s="1"/>
@@ -13522,7 +13717,7 @@
       <c r="K246" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="L246" s="25" t="s">
+      <c r="L246" s="22" t="s">
         <v>488</v>
       </c>
       <c r="M246" s="1"/>
@@ -13556,10 +13751,14 @@
         <v>39</v>
       </c>
       <c r="J247" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K247" s="1"/>
-      <c r="L247" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="K247" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L247" s="21">
+        <v>46177</v>
+      </c>
       <c r="M247" s="1"/>
     </row>
     <row r="248" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13591,10 +13790,14 @@
         <v>20</v>
       </c>
       <c r="J248" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K248" s="1"/>
-      <c r="L248" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="K248" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L248" s="21">
+        <v>46175</v>
+      </c>
       <c r="M248" s="1"/>
     </row>
     <row r="249" spans="1:13" x14ac:dyDescent="0.25">
@@ -13626,10 +13829,14 @@
         <v>39</v>
       </c>
       <c r="J249" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K249" s="1"/>
-      <c r="L249" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="K249" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="L249" s="21">
+        <v>46175</v>
+      </c>
       <c r="M249" s="1"/>
     </row>
     <row r="250" spans="1:13" x14ac:dyDescent="0.25">
@@ -13661,12 +13868,14 @@
         <v>39</v>
       </c>
       <c r="J250" s="1" t="s">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="K250" s="1" t="s">
-        <v>750</v>
-      </c>
-      <c r="L250" s="1"/>
+        <v>60</v>
+      </c>
+      <c r="L250" s="21">
+        <v>46176</v>
+      </c>
       <c r="M250" s="1"/>
     </row>
     <row r="251" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -13684,22 +13893,26 @@
         <v>278</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="G251" s="1" t="s">
         <v>18</v>
       </c>
       <c r="H251" s="1" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="I251" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J251" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K251" s="1"/>
-      <c r="L251" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="K251" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="L251" s="21">
+        <v>46176</v>
+      </c>
       <c r="M251" s="1"/>
     </row>
     <row r="252" spans="1:13" x14ac:dyDescent="0.25">
@@ -13725,7 +13938,7 @@
         <v>18</v>
       </c>
       <c r="H252" s="1" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="I252" s="1" t="s">
         <v>39</v>
@@ -13734,7 +13947,7 @@
         <v>21</v>
       </c>
       <c r="K252" s="1"/>
-      <c r="L252" s="25" t="s">
+      <c r="L252" s="22" t="s">
         <v>488</v>
       </c>
       <c r="M252" s="1"/>
@@ -13756,13 +13969,13 @@
         <v>215</v>
       </c>
       <c r="F253" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="G253" s="1" t="s">
         <v>754</v>
       </c>
-      <c r="G253" s="1" t="s">
+      <c r="H253" s="1" t="s">
         <v>755</v>
-      </c>
-      <c r="H253" s="1" t="s">
-        <v>756</v>
       </c>
       <c r="I253" s="1" t="s">
         <v>20</v>
@@ -13771,9 +13984,9 @@
         <v>21</v>
       </c>
       <c r="K253" s="1" t="s">
-        <v>757</v>
-      </c>
-      <c r="L253" s="25" t="s">
+        <v>756</v>
+      </c>
+      <c r="L253" s="22" t="s">
         <v>488</v>
       </c>
       <c r="M253" s="1"/>
@@ -13786,7 +13999,7 @@
         <v>747</v>
       </c>
       <c r="C254" s="15" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="D254" s="1" t="s">
         <v>15</v>
@@ -13801,7 +14014,7 @@
         <v>28</v>
       </c>
       <c r="H254" s="1" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="I254" s="1" t="s">
         <v>64</v>
@@ -13810,9 +14023,9 @@
         <v>65</v>
       </c>
       <c r="K254" s="1" t="s">
-        <v>760</v>
-      </c>
-      <c r="L254" s="1"/>
+        <v>759</v>
+      </c>
+      <c r="L254" s="22"/>
       <c r="M254" s="1"/>
     </row>
     <row r="255" spans="1:13" x14ac:dyDescent="0.25">
@@ -13823,7 +14036,7 @@
         <v>747</v>
       </c>
       <c r="C255" s="15" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="D255" s="1" t="s">
         <v>15</v>
@@ -13835,10 +14048,10 @@
         <v>328</v>
       </c>
       <c r="G255" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="H255" s="1" t="s">
         <v>762</v>
-      </c>
-      <c r="H255" s="1" t="s">
-        <v>763</v>
       </c>
       <c r="I255" s="1" t="s">
         <v>20</v>
@@ -13847,9 +14060,9 @@
         <v>65</v>
       </c>
       <c r="K255" s="1" t="s">
-        <v>760</v>
-      </c>
-      <c r="L255" s="1"/>
+        <v>759</v>
+      </c>
+      <c r="L255" s="22"/>
       <c r="M255" s="1"/>
     </row>
     <row r="256" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -13860,7 +14073,7 @@
         <v>747</v>
       </c>
       <c r="C256" s="15" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="D256" s="1" t="s">
         <v>15</v>
@@ -13869,24 +14082,26 @@
         <v>16</v>
       </c>
       <c r="F256" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="G256" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="H256" s="1" t="s">
         <v>764</v>
-      </c>
-      <c r="G256" s="1" t="s">
-        <v>755</v>
-      </c>
-      <c r="H256" s="1" t="s">
-        <v>765</v>
       </c>
       <c r="I256" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J256" s="1" t="s">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="K256" s="1" t="s">
-        <v>760</v>
-      </c>
-      <c r="L256" s="1"/>
+        <v>54</v>
+      </c>
+      <c r="L256" s="21">
+        <v>46177</v>
+      </c>
       <c r="M256" s="1"/>
     </row>
     <row r="257" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -13897,7 +14112,7 @@
         <v>747</v>
       </c>
       <c r="C257" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D257" s="1" t="s">
         <v>15</v>
@@ -13906,13 +14121,13 @@
         <v>43</v>
       </c>
       <c r="F257" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="G257" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="H257" s="1" t="s">
         <v>767</v>
-      </c>
-      <c r="G257" s="1" t="s">
-        <v>755</v>
-      </c>
-      <c r="H257" s="1" t="s">
-        <v>768</v>
       </c>
       <c r="I257" s="1" t="s">
         <v>39</v>
@@ -13921,7 +14136,7 @@
         <v>65</v>
       </c>
       <c r="K257" s="1"/>
-      <c r="L257" s="1"/>
+      <c r="L257" s="22"/>
       <c r="M257" s="1"/>
     </row>
     <row r="258" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -13932,7 +14147,7 @@
         <v>747</v>
       </c>
       <c r="C258" s="15" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="D258" s="1" t="s">
         <v>15</v>
@@ -13941,13 +14156,13 @@
         <v>43</v>
       </c>
       <c r="F258" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="G258" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="H258" s="1" t="s">
         <v>770</v>
-      </c>
-      <c r="G258" s="1" t="s">
-        <v>755</v>
-      </c>
-      <c r="H258" s="1" t="s">
-        <v>771</v>
       </c>
       <c r="I258" s="1" t="s">
         <v>64</v>
@@ -13958,11 +14173,11 @@
       <c r="K258" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="L258" s="25" t="s">
+      <c r="L258" s="22" t="s">
         <v>488</v>
       </c>
       <c r="M258" s="1" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="259" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -13973,7 +14188,7 @@
         <v>747</v>
       </c>
       <c r="C259" s="15" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="D259" s="1" t="s">
         <v>25</v>
@@ -13982,13 +14197,13 @@
         <v>215</v>
       </c>
       <c r="F259" s="1" t="s">
+        <v>773</v>
+      </c>
+      <c r="G259" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="H259" s="1" t="s">
         <v>774</v>
-      </c>
-      <c r="G259" s="1" t="s">
-        <v>755</v>
-      </c>
-      <c r="H259" s="1" t="s">
-        <v>775</v>
       </c>
       <c r="I259" s="1" t="s">
         <v>20</v>
@@ -13997,13 +14212,13 @@
         <v>21</v>
       </c>
       <c r="K259" s="1" t="s">
+        <v>775</v>
+      </c>
+      <c r="L259" s="22" t="s">
+        <v>747</v>
+      </c>
+      <c r="M259" s="1" t="s">
         <v>776</v>
-      </c>
-      <c r="L259" s="25" t="s">
-        <v>747</v>
-      </c>
-      <c r="M259" s="1" t="s">
-        <v>777</v>
       </c>
     </row>
     <row r="260" spans="1:13" x14ac:dyDescent="0.25">
@@ -14026,10 +14241,10 @@
         <v>328</v>
       </c>
       <c r="G260" s="1" t="s">
+        <v>777</v>
+      </c>
+      <c r="H260" s="1" t="s">
         <v>778</v>
-      </c>
-      <c r="H260" s="1" t="s">
-        <v>779</v>
       </c>
       <c r="I260" s="1" t="s">
         <v>20</v>
@@ -14038,9 +14253,9 @@
         <v>65</v>
       </c>
       <c r="K260" s="1" t="s">
-        <v>935</v>
-      </c>
-      <c r="L260" s="8"/>
+        <v>934</v>
+      </c>
+      <c r="L260" s="21"/>
       <c r="M260" s="1"/>
     </row>
     <row r="261" spans="1:13" x14ac:dyDescent="0.25">
@@ -14063,10 +14278,10 @@
         <v>328</v>
       </c>
       <c r="G261" s="1" t="s">
+        <v>780</v>
+      </c>
+      <c r="H261" s="1" t="s">
         <v>781</v>
-      </c>
-      <c r="H261" s="1" t="s">
-        <v>782</v>
       </c>
       <c r="I261" s="1" t="s">
         <v>39</v>
@@ -14075,9 +14290,9 @@
         <v>65</v>
       </c>
       <c r="K261" s="1" t="s">
-        <v>760</v>
-      </c>
-      <c r="L261" s="8"/>
+        <v>759</v>
+      </c>
+      <c r="L261" s="21"/>
       <c r="M261" s="1"/>
     </row>
     <row r="262" spans="1:13" x14ac:dyDescent="0.25">
@@ -14097,13 +14312,13 @@
         <v>232</v>
       </c>
       <c r="F262" s="1" t="s">
+        <v>782</v>
+      </c>
+      <c r="G262" s="1" t="s">
         <v>783</v>
       </c>
-      <c r="G262" s="1" t="s">
+      <c r="H262" s="1" t="s">
         <v>784</v>
-      </c>
-      <c r="H262" s="1" t="s">
-        <v>785</v>
       </c>
       <c r="I262" s="1" t="s">
         <v>20</v>
@@ -14114,11 +14329,11 @@
       <c r="K262" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="L262" s="23">
+      <c r="L262" s="21">
         <v>46175</v>
       </c>
       <c r="M262" s="1" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="263" spans="1:13" x14ac:dyDescent="0.25">
@@ -14138,13 +14353,13 @@
         <v>232</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="G263" s="1" t="s">
+        <v>783</v>
+      </c>
+      <c r="H263" s="1" t="s">
         <v>784</v>
-      </c>
-      <c r="H263" s="1" t="s">
-        <v>785</v>
       </c>
       <c r="I263" s="1" t="s">
         <v>20</v>
@@ -14155,11 +14370,11 @@
       <c r="K263" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="L263" s="23">
+      <c r="L263" s="21">
         <v>46175</v>
       </c>
       <c r="M263" s="1" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="264" spans="1:13" x14ac:dyDescent="0.25">
@@ -14182,10 +14397,10 @@
         <v>731</v>
       </c>
       <c r="G264" s="1" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="H264" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="I264" s="1" t="s">
         <v>64</v>
@@ -14196,7 +14411,7 @@
       <c r="K264" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="L264" s="23">
+      <c r="L264" s="21">
         <v>46177</v>
       </c>
       <c r="M264" s="1"/>
@@ -14218,26 +14433,26 @@
         <v>43</v>
       </c>
       <c r="F265" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="G265" s="1" t="s">
         <v>789</v>
       </c>
-      <c r="G265" s="1" t="s">
+      <c r="H265" s="1" t="s">
         <v>790</v>
-      </c>
-      <c r="H265" s="1" t="s">
-        <v>791</v>
       </c>
       <c r="I265" s="1" t="s">
         <v>39</v>
       </c>
       <c r="J265" s="1" t="s">
+        <v>791</v>
+      </c>
+      <c r="K265" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="L265" s="21"/>
+      <c r="M265" s="1" t="s">
         <v>792</v>
-      </c>
-      <c r="K265" s="1" t="s">
-        <v>780</v>
-      </c>
-      <c r="L265" s="8"/>
-      <c r="M265" s="1" t="s">
-        <v>793</v>
       </c>
     </row>
     <row r="266" spans="1:13" x14ac:dyDescent="0.25">
@@ -14257,13 +14472,13 @@
         <v>71</v>
       </c>
       <c r="F266" s="1" t="s">
+        <v>793</v>
+      </c>
+      <c r="G266" s="1" t="s">
         <v>794</v>
       </c>
-      <c r="G266" s="1" t="s">
+      <c r="H266" s="1" t="s">
         <v>795</v>
-      </c>
-      <c r="H266" s="1" t="s">
-        <v>796</v>
       </c>
       <c r="I266" s="1" t="s">
         <v>20</v>
@@ -14272,9 +14487,9 @@
         <v>65</v>
       </c>
       <c r="K266" s="1" t="s">
-        <v>780</v>
-      </c>
-      <c r="L266" s="8"/>
+        <v>779</v>
+      </c>
+      <c r="L266" s="21"/>
       <c r="M266" s="1"/>
     </row>
     <row r="267" spans="1:13" x14ac:dyDescent="0.25">
@@ -14294,13 +14509,13 @@
         <v>215</v>
       </c>
       <c r="F267" s="1" t="s">
+        <v>796</v>
+      </c>
+      <c r="G267" s="1" t="s">
         <v>797</v>
       </c>
-      <c r="G267" s="1" t="s">
+      <c r="H267" s="1" t="s">
         <v>798</v>
-      </c>
-      <c r="H267" s="1" t="s">
-        <v>799</v>
       </c>
       <c r="I267" s="1" t="s">
         <v>64</v>
@@ -14311,7 +14526,7 @@
       <c r="K267" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="L267" s="23">
+      <c r="L267" s="21">
         <v>46176</v>
       </c>
       <c r="M267" s="1"/>
@@ -14333,13 +14548,13 @@
         <v>232</v>
       </c>
       <c r="F268" s="1" t="s">
+        <v>799</v>
+      </c>
+      <c r="G268" s="1" t="s">
+        <v>783</v>
+      </c>
+      <c r="H268" s="1" t="s">
         <v>800</v>
-      </c>
-      <c r="G268" s="1" t="s">
-        <v>784</v>
-      </c>
-      <c r="H268" s="1" t="s">
-        <v>801</v>
       </c>
       <c r="I268" s="1" t="s">
         <v>20</v>
@@ -14348,19 +14563,19 @@
         <v>65</v>
       </c>
       <c r="K268" s="1" t="s">
-        <v>780</v>
-      </c>
-      <c r="L268" s="8"/>
+        <v>779</v>
+      </c>
+      <c r="L268" s="21"/>
       <c r="M268" s="1"/>
     </row>
     <row r="269" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A269" s="1">
         <v>268</v>
       </c>
-      <c r="B269" s="23">
+      <c r="B269" s="21">
         <v>46175</v>
       </c>
-      <c r="C269" s="30">
+      <c r="C269" s="27">
         <v>0.55138888888888893</v>
       </c>
       <c r="D269" s="1" t="s">
@@ -14370,13 +14585,13 @@
         <v>16</v>
       </c>
       <c r="F269" s="1" t="s">
+        <v>801</v>
+      </c>
+      <c r="G269" s="1" t="s">
         <v>802</v>
       </c>
-      <c r="G269" s="1" t="s">
+      <c r="H269" s="1" t="s">
         <v>803</v>
-      </c>
-      <c r="H269" s="1" t="s">
-        <v>804</v>
       </c>
       <c r="I269" s="1" t="s">
         <v>20</v>
@@ -14385,11 +14600,11 @@
         <v>65</v>
       </c>
       <c r="K269" s="1" t="s">
-        <v>780</v>
-      </c>
-      <c r="L269" s="8"/>
+        <v>779</v>
+      </c>
+      <c r="L269" s="21"/>
       <c r="M269" s="1" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="270" spans="1:13" x14ac:dyDescent="0.25">
@@ -14409,13 +14624,13 @@
         <v>232</v>
       </c>
       <c r="F270" s="1" t="s">
+        <v>805</v>
+      </c>
+      <c r="G270" s="1" t="s">
         <v>806</v>
       </c>
-      <c r="G270" s="1" t="s">
+      <c r="H270" s="1" t="s">
         <v>807</v>
-      </c>
-      <c r="H270" s="1" t="s">
-        <v>808</v>
       </c>
       <c r="I270" s="1" t="s">
         <v>64</v>
@@ -14424,11 +14639,11 @@
         <v>21</v>
       </c>
       <c r="K270" s="1" t="s">
+        <v>808</v>
+      </c>
+      <c r="L270" s="21"/>
+      <c r="M270" s="1" t="s">
         <v>809</v>
-      </c>
-      <c r="L270" s="23"/>
-      <c r="M270" s="1" t="s">
-        <v>810</v>
       </c>
     </row>
     <row r="271" spans="1:13" x14ac:dyDescent="0.25">
@@ -14448,13 +14663,13 @@
         <v>43</v>
       </c>
       <c r="F271" s="1" t="s">
+        <v>810</v>
+      </c>
+      <c r="G271" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="H271" s="1" t="s">
         <v>811</v>
-      </c>
-      <c r="G271" s="1" t="s">
-        <v>790</v>
-      </c>
-      <c r="H271" s="1" t="s">
-        <v>812</v>
       </c>
       <c r="I271" s="1" t="s">
         <v>39</v>
@@ -14465,11 +14680,11 @@
       <c r="K271" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L271" s="23">
+      <c r="L271" s="21">
         <v>46175</v>
       </c>
       <c r="M271" s="1" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="272" spans="1:13" x14ac:dyDescent="0.25">
@@ -14489,24 +14704,26 @@
         <v>89</v>
       </c>
       <c r="F272" s="1" t="s">
+        <v>813</v>
+      </c>
+      <c r="G272" s="1" t="s">
+        <v>806</v>
+      </c>
+      <c r="H272" s="1" t="s">
         <v>814</v>
-      </c>
-      <c r="G272" s="1" t="s">
-        <v>807</v>
-      </c>
-      <c r="H272" s="1" t="s">
-        <v>815</v>
       </c>
       <c r="I272" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J272" s="1" t="s">
-        <v>65</v>
+        <v>935</v>
       </c>
       <c r="K272" s="1" t="s">
-        <v>760</v>
-      </c>
-      <c r="L272" s="8"/>
+        <v>74</v>
+      </c>
+      <c r="L272" s="21">
+        <v>46178</v>
+      </c>
       <c r="M272" s="1"/>
     </row>
     <row r="273" spans="1:13" x14ac:dyDescent="0.25">
@@ -14526,13 +14743,13 @@
         <v>71</v>
       </c>
       <c r="F273" s="1" t="s">
+        <v>815</v>
+      </c>
+      <c r="G273" s="1" t="s">
+        <v>777</v>
+      </c>
+      <c r="H273" s="1" t="s">
         <v>816</v>
-      </c>
-      <c r="G273" s="1" t="s">
-        <v>778</v>
-      </c>
-      <c r="H273" s="1" t="s">
-        <v>817</v>
       </c>
       <c r="I273" s="1" t="s">
         <v>20</v>
@@ -14543,11 +14760,11 @@
       <c r="K273" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="L273" s="23">
+      <c r="L273" s="21">
         <v>46177</v>
       </c>
       <c r="M273" s="1" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="274" spans="1:13" x14ac:dyDescent="0.25">
@@ -14567,13 +14784,13 @@
         <v>80</v>
       </c>
       <c r="F274" s="1" t="s">
+        <v>818</v>
+      </c>
+      <c r="G274" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="H274" s="1" t="s">
         <v>819</v>
-      </c>
-      <c r="G274" s="1" t="s">
-        <v>790</v>
-      </c>
-      <c r="H274" s="1" t="s">
-        <v>820</v>
       </c>
       <c r="I274" s="1" t="s">
         <v>39</v>
@@ -14584,11 +14801,11 @@
       <c r="K274" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L274" s="23">
+      <c r="L274" s="21">
         <v>46175</v>
       </c>
       <c r="M274" s="1" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="275" spans="1:13" x14ac:dyDescent="0.25">
@@ -14608,13 +14825,13 @@
         <v>50</v>
       </c>
       <c r="F275" s="1" t="s">
+        <v>820</v>
+      </c>
+      <c r="G275" s="1" t="s">
+        <v>806</v>
+      </c>
+      <c r="H275" s="1" t="s">
         <v>821</v>
-      </c>
-      <c r="G275" s="1" t="s">
-        <v>807</v>
-      </c>
-      <c r="H275" s="1" t="s">
-        <v>822</v>
       </c>
       <c r="I275" s="1" t="s">
         <v>20</v>
@@ -14625,7 +14842,7 @@
       <c r="K275" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="L275" s="23">
+      <c r="L275" s="21">
         <v>46175</v>
       </c>
       <c r="M275" s="1"/>
@@ -14650,10 +14867,10 @@
         <v>726</v>
       </c>
       <c r="G276" s="1" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="H276" s="1" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="I276" s="1" t="s">
         <v>64</v>
@@ -14662,13 +14879,13 @@
         <v>21</v>
       </c>
       <c r="K276" s="1" t="s">
-        <v>760</v>
-      </c>
-      <c r="L276" s="23">
+        <v>759</v>
+      </c>
+      <c r="L276" s="21">
         <v>46175</v>
       </c>
       <c r="M276" s="1" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="277" spans="1:13" x14ac:dyDescent="0.25">
@@ -14691,10 +14908,10 @@
         <v>309</v>
       </c>
       <c r="G277" s="1" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="H277" s="1" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="I277" s="1" t="s">
         <v>20</v>
@@ -14703,13 +14920,13 @@
         <v>21</v>
       </c>
       <c r="K277" s="1" t="s">
-        <v>928</v>
-      </c>
-      <c r="L277" s="23">
+        <v>927</v>
+      </c>
+      <c r="L277" s="21">
         <v>46175</v>
       </c>
       <c r="M277" s="1" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="278" spans="1:13" x14ac:dyDescent="0.25">
@@ -14729,13 +14946,13 @@
         <v>232</v>
       </c>
       <c r="F278" s="1" t="s">
+        <v>824</v>
+      </c>
+      <c r="G278" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="H278" s="1" t="s">
         <v>825</v>
-      </c>
-      <c r="G278" s="1" t="s">
-        <v>790</v>
-      </c>
-      <c r="H278" s="1" t="s">
-        <v>826</v>
       </c>
       <c r="I278" s="1" t="s">
         <v>39</v>
@@ -14744,9 +14961,9 @@
         <v>21</v>
       </c>
       <c r="K278" s="1" t="s">
-        <v>928</v>
-      </c>
-      <c r="L278" s="23">
+        <v>927</v>
+      </c>
+      <c r="L278" s="21">
         <v>46175</v>
       </c>
       <c r="M278" s="1"/>
@@ -14768,13 +14985,13 @@
         <v>71</v>
       </c>
       <c r="F279" s="1" t="s">
+        <v>826</v>
+      </c>
+      <c r="G279" s="1" t="s">
+        <v>797</v>
+      </c>
+      <c r="H279" s="1" t="s">
         <v>827</v>
-      </c>
-      <c r="G279" s="1" t="s">
-        <v>798</v>
-      </c>
-      <c r="H279" s="1" t="s">
-        <v>828</v>
       </c>
       <c r="I279" s="1" t="s">
         <v>20</v>
@@ -14785,11 +15002,11 @@
       <c r="K279" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="L279" s="23">
+      <c r="L279" s="21">
         <v>46177</v>
       </c>
       <c r="M279" s="1" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="280" spans="1:13" x14ac:dyDescent="0.25">
@@ -14812,10 +15029,10 @@
         <v>328</v>
       </c>
       <c r="G280" s="1" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="H280" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="I280" s="1" t="s">
         <v>39</v>
@@ -14824,9 +15041,9 @@
         <v>65</v>
       </c>
       <c r="K280" s="1" t="s">
-        <v>760</v>
-      </c>
-      <c r="L280" s="8"/>
+        <v>759</v>
+      </c>
+      <c r="L280" s="21"/>
       <c r="M280" s="1"/>
     </row>
     <row r="281" spans="1:13" x14ac:dyDescent="0.25">
@@ -14846,13 +15063,13 @@
         <v>16</v>
       </c>
       <c r="F281" s="1" t="s">
+        <v>829</v>
+      </c>
+      <c r="G281" s="1" t="s">
         <v>830</v>
       </c>
-      <c r="G281" s="1" t="s">
+      <c r="H281" s="1" t="s">
         <v>831</v>
-      </c>
-      <c r="H281" s="1" t="s">
-        <v>832</v>
       </c>
       <c r="I281" s="1" t="s">
         <v>20</v>
@@ -14863,7 +15080,7 @@
       <c r="K281" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L281" s="23">
+      <c r="L281" s="21">
         <v>46177</v>
       </c>
       <c r="M281" s="1"/>
@@ -14885,13 +15102,13 @@
         <v>232</v>
       </c>
       <c r="F282" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="G282" s="1" t="s">
+        <v>777</v>
+      </c>
+      <c r="H282" s="1" t="s">
         <v>833</v>
-      </c>
-      <c r="G282" s="1" t="s">
-        <v>778</v>
-      </c>
-      <c r="H282" s="1" t="s">
-        <v>834</v>
       </c>
       <c r="I282" s="1" t="s">
         <v>20</v>
@@ -14900,11 +15117,9 @@
         <v>65</v>
       </c>
       <c r="K282" s="1" t="s">
-        <v>780</v>
-      </c>
-      <c r="L282" s="8">
-        <v>46177</v>
-      </c>
+        <v>779</v>
+      </c>
+      <c r="L282" s="21"/>
       <c r="M282" s="1"/>
     </row>
     <row r="283" spans="1:13" x14ac:dyDescent="0.25">
@@ -14924,13 +15139,13 @@
         <v>16</v>
       </c>
       <c r="F283" s="1" t="s">
+        <v>829</v>
+      </c>
+      <c r="G283" s="1" t="s">
         <v>830</v>
       </c>
-      <c r="G283" s="1" t="s">
-        <v>831</v>
-      </c>
       <c r="H283" s="1" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="I283" s="1" t="s">
         <v>20</v>
@@ -14941,11 +15156,11 @@
       <c r="K283" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="L283" s="23">
+      <c r="L283" s="21">
         <v>46177</v>
       </c>
       <c r="M283" s="1" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="284" spans="1:13" x14ac:dyDescent="0.25">
@@ -14965,13 +15180,13 @@
         <v>232</v>
       </c>
       <c r="F284" s="1" t="s">
+        <v>836</v>
+      </c>
+      <c r="G284" s="1" t="s">
+        <v>780</v>
+      </c>
+      <c r="H284" s="1" t="s">
         <v>837</v>
-      </c>
-      <c r="G284" s="1" t="s">
-        <v>781</v>
-      </c>
-      <c r="H284" s="1" t="s">
-        <v>838</v>
       </c>
       <c r="I284" s="1" t="s">
         <v>39</v>
@@ -14980,9 +15195,9 @@
         <v>65</v>
       </c>
       <c r="K284" s="1" t="s">
-        <v>760</v>
-      </c>
-      <c r="L284" s="8"/>
+        <v>759</v>
+      </c>
+      <c r="L284" s="21"/>
       <c r="M284" s="1"/>
     </row>
     <row r="285" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -15005,10 +15220,10 @@
         <v>328</v>
       </c>
       <c r="G285" s="1" t="s">
+        <v>838</v>
+      </c>
+      <c r="H285" s="1" t="s">
         <v>839</v>
-      </c>
-      <c r="H285" s="1" t="s">
-        <v>840</v>
       </c>
       <c r="I285" s="1" t="s">
         <v>39</v>
@@ -15017,9 +15232,9 @@
         <v>65</v>
       </c>
       <c r="K285" s="1" t="s">
-        <v>760</v>
-      </c>
-      <c r="L285" s="8"/>
+        <v>759</v>
+      </c>
+      <c r="L285" s="21"/>
       <c r="M285" s="1"/>
     </row>
     <row r="286" spans="1:13" x14ac:dyDescent="0.25">
@@ -15039,13 +15254,13 @@
         <v>232</v>
       </c>
       <c r="F286" s="1" t="s">
+        <v>840</v>
+      </c>
+      <c r="G286" s="1" t="s">
+        <v>777</v>
+      </c>
+      <c r="H286" s="1" t="s">
         <v>841</v>
-      </c>
-      <c r="G286" s="1" t="s">
-        <v>778</v>
-      </c>
-      <c r="H286" s="1" t="s">
-        <v>842</v>
       </c>
       <c r="I286" s="1" t="s">
         <v>20</v>
@@ -15054,9 +15269,9 @@
         <v>65</v>
       </c>
       <c r="K286" s="1" t="s">
-        <v>935</v>
-      </c>
-      <c r="L286" s="8"/>
+        <v>934</v>
+      </c>
+      <c r="L286" s="21"/>
       <c r="M286" s="1"/>
     </row>
     <row r="287" spans="1:13" x14ac:dyDescent="0.25">
@@ -15079,10 +15294,10 @@
         <v>182</v>
       </c>
       <c r="G287" s="1" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="H287" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="I287" s="1" t="s">
         <v>64</v>
@@ -15093,11 +15308,11 @@
       <c r="K287" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="L287" s="23">
+      <c r="L287" s="21">
         <v>46177</v>
       </c>
       <c r="M287" s="1" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="288" spans="1:13" x14ac:dyDescent="0.25">
@@ -15117,13 +15332,13 @@
         <v>71</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="G288" s="1" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="H288" s="1" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="I288" s="1" t="s">
         <v>20</v>
@@ -15134,7 +15349,7 @@
       <c r="K288" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="L288" s="23">
+      <c r="L288" s="21">
         <v>46177</v>
       </c>
       <c r="M288" s="1"/>
@@ -15156,13 +15371,13 @@
         <v>16</v>
       </c>
       <c r="F289" s="1" t="s">
+        <v>844</v>
+      </c>
+      <c r="G289" s="1" t="s">
+        <v>783</v>
+      </c>
+      <c r="H289" s="1" t="s">
         <v>845</v>
-      </c>
-      <c r="G289" s="1" t="s">
-        <v>784</v>
-      </c>
-      <c r="H289" s="1" t="s">
-        <v>846</v>
       </c>
       <c r="I289" s="1" t="s">
         <v>20</v>
@@ -15173,11 +15388,11 @@
       <c r="K289" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="L289" s="23">
+      <c r="L289" s="21">
         <v>46177</v>
       </c>
       <c r="M289" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="290" spans="1:13" x14ac:dyDescent="0.25">
@@ -15197,13 +15412,13 @@
         <v>16</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="G290" s="1" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="H290" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="I290" s="1" t="s">
         <v>20</v>
@@ -15214,11 +15429,11 @@
       <c r="K290" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L290" s="23">
+      <c r="L290" s="21">
         <v>46176</v>
       </c>
       <c r="M290" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="291" spans="1:13" x14ac:dyDescent="0.25">
@@ -15238,13 +15453,13 @@
         <v>16</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="G291" s="1" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="H291" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="I291" s="1" t="s">
         <v>20</v>
@@ -15255,11 +15470,11 @@
       <c r="K291" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L291" s="23">
+      <c r="L291" s="21">
         <v>46176</v>
       </c>
       <c r="M291" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="292" spans="1:13" x14ac:dyDescent="0.25">
@@ -15279,13 +15494,13 @@
         <v>16</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="G292" s="1" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="H292" s="1" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="I292" s="1" t="s">
         <v>39</v>
@@ -15296,11 +15511,11 @@
       <c r="K292" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L292" s="23">
+      <c r="L292" s="21">
         <v>46176</v>
       </c>
       <c r="M292" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="293" spans="1:13" x14ac:dyDescent="0.25">
@@ -15323,10 +15538,10 @@
         <v>72</v>
       </c>
       <c r="G293" s="1" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="H293" s="1" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="I293" s="1" t="s">
         <v>20</v>
@@ -15337,7 +15552,7 @@
       <c r="K293" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="L293" s="23">
+      <c r="L293" s="21">
         <v>46176</v>
       </c>
       <c r="M293" s="1"/>
@@ -15359,13 +15574,13 @@
         <v>232</v>
       </c>
       <c r="F294" s="1" t="s">
+        <v>852</v>
+      </c>
+      <c r="G294" s="1" t="s">
         <v>853</v>
       </c>
-      <c r="G294" s="1" t="s">
+      <c r="H294" s="1" t="s">
         <v>854</v>
-      </c>
-      <c r="H294" s="1" t="s">
-        <v>855</v>
       </c>
       <c r="I294" s="1" t="s">
         <v>20</v>
@@ -15376,11 +15591,11 @@
       <c r="K294" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="L294" s="23">
+      <c r="L294" s="21">
         <v>46177</v>
       </c>
       <c r="M294" s="1" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="295" spans="1:13" x14ac:dyDescent="0.25">
@@ -15400,13 +15615,13 @@
         <v>89</v>
       </c>
       <c r="F295" s="1" t="s">
+        <v>855</v>
+      </c>
+      <c r="G295" s="1" t="s">
+        <v>830</v>
+      </c>
+      <c r="H295" s="1" t="s">
         <v>856</v>
-      </c>
-      <c r="G295" s="1" t="s">
-        <v>831</v>
-      </c>
-      <c r="H295" s="1" t="s">
-        <v>857</v>
       </c>
       <c r="I295" s="1" t="s">
         <v>64</v>
@@ -15417,11 +15632,11 @@
       <c r="K295" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="L295" s="23">
+      <c r="L295" s="21">
         <v>46177</v>
       </c>
       <c r="M295" s="1" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="296" spans="1:13" x14ac:dyDescent="0.25">
@@ -15441,13 +15656,13 @@
         <v>89</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="G296" s="1" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="H296" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="I296" s="1" t="s">
         <v>64</v>
@@ -15458,11 +15673,11 @@
       <c r="K296" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="L296" s="23">
+      <c r="L296" s="21">
         <v>46177</v>
       </c>
       <c r="M296" s="1" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="297" spans="1:13" x14ac:dyDescent="0.25">
@@ -15482,13 +15697,13 @@
         <v>89</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="G297" s="1" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="H297" s="1" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="I297" s="1" t="s">
         <v>20</v>
@@ -15499,11 +15714,11 @@
       <c r="K297" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L297" s="23">
+      <c r="L297" s="21">
         <v>46177</v>
       </c>
       <c r="M297" s="1" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="298" spans="1:13" x14ac:dyDescent="0.25">
@@ -15526,10 +15741,10 @@
         <v>274</v>
       </c>
       <c r="G298" s="1" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="H298" s="1" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="I298" s="1" t="s">
         <v>64</v>
@@ -15540,7 +15755,7 @@
       <c r="K298" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L298" s="23">
+      <c r="L298" s="21">
         <v>46177</v>
       </c>
       <c r="M298" s="1"/>
@@ -15562,26 +15777,26 @@
         <v>43</v>
       </c>
       <c r="F299" s="1" t="s">
+        <v>860</v>
+      </c>
+      <c r="G299" s="1" t="s">
+        <v>838</v>
+      </c>
+      <c r="H299" s="1" t="s">
         <v>861</v>
-      </c>
-      <c r="G299" s="1" t="s">
-        <v>839</v>
-      </c>
-      <c r="H299" s="1" t="s">
-        <v>862</v>
       </c>
       <c r="I299" s="1" t="s">
         <v>39</v>
       </c>
       <c r="J299" s="1" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="K299" s="1" t="s">
+        <v>862</v>
+      </c>
+      <c r="L299" s="21"/>
+      <c r="M299" s="1" t="s">
         <v>863</v>
-      </c>
-      <c r="L299" s="8"/>
-      <c r="M299" s="1" t="s">
-        <v>864</v>
       </c>
     </row>
     <row r="300" spans="1:13" x14ac:dyDescent="0.25">
@@ -15601,13 +15816,13 @@
         <v>71</v>
       </c>
       <c r="F300" s="1" t="s">
+        <v>864</v>
+      </c>
+      <c r="G300" s="1" t="s">
+        <v>783</v>
+      </c>
+      <c r="H300" s="1" t="s">
         <v>865</v>
-      </c>
-      <c r="G300" s="1" t="s">
-        <v>784</v>
-      </c>
-      <c r="H300" s="1" t="s">
-        <v>866</v>
       </c>
       <c r="I300" s="1" t="s">
         <v>20</v>
@@ -15618,11 +15833,11 @@
       <c r="K300" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L300" s="23">
+      <c r="L300" s="21">
         <v>46176</v>
       </c>
       <c r="M300" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="301" spans="1:13" x14ac:dyDescent="0.25">
@@ -15642,13 +15857,13 @@
         <v>50</v>
       </c>
       <c r="F301" s="1" t="s">
+        <v>866</v>
+      </c>
+      <c r="G301" s="1" t="s">
+        <v>783</v>
+      </c>
+      <c r="H301" s="1" t="s">
         <v>867</v>
-      </c>
-      <c r="G301" s="1" t="s">
-        <v>784</v>
-      </c>
-      <c r="H301" s="1" t="s">
-        <v>868</v>
       </c>
       <c r="I301" s="1" t="s">
         <v>39</v>
@@ -15657,9 +15872,9 @@
         <v>65</v>
       </c>
       <c r="K301" s="1" t="s">
-        <v>780</v>
-      </c>
-      <c r="L301" s="8"/>
+        <v>779</v>
+      </c>
+      <c r="L301" s="21"/>
       <c r="M301" s="1"/>
     </row>
     <row r="302" spans="1:13" x14ac:dyDescent="0.25">
@@ -15679,13 +15894,13 @@
         <v>43</v>
       </c>
       <c r="F302" s="1" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="G302" s="1" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="H302" s="1" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="I302" s="1" t="s">
         <v>39</v>
@@ -15696,11 +15911,11 @@
       <c r="K302" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L302" s="23">
+      <c r="L302" s="21">
         <v>46176</v>
       </c>
       <c r="M302" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="303" spans="1:13" x14ac:dyDescent="0.25">
@@ -15720,13 +15935,13 @@
         <v>50</v>
       </c>
       <c r="F303" s="1" t="s">
+        <v>869</v>
+      </c>
+      <c r="G303" s="1" t="s">
+        <v>806</v>
+      </c>
+      <c r="H303" s="1" t="s">
         <v>870</v>
-      </c>
-      <c r="G303" s="1" t="s">
-        <v>807</v>
-      </c>
-      <c r="H303" s="1" t="s">
-        <v>871</v>
       </c>
       <c r="I303" s="1" t="s">
         <v>20</v>
@@ -15737,11 +15952,11 @@
       <c r="K303" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L303" s="23">
+      <c r="L303" s="21">
         <v>46176</v>
       </c>
       <c r="M303" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="304" spans="1:13" x14ac:dyDescent="0.25">
@@ -15764,10 +15979,10 @@
         <v>332</v>
       </c>
       <c r="G304" s="1" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="H304" s="1" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="I304" s="1" t="s">
         <v>20</v>
@@ -15778,11 +15993,11 @@
       <c r="K304" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L304" s="23">
+      <c r="L304" s="21">
         <v>46176</v>
       </c>
       <c r="M304" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="305" spans="1:13" x14ac:dyDescent="0.25">
@@ -15805,10 +16020,10 @@
         <v>618</v>
       </c>
       <c r="G305" s="1" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="H305" s="1" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="I305" s="1" t="s">
         <v>64</v>
@@ -15819,11 +16034,11 @@
       <c r="K305" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L305" s="23">
+      <c r="L305" s="21">
         <v>46176</v>
       </c>
       <c r="M305" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="306" spans="1:13" x14ac:dyDescent="0.25">
@@ -15843,13 +16058,13 @@
         <v>43</v>
       </c>
       <c r="F306" s="1" t="s">
+        <v>873</v>
+      </c>
+      <c r="G306" s="1" t="s">
+        <v>806</v>
+      </c>
+      <c r="H306" s="1" t="s">
         <v>874</v>
-      </c>
-      <c r="G306" s="1" t="s">
-        <v>807</v>
-      </c>
-      <c r="H306" s="1" t="s">
-        <v>875</v>
       </c>
       <c r="I306" s="1" t="s">
         <v>20</v>
@@ -15860,11 +16075,11 @@
       <c r="K306" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L306" s="23">
+      <c r="L306" s="21">
         <v>46176</v>
       </c>
       <c r="M306" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="307" spans="1:13" x14ac:dyDescent="0.25">
@@ -15887,10 +16102,10 @@
         <v>484</v>
       </c>
       <c r="G307" s="1" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="H307" s="1" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="I307" s="1" t="s">
         <v>20</v>
@@ -15901,11 +16116,11 @@
       <c r="K307" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L307" s="23">
+      <c r="L307" s="21">
         <v>46177</v>
       </c>
       <c r="M307" s="1" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="308" spans="1:13" x14ac:dyDescent="0.25">
@@ -15928,10 +16143,10 @@
         <v>309</v>
       </c>
       <c r="G308" s="1" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="H308" s="1" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="I308" s="1" t="s">
         <v>20</v>
@@ -15940,9 +16155,9 @@
         <v>21</v>
       </c>
       <c r="K308" s="1" t="s">
-        <v>780</v>
-      </c>
-      <c r="L308" s="23">
+        <v>779</v>
+      </c>
+      <c r="L308" s="21">
         <v>46177</v>
       </c>
       <c r="M308" s="1"/>
@@ -15967,10 +16182,10 @@
         <v>328</v>
       </c>
       <c r="G309" s="1" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H309" s="1" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="I309" s="1" t="s">
         <v>39</v>
@@ -15979,9 +16194,9 @@
         <v>65</v>
       </c>
       <c r="K309" s="1" t="s">
-        <v>760</v>
-      </c>
-      <c r="L309" s="8"/>
+        <v>759</v>
+      </c>
+      <c r="L309" s="21"/>
       <c r="M309" s="1"/>
     </row>
     <row r="310" spans="1:13" x14ac:dyDescent="0.25">
@@ -16001,13 +16216,13 @@
         <v>71</v>
       </c>
       <c r="F310" s="1" t="s">
+        <v>878</v>
+      </c>
+      <c r="G310" s="1" t="s">
+        <v>794</v>
+      </c>
+      <c r="H310" s="1" t="s">
         <v>879</v>
-      </c>
-      <c r="G310" s="1" t="s">
-        <v>795</v>
-      </c>
-      <c r="H310" s="1" t="s">
-        <v>880</v>
       </c>
       <c r="I310" s="1" t="s">
         <v>20</v>
@@ -16016,7 +16231,7 @@
         <v>65</v>
       </c>
       <c r="K310" s="1"/>
-      <c r="L310" s="8"/>
+      <c r="L310" s="21"/>
       <c r="M310" s="1"/>
     </row>
     <row r="311" spans="1:13" x14ac:dyDescent="0.25">
@@ -16036,13 +16251,13 @@
         <v>232</v>
       </c>
       <c r="F311" s="1" t="s">
+        <v>824</v>
+      </c>
+      <c r="G311" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="H311" s="1" t="s">
         <v>825</v>
-      </c>
-      <c r="G311" s="1" t="s">
-        <v>790</v>
-      </c>
-      <c r="H311" s="1" t="s">
-        <v>826</v>
       </c>
       <c r="I311" s="1" t="s">
         <v>39</v>
@@ -16053,7 +16268,7 @@
       <c r="K311" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L311" s="23">
+      <c r="L311" s="21">
         <v>46177</v>
       </c>
       <c r="M311" s="1"/>
@@ -16078,21 +16293,21 @@
         <v>220</v>
       </c>
       <c r="G312" s="1" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H312" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="I312" s="1" t="s">
         <v>64</v>
       </c>
       <c r="J312" s="1" t="s">
+        <v>881</v>
+      </c>
+      <c r="K312" s="1" t="s">
         <v>882</v>
       </c>
-      <c r="K312" s="1" t="s">
-        <v>883</v>
-      </c>
-      <c r="L312" s="8">
+      <c r="L312" s="21">
         <v>46177</v>
       </c>
       <c r="M312" s="1"/>
@@ -16114,13 +16329,13 @@
         <v>232</v>
       </c>
       <c r="F313" s="1" t="s">
+        <v>883</v>
+      </c>
+      <c r="G313" s="1" t="s">
+        <v>806</v>
+      </c>
+      <c r="H313" s="1" t="s">
         <v>884</v>
-      </c>
-      <c r="G313" s="1" t="s">
-        <v>807</v>
-      </c>
-      <c r="H313" s="1" t="s">
-        <v>885</v>
       </c>
       <c r="I313" s="1" t="s">
         <v>64</v>
@@ -16129,13 +16344,13 @@
         <v>21</v>
       </c>
       <c r="K313" s="1" t="s">
-        <v>780</v>
-      </c>
-      <c r="L313" s="23">
+        <v>779</v>
+      </c>
+      <c r="L313" s="21">
         <v>46177</v>
       </c>
       <c r="M313" s="1" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="314" spans="1:13" x14ac:dyDescent="0.25">
@@ -16155,13 +16370,13 @@
         <v>232</v>
       </c>
       <c r="F314" s="1" t="s">
+        <v>836</v>
+      </c>
+      <c r="G314" s="1" t="s">
+        <v>780</v>
+      </c>
+      <c r="H314" s="1" t="s">
         <v>837</v>
-      </c>
-      <c r="G314" s="1" t="s">
-        <v>781</v>
-      </c>
-      <c r="H314" s="1" t="s">
-        <v>838</v>
       </c>
       <c r="I314" s="1" t="s">
         <v>39</v>
@@ -16172,7 +16387,7 @@
       <c r="K314" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L314" s="23">
+      <c r="L314" s="21">
         <v>46177</v>
       </c>
       <c r="M314" s="1"/>
@@ -16194,13 +16409,13 @@
         <v>232</v>
       </c>
       <c r="F315" s="1" t="s">
+        <v>885</v>
+      </c>
+      <c r="G315" s="1" t="s">
+        <v>777</v>
+      </c>
+      <c r="H315" s="1" t="s">
         <v>886</v>
-      </c>
-      <c r="G315" s="1" t="s">
-        <v>778</v>
-      </c>
-      <c r="H315" s="1" t="s">
-        <v>887</v>
       </c>
       <c r="I315" s="1" t="s">
         <v>20</v>
@@ -16209,9 +16424,9 @@
         <v>65</v>
       </c>
       <c r="K315" s="1" t="s">
-        <v>935</v>
-      </c>
-      <c r="L315" s="8"/>
+        <v>934</v>
+      </c>
+      <c r="L315" s="21"/>
       <c r="M315" s="1"/>
     </row>
     <row r="316" spans="1:13" x14ac:dyDescent="0.25">
@@ -16234,21 +16449,23 @@
         <v>51</v>
       </c>
       <c r="G316" s="1" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="H316" s="1" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I316" s="1" t="s">
         <v>39</v>
       </c>
       <c r="J316" s="1" t="s">
-        <v>65</v>
+        <v>935</v>
       </c>
       <c r="K316" s="1" t="s">
-        <v>760</v>
-      </c>
-      <c r="L316" s="8"/>
+        <v>74</v>
+      </c>
+      <c r="L316" s="21">
+        <v>46178</v>
+      </c>
       <c r="M316" s="1"/>
     </row>
     <row r="317" spans="1:13" x14ac:dyDescent="0.25">
@@ -16271,21 +16488,23 @@
         <v>51</v>
       </c>
       <c r="G317" s="1" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="H317" s="1" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="I317" s="1" t="s">
         <v>39</v>
       </c>
       <c r="J317" s="1" t="s">
-        <v>65</v>
+        <v>935</v>
       </c>
       <c r="K317" s="1" t="s">
-        <v>760</v>
-      </c>
-      <c r="L317" s="8"/>
+        <v>74</v>
+      </c>
+      <c r="L317" s="21">
+        <v>46178</v>
+      </c>
       <c r="M317" s="1"/>
     </row>
     <row r="318" spans="1:13" x14ac:dyDescent="0.25">
@@ -16305,24 +16524,24 @@
         <v>43</v>
       </c>
       <c r="F318" s="1" t="s">
+        <v>889</v>
+      </c>
+      <c r="G318" s="1" t="s">
+        <v>783</v>
+      </c>
+      <c r="H318" s="1" t="s">
         <v>890</v>
-      </c>
-      <c r="G318" s="1" t="s">
-        <v>784</v>
-      </c>
-      <c r="H318" s="1" t="s">
-        <v>891</v>
       </c>
       <c r="I318" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J318" s="1" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="K318" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="L318" s="8">
+      <c r="L318" s="21">
         <v>46176</v>
       </c>
       <c r="M318" s="1"/>
@@ -16344,26 +16563,26 @@
         <v>43</v>
       </c>
       <c r="F319" s="1" t="s">
+        <v>891</v>
+      </c>
+      <c r="G319" s="1" t="s">
+        <v>838</v>
+      </c>
+      <c r="H319" s="1" t="s">
         <v>892</v>
-      </c>
-      <c r="G319" s="1" t="s">
-        <v>839</v>
-      </c>
-      <c r="H319" s="1" t="s">
-        <v>893</v>
       </c>
       <c r="I319" s="1" t="s">
         <v>39</v>
       </c>
       <c r="J319" s="1" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="K319" s="1" t="s">
-        <v>780</v>
-      </c>
-      <c r="L319" s="8"/>
+        <v>779</v>
+      </c>
+      <c r="L319" s="21"/>
       <c r="M319" s="1" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="320" spans="1:13" x14ac:dyDescent="0.25">
@@ -16386,21 +16605,23 @@
         <v>51</v>
       </c>
       <c r="G320" s="1" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="H320" s="1" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="I320" s="1" t="s">
         <v>39</v>
       </c>
       <c r="J320" s="1" t="s">
-        <v>65</v>
+        <v>935</v>
       </c>
       <c r="K320" s="1" t="s">
-        <v>760</v>
-      </c>
-      <c r="L320" s="8"/>
+        <v>74</v>
+      </c>
+      <c r="L320" s="21">
+        <v>46178</v>
+      </c>
       <c r="M320" s="1"/>
     </row>
     <row r="321" spans="1:13" x14ac:dyDescent="0.25">
@@ -16420,13 +16641,13 @@
         <v>89</v>
       </c>
       <c r="F321" s="1" t="s">
+        <v>895</v>
+      </c>
+      <c r="G321" s="1" t="s">
+        <v>780</v>
+      </c>
+      <c r="H321" s="1" t="s">
         <v>896</v>
-      </c>
-      <c r="G321" s="1" t="s">
-        <v>781</v>
-      </c>
-      <c r="H321" s="1" t="s">
-        <v>897</v>
       </c>
       <c r="I321" s="1" t="s">
         <v>39</v>
@@ -16435,13 +16656,13 @@
         <v>21</v>
       </c>
       <c r="K321" s="1" t="s">
-        <v>760</v>
-      </c>
-      <c r="L321" s="23">
+        <v>759</v>
+      </c>
+      <c r="L321" s="21">
         <v>46177</v>
       </c>
       <c r="M321" s="1" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="322" spans="1:13" x14ac:dyDescent="0.25">
@@ -16461,13 +16682,13 @@
         <v>89</v>
       </c>
       <c r="F322" s="1" t="s">
+        <v>898</v>
+      </c>
+      <c r="G322" s="1" t="s">
+        <v>783</v>
+      </c>
+      <c r="H322" s="1" t="s">
         <v>899</v>
-      </c>
-      <c r="G322" s="1" t="s">
-        <v>784</v>
-      </c>
-      <c r="H322" s="1" t="s">
-        <v>900</v>
       </c>
       <c r="I322" s="1" t="s">
         <v>64</v>
@@ -16478,11 +16699,11 @@
       <c r="K322" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="L322" s="23">
+      <c r="L322" s="21">
         <v>46177</v>
       </c>
       <c r="M322" s="1" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="323" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -16505,10 +16726,10 @@
         <v>633</v>
       </c>
       <c r="G323" s="1" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H323" s="1" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="I323" s="1" t="s">
         <v>39</v>
@@ -16517,20 +16738,20 @@
         <v>65</v>
       </c>
       <c r="K323" s="1" t="s">
-        <v>780</v>
-      </c>
-      <c r="L323" s="8"/>
+        <v>779</v>
+      </c>
+      <c r="L323" s="21"/>
       <c r="M323" s="1"/>
     </row>
     <row r="324" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A324" s="2">
-        <v>323</v>
-      </c>
-      <c r="B324" s="25" t="s">
+        <v>324</v>
+      </c>
+      <c r="B324" s="22" t="s">
         <v>747</v>
       </c>
-      <c r="C324" s="25" t="s">
-        <v>902</v>
+      <c r="C324" s="22" t="s">
+        <v>901</v>
       </c>
       <c r="D324" s="1" t="s">
         <v>15</v>
@@ -16545,31 +16766,31 @@
         <v>18</v>
       </c>
       <c r="H324" s="1" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="I324" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="J324" s="29" t="s">
+      <c r="J324" s="26" t="s">
         <v>21</v>
       </c>
       <c r="K324" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="L324" s="9" t="s">
+      <c r="L324" s="22" t="s">
         <v>747</v>
       </c>
       <c r="M324" s="1"/>
     </row>
     <row r="325" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A325" s="2">
-        <v>324</v>
-      </c>
-      <c r="B325" s="25" t="s">
+        <v>325</v>
+      </c>
+      <c r="B325" s="22" t="s">
         <v>747</v>
       </c>
-      <c r="C325" s="25" t="s">
-        <v>904</v>
+      <c r="C325" s="22" t="s">
+        <v>903</v>
       </c>
       <c r="D325" s="1" t="s">
         <v>25</v>
@@ -16578,37 +16799,37 @@
         <v>71</v>
       </c>
       <c r="F325" s="1" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="G325" s="1" t="s">
         <v>28</v>
       </c>
       <c r="H325" s="1" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="I325" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="J325" s="29" t="s">
+      <c r="J325" s="26" t="s">
         <v>21</v>
       </c>
       <c r="K325" s="1" t="s">
-        <v>930</v>
-      </c>
-      <c r="L325" s="9" t="s">
+        <v>929</v>
+      </c>
+      <c r="L325" s="22" t="s">
         <v>747</v>
       </c>
       <c r="M325" s="1"/>
     </row>
     <row r="326" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A326" s="2">
-        <v>325</v>
-      </c>
-      <c r="B326" s="25" t="s">
+        <v>392</v>
+      </c>
+      <c r="B326" s="22" t="s">
+        <v>906</v>
+      </c>
+      <c r="C326" s="22" t="s">
         <v>907</v>
-      </c>
-      <c r="C326" s="25" t="s">
-        <v>908</v>
       </c>
       <c r="D326" s="1" t="s">
         <v>15</v>
@@ -16617,37 +16838,37 @@
         <v>309</v>
       </c>
       <c r="F326" s="1" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="G326" s="1" t="s">
         <v>18</v>
       </c>
       <c r="H326" s="1" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="I326" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="J326" s="29" t="s">
-        <v>21</v>
-      </c>
-      <c r="K326" s="29" t="s">
-        <v>929</v>
-      </c>
-      <c r="L326" s="8">
+      <c r="J326" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="K326" s="26" t="s">
+        <v>928</v>
+      </c>
+      <c r="L326" s="21">
         <v>46177</v>
       </c>
       <c r="M326" s="1"/>
     </row>
     <row r="327" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A327" s="2">
-        <v>326</v>
-      </c>
-      <c r="B327" s="25" t="s">
+        <v>406</v>
+      </c>
+      <c r="B327" s="22" t="s">
+        <v>910</v>
+      </c>
+      <c r="C327" s="22" t="s">
         <v>911</v>
-      </c>
-      <c r="C327" s="25" t="s">
-        <v>912</v>
       </c>
       <c r="D327" s="1" t="s">
         <v>15</v>
@@ -16656,35 +16877,33 @@
         <v>43</v>
       </c>
       <c r="F327" s="1" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="G327" s="1" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H327" s="1" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="I327" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="J327" s="29" t="s">
-        <v>21</v>
-      </c>
-      <c r="K327" s="1" t="s">
-        <v>939</v>
-      </c>
-      <c r="L327" s="9"/>
+      <c r="J327" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="K327" s="1"/>
+      <c r="L327" s="22"/>
       <c r="M327" s="1"/>
     </row>
     <row r="328" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A328" s="2">
-        <v>327</v>
-      </c>
-      <c r="B328" s="25" t="s">
-        <v>907</v>
-      </c>
-      <c r="C328" s="25" t="s">
-        <v>914</v>
+        <v>412</v>
+      </c>
+      <c r="B328" s="22" t="s">
+        <v>906</v>
+      </c>
+      <c r="C328" s="22" t="s">
+        <v>913</v>
       </c>
       <c r="D328" s="1" t="s">
         <v>15</v>
@@ -16693,24 +16912,24 @@
         <v>80</v>
       </c>
       <c r="F328" s="1" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="G328" s="1" t="s">
         <v>334</v>
       </c>
       <c r="H328" s="1" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="I328" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="J328" s="29" t="s">
-        <v>21</v>
-      </c>
-      <c r="K328" s="29" t="s">
+      <c r="J328" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="K328" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="L328" s="8">
+      <c r="L328" s="21">
         <v>46177</v>
       </c>
       <c r="M328" s="1"/>
@@ -16983,19 +17202,19 @@
         <v>1</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>916</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>917</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>918</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>919</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>920</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>921</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">

--- a/CONSOLIDADO DASHBOARD VILLA.xlsx
+++ b/CONSOLIDADO DASHBOARD VILLA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FCHAVEZC\Desktop\KPIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93A5A8CB-487D-4C6F-9922-CBBA01D21158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D67BC2B2-8269-444E-B8AB-12CFC5C2C9E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4086" uniqueCount="1111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4689" uniqueCount="1270">
   <si>
     <t>ID</t>
   </si>
@@ -3354,6 +3354,483 @@
   </si>
   <si>
     <t>Puerta corrediza se salió por completo de su riel de guía</t>
+  </si>
+  <si>
+    <t>Gasfitería / Sanitarios</t>
+  </si>
+  <si>
+    <t>Se visualiza que el pozo de agua tratada está lleno.</t>
+  </si>
+  <si>
+    <t>Sala de Cómputo 307</t>
+  </si>
+  <si>
+    <t>Electricidad</t>
+  </si>
+  <si>
+    <t>Caja del interruptor se encuentra salida.</t>
+  </si>
+  <si>
+    <t>Jose Rodas  Tecnico Electricista</t>
+  </si>
+  <si>
+    <t>Climatización</t>
+  </si>
+  <si>
+    <t>Panel de aire acondicionado se encuentra apagado.</t>
+  </si>
+  <si>
+    <t>1er piso al lado de Aula 101</t>
+  </si>
+  <si>
+    <t>Electricidad / Iluminación</t>
+  </si>
+  <si>
+    <t>La luminaria de un pasillo se encuentra encendida</t>
+  </si>
+  <si>
+    <t>Limpieza + Orden</t>
+  </si>
+  <si>
+    <t>Materiales en desuso dejados en el área</t>
+  </si>
+  <si>
+    <t>Angel Yataco  Tecnico Electricista</t>
+  </si>
+  <si>
+    <t>1er piso (pasadizo)</t>
+  </si>
+  <si>
+    <t>Seguridad e Higiene</t>
+  </si>
+  <si>
+    <t>Parantes de los extintores se encuentran sin señalética</t>
+  </si>
+  <si>
+    <t>1er piso (sala de estudio/ascensor)</t>
+  </si>
+  <si>
+    <t>Extintores se encuentran sin señalética ni numeración</t>
+  </si>
+  <si>
+    <t>La pileta se encuentra apagada.</t>
+  </si>
+  <si>
+    <t>Plaza 1</t>
+  </si>
+  <si>
+    <t>Perro pequeño marrón ladrando y mordiendo a alumnos</t>
+  </si>
+  <si>
+    <t>SSHH Damas (2do piso)</t>
+  </si>
+  <si>
+    <t>Infraestructura / Cerrajería</t>
+  </si>
+  <si>
+    <t>Reposición de brazo hidráulico.</t>
+  </si>
+  <si>
+    <t>Anexo de Microbiología 308</t>
+  </si>
+  <si>
+    <t>Aire acondicionado presenta goteo/chorreo de agua</t>
+  </si>
+  <si>
+    <t>Mantenimiento / SSHH</t>
+  </si>
+  <si>
+    <t>Tapas de los dispensadores de jabón se encuentran salidas</t>
+  </si>
+  <si>
+    <t>Aula P204</t>
+  </si>
+  <si>
+    <t>Alarma contra incendios activada emitiendo pitido</t>
+  </si>
+  <si>
+    <t>Ruido o interferencia extraña en los parlantes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personal de Soporte técnico </t>
+  </si>
+  <si>
+    <t>villa 1</t>
+  </si>
+  <si>
+    <t>Pabellon A</t>
+  </si>
+  <si>
+    <t>Baño Discapacitados</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cerradura </t>
+  </si>
+  <si>
+    <t>La chapa de la puerta está malograda y no cierra.</t>
+  </si>
+  <si>
+    <t>SSHH Varones (1er piso)</t>
+  </si>
+  <si>
+    <t>Sanitario</t>
+  </si>
+  <si>
+    <t>Filtración severa: sale agua por la manija del inodoro.</t>
+  </si>
+  <si>
+    <t>Áreas Comunes</t>
+  </si>
+  <si>
+    <t>Presencia de un ave (pajarito) dentro de las instalaciones.</t>
+  </si>
+  <si>
+    <t>Requerimiento urgente de limpieza en el baño.</t>
+  </si>
+  <si>
+    <t>personal de Limpieza</t>
+  </si>
+  <si>
+    <t>2do Piso</t>
+  </si>
+  <si>
+    <t>Limpieza</t>
+  </si>
+  <si>
+    <t>Materiales de trabajo expuestos y dejados sin supervisión.</t>
+  </si>
+  <si>
+    <t>Frente a Almacenes</t>
+  </si>
+  <si>
+    <t>Acumulación de suciedad; se requiere barrer la zona.</t>
+  </si>
+  <si>
+    <t>Administrativo</t>
+  </si>
+  <si>
+    <t>Reporte de ausentismo crítico: 9 faltas en solo dos días.</t>
+  </si>
+  <si>
+    <t>Baño Cafetería Damas</t>
+  </si>
+  <si>
+    <t>Inodoro completamente atorado (el personal no logró despejarlo).</t>
+  </si>
+  <si>
+    <t>Baño Colaboradores</t>
+  </si>
+  <si>
+    <t>Continuidad de goteo de agua en grifería/llave.</t>
+  </si>
+  <si>
+    <t>SSHH 3er Piso</t>
+  </si>
+  <si>
+    <t>Desabastecimiento de papel higiénico en el último cubículo.</t>
+  </si>
+  <si>
+    <t>Inodoro desborda demasiada agua.</t>
+  </si>
+  <si>
+    <t>Accesos</t>
+  </si>
+  <si>
+    <t>Manija de la puerta se encontró rota.</t>
+  </si>
+  <si>
+    <t>Todos los SSHH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generales </t>
+  </si>
+  <si>
+    <t>Instalación de acrílicos para las hojas de control de limpieza.</t>
+  </si>
+  <si>
+    <t>Luis Matos - Tecncico Electricista</t>
+  </si>
+  <si>
+    <t>Lab. Microbiología 206</t>
+  </si>
+  <si>
+    <t>Puerta corrediza se salió de su riel. Indica ambiente libre hasta las 12:30.</t>
+  </si>
+  <si>
+    <t>Laboratorio 205</t>
+  </si>
+  <si>
+    <t>Coordinación de horarios para atención en el aula.</t>
+  </si>
+  <si>
+    <t>Villa 2 / Pabellón O</t>
+  </si>
+  <si>
+    <t>Anexo 308</t>
+  </si>
+  <si>
+    <t>Gotera constante saliendo del equipo de aire acondicionado.</t>
+  </si>
+  <si>
+    <t>SSHH (Piso 1 - Baño pequeño)</t>
+  </si>
+  <si>
+    <t>Inodoros se encuentran sucios; se solicita limpieza urgente.</t>
+  </si>
+  <si>
+    <t>SSHH Damas (Piso 1 - Baño grande)</t>
+  </si>
+  <si>
+    <t>El perchero/colgador de ropa se está desprendiendo de la pared.</t>
+  </si>
+  <si>
+    <t>SSHH Damas (Piso 1)</t>
+  </si>
+  <si>
+    <t>Mantenimiento preventivo / correctivo de cerrajería.</t>
+  </si>
+  <si>
+    <t>SSHH contiguo al Comedor</t>
+  </si>
+  <si>
+    <t>Estructura del lavadero presenta descascaramiento.</t>
+  </si>
+  <si>
+    <t>Aulas K101 y K102</t>
+  </si>
+  <si>
+    <t>Eventos</t>
+  </si>
+  <si>
+    <t>En Proceso</t>
+  </si>
+  <si>
+    <t>Angel Yataco Tecnico Electricista</t>
+  </si>
+  <si>
+    <t>TI / Multimedia</t>
+  </si>
+  <si>
+    <t>Ruido o interferencia extraña en los parlantes</t>
+  </si>
+  <si>
+    <t>Angel Yatako - Tecnico de Electricidad.</t>
+  </si>
+  <si>
+    <t>Filtración severa: sale agua por la manija del inodoro</t>
+  </si>
+  <si>
+    <t>Seguridad / Medio Amb.</t>
+  </si>
+  <si>
+    <t>Presencia de un ave (pajarito) dentro de las instalaciones</t>
+  </si>
+  <si>
+    <t>Requerimiento urgente de limpieza en el baño</t>
+  </si>
+  <si>
+    <t>Personal de Limpieza</t>
+  </si>
+  <si>
+    <t>Limpieza / Orden</t>
+  </si>
+  <si>
+    <t>Materiales de trabajo expuestos y dejados sin supervisión</t>
+  </si>
+  <si>
+    <t>Gestión de Personal</t>
+  </si>
+  <si>
+    <t>Reporte de ausentismo crítico: 9 faltas en solo dos días</t>
+  </si>
+  <si>
+    <t>Inodoro completamente atorado (el personal no logró despejarlo)</t>
+  </si>
+  <si>
+    <t>Continuidad de goteo de agua en grifería/llave</t>
+  </si>
+  <si>
+    <t>Limpieza / Abastecimiento</t>
+  </si>
+  <si>
+    <t>Desabastecimiento de papel higiénico en el último cubículo</t>
+  </si>
+  <si>
+    <t>Inodoro desborda demasiada agua</t>
+  </si>
+  <si>
+    <t>Manija de la puerta se encontró rota</t>
+  </si>
+  <si>
+    <t>Infraestructura / SSGG</t>
+  </si>
+  <si>
+    <t>Instalación de acrílicos para las hojas de control de limpieza</t>
+  </si>
+  <si>
+    <t>Puerta corrediza se salió de su riel. Indica ambiente libre hasta las 12:30</t>
+  </si>
+  <si>
+    <t>Operaciones / Coordinación</t>
+  </si>
+  <si>
+    <t>Coordinación de horarios para atención en el aula</t>
+  </si>
+  <si>
+    <t>Luis Matos  - Tecnico de Electricidad.</t>
+  </si>
+  <si>
+    <t>Villa 2 + Pabellón O</t>
+  </si>
+  <si>
+    <t>Gotera constante saliendo del equipo de aire acondicionado</t>
+  </si>
+  <si>
+    <t>Jose Rodas  - Tecnico de Electricidad.</t>
+  </si>
+  <si>
+    <t>Mobiliario / Infraest.</t>
+  </si>
+  <si>
+    <t>El perchero/colgador de ropa se está desprendiendo de la pared</t>
+  </si>
+  <si>
+    <t>Faltan colocar 4 acrílicos de control de actividades.</t>
+  </si>
+  <si>
+    <t>SSHH Varones (3er piso)</t>
+  </si>
+  <si>
+    <t>Persiste goteo en llave afectando las gavetas y el piso.</t>
+  </si>
+  <si>
+    <t>SSHH Damas (3er piso)</t>
+  </si>
+  <si>
+    <t>Desperfecto o anomalía en la puerta de salida.</t>
+  </si>
+  <si>
+    <t>Acumulación de agua / Necesidad de limpieza urgente.</t>
+  </si>
+  <si>
+    <t>Salón UCID</t>
+  </si>
+  <si>
+    <t>Goteo de agua proveniente del aire acondicionado.</t>
+  </si>
+  <si>
+    <t>SSHH Hombres (1er piso)</t>
+  </si>
+  <si>
+    <t>Tubería expuesta / Hueco abierto en la pared.</t>
+  </si>
+  <si>
+    <t>Zona Bioterio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Electricidad </t>
+  </si>
+  <si>
+    <t>Luz de emergencia se desprendió o salió de su posición.</t>
+  </si>
+  <si>
+    <t>SSHH Discapacitados (1°piso)</t>
+  </si>
+  <si>
+    <t>Inodoro atorado.</t>
+  </si>
+  <si>
+    <t>Reporte crítico: No hay suministro de agua en toda el área.</t>
+  </si>
+  <si>
+    <t>Lab. Biología Molecular N-103</t>
+  </si>
+  <si>
+    <t>Los bordes de aluminio de la pizarra acrílica se cayeron.</t>
+  </si>
+  <si>
+    <t>Mantenimiento preventivo / correctivo de cerrajería</t>
+  </si>
+  <si>
+    <t>Jose Rodas  - Tecnico Electricidad</t>
+  </si>
+  <si>
+    <t>Aula K101 y K102</t>
+  </si>
+  <si>
+    <t>Área de Autoclave</t>
+  </si>
+  <si>
+    <t>Fuga de agua en la tubería al usar el equipo.</t>
+  </si>
+  <si>
+    <t>Probable filtración de agua en el fluxómetro.</t>
+  </si>
+  <si>
+    <t>SSHH Mujeres (1er piso)</t>
+  </si>
+  <si>
+    <t>Dispensador de jabón inoperativo.</t>
+  </si>
+  <si>
+    <t>SSHH Discapacitados</t>
+  </si>
+  <si>
+    <t>Fufraestructura</t>
+  </si>
+  <si>
+    <t>Fuga de agua en el caño.</t>
+  </si>
+  <si>
+    <t>José Rodas ingresó a reparar la fuga</t>
+  </si>
+  <si>
+    <t>Auditorio (2do piso)</t>
+  </si>
+  <si>
+    <t>Inicio de trabajos técnicos / mantenimiento en el área.</t>
+  </si>
+  <si>
+    <t>Reportado por Roxana Eulen para conocimiento.</t>
+  </si>
+  <si>
+    <t>Postes Caballeriza</t>
+  </si>
+  <si>
+    <t>Electicidad</t>
+  </si>
+  <si>
+    <t>Corte de energía controlado para ejecutar labores de limpieza.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juan Hernandez -Tecnico de servicios generales </t>
+  </si>
+  <si>
+    <t>Gestión de Activos</t>
+  </si>
+  <si>
+    <t>Infraestructura / Mobiliario</t>
+  </si>
+  <si>
+    <t>Traslado y movimiento físico de armarios culminado.</t>
+  </si>
+  <si>
+    <t>Reclamo de antigüedad: Solicitud del 26 de mayo para revisión de aires acondicionados sigue sin atención.</t>
+  </si>
+  <si>
+    <t>Reincidencia: Puerta corrediza continúa salida de su riel y pendiente de reparación.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">francisco chavez </t>
+  </si>
+  <si>
+    <t>Reclamo de antigüedad: Solicitud del 26 de mayo para revisión de aires acon</t>
+  </si>
+  <si>
+    <t>UZIT</t>
+  </si>
+  <si>
+    <t>POZO TUBULAR</t>
   </si>
 </sst>
 </file>
@@ -3468,7 +3945,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -3568,9 +4045,6 @@
     <xf numFmtId="14" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -3610,77 +4084,17 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="93">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFB7F0E5"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFB7F0E5"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE7E6E6"/>
-          <bgColor rgb="FFE7E6E6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBDD7EE"/>
-          <bgColor rgb="FFBDD7EE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFE699"/>
-          <bgColor rgb="FFFFE699"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFE699"/>
-          <bgColor rgb="FFFFE699"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="87">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -4364,6 +4778,24 @@
           <bgColor rgb="FFB7F0E5"/>
         </patternFill>
       </fill>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFB7F0E5"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFB7F0E5"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="general" vertical="top" wrapText="1"/>
     </dxf>
     <dxf>
@@ -4401,24 +4833,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="REGISTRO_DIARIO" displayName="REGISTRO_DIARIO" ref="A1:M421" totalsRowShown="0" headerRowDxfId="92" dataDxfId="91">
-  <autoFilter ref="A1:M421" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="REGISTRO_DIARIO" displayName="REGISTRO_DIARIO" ref="A1:M525" totalsRowShown="0" headerRowDxfId="86" dataDxfId="85">
+  <autoFilter ref="A1:M525" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID" dataDxfId="0"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Fecha" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Hora" dataDxfId="90"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Sede" dataDxfId="89"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Pabellón / Área" dataDxfId="88"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Ambiente" dataDxfId="87"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Rubro" dataDxfId="86"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Observación" dataDxfId="85"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Prioridad" dataDxfId="84"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Estado" dataDxfId="83"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Técnico Asignado" dataDxfId="82"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Fecha Cierre" dataDxfId="81"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Comentario Técnico" dataDxfId="80"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID" dataDxfId="84"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Fecha" dataDxfId="83"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Hora" dataDxfId="82"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Sede" dataDxfId="81"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Pabellón / Área" dataDxfId="80"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Ambiente" dataDxfId="79"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Rubro" dataDxfId="78"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Observación" dataDxfId="77"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Prioridad" dataDxfId="76"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Estado" dataDxfId="75"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Técnico Asignado" dataDxfId="74"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Fecha Cierre" dataDxfId="73"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Comentario Técnico" dataDxfId="72"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -4707,7 +5139,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M426"/>
+  <dimension ref="A1:M525"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="29" customWidth="1"/>
@@ -16716,7 +17148,7 @@
       </c>
     </row>
     <row r="308" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A308" s="30">
+      <c r="A308" s="22">
         <v>307</v>
       </c>
       <c r="B308" s="31">
@@ -16755,79 +17187,79 @@
       <c r="M308" s="33"/>
     </row>
     <row r="309" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A309" s="35">
+      <c r="A309" s="22">
         <v>308</v>
       </c>
-      <c r="B309" s="36">
+      <c r="B309" s="35">
         <v>46177</v>
       </c>
-      <c r="C309" s="37">
+      <c r="C309" s="36">
         <v>0.30277777777777776</v>
       </c>
-      <c r="D309" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E309" s="38" t="s">
+      <c r="D309" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E309" s="37" t="s">
         <v>71</v>
       </c>
-      <c r="F309" s="38" t="s">
+      <c r="F309" s="37" t="s">
         <v>328</v>
       </c>
-      <c r="G309" s="38" t="s">
+      <c r="G309" s="37" t="s">
         <v>838</v>
       </c>
-      <c r="H309" s="38" t="s">
+      <c r="H309" s="37" t="s">
         <v>877</v>
       </c>
-      <c r="I309" s="38" t="s">
+      <c r="I309" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="J309" s="38" t="s">
+      <c r="J309" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K309" s="38" t="s">
+      <c r="K309" s="37" t="s">
         <v>759</v>
       </c>
-      <c r="L309" s="39"/>
-      <c r="M309" s="38"/>
+      <c r="L309" s="38"/>
+      <c r="M309" s="37"/>
     </row>
     <row r="310" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A310" s="35">
+      <c r="A310" s="22">
         <v>309</v>
       </c>
-      <c r="B310" s="36">
+      <c r="B310" s="35">
         <v>46177</v>
       </c>
-      <c r="C310" s="37">
+      <c r="C310" s="36">
         <v>0.31111111111111112</v>
       </c>
-      <c r="D310" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E310" s="38" t="s">
+      <c r="D310" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E310" s="37" t="s">
         <v>71</v>
       </c>
-      <c r="F310" s="38" t="s">
+      <c r="F310" s="37" t="s">
         <v>878</v>
       </c>
-      <c r="G310" s="38" t="s">
+      <c r="G310" s="37" t="s">
         <v>794</v>
       </c>
-      <c r="H310" s="38" t="s">
+      <c r="H310" s="37" t="s">
         <v>879</v>
       </c>
-      <c r="I310" s="38" t="s">
+      <c r="I310" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="J310" s="38" t="s">
+      <c r="J310" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K310" s="38"/>
-      <c r="L310" s="39"/>
-      <c r="M310" s="38"/>
+      <c r="K310" s="37"/>
+      <c r="L310" s="38"/>
+      <c r="M310" s="37"/>
     </row>
     <row r="311" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A311" s="30">
+      <c r="A311" s="25">
         <v>310</v>
       </c>
       <c r="B311" s="31">
@@ -16866,44 +17298,46 @@
       <c r="M311" s="33"/>
     </row>
     <row r="312" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A312" s="40"/>
-      <c r="B312" s="41">
+      <c r="A312" s="22">
+        <v>311</v>
+      </c>
+      <c r="B312" s="40">
         <v>46177</v>
       </c>
-      <c r="C312" s="42">
+      <c r="C312" s="41">
         <v>0.33819444444444446</v>
       </c>
-      <c r="D312" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="E312" s="43" t="s">
+      <c r="D312" s="42" t="s">
+        <v>15</v>
+      </c>
+      <c r="E312" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="F312" s="43" t="s">
+      <c r="F312" s="42" t="s">
         <v>220</v>
       </c>
-      <c r="G312" s="43" t="s">
+      <c r="G312" s="42" t="s">
         <v>802</v>
       </c>
-      <c r="H312" s="43" t="s">
+      <c r="H312" s="42" t="s">
         <v>880</v>
       </c>
-      <c r="I312" s="43" t="s">
+      <c r="I312" s="42" t="s">
         <v>64</v>
       </c>
-      <c r="J312" s="43" t="s">
+      <c r="J312" s="42" t="s">
         <v>791</v>
       </c>
-      <c r="K312" s="43" t="s">
+      <c r="K312" s="42" t="s">
         <v>881</v>
       </c>
-      <c r="L312" s="41">
+      <c r="L312" s="40">
         <v>46177</v>
       </c>
-      <c r="M312" s="43"/>
+      <c r="M312" s="42"/>
     </row>
     <row r="313" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A313" s="30">
+      <c r="A313" s="22">
         <v>312</v>
       </c>
       <c r="B313" s="31">
@@ -16944,7 +17378,7 @@
       </c>
     </row>
     <row r="314" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A314" s="30">
+      <c r="A314" s="22">
         <v>313</v>
       </c>
       <c r="B314" s="31">
@@ -16983,44 +17417,44 @@
       <c r="M314" s="33"/>
     </row>
     <row r="315" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A315" s="35">
+      <c r="A315" s="25">
         <v>314</v>
       </c>
-      <c r="B315" s="36">
+      <c r="B315" s="35">
         <v>46177</v>
       </c>
-      <c r="C315" s="37">
+      <c r="C315" s="36">
         <v>0.37986111111111109</v>
       </c>
-      <c r="D315" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E315" s="38" t="s">
+      <c r="D315" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E315" s="37" t="s">
         <v>232</v>
       </c>
-      <c r="F315" s="38" t="s">
+      <c r="F315" s="37" t="s">
         <v>884</v>
       </c>
-      <c r="G315" s="38" t="s">
+      <c r="G315" s="37" t="s">
         <v>777</v>
       </c>
-      <c r="H315" s="38" t="s">
+      <c r="H315" s="37" t="s">
         <v>885</v>
       </c>
-      <c r="I315" s="38" t="s">
+      <c r="I315" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="J315" s="38" t="s">
+      <c r="J315" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K315" s="38" t="s">
+      <c r="K315" s="37" t="s">
         <v>940</v>
       </c>
-      <c r="L315" s="39"/>
-      <c r="M315" s="38"/>
+      <c r="L315" s="38"/>
+      <c r="M315" s="37"/>
     </row>
     <row r="316" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A316" s="30">
+      <c r="A316" s="22">
         <v>315</v>
       </c>
       <c r="B316" s="31">
@@ -17059,7 +17493,7 @@
       <c r="M316" s="33"/>
     </row>
     <row r="317" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A317" s="30">
+      <c r="A317" s="22">
         <v>316</v>
       </c>
       <c r="B317" s="31">
@@ -17098,7 +17532,7 @@
       <c r="M317" s="33"/>
     </row>
     <row r="318" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A318" s="30">
+      <c r="A318" s="22">
         <v>317</v>
       </c>
       <c r="B318" s="31">
@@ -17137,39 +17571,41 @@
       <c r="M318" s="33"/>
     </row>
     <row r="319" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A319" s="40"/>
-      <c r="B319" s="41">
+      <c r="A319" s="39">
+        <v>318</v>
+      </c>
+      <c r="B319" s="40">
         <v>46177</v>
       </c>
-      <c r="C319" s="42">
+      <c r="C319" s="41">
         <v>0.46875</v>
       </c>
-      <c r="D319" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="E319" s="43" t="s">
+      <c r="D319" s="42" t="s">
+        <v>15</v>
+      </c>
+      <c r="E319" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="F319" s="43" t="s">
+      <c r="F319" s="42" t="s">
         <v>890</v>
       </c>
-      <c r="G319" s="43" t="s">
+      <c r="G319" s="42" t="s">
         <v>838</v>
       </c>
-      <c r="H319" s="43" t="s">
+      <c r="H319" s="42" t="s">
         <v>891</v>
       </c>
-      <c r="I319" s="43" t="s">
+      <c r="I319" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="J319" s="43" t="s">
+      <c r="J319" s="42" t="s">
         <v>791</v>
       </c>
-      <c r="K319" s="43" t="s">
+      <c r="K319" s="42" t="s">
         <v>779</v>
       </c>
-      <c r="L319" s="43"/>
-      <c r="M319" s="43" t="s">
+      <c r="L319" s="42"/>
+      <c r="M319" s="42" t="s">
         <v>892</v>
       </c>
     </row>
@@ -17213,7 +17649,7 @@
       <c r="M320" s="33"/>
     </row>
     <row r="321" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A321" s="30">
+      <c r="A321" s="22">
         <v>320</v>
       </c>
       <c r="B321" s="31">
@@ -17254,7 +17690,7 @@
       </c>
     </row>
     <row r="322" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A322" s="30">
+      <c r="A322" s="39">
         <v>321</v>
       </c>
       <c r="B322" s="31">
@@ -17295,3713 +17731,3713 @@
       </c>
     </row>
     <row r="323" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A323" s="35">
+      <c r="A323" s="30">
         <v>322</v>
       </c>
-      <c r="B323" s="36">
+      <c r="B323" s="35">
         <v>46177</v>
       </c>
-      <c r="C323" s="37">
+      <c r="C323" s="36">
         <v>0.56111111111111112</v>
       </c>
-      <c r="D323" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E323" s="38" t="s">
+      <c r="D323" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E323" s="37" t="s">
         <v>50</v>
       </c>
-      <c r="F323" s="38" t="s">
+      <c r="F323" s="37" t="s">
         <v>633</v>
       </c>
-      <c r="G323" s="38" t="s">
+      <c r="G323" s="37" t="s">
         <v>838</v>
       </c>
-      <c r="H323" s="38" t="s">
+      <c r="H323" s="37" t="s">
         <v>899</v>
       </c>
-      <c r="I323" s="38" t="s">
+      <c r="I323" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="J323" s="38" t="s">
+      <c r="J323" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K323" s="38" t="s">
+      <c r="K323" s="37" t="s">
         <v>779</v>
       </c>
-      <c r="L323" s="39"/>
-      <c r="M323" s="38"/>
+      <c r="L323" s="38"/>
+      <c r="M323" s="37"/>
     </row>
     <row r="324" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A324" s="48">
+      <c r="A324" s="22">
         <v>323</v>
       </c>
-      <c r="B324" s="45">
+      <c r="B324" s="44">
         <v>46175</v>
       </c>
-      <c r="C324" s="46">
+      <c r="C324" s="45">
         <v>0.35069444444444442</v>
       </c>
-      <c r="D324" s="44" t="s">
-        <v>15</v>
-      </c>
-      <c r="E324" s="44" t="s">
+      <c r="D324" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E324" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="F324" s="44" t="s">
+      <c r="F324" s="43" t="s">
         <v>715</v>
       </c>
-      <c r="G324" s="44" t="s">
+      <c r="G324" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="H324" s="44" t="s">
+      <c r="H324" s="43" t="s">
         <v>901</v>
       </c>
-      <c r="I324" s="44" t="s">
+      <c r="I324" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="J324" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="K324" s="44" t="s">
+      <c r="J324" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="K324" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="L324" s="47">
+      <c r="L324" s="46">
         <v>46175</v>
       </c>
-      <c r="M324" s="44"/>
+      <c r="M324" s="43"/>
     </row>
     <row r="325" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A325" s="48">
+      <c r="A325" s="39">
         <v>324</v>
       </c>
-      <c r="B325" s="45">
+      <c r="B325" s="44">
         <v>46175</v>
       </c>
-      <c r="C325" s="46">
+      <c r="C325" s="45">
         <v>0.39444444444444443</v>
       </c>
-      <c r="D325" s="44" t="s">
+      <c r="D325" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="E325" s="44" t="s">
+      <c r="E325" s="43" t="s">
         <v>71</v>
       </c>
-      <c r="F325" s="44" t="s">
+      <c r="F325" s="43" t="s">
         <v>903</v>
       </c>
-      <c r="G325" s="44" t="s">
+      <c r="G325" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="H325" s="44" t="s">
+      <c r="H325" s="43" t="s">
         <v>904</v>
       </c>
-      <c r="I325" s="44" t="s">
+      <c r="I325" s="43" t="s">
         <v>64</v>
       </c>
-      <c r="J325" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="K325" s="44" t="s">
+      <c r="J325" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="K325" s="43" t="s">
         <v>928</v>
       </c>
-      <c r="L325" s="47">
+      <c r="L325" s="46">
         <v>46175</v>
       </c>
-      <c r="M325" s="44"/>
+      <c r="M325" s="43"/>
     </row>
     <row r="326" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A326" s="48">
+      <c r="A326" s="30">
         <v>325</v>
       </c>
-      <c r="B326" s="45">
+      <c r="B326" s="44">
         <v>46177</v>
       </c>
-      <c r="C326" s="46">
+      <c r="C326" s="45">
         <v>0.27708333333333335</v>
       </c>
-      <c r="D326" s="44" t="s">
-        <v>15</v>
-      </c>
-      <c r="E326" s="44" t="s">
+      <c r="D326" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E326" s="43" t="s">
         <v>309</v>
       </c>
-      <c r="F326" s="44" t="s">
+      <c r="F326" s="43" t="s">
         <v>907</v>
       </c>
-      <c r="G326" s="44" t="s">
+      <c r="G326" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="H326" s="44" t="s">
+      <c r="H326" s="43" t="s">
         <v>908</v>
       </c>
-      <c r="I326" s="44" t="s">
+      <c r="I326" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="J326" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="K326" s="44" t="s">
+      <c r="J326" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="K326" s="43" t="s">
         <v>927</v>
       </c>
-      <c r="L326" s="47">
+      <c r="L326" s="46">
         <v>46175</v>
       </c>
-      <c r="M326" s="44"/>
+      <c r="M326" s="43"/>
     </row>
     <row r="327" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A327" s="35">
+      <c r="A327" s="22">
         <v>326</v>
       </c>
-      <c r="B327" s="36">
+      <c r="B327" s="35">
         <v>46178</v>
       </c>
-      <c r="C327" s="37">
+      <c r="C327" s="36">
         <v>0.53541666666666665</v>
       </c>
-      <c r="D327" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E327" s="38" t="s">
+      <c r="D327" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E327" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="F327" s="38" t="s">
+      <c r="F327" s="37" t="s">
         <v>890</v>
       </c>
-      <c r="G327" s="38" t="s">
+      <c r="G327" s="37" t="s">
         <v>754</v>
       </c>
-      <c r="H327" s="38" t="s">
+      <c r="H327" s="37" t="s">
         <v>911</v>
       </c>
-      <c r="I327" s="38" t="s">
+      <c r="I327" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="J327" s="38" t="s">
+      <c r="J327" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K327" s="38"/>
-      <c r="L327" s="39"/>
-      <c r="M327" s="38"/>
+      <c r="K327" s="37"/>
+      <c r="L327" s="38"/>
+      <c r="M327" s="37"/>
     </row>
     <row r="328" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A328" s="48">
+      <c r="A328" s="39">
         <v>327</v>
       </c>
-      <c r="B328" s="45">
+      <c r="B328" s="44">
         <v>46177</v>
       </c>
-      <c r="C328" s="46">
+      <c r="C328" s="45">
         <v>0.74513888888888891</v>
       </c>
-      <c r="D328" s="44" t="s">
-        <v>15</v>
-      </c>
-      <c r="E328" s="44" t="s">
+      <c r="D328" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E328" s="43" t="s">
         <v>80</v>
       </c>
-      <c r="F328" s="44" t="s">
+      <c r="F328" s="43" t="s">
         <v>913</v>
       </c>
-      <c r="G328" s="44" t="s">
+      <c r="G328" s="43" t="s">
         <v>334</v>
       </c>
-      <c r="H328" s="44" t="s">
+      <c r="H328" s="43" t="s">
         <v>914</v>
       </c>
-      <c r="I328" s="44" t="s">
+      <c r="I328" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="J328" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="K328" s="44" t="s">
+      <c r="J328" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="K328" s="43" t="s">
         <v>54</v>
       </c>
-      <c r="L328" s="47">
+      <c r="L328" s="46">
         <v>46175</v>
       </c>
-      <c r="M328" s="44"/>
+      <c r="M328" s="43"/>
     </row>
     <row r="329" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A329" s="48">
+      <c r="A329" s="30">
         <v>328</v>
       </c>
-      <c r="B329" s="45">
+      <c r="B329" s="44">
         <v>46178</v>
       </c>
-      <c r="C329" s="46">
+      <c r="C329" s="45">
         <v>0.29375000000000001</v>
       </c>
-      <c r="D329" s="44" t="s">
-        <v>15</v>
-      </c>
-      <c r="E329" s="44" t="s">
+      <c r="D329" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E329" s="43" t="s">
         <v>71</v>
       </c>
-      <c r="F329" s="44" t="s">
+      <c r="F329" s="43" t="s">
         <v>941</v>
       </c>
-      <c r="G329" s="44" t="s">
+      <c r="G329" s="43" t="s">
         <v>754</v>
       </c>
-      <c r="H329" s="44" t="s">
+      <c r="H329" s="43" t="s">
         <v>942</v>
       </c>
-      <c r="I329" s="44" t="s">
+      <c r="I329" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="J329" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="K329" s="44" t="s">
+      <c r="J329" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="K329" s="43" t="s">
         <v>943</v>
       </c>
-      <c r="L329" s="47">
+      <c r="L329" s="46">
         <v>46178</v>
       </c>
-      <c r="M329" s="44"/>
+      <c r="M329" s="43"/>
     </row>
     <row r="330" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A330" s="35">
+      <c r="A330" s="22">
         <v>329</v>
       </c>
-      <c r="B330" s="36">
+      <c r="B330" s="35">
         <v>46178</v>
       </c>
-      <c r="C330" s="37">
+      <c r="C330" s="36">
         <v>0.30833333333333335</v>
       </c>
-      <c r="D330" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E330" s="38" t="s">
+      <c r="D330" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E330" s="37" t="s">
         <v>89</v>
       </c>
-      <c r="F330" s="38" t="s">
+      <c r="F330" s="37" t="s">
         <v>89</v>
       </c>
-      <c r="G330" s="38" t="s">
+      <c r="G330" s="37" t="s">
         <v>317</v>
       </c>
-      <c r="H330" s="38" t="s">
+      <c r="H330" s="37" t="s">
         <v>944</v>
       </c>
-      <c r="I330" s="38" t="s">
+      <c r="I330" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="J330" s="38" t="s">
+      <c r="J330" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K330" s="38" t="s">
+      <c r="K330" s="37" t="s">
         <v>945</v>
       </c>
-      <c r="L330" s="39"/>
-      <c r="M330" s="38"/>
+      <c r="L330" s="38"/>
+      <c r="M330" s="37"/>
     </row>
     <row r="331" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A331" s="35">
+      <c r="A331" s="39">
         <v>330</v>
       </c>
-      <c r="B331" s="36">
+      <c r="B331" s="35">
         <v>46178</v>
       </c>
-      <c r="C331" s="37">
+      <c r="C331" s="36">
         <v>0.30833333333333335</v>
       </c>
-      <c r="D331" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E331" s="38" t="s">
+      <c r="D331" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E331" s="37" t="s">
         <v>232</v>
       </c>
-      <c r="F331" s="38" t="s">
+      <c r="F331" s="37" t="s">
         <v>232</v>
       </c>
-      <c r="G331" s="38" t="s">
+      <c r="G331" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="H331" s="38" t="s">
+      <c r="H331" s="37" t="s">
         <v>946</v>
       </c>
-      <c r="I331" s="38" t="s">
+      <c r="I331" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="J331" s="38" t="s">
+      <c r="J331" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K331" s="38" t="s">
+      <c r="K331" s="37" t="s">
         <v>945</v>
       </c>
-      <c r="L331" s="39"/>
-      <c r="M331" s="38"/>
+      <c r="L331" s="38"/>
+      <c r="M331" s="37"/>
     </row>
     <row r="332" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A332" s="35">
+      <c r="A332" s="30">
         <v>331</v>
       </c>
-      <c r="B332" s="36">
+      <c r="B332" s="35">
         <v>46178</v>
       </c>
-      <c r="C332" s="37">
+      <c r="C332" s="36">
         <v>0.31458333333333333</v>
       </c>
-      <c r="D332" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E332" s="38" t="s">
+      <c r="D332" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E332" s="37" t="s">
         <v>232</v>
       </c>
-      <c r="F332" s="38" t="s">
+      <c r="F332" s="37" t="s">
         <v>947</v>
       </c>
-      <c r="G332" s="38" t="s">
+      <c r="G332" s="37" t="s">
         <v>948</v>
       </c>
-      <c r="H332" s="38" t="s">
+      <c r="H332" s="37" t="s">
         <v>949</v>
       </c>
-      <c r="I332" s="38" t="s">
+      <c r="I332" s="37" t="s">
         <v>64</v>
       </c>
-      <c r="J332" s="38" t="s">
+      <c r="J332" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K332" s="38" t="s">
+      <c r="K332" s="37" t="s">
         <v>945</v>
       </c>
-      <c r="L332" s="39"/>
-      <c r="M332" s="38"/>
+      <c r="L332" s="38"/>
+      <c r="M332" s="37"/>
     </row>
     <row r="333" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A333" s="48">
+      <c r="A333" s="22">
         <v>332</v>
       </c>
-      <c r="B333" s="45">
+      <c r="B333" s="44">
         <v>46178</v>
       </c>
-      <c r="C333" s="46">
+      <c r="C333" s="45">
         <v>0.31458333333333333</v>
       </c>
-      <c r="D333" s="44" t="s">
-        <v>15</v>
-      </c>
-      <c r="E333" s="44" t="s">
+      <c r="D333" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E333" s="43" t="s">
         <v>43</v>
       </c>
-      <c r="F333" s="44" t="s">
+      <c r="F333" s="43" t="s">
         <v>890</v>
       </c>
-      <c r="G333" s="44" t="s">
+      <c r="G333" s="43" t="s">
         <v>948</v>
       </c>
-      <c r="H333" s="44" t="s">
+      <c r="H333" s="43" t="s">
         <v>950</v>
       </c>
-      <c r="I333" s="44" t="s">
+      <c r="I333" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="J333" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="K333" s="44" t="s">
+      <c r="J333" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="K333" s="43" t="s">
         <v>943</v>
       </c>
-      <c r="L333" s="47">
+      <c r="L333" s="46">
         <v>46178</v>
       </c>
-      <c r="M333" s="44"/>
+      <c r="M333" s="43"/>
     </row>
     <row r="334" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A334" s="35">
+      <c r="A334" s="39">
         <v>333</v>
       </c>
-      <c r="B334" s="36">
+      <c r="B334" s="35">
         <v>46178</v>
       </c>
-      <c r="C334" s="37">
+      <c r="C334" s="36">
         <v>0.31805555555555554</v>
       </c>
-      <c r="D334" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E334" s="38" t="s">
+      <c r="D334" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E334" s="37" t="s">
         <v>232</v>
       </c>
-      <c r="F334" s="38" t="s">
+      <c r="F334" s="37" t="s">
         <v>951</v>
       </c>
-      <c r="G334" s="38" t="s">
+      <c r="G334" s="37" t="s">
         <v>317</v>
       </c>
-      <c r="H334" s="38" t="s">
+      <c r="H334" s="37" t="s">
         <v>952</v>
       </c>
-      <c r="I334" s="38" t="s">
+      <c r="I334" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="J334" s="38" t="s">
+      <c r="J334" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K334" s="38" t="s">
+      <c r="K334" s="37" t="s">
         <v>945</v>
       </c>
-      <c r="L334" s="39"/>
-      <c r="M334" s="38"/>
+      <c r="L334" s="38"/>
+      <c r="M334" s="37"/>
     </row>
     <row r="335" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A335" s="48">
+      <c r="A335" s="30">
         <v>334</v>
       </c>
-      <c r="B335" s="45">
+      <c r="B335" s="44">
         <v>46178</v>
       </c>
-      <c r="C335" s="46">
+      <c r="C335" s="45">
         <v>0.80069444444444449</v>
       </c>
-      <c r="D335" s="44" t="s">
-        <v>15</v>
-      </c>
-      <c r="E335" s="44" t="s">
+      <c r="D335" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E335" s="43" t="s">
         <v>278</v>
       </c>
-      <c r="F335" s="44" t="s">
+      <c r="F335" s="43" t="s">
         <v>953</v>
       </c>
-      <c r="G335" s="44" t="s">
+      <c r="G335" s="43" t="s">
         <v>754</v>
       </c>
-      <c r="H335" s="44" t="s">
+      <c r="H335" s="43" t="s">
         <v>954</v>
       </c>
-      <c r="I335" s="44" t="s">
+      <c r="I335" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="J335" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="K335" s="44" t="s">
+      <c r="J335" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="K335" s="43" t="s">
         <v>955</v>
       </c>
-      <c r="L335" s="47">
+      <c r="L335" s="46">
         <v>46178</v>
       </c>
-      <c r="M335" s="44"/>
+      <c r="M335" s="43"/>
     </row>
     <row r="336" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A336" s="35">
+      <c r="A336" s="22">
         <v>335</v>
       </c>
-      <c r="B336" s="36">
+      <c r="B336" s="35">
         <v>46178</v>
       </c>
-      <c r="C336" s="37">
+      <c r="C336" s="36">
         <v>0.37291666666666667</v>
       </c>
-      <c r="D336" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E336" s="38" t="s">
+      <c r="D336" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E336" s="37" t="s">
         <v>232</v>
       </c>
-      <c r="F336" s="38" t="s">
+      <c r="F336" s="37" t="s">
         <v>956</v>
       </c>
-      <c r="G336" s="38" t="s">
+      <c r="G336" s="37" t="s">
         <v>317</v>
       </c>
-      <c r="H336" s="38" t="s">
+      <c r="H336" s="37" t="s">
         <v>885</v>
       </c>
-      <c r="I336" s="38" t="s">
+      <c r="I336" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="J336" s="38" t="s">
+      <c r="J336" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K336" s="38" t="s">
+      <c r="K336" s="37" t="s">
         <v>945</v>
       </c>
-      <c r="L336" s="39"/>
-      <c r="M336" s="38"/>
+      <c r="L336" s="38"/>
+      <c r="M336" s="37"/>
     </row>
     <row r="337" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A337" s="35">
+      <c r="A337" s="39">
         <v>336</v>
       </c>
-      <c r="B337" s="36">
+      <c r="B337" s="35">
         <v>46178</v>
       </c>
-      <c r="C337" s="37">
+      <c r="C337" s="36">
         <v>0.37986111111111109</v>
       </c>
-      <c r="D337" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E337" s="38" t="s">
+      <c r="D337" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E337" s="37" t="s">
         <v>232</v>
       </c>
-      <c r="F337" s="38" t="s">
+      <c r="F337" s="37" t="s">
         <v>957</v>
       </c>
-      <c r="G337" s="38" t="s">
+      <c r="G337" s="37" t="s">
         <v>948</v>
       </c>
-      <c r="H337" s="38" t="s">
+      <c r="H337" s="37" t="s">
         <v>883</v>
       </c>
-      <c r="I337" s="38" t="s">
+      <c r="I337" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="J337" s="38" t="s">
+      <c r="J337" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K337" s="38" t="s">
+      <c r="K337" s="37" t="s">
         <v>945</v>
       </c>
-      <c r="L337" s="39"/>
-      <c r="M337" s="38"/>
+      <c r="L337" s="38"/>
+      <c r="M337" s="37"/>
     </row>
     <row r="338" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A338" s="48">
+      <c r="A338" s="30">
         <v>337</v>
       </c>
-      <c r="B338" s="45">
+      <c r="B338" s="44">
         <v>46178</v>
       </c>
-      <c r="C338" s="46">
+      <c r="C338" s="45">
         <v>0.38611111111111113</v>
       </c>
-      <c r="D338" s="44" t="s">
-        <v>15</v>
-      </c>
-      <c r="E338" s="44" t="s">
+      <c r="D338" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E338" s="43" t="s">
         <v>71</v>
       </c>
-      <c r="F338" s="44" t="s">
+      <c r="F338" s="43" t="s">
         <v>958</v>
       </c>
-      <c r="G338" s="44" t="s">
+      <c r="G338" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="H338" s="44" t="s">
+      <c r="H338" s="43" t="s">
         <v>959</v>
       </c>
-      <c r="I338" s="44" t="s">
+      <c r="I338" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="J338" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="K338" s="44" t="s">
+      <c r="J338" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="K338" s="43" t="s">
         <v>943</v>
       </c>
-      <c r="L338" s="47">
+      <c r="L338" s="46">
         <v>46178</v>
       </c>
-      <c r="M338" s="44"/>
+      <c r="M338" s="43"/>
     </row>
     <row r="339" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A339" s="35">
+      <c r="A339" s="22">
         <v>338</v>
       </c>
-      <c r="B339" s="36">
+      <c r="B339" s="35">
         <v>46178</v>
       </c>
-      <c r="C339" s="37">
+      <c r="C339" s="36">
         <v>0.39513888888888887</v>
       </c>
-      <c r="D339" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E339" s="38" t="s">
+      <c r="D339" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E339" s="37" t="s">
         <v>89</v>
       </c>
-      <c r="F339" s="38" t="s">
+      <c r="F339" s="37" t="s">
         <v>682</v>
       </c>
-      <c r="G339" s="38" t="s">
+      <c r="G339" s="37" t="s">
         <v>948</v>
       </c>
-      <c r="H339" s="38" t="s">
+      <c r="H339" s="37" t="s">
         <v>960</v>
       </c>
-      <c r="I339" s="38" t="s">
+      <c r="I339" s="37" t="s">
         <v>64</v>
       </c>
-      <c r="J339" s="38" t="s">
+      <c r="J339" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K339" s="38" t="s">
+      <c r="K339" s="37" t="s">
         <v>945</v>
       </c>
-      <c r="L339" s="39"/>
-      <c r="M339" s="38"/>
+      <c r="L339" s="38"/>
+      <c r="M339" s="37"/>
     </row>
     <row r="340" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A340" s="35">
+      <c r="A340" s="39">
         <v>339</v>
       </c>
-      <c r="B340" s="36">
+      <c r="B340" s="35">
         <v>46178</v>
       </c>
-      <c r="C340" s="37">
+      <c r="C340" s="36">
         <v>0.3972222222222222</v>
       </c>
-      <c r="D340" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E340" s="38" t="s">
+      <c r="D340" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E340" s="37" t="s">
         <v>89</v>
       </c>
-      <c r="F340" s="38" t="s">
+      <c r="F340" s="37" t="s">
         <v>961</v>
       </c>
-      <c r="G340" s="38" t="s">
+      <c r="G340" s="37" t="s">
         <v>948</v>
       </c>
-      <c r="H340" s="38" t="s">
+      <c r="H340" s="37" t="s">
         <v>962</v>
       </c>
-      <c r="I340" s="38" t="s">
+      <c r="I340" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="J340" s="38" t="s">
+      <c r="J340" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K340" s="38" t="s">
+      <c r="K340" s="37" t="s">
         <v>945</v>
       </c>
-      <c r="L340" s="39"/>
-      <c r="M340" s="38"/>
+      <c r="L340" s="38"/>
+      <c r="M340" s="37"/>
     </row>
     <row r="341" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A341" s="35">
+      <c r="A341" s="30">
         <v>340</v>
       </c>
-      <c r="B341" s="36">
+      <c r="B341" s="35">
         <v>46178</v>
       </c>
-      <c r="C341" s="37">
+      <c r="C341" s="36">
         <v>0.41944444444444445</v>
       </c>
-      <c r="D341" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E341" s="38" t="s">
+      <c r="D341" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E341" s="37" t="s">
         <v>71</v>
       </c>
-      <c r="F341" s="38" t="s">
+      <c r="F341" s="37" t="s">
         <v>963</v>
       </c>
-      <c r="G341" s="38" t="s">
+      <c r="G341" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="H341" s="38" t="s">
+      <c r="H341" s="37" t="s">
         <v>964</v>
       </c>
-      <c r="I341" s="38" t="s">
+      <c r="I341" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="J341" s="38" t="s">
+      <c r="J341" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K341" s="38" t="s">
+      <c r="K341" s="37" t="s">
         <v>945</v>
       </c>
-      <c r="L341" s="39"/>
-      <c r="M341" s="38"/>
+      <c r="L341" s="38"/>
+      <c r="M341" s="37"/>
     </row>
     <row r="342" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A342" s="35">
+      <c r="A342" s="22">
         <v>341</v>
       </c>
-      <c r="B342" s="36">
+      <c r="B342" s="35">
         <v>46178</v>
       </c>
-      <c r="C342" s="37">
+      <c r="C342" s="36">
         <v>0.40069444444444446</v>
       </c>
-      <c r="D342" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E342" s="38" t="s">
+      <c r="D342" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E342" s="37" t="s">
         <v>80</v>
       </c>
-      <c r="F342" s="38" t="s">
+      <c r="F342" s="37" t="s">
         <v>965</v>
       </c>
-      <c r="G342" s="38" t="s">
+      <c r="G342" s="37" t="s">
         <v>754</v>
       </c>
-      <c r="H342" s="38" t="s">
+      <c r="H342" s="37" t="s">
         <v>966</v>
       </c>
-      <c r="I342" s="38" t="s">
+      <c r="I342" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="J342" s="38" t="s">
+      <c r="J342" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K342" s="38" t="s">
+      <c r="K342" s="37" t="s">
         <v>945</v>
       </c>
-      <c r="L342" s="39"/>
-      <c r="M342" s="38"/>
+      <c r="L342" s="38"/>
+      <c r="M342" s="37"/>
     </row>
     <row r="343" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A343" s="35">
+      <c r="A343" s="39">
         <v>342</v>
       </c>
-      <c r="B343" s="36">
+      <c r="B343" s="35">
         <v>46178</v>
       </c>
-      <c r="C343" s="37">
+      <c r="C343" s="36">
         <v>0.42638888888888887</v>
       </c>
-      <c r="D343" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E343" s="38" t="s">
+      <c r="D343" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E343" s="37" t="s">
         <v>80</v>
       </c>
-      <c r="F343" s="38" t="s">
+      <c r="F343" s="37" t="s">
         <v>967</v>
       </c>
-      <c r="G343" s="38" t="s">
+      <c r="G343" s="37" t="s">
         <v>754</v>
       </c>
-      <c r="H343" s="38" t="s">
+      <c r="H343" s="37" t="s">
         <v>966</v>
       </c>
-      <c r="I343" s="38" t="s">
+      <c r="I343" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="J343" s="38" t="s">
+      <c r="J343" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K343" s="38" t="s">
+      <c r="K343" s="37" t="s">
         <v>945</v>
       </c>
-      <c r="L343" s="39"/>
-      <c r="M343" s="38"/>
+      <c r="L343" s="38"/>
+      <c r="M343" s="37"/>
     </row>
     <row r="344" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A344" s="35">
+      <c r="A344" s="30">
         <v>343</v>
       </c>
-      <c r="B344" s="36">
+      <c r="B344" s="35">
         <v>46178</v>
       </c>
-      <c r="C344" s="37">
+      <c r="C344" s="36">
         <v>0.42569444444444443</v>
       </c>
-      <c r="D344" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E344" s="38" t="s">
+      <c r="D344" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E344" s="37" t="s">
         <v>71</v>
       </c>
-      <c r="F344" s="38" t="s">
+      <c r="F344" s="37" t="s">
         <v>349</v>
       </c>
-      <c r="G344" s="38" t="s">
+      <c r="G344" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="H344" s="38" t="s">
+      <c r="H344" s="37" t="s">
         <v>968</v>
       </c>
-      <c r="I344" s="38" t="s">
+      <c r="I344" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="J344" s="38" t="s">
+      <c r="J344" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K344" s="38" t="s">
+      <c r="K344" s="37" t="s">
         <v>945</v>
       </c>
-      <c r="L344" s="39"/>
-      <c r="M344" s="38"/>
+      <c r="L344" s="38"/>
+      <c r="M344" s="37"/>
     </row>
     <row r="345" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A345" s="35">
+      <c r="A345" s="22">
         <v>344</v>
       </c>
-      <c r="B345" s="36">
+      <c r="B345" s="35">
         <v>46178</v>
       </c>
-      <c r="C345" s="37">
+      <c r="C345" s="36">
         <v>0.50972222222222219</v>
       </c>
-      <c r="D345" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E345" s="38" t="s">
+      <c r="D345" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E345" s="37" t="s">
         <v>80</v>
       </c>
-      <c r="F345" s="38" t="s">
+      <c r="F345" s="37" t="s">
         <v>969</v>
       </c>
-      <c r="G345" s="38" t="s">
+      <c r="G345" s="37" t="s">
         <v>754</v>
       </c>
-      <c r="H345" s="38" t="s">
+      <c r="H345" s="37" t="s">
         <v>970</v>
       </c>
-      <c r="I345" s="38" t="s">
+      <c r="I345" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="J345" s="38" t="s">
+      <c r="J345" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K345" s="38" t="s">
+      <c r="K345" s="37" t="s">
         <v>945</v>
       </c>
-      <c r="L345" s="39"/>
-      <c r="M345" s="38"/>
+      <c r="L345" s="38"/>
+      <c r="M345" s="37"/>
     </row>
     <row r="346" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A346" s="35">
+      <c r="A346" s="39">
         <v>345</v>
       </c>
-      <c r="B346" s="36">
+      <c r="B346" s="35">
         <v>46178</v>
       </c>
-      <c r="C346" s="37">
+      <c r="C346" s="36">
         <v>0.54027777777777775</v>
       </c>
-      <c r="D346" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E346" s="38" t="s">
+      <c r="D346" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E346" s="37" t="s">
         <v>89</v>
       </c>
-      <c r="F346" s="38" t="s">
+      <c r="F346" s="37" t="s">
         <v>971</v>
       </c>
-      <c r="G346" s="38" t="s">
+      <c r="G346" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="H346" s="38" t="s">
+      <c r="H346" s="37" t="s">
         <v>972</v>
       </c>
-      <c r="I346" s="38" t="s">
+      <c r="I346" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="J346" s="38" t="s">
+      <c r="J346" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K346" s="38" t="s">
+      <c r="K346" s="37" t="s">
         <v>945</v>
       </c>
-      <c r="L346" s="39"/>
-      <c r="M346" s="38"/>
+      <c r="L346" s="38"/>
+      <c r="M346" s="37"/>
     </row>
     <row r="347" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A347" s="35">
+      <c r="A347" s="30">
         <v>346</v>
       </c>
-      <c r="B347" s="36">
+      <c r="B347" s="35">
         <v>46178</v>
       </c>
-      <c r="C347" s="37">
+      <c r="C347" s="36">
         <v>0.55486111111111114</v>
       </c>
-      <c r="D347" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E347" s="38" t="s">
+      <c r="D347" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E347" s="37" t="s">
         <v>80</v>
       </c>
-      <c r="F347" s="38" t="s">
+      <c r="F347" s="37" t="s">
         <v>415</v>
       </c>
-      <c r="G347" s="38" t="s">
+      <c r="G347" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="H347" s="38" t="s">
+      <c r="H347" s="37" t="s">
         <v>973</v>
       </c>
-      <c r="I347" s="38" t="s">
+      <c r="I347" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="J347" s="38" t="s">
+      <c r="J347" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K347" s="38" t="s">
+      <c r="K347" s="37" t="s">
         <v>945</v>
       </c>
-      <c r="L347" s="39"/>
-      <c r="M347" s="38"/>
+      <c r="L347" s="38"/>
+      <c r="M347" s="37"/>
     </row>
     <row r="348" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A348" s="35">
+      <c r="A348" s="22">
         <v>347</v>
       </c>
-      <c r="B348" s="36">
+      <c r="B348" s="35">
         <v>46178</v>
       </c>
-      <c r="C348" s="37">
+      <c r="C348" s="36">
         <v>0.30972222222222223</v>
       </c>
-      <c r="D348" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E348" s="38" t="s">
+      <c r="D348" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E348" s="37" t="s">
         <v>71</v>
       </c>
-      <c r="F348" s="38" t="s">
+      <c r="F348" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="G348" s="38" t="s">
+      <c r="G348" s="37" t="s">
         <v>754</v>
       </c>
-      <c r="H348" s="38" t="s">
+      <c r="H348" s="37" t="s">
         <v>974</v>
       </c>
-      <c r="I348" s="38" t="s">
+      <c r="I348" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="J348" s="38" t="s">
+      <c r="J348" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K348" s="38" t="s">
+      <c r="K348" s="37" t="s">
         <v>945</v>
       </c>
-      <c r="L348" s="39"/>
-      <c r="M348" s="38"/>
+      <c r="L348" s="38"/>
+      <c r="M348" s="37"/>
     </row>
     <row r="349" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A349" s="35">
+      <c r="A349" s="39">
         <v>348</v>
       </c>
-      <c r="B349" s="36">
+      <c r="B349" s="35">
         <v>46178</v>
       </c>
-      <c r="C349" s="37">
+      <c r="C349" s="36">
         <v>0.52638888888888891</v>
       </c>
-      <c r="D349" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E349" s="38" t="s">
+      <c r="D349" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E349" s="37" t="s">
         <v>89</v>
       </c>
-      <c r="F349" s="38" t="s">
+      <c r="F349" s="37" t="s">
         <v>975</v>
       </c>
-      <c r="G349" s="38" t="s">
+      <c r="G349" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="H349" s="38" t="s">
+      <c r="H349" s="37" t="s">
         <v>976</v>
       </c>
-      <c r="I349" s="38" t="s">
+      <c r="I349" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="J349" s="38" t="s">
+      <c r="J349" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K349" s="38" t="s">
+      <c r="K349" s="37" t="s">
         <v>945</v>
       </c>
-      <c r="L349" s="39"/>
-      <c r="M349" s="38"/>
+      <c r="L349" s="38"/>
+      <c r="M349" s="37"/>
     </row>
     <row r="350" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A350" s="35">
+      <c r="A350" s="30">
         <v>349</v>
       </c>
-      <c r="B350" s="36">
+      <c r="B350" s="35">
         <v>46178</v>
       </c>
-      <c r="C350" s="37">
+      <c r="C350" s="36">
         <v>0.53541666666666665</v>
       </c>
-      <c r="D350" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E350" s="38" t="s">
+      <c r="D350" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E350" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="F350" s="38" t="s">
+      <c r="F350" s="37" t="s">
         <v>890</v>
       </c>
-      <c r="G350" s="38" t="s">
+      <c r="G350" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="H350" s="38" t="s">
+      <c r="H350" s="37" t="s">
         <v>977</v>
       </c>
-      <c r="I350" s="38" t="s">
+      <c r="I350" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="J350" s="38" t="s">
-        <v>21</v>
-      </c>
-      <c r="K350" s="38" t="s">
+      <c r="J350" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="K350" s="37" t="s">
         <v>978</v>
       </c>
-      <c r="L350" s="39">
+      <c r="L350" s="38">
         <v>46178</v>
       </c>
-      <c r="M350" s="38"/>
+      <c r="M350" s="37"/>
     </row>
     <row r="351" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A351" s="35">
+      <c r="A351" s="22">
         <v>350</v>
       </c>
-      <c r="B351" s="36">
+      <c r="B351" s="35">
         <v>46178</v>
       </c>
-      <c r="C351" s="37">
+      <c r="C351" s="36">
         <v>0.55902777777777779</v>
       </c>
-      <c r="D351" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E351" s="38" t="s">
+      <c r="D351" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E351" s="37" t="s">
         <v>71</v>
       </c>
-      <c r="F351" s="38" t="s">
+      <c r="F351" s="37" t="s">
         <v>979</v>
       </c>
-      <c r="G351" s="38" t="s">
+      <c r="G351" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="H351" s="38" t="s">
+      <c r="H351" s="37" t="s">
         <v>980</v>
       </c>
-      <c r="I351" s="38" t="s">
+      <c r="I351" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="J351" s="38" t="s">
+      <c r="J351" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K351" s="38" t="s">
+      <c r="K351" s="37" t="s">
         <v>945</v>
       </c>
-      <c r="L351" s="39"/>
-      <c r="M351" s="38"/>
+      <c r="L351" s="38"/>
+      <c r="M351" s="37"/>
     </row>
     <row r="352" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A352" s="35">
+      <c r="A352" s="39">
         <v>351</v>
       </c>
-      <c r="B352" s="36">
+      <c r="B352" s="35">
         <v>46178</v>
       </c>
-      <c r="C352" s="37">
+      <c r="C352" s="36">
         <v>0.59861111111111109</v>
       </c>
-      <c r="D352" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E352" s="38" t="s">
+      <c r="D352" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E352" s="37" t="s">
         <v>981</v>
       </c>
-      <c r="F352" s="38" t="s">
+      <c r="F352" s="37" t="s">
         <v>982</v>
       </c>
-      <c r="G352" s="38" t="s">
+      <c r="G352" s="37" t="s">
         <v>317</v>
       </c>
-      <c r="H352" s="38" t="s">
+      <c r="H352" s="37" t="s">
         <v>983</v>
       </c>
-      <c r="I352" s="38" t="s">
+      <c r="I352" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="J352" s="38" t="s">
+      <c r="J352" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K352" s="38" t="s">
+      <c r="K352" s="37" t="s">
         <v>945</v>
       </c>
-      <c r="L352" s="39"/>
-      <c r="M352" s="38"/>
+      <c r="L352" s="38"/>
+      <c r="M352" s="37"/>
     </row>
     <row r="353" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A353" s="35">
+      <c r="A353" s="30">
         <v>352</v>
       </c>
-      <c r="B353" s="36">
+      <c r="B353" s="35">
         <v>46178</v>
       </c>
-      <c r="C353" s="37">
+      <c r="C353" s="36">
         <v>0.66527777777777775</v>
       </c>
-      <c r="D353" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E353" s="38" t="s">
+      <c r="D353" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E353" s="37" t="s">
         <v>984</v>
       </c>
-      <c r="F353" s="38" t="s">
+      <c r="F353" s="37" t="s">
         <v>985</v>
       </c>
-      <c r="G353" s="38" t="s">
+      <c r="G353" s="37" t="s">
         <v>754</v>
       </c>
-      <c r="H353" s="38" t="s">
+      <c r="H353" s="37" t="s">
         <v>986</v>
       </c>
-      <c r="I353" s="38" t="s">
+      <c r="I353" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="J353" s="38" t="s">
+      <c r="J353" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K353" s="38" t="s">
+      <c r="K353" s="37" t="s">
         <v>945</v>
       </c>
-      <c r="L353" s="39"/>
-      <c r="M353" s="38"/>
+      <c r="L353" s="38"/>
+      <c r="M353" s="37"/>
     </row>
     <row r="354" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A354" s="35">
+      <c r="A354" s="22">
         <v>353</v>
       </c>
-      <c r="B354" s="36">
+      <c r="B354" s="35">
         <v>46178</v>
       </c>
-      <c r="C354" s="37">
+      <c r="C354" s="36">
         <v>0.77569444444444446</v>
       </c>
-      <c r="D354" s="38" t="s">
+      <c r="D354" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="E354" s="38" t="s">
+      <c r="E354" s="37" t="s">
         <v>984</v>
       </c>
-      <c r="F354" s="38" t="s">
+      <c r="F354" s="37" t="s">
         <v>987</v>
       </c>
-      <c r="G354" s="38" t="s">
+      <c r="G354" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="H354" s="38" t="s">
+      <c r="H354" s="37" t="s">
         <v>988</v>
       </c>
-      <c r="I354" s="38" t="s">
+      <c r="I354" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="J354" s="38" t="s">
+      <c r="J354" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K354" s="38" t="s">
+      <c r="K354" s="37" t="s">
         <v>945</v>
       </c>
-      <c r="L354" s="39"/>
-      <c r="M354" s="38"/>
+      <c r="L354" s="38"/>
+      <c r="M354" s="37"/>
     </row>
     <row r="355" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A355" s="48">
+      <c r="A355" s="39">
         <v>354</v>
       </c>
-      <c r="B355" s="45">
+      <c r="B355" s="44">
         <v>46178</v>
       </c>
-      <c r="C355" s="46">
+      <c r="C355" s="45">
         <v>0.66597222222222219</v>
       </c>
-      <c r="D355" s="44" t="s">
+      <c r="D355" s="43" t="s">
         <v>989</v>
       </c>
-      <c r="E355" s="44" t="s">
+      <c r="E355" s="43" t="s">
         <v>278</v>
       </c>
-      <c r="F355" s="44" t="s">
+      <c r="F355" s="43" t="s">
         <v>990</v>
       </c>
-      <c r="G355" s="44" t="s">
+      <c r="G355" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="H355" s="44" t="s">
+      <c r="H355" s="43" t="s">
         <v>991</v>
       </c>
-      <c r="I355" s="44" t="s">
+      <c r="I355" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="J355" s="44" t="s">
+      <c r="J355" s="43" t="s">
         <v>791</v>
       </c>
-      <c r="K355" s="44"/>
-      <c r="L355" s="48"/>
-      <c r="M355" s="44"/>
+      <c r="K355" s="43"/>
+      <c r="L355" s="47"/>
+      <c r="M355" s="43"/>
     </row>
     <row r="356" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A356" s="48">
+      <c r="A356" s="30">
         <v>355</v>
       </c>
-      <c r="B356" s="45">
+      <c r="B356" s="44">
         <v>46178</v>
       </c>
-      <c r="C356" s="46">
+      <c r="C356" s="45">
         <v>0.69444444444444442</v>
       </c>
-      <c r="D356" s="44" t="s">
+      <c r="D356" s="43" t="s">
         <v>992</v>
       </c>
-      <c r="E356" s="44" t="s">
+      <c r="E356" s="43" t="s">
         <v>993</v>
       </c>
-      <c r="F356" s="44" t="s">
+      <c r="F356" s="43" t="s">
         <v>994</v>
       </c>
-      <c r="G356" s="44" t="s">
+      <c r="G356" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="H356" s="44" t="s">
+      <c r="H356" s="43" t="s">
         <v>995</v>
       </c>
-      <c r="I356" s="44" t="s">
+      <c r="I356" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="J356" s="44" t="s">
+      <c r="J356" s="43" t="s">
         <v>791</v>
       </c>
-      <c r="K356" s="44"/>
-      <c r="L356" s="48"/>
-      <c r="M356" s="44"/>
+      <c r="K356" s="43"/>
+      <c r="L356" s="47"/>
+      <c r="M356" s="43"/>
     </row>
     <row r="357" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A357" s="35">
+      <c r="A357" s="22">
         <v>356</v>
       </c>
-      <c r="B357" s="36">
+      <c r="B357" s="35">
         <v>46179</v>
       </c>
-      <c r="C357" s="37">
+      <c r="C357" s="36">
         <v>0.28888888888888886</v>
       </c>
-      <c r="D357" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E357" s="38" t="s">
+      <c r="D357" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E357" s="37" t="s">
         <v>89</v>
       </c>
-      <c r="F357" s="38" t="s">
+      <c r="F357" s="37" t="s">
         <v>682</v>
       </c>
-      <c r="G357" s="38" t="s">
+      <c r="G357" s="37" t="s">
         <v>948</v>
       </c>
-      <c r="H357" s="38" t="s">
+      <c r="H357" s="37" t="s">
         <v>996</v>
       </c>
-      <c r="I357" s="38" t="s">
+      <c r="I357" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="J357" s="38" t="s">
+      <c r="J357" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K357" s="38" t="s">
+      <c r="K357" s="37" t="s">
         <v>945</v>
       </c>
-      <c r="L357" s="39"/>
-      <c r="M357" s="38"/>
+      <c r="L357" s="38"/>
+      <c r="M357" s="37"/>
     </row>
     <row r="358" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A358" s="35">
+      <c r="A358" s="39">
         <v>357</v>
       </c>
-      <c r="B358" s="36">
+      <c r="B358" s="35">
         <v>46179</v>
       </c>
-      <c r="C358" s="37">
+      <c r="C358" s="36">
         <v>0.30555555555555558</v>
       </c>
-      <c r="D358" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E358" s="38" t="s">
+      <c r="D358" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E358" s="37" t="s">
         <v>71</v>
       </c>
-      <c r="F358" s="38" t="s">
+      <c r="F358" s="37" t="s">
         <v>328</v>
       </c>
-      <c r="G358" s="38" t="s">
+      <c r="G358" s="37" t="s">
         <v>948</v>
       </c>
-      <c r="H358" s="38" t="s">
+      <c r="H358" s="37" t="s">
         <v>997</v>
       </c>
-      <c r="I358" s="38" t="s">
+      <c r="I358" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="J358" s="38" t="s">
+      <c r="J358" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K358" s="38" t="s">
+      <c r="K358" s="37" t="s">
         <v>945</v>
       </c>
-      <c r="L358" s="39"/>
-      <c r="M358" s="38"/>
+      <c r="L358" s="38"/>
+      <c r="M358" s="37"/>
     </row>
     <row r="359" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A359" s="48">
+      <c r="A359" s="30">
         <v>358</v>
       </c>
-      <c r="B359" s="45">
+      <c r="B359" s="44">
         <v>46179</v>
       </c>
-      <c r="C359" s="46">
+      <c r="C359" s="45">
         <v>0.30902777777777779</v>
       </c>
-      <c r="D359" s="44" t="s">
-        <v>15</v>
-      </c>
-      <c r="E359" s="44" t="s">
+      <c r="D359" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E359" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="F359" s="44" t="s">
+      <c r="F359" s="43" t="s">
         <v>998</v>
       </c>
-      <c r="G359" s="44" t="s">
+      <c r="G359" s="43" t="s">
         <v>754</v>
       </c>
-      <c r="H359" s="44" t="s">
+      <c r="H359" s="43" t="s">
         <v>999</v>
       </c>
-      <c r="I359" s="44" t="s">
+      <c r="I359" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="J359" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="K359" s="44" t="s">
+      <c r="J359" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="K359" s="43" t="s">
         <v>943</v>
       </c>
-      <c r="L359" s="47">
+      <c r="L359" s="46">
         <v>46179</v>
       </c>
-      <c r="M359" s="44"/>
+      <c r="M359" s="43"/>
     </row>
     <row r="360" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A360" s="48">
+      <c r="A360" s="22">
         <v>359</v>
       </c>
-      <c r="B360" s="45">
+      <c r="B360" s="44">
         <v>46179</v>
       </c>
-      <c r="C360" s="46">
+      <c r="C360" s="45">
         <v>0.31041666666666667</v>
       </c>
-      <c r="D360" s="44" t="s">
-        <v>15</v>
-      </c>
-      <c r="E360" s="44" t="s">
+      <c r="D360" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E360" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="F360" s="44" t="s">
+      <c r="F360" s="43" t="s">
         <v>799</v>
       </c>
-      <c r="G360" s="44" t="s">
+      <c r="G360" s="43" t="s">
         <v>948</v>
       </c>
-      <c r="H360" s="44" t="s">
+      <c r="H360" s="43" t="s">
         <v>1000</v>
       </c>
-      <c r="I360" s="44" t="s">
+      <c r="I360" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="J360" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="K360" s="44" t="s">
+      <c r="J360" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="K360" s="43" t="s">
         <v>943</v>
       </c>
-      <c r="L360" s="47">
+      <c r="L360" s="46">
         <v>46179</v>
       </c>
-      <c r="M360" s="44"/>
+      <c r="M360" s="43"/>
     </row>
     <row r="361" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A361" s="48">
+      <c r="A361" s="39">
         <v>360</v>
       </c>
-      <c r="B361" s="45">
+      <c r="B361" s="44">
         <v>46179</v>
       </c>
-      <c r="C361" s="46">
+      <c r="C361" s="45">
         <v>0.31666666666666665</v>
       </c>
-      <c r="D361" s="44" t="s">
-        <v>15</v>
-      </c>
-      <c r="E361" s="44" t="s">
+      <c r="D361" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E361" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="F361" s="44" t="s">
+      <c r="F361" s="43" t="s">
         <v>1001</v>
       </c>
-      <c r="G361" s="44" t="s">
+      <c r="G361" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="H361" s="44" t="s">
+      <c r="H361" s="43" t="s">
         <v>1002</v>
       </c>
-      <c r="I361" s="44" t="s">
+      <c r="I361" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="J361" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="K361" s="44" t="s">
+      <c r="J361" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="K361" s="43" t="s">
         <v>1003</v>
       </c>
-      <c r="L361" s="47">
+      <c r="L361" s="46">
         <v>46179</v>
       </c>
-      <c r="M361" s="44"/>
+      <c r="M361" s="43"/>
     </row>
     <row r="362" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A362" s="48">
+      <c r="A362" s="30">
         <v>361</v>
       </c>
-      <c r="B362" s="45">
+      <c r="B362" s="44">
         <v>46179</v>
       </c>
-      <c r="C362" s="46">
+      <c r="C362" s="45">
         <v>0.32291666666666669</v>
       </c>
-      <c r="D362" s="44" t="s">
-        <v>15</v>
-      </c>
-      <c r="E362" s="44" t="s">
+      <c r="D362" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E362" s="43" t="s">
         <v>71</v>
       </c>
-      <c r="F362" s="44" t="s">
+      <c r="F362" s="43" t="s">
         <v>1004</v>
       </c>
-      <c r="G362" s="44" t="s">
+      <c r="G362" s="43" t="s">
         <v>1005</v>
       </c>
-      <c r="H362" s="44" t="s">
+      <c r="H362" s="43" t="s">
         <v>1006</v>
       </c>
-      <c r="I362" s="44" t="s">
+      <c r="I362" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="J362" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="K362" s="44" t="s">
+      <c r="J362" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="K362" s="43" t="s">
         <v>943</v>
       </c>
-      <c r="L362" s="47">
+      <c r="L362" s="46">
         <v>46179</v>
       </c>
-      <c r="M362" s="44"/>
+      <c r="M362" s="43"/>
     </row>
     <row r="363" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A363" s="35">
+      <c r="A363" s="22">
         <v>362</v>
       </c>
-      <c r="B363" s="36">
+      <c r="B363" s="35">
         <v>46179</v>
       </c>
-      <c r="C363" s="37">
+      <c r="C363" s="36">
         <v>0.32500000000000001</v>
       </c>
-      <c r="D363" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E363" s="38" t="s">
+      <c r="D363" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E363" s="37" t="s">
         <v>50</v>
       </c>
-      <c r="F363" s="38" t="s">
+      <c r="F363" s="37" t="s">
         <v>1007</v>
       </c>
-      <c r="G363" s="38" t="s">
+      <c r="G363" s="37" t="s">
         <v>754</v>
       </c>
-      <c r="H363" s="38" t="s">
+      <c r="H363" s="37" t="s">
         <v>1008</v>
       </c>
-      <c r="I363" s="38" t="s">
+      <c r="I363" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="J363" s="38" t="s">
+      <c r="J363" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K363" s="38" t="s">
+      <c r="K363" s="37" t="s">
         <v>945</v>
       </c>
-      <c r="L363" s="39"/>
-      <c r="M363" s="38"/>
+      <c r="L363" s="38"/>
+      <c r="M363" s="37"/>
     </row>
     <row r="364" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A364" s="35">
+      <c r="A364" s="39">
         <v>363</v>
       </c>
-      <c r="B364" s="36">
+      <c r="B364" s="35">
         <v>46179</v>
       </c>
-      <c r="C364" s="37">
+      <c r="C364" s="36">
         <v>0.33124999999999999</v>
       </c>
-      <c r="D364" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E364" s="38" t="s">
+      <c r="D364" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E364" s="37" t="s">
         <v>80</v>
       </c>
-      <c r="F364" s="38" t="s">
+      <c r="F364" s="37" t="s">
         <v>1009</v>
       </c>
-      <c r="G364" s="38" t="s">
+      <c r="G364" s="37" t="s">
         <v>1005</v>
       </c>
-      <c r="H364" s="38" t="s">
+      <c r="H364" s="37" t="s">
         <v>1010</v>
       </c>
-      <c r="I364" s="38" t="s">
+      <c r="I364" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="J364" s="38" t="s">
+      <c r="J364" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K364" s="38" t="s">
+      <c r="K364" s="37" t="s">
         <v>945</v>
       </c>
-      <c r="L364" s="39"/>
-      <c r="M364" s="38"/>
+      <c r="L364" s="38"/>
+      <c r="M364" s="37"/>
     </row>
     <row r="365" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A365" s="48">
+      <c r="A365" s="30">
         <v>364</v>
       </c>
-      <c r="B365" s="45">
+      <c r="B365" s="44">
         <v>46179</v>
       </c>
-      <c r="C365" s="46">
+      <c r="C365" s="45">
         <v>0.33819444444444446</v>
       </c>
-      <c r="D365" s="44" t="s">
-        <v>15</v>
-      </c>
-      <c r="E365" s="44" t="s">
+      <c r="D365" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E365" s="43" t="s">
         <v>43</v>
       </c>
-      <c r="F365" s="44" t="s">
+      <c r="F365" s="43" t="s">
         <v>220</v>
       </c>
-      <c r="G365" s="44" t="s">
+      <c r="G365" s="43" t="s">
         <v>754</v>
       </c>
-      <c r="H365" s="44" t="s">
+      <c r="H365" s="43" t="s">
         <v>1011</v>
       </c>
-      <c r="I365" s="44" t="s">
+      <c r="I365" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="J365" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="K365" s="44" t="s">
+      <c r="J365" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="K365" s="43" t="s">
         <v>1003</v>
       </c>
-      <c r="L365" s="47">
+      <c r="L365" s="46">
         <v>46179</v>
       </c>
-      <c r="M365" s="44"/>
+      <c r="M365" s="43"/>
     </row>
     <row r="366" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A366" s="48">
+      <c r="A366" s="22">
         <v>365</v>
       </c>
-      <c r="B366" s="45">
+      <c r="B366" s="44">
         <v>46179</v>
       </c>
-      <c r="C366" s="46">
+      <c r="C366" s="45">
         <v>0.33958333333333335</v>
       </c>
-      <c r="D366" s="44" t="s">
-        <v>15</v>
-      </c>
-      <c r="E366" s="44" t="s">
+      <c r="D366" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E366" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="F366" s="44" t="s">
+      <c r="F366" s="43" t="s">
         <v>1012</v>
       </c>
-      <c r="G366" s="44" t="s">
+      <c r="G366" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="H366" s="44" t="s">
+      <c r="H366" s="43" t="s">
         <v>1013</v>
       </c>
-      <c r="I366" s="44" t="s">
+      <c r="I366" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="J366" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="K366" s="44" t="s">
+      <c r="J366" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="K366" s="43" t="s">
         <v>943</v>
       </c>
-      <c r="L366" s="47">
+      <c r="L366" s="46">
         <v>46179</v>
       </c>
-      <c r="M366" s="44"/>
+      <c r="M366" s="43"/>
     </row>
     <row r="367" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A367" s="35">
+      <c r="A367" s="39">
         <v>366</v>
       </c>
-      <c r="B367" s="36">
+      <c r="B367" s="35">
         <v>46179</v>
       </c>
-      <c r="C367" s="37">
+      <c r="C367" s="36">
         <v>0.34027777777777779</v>
       </c>
-      <c r="D367" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E367" s="38" t="s">
+      <c r="D367" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E367" s="37" t="s">
         <v>89</v>
       </c>
-      <c r="F367" s="38" t="s">
+      <c r="F367" s="37" t="s">
         <v>89</v>
       </c>
-      <c r="G367" s="38" t="s">
+      <c r="G367" s="37" t="s">
         <v>317</v>
       </c>
-      <c r="H367" s="38" t="s">
+      <c r="H367" s="37" t="s">
         <v>1014</v>
       </c>
-      <c r="I367" s="38" t="s">
+      <c r="I367" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="J367" s="38" t="s">
+      <c r="J367" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K367" s="38" t="s">
+      <c r="K367" s="37" t="s">
         <v>945</v>
       </c>
-      <c r="L367" s="39"/>
-      <c r="M367" s="38"/>
+      <c r="L367" s="38"/>
+      <c r="M367" s="37"/>
     </row>
     <row r="368" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A368" s="35">
+      <c r="A368" s="30">
         <v>367</v>
       </c>
-      <c r="B368" s="36">
+      <c r="B368" s="35">
         <v>46179</v>
       </c>
-      <c r="C368" s="37">
+      <c r="C368" s="36">
         <v>0.36458333333333331</v>
       </c>
-      <c r="D368" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E368" s="38" t="s">
+      <c r="D368" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E368" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="F368" s="38" t="s">
+      <c r="F368" s="37" t="s">
         <v>328</v>
       </c>
-      <c r="G368" s="38" t="s">
+      <c r="G368" s="37" t="s">
         <v>317</v>
       </c>
-      <c r="H368" s="38" t="s">
+      <c r="H368" s="37" t="s">
         <v>1015</v>
       </c>
-      <c r="I368" s="38" t="s">
+      <c r="I368" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="J368" s="38" t="s">
+      <c r="J368" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K368" s="38" t="s">
+      <c r="K368" s="37" t="s">
         <v>945</v>
       </c>
-      <c r="L368" s="39"/>
-      <c r="M368" s="38"/>
+      <c r="L368" s="38"/>
+      <c r="M368" s="37"/>
     </row>
     <row r="369" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A369" s="35">
+      <c r="A369" s="22">
         <v>368</v>
       </c>
-      <c r="B369" s="36">
+      <c r="B369" s="35">
         <v>46179</v>
       </c>
-      <c r="C369" s="37">
+      <c r="C369" s="36">
         <v>0.36666666666666664</v>
       </c>
-      <c r="D369" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E369" s="38" t="s">
+      <c r="D369" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E369" s="37" t="s">
         <v>278</v>
       </c>
-      <c r="F369" s="38" t="s">
+      <c r="F369" s="37" t="s">
         <v>1016</v>
       </c>
-      <c r="G369" s="38" t="s">
+      <c r="G369" s="37" t="s">
         <v>754</v>
       </c>
-      <c r="H369" s="38" t="s">
+      <c r="H369" s="37" t="s">
         <v>1017</v>
       </c>
-      <c r="I369" s="38" t="s">
+      <c r="I369" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="J369" s="38" t="s">
+      <c r="J369" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K369" s="38" t="s">
+      <c r="K369" s="37" t="s">
         <v>945</v>
       </c>
-      <c r="L369" s="39"/>
-      <c r="M369" s="38"/>
+      <c r="L369" s="38"/>
+      <c r="M369" s="37"/>
     </row>
     <row r="370" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A370" s="35">
+      <c r="A370" s="39">
         <v>369</v>
       </c>
-      <c r="B370" s="36">
+      <c r="B370" s="35">
         <v>46179</v>
       </c>
-      <c r="C370" s="37">
+      <c r="C370" s="36">
         <v>0.38472222222222224</v>
       </c>
-      <c r="D370" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E370" s="38" t="s">
+      <c r="D370" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E370" s="37" t="s">
         <v>278</v>
       </c>
-      <c r="F370" s="38" t="s">
+      <c r="F370" s="37" t="s">
         <v>1016</v>
       </c>
-      <c r="G370" s="38" t="s">
+      <c r="G370" s="37" t="s">
         <v>754</v>
       </c>
-      <c r="H370" s="38" t="s">
+      <c r="H370" s="37" t="s">
         <v>1018</v>
       </c>
-      <c r="I370" s="38" t="s">
+      <c r="I370" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="J370" s="38" t="s">
+      <c r="J370" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K370" s="38" t="s">
+      <c r="K370" s="37" t="s">
         <v>945</v>
       </c>
-      <c r="L370" s="39"/>
-      <c r="M370" s="38"/>
+      <c r="L370" s="38"/>
+      <c r="M370" s="37"/>
     </row>
     <row r="371" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A371" s="35">
+      <c r="A371" s="30">
         <v>370</v>
       </c>
-      <c r="B371" s="36">
+      <c r="B371" s="35">
         <v>46179</v>
       </c>
-      <c r="C371" s="37">
+      <c r="C371" s="36">
         <v>0.38472222222222224</v>
       </c>
-      <c r="D371" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E371" s="38" t="s">
+      <c r="D371" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E371" s="37" t="s">
         <v>71</v>
       </c>
-      <c r="F371" s="38" t="s">
+      <c r="F371" s="37" t="s">
         <v>1019</v>
       </c>
-      <c r="G371" s="38" t="s">
+      <c r="G371" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="H371" s="38" t="s">
+      <c r="H371" s="37" t="s">
         <v>1020</v>
       </c>
-      <c r="I371" s="38" t="s">
+      <c r="I371" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="J371" s="38" t="s">
+      <c r="J371" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K371" s="38" t="s">
+      <c r="K371" s="37" t="s">
         <v>945</v>
       </c>
-      <c r="L371" s="39"/>
-      <c r="M371" s="38"/>
+      <c r="L371" s="38"/>
+      <c r="M371" s="37"/>
     </row>
     <row r="372" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A372" s="35">
+      <c r="A372" s="22">
         <v>371</v>
       </c>
-      <c r="B372" s="36">
+      <c r="B372" s="35">
         <v>46179</v>
       </c>
-      <c r="C372" s="37">
+      <c r="C372" s="36">
         <v>0.38333333333333336</v>
       </c>
-      <c r="D372" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E372" s="38" t="s">
+      <c r="D372" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E372" s="37" t="s">
         <v>80</v>
       </c>
-      <c r="F372" s="38" t="s">
+      <c r="F372" s="37" t="s">
         <v>1021</v>
       </c>
-      <c r="G372" s="38" t="s">
+      <c r="G372" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="H372" s="38" t="s">
+      <c r="H372" s="37" t="s">
         <v>1022</v>
       </c>
-      <c r="I372" s="38" t="s">
+      <c r="I372" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="J372" s="38" t="s">
+      <c r="J372" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K372" s="38" t="s">
+      <c r="K372" s="37" t="s">
         <v>945</v>
       </c>
-      <c r="L372" s="39"/>
-      <c r="M372" s="38"/>
+      <c r="L372" s="38"/>
+      <c r="M372" s="37"/>
     </row>
     <row r="373" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A373" s="35">
+      <c r="A373" s="39">
         <v>372</v>
       </c>
-      <c r="B373" s="36">
+      <c r="B373" s="35">
         <v>46179</v>
       </c>
-      <c r="C373" s="37">
+      <c r="C373" s="36">
         <v>0.39930555555555558</v>
       </c>
-      <c r="D373" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E373" s="38" t="s">
+      <c r="D373" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E373" s="37" t="s">
         <v>71</v>
       </c>
-      <c r="F373" s="38" t="s">
+      <c r="F373" s="37" t="s">
         <v>1023</v>
       </c>
-      <c r="G373" s="38" t="s">
+      <c r="G373" s="37" t="s">
         <v>1005</v>
       </c>
-      <c r="H373" s="38" t="s">
+      <c r="H373" s="37" t="s">
         <v>1024</v>
       </c>
-      <c r="I373" s="38" t="s">
+      <c r="I373" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="J373" s="38" t="s">
+      <c r="J373" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K373" s="38" t="s">
+      <c r="K373" s="37" t="s">
         <v>945</v>
       </c>
-      <c r="L373" s="39"/>
-      <c r="M373" s="38"/>
+      <c r="L373" s="38"/>
+      <c r="M373" s="37"/>
     </row>
     <row r="374" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A374" s="35">
+      <c r="A374" s="30">
         <v>373</v>
       </c>
-      <c r="B374" s="36">
+      <c r="B374" s="35">
         <v>46179</v>
       </c>
-      <c r="C374" s="37">
+      <c r="C374" s="36">
         <v>0.40555555555555556</v>
       </c>
-      <c r="D374" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E374" s="38" t="s">
+      <c r="D374" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E374" s="37" t="s">
         <v>71</v>
       </c>
-      <c r="F374" s="38" t="s">
+      <c r="F374" s="37" t="s">
         <v>1025</v>
       </c>
-      <c r="G374" s="38" t="s">
+      <c r="G374" s="37" t="s">
         <v>1005</v>
       </c>
-      <c r="H374" s="38" t="s">
+      <c r="H374" s="37" t="s">
         <v>1026</v>
       </c>
-      <c r="I374" s="38" t="s">
+      <c r="I374" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="J374" s="38" t="s">
+      <c r="J374" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K374" s="38" t="s">
+      <c r="K374" s="37" t="s">
         <v>945</v>
       </c>
-      <c r="L374" s="39"/>
-      <c r="M374" s="38"/>
+      <c r="L374" s="38"/>
+      <c r="M374" s="37"/>
     </row>
     <row r="375" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A375" s="35">
+      <c r="A375" s="22">
         <v>374</v>
       </c>
-      <c r="B375" s="36">
+      <c r="B375" s="35">
         <v>46179</v>
       </c>
-      <c r="C375" s="37">
+      <c r="C375" s="36">
         <v>0.43958333333333333</v>
       </c>
-      <c r="D375" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E375" s="38" t="s">
+      <c r="D375" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E375" s="37" t="s">
         <v>278</v>
       </c>
-      <c r="F375" s="38" t="s">
+      <c r="F375" s="37" t="s">
         <v>1027</v>
       </c>
-      <c r="G375" s="38" t="s">
+      <c r="G375" s="37" t="s">
         <v>1005</v>
       </c>
-      <c r="H375" s="38" t="s">
+      <c r="H375" s="37" t="s">
         <v>1028</v>
       </c>
-      <c r="I375" s="38" t="s">
+      <c r="I375" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="J375" s="38" t="s">
+      <c r="J375" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K375" s="38" t="s">
+      <c r="K375" s="37" t="s">
         <v>945</v>
       </c>
-      <c r="L375" s="39"/>
-      <c r="M375" s="38"/>
+      <c r="L375" s="38"/>
+      <c r="M375" s="37"/>
     </row>
     <row r="376" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A376" s="48">
+      <c r="A376" s="39">
         <v>375</v>
       </c>
-      <c r="B376" s="45">
+      <c r="B376" s="44">
         <v>46179</v>
       </c>
-      <c r="C376" s="46">
+      <c r="C376" s="45">
         <v>0.41666666666666669</v>
       </c>
-      <c r="D376" s="44" t="s">
-        <v>15</v>
-      </c>
-      <c r="E376" s="44" t="s">
+      <c r="D376" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E376" s="43" t="s">
         <v>71</v>
       </c>
-      <c r="F376" s="44" t="s">
+      <c r="F376" s="43" t="s">
         <v>1029</v>
       </c>
-      <c r="G376" s="44" t="s">
+      <c r="G376" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="H376" s="44" t="s">
+      <c r="H376" s="43" t="s">
         <v>1030</v>
       </c>
-      <c r="I376" s="44" t="s">
+      <c r="I376" s="43" t="s">
         <v>64</v>
       </c>
-      <c r="J376" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="K376" s="44" t="s">
+      <c r="J376" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="K376" s="43" t="s">
         <v>943</v>
       </c>
-      <c r="L376" s="47">
+      <c r="L376" s="46">
         <v>46179</v>
       </c>
-      <c r="M376" s="44"/>
+      <c r="M376" s="43"/>
     </row>
     <row r="377" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A377" s="35">
+      <c r="A377" s="30">
         <v>376</v>
       </c>
-      <c r="B377" s="36">
+      <c r="B377" s="35">
         <v>46179</v>
       </c>
-      <c r="C377" s="37">
+      <c r="C377" s="36">
         <v>0.50069444444444444</v>
       </c>
-      <c r="D377" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E377" s="38" t="s">
+      <c r="D377" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E377" s="37" t="s">
         <v>89</v>
       </c>
-      <c r="F377" s="38" t="s">
+      <c r="F377" s="37" t="s">
         <v>975</v>
       </c>
-      <c r="G377" s="38" t="s">
+      <c r="G377" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="H377" s="38" t="s">
+      <c r="H377" s="37" t="s">
         <v>1031</v>
       </c>
-      <c r="I377" s="38" t="s">
+      <c r="I377" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="J377" s="38" t="s">
+      <c r="J377" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K377" s="38" t="s">
+      <c r="K377" s="37" t="s">
         <v>945</v>
       </c>
-      <c r="L377" s="39"/>
-      <c r="M377" s="38"/>
+      <c r="L377" s="38"/>
+      <c r="M377" s="37"/>
     </row>
     <row r="378" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A378" s="48">
+      <c r="A378" s="22">
         <v>377</v>
       </c>
-      <c r="B378" s="45">
+      <c r="B378" s="44">
         <v>46179</v>
       </c>
-      <c r="C378" s="46">
+      <c r="C378" s="45">
         <v>0.5229166666666667</v>
       </c>
-      <c r="D378" s="44" t="s">
-        <v>15</v>
-      </c>
-      <c r="E378" s="44" t="s">
+      <c r="D378" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E378" s="43" t="s">
         <v>215</v>
       </c>
-      <c r="F378" s="44" t="s">
+      <c r="F378" s="43" t="s">
         <v>1032</v>
       </c>
-      <c r="G378" s="44" t="s">
+      <c r="G378" s="43" t="s">
         <v>948</v>
       </c>
-      <c r="H378" s="44" t="s">
+      <c r="H378" s="43" t="s">
         <v>1033</v>
       </c>
-      <c r="I378" s="44" t="s">
+      <c r="I378" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="J378" s="44" t="s">
+      <c r="J378" s="43" t="s">
         <v>791</v>
       </c>
-      <c r="K378" s="44" t="s">
+      <c r="K378" s="43" t="s">
         <v>943</v>
       </c>
-      <c r="L378" s="47">
+      <c r="L378" s="46">
         <v>46179</v>
       </c>
-      <c r="M378" s="44"/>
+      <c r="M378" s="43"/>
     </row>
     <row r="379" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A379" s="35">
+      <c r="A379" s="39">
         <v>378</v>
       </c>
-      <c r="B379" s="36">
+      <c r="B379" s="35">
         <v>46179</v>
       </c>
-      <c r="C379" s="37">
+      <c r="C379" s="36">
         <v>0.52777777777777779</v>
       </c>
-      <c r="D379" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E379" s="38" t="s">
+      <c r="D379" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E379" s="37" t="s">
         <v>278</v>
       </c>
-      <c r="F379" s="38" t="s">
+      <c r="F379" s="37" t="s">
         <v>1034</v>
       </c>
-      <c r="G379" s="38" t="s">
+      <c r="G379" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="H379" s="38" t="s">
+      <c r="H379" s="37" t="s">
         <v>1035</v>
       </c>
-      <c r="I379" s="38" t="s">
+      <c r="I379" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="J379" s="38" t="s">
+      <c r="J379" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K379" s="38" t="s">
+      <c r="K379" s="37" t="s">
         <v>945</v>
       </c>
-      <c r="L379" s="39"/>
-      <c r="M379" s="38"/>
+      <c r="L379" s="38"/>
+      <c r="M379" s="37"/>
     </row>
     <row r="380" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A380" s="48">
+      <c r="A380" s="30">
         <v>379</v>
       </c>
-      <c r="B380" s="45">
+      <c r="B380" s="44">
         <v>46179</v>
       </c>
-      <c r="C380" s="46">
+      <c r="C380" s="45">
         <v>0.58125000000000004</v>
       </c>
-      <c r="D380" s="44" t="s">
-        <v>15</v>
-      </c>
-      <c r="E380" s="44" t="s">
+      <c r="D380" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E380" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="F380" s="44" t="s">
+      <c r="F380" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="G380" s="44" t="s">
+      <c r="G380" s="43" t="s">
         <v>754</v>
       </c>
-      <c r="H380" s="44" t="s">
+      <c r="H380" s="43" t="s">
         <v>1036</v>
       </c>
-      <c r="I380" s="44" t="s">
+      <c r="I380" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="J380" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="K380" s="44" t="s">
+      <c r="J380" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="K380" s="43" t="s">
         <v>1003</v>
       </c>
-      <c r="L380" s="47">
+      <c r="L380" s="46">
         <v>46179</v>
       </c>
-      <c r="M380" s="44"/>
+      <c r="M380" s="43"/>
     </row>
     <row r="381" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A381" s="35">
+      <c r="A381" s="22">
         <v>380</v>
       </c>
-      <c r="B381" s="36">
+      <c r="B381" s="35">
         <v>46179</v>
       </c>
-      <c r="C381" s="37">
+      <c r="C381" s="36">
         <v>0.65902777777777777</v>
       </c>
-      <c r="D381" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E381" s="38" t="s">
+      <c r="D381" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E381" s="37" t="s">
         <v>89</v>
       </c>
-      <c r="F381" s="38" t="s">
+      <c r="F381" s="37" t="s">
         <v>1037</v>
       </c>
-      <c r="G381" s="38" t="s">
+      <c r="G381" s="37" t="s">
         <v>754</v>
       </c>
-      <c r="H381" s="38" t="s">
+      <c r="H381" s="37" t="s">
         <v>1038</v>
       </c>
-      <c r="I381" s="38" t="s">
+      <c r="I381" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="J381" s="38" t="s">
+      <c r="J381" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K381" s="38" t="s">
+      <c r="K381" s="37" t="s">
         <v>945</v>
       </c>
-      <c r="L381" s="39"/>
-      <c r="M381" s="38"/>
+      <c r="L381" s="38"/>
+      <c r="M381" s="37"/>
     </row>
     <row r="382" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A382" s="35">
+      <c r="A382" s="39">
         <v>381</v>
       </c>
-      <c r="B382" s="36">
+      <c r="B382" s="35">
         <v>46179</v>
       </c>
-      <c r="C382" s="37">
+      <c r="C382" s="36">
         <v>0.71111111111111114</v>
       </c>
-      <c r="D382" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E382" s="38" t="s">
+      <c r="D382" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E382" s="37" t="s">
         <v>89</v>
       </c>
-      <c r="F382" s="38" t="s">
+      <c r="F382" s="37" t="s">
         <v>1039</v>
       </c>
-      <c r="G382" s="38" t="s">
+      <c r="G382" s="37" t="s">
         <v>754</v>
       </c>
-      <c r="H382" s="38" t="s">
+      <c r="H382" s="37" t="s">
         <v>1040</v>
       </c>
-      <c r="I382" s="38" t="s">
+      <c r="I382" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="J382" s="38" t="s">
+      <c r="J382" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K382" s="38" t="s">
+      <c r="K382" s="37" t="s">
         <v>945</v>
       </c>
-      <c r="L382" s="39"/>
-      <c r="M382" s="38"/>
+      <c r="L382" s="38"/>
+      <c r="M382" s="37"/>
     </row>
     <row r="383" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A383" s="35">
+      <c r="A383" s="30">
         <v>382</v>
       </c>
-      <c r="B383" s="36">
+      <c r="B383" s="35">
         <v>46179</v>
       </c>
-      <c r="C383" s="37">
+      <c r="C383" s="36">
         <v>0.77013888888888893</v>
       </c>
-      <c r="D383" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E383" s="38" t="s">
+      <c r="D383" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E383" s="37" t="s">
         <v>278</v>
       </c>
-      <c r="F383" s="38" t="s">
+      <c r="F383" s="37" t="s">
         <v>1041</v>
       </c>
-      <c r="G383" s="38" t="s">
+      <c r="G383" s="37" t="s">
         <v>948</v>
       </c>
-      <c r="H383" s="38" t="s">
+      <c r="H383" s="37" t="s">
         <v>1042</v>
       </c>
-      <c r="I383" s="38" t="s">
+      <c r="I383" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="J383" s="38" t="s">
+      <c r="J383" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K383" s="38" t="s">
+      <c r="K383" s="37" t="s">
         <v>945</v>
       </c>
-      <c r="L383" s="39"/>
-      <c r="M383" s="38"/>
+      <c r="L383" s="38"/>
+      <c r="M383" s="37"/>
     </row>
     <row r="384" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A384" s="35">
+      <c r="A384" s="22">
         <v>383</v>
       </c>
-      <c r="B384" s="36">
+      <c r="B384" s="35">
         <v>46179</v>
       </c>
-      <c r="C384" s="37">
+      <c r="C384" s="36">
         <v>0.36875000000000002</v>
       </c>
-      <c r="D384" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E384" s="38" t="s">
+      <c r="D384" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E384" s="37" t="s">
         <v>232</v>
       </c>
-      <c r="F384" s="38" t="s">
+      <c r="F384" s="37" t="s">
         <v>522</v>
       </c>
-      <c r="G384" s="38" t="s">
+      <c r="G384" s="37" t="s">
         <v>754</v>
       </c>
-      <c r="H384" s="38" t="s">
+      <c r="H384" s="37" t="s">
         <v>1043</v>
       </c>
-      <c r="I384" s="38" t="s">
+      <c r="I384" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="J384" s="38" t="s">
-        <v>21</v>
-      </c>
-      <c r="K384" s="38" t="s">
+      <c r="J384" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="K384" s="37" t="s">
         <v>1003</v>
       </c>
-      <c r="L384" s="39">
+      <c r="L384" s="38">
         <v>46179</v>
       </c>
-      <c r="M384" s="38"/>
+      <c r="M384" s="37"/>
     </row>
     <row r="385" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A385" s="35">
+      <c r="A385" s="39">
         <v>384</v>
       </c>
-      <c r="B385" s="36">
+      <c r="B385" s="35">
         <v>46179</v>
       </c>
-      <c r="C385" s="37">
+      <c r="C385" s="36">
         <v>0.28541666666666665</v>
       </c>
-      <c r="D385" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E385" s="38" t="s">
+      <c r="D385" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E385" s="37" t="s">
         <v>1044</v>
       </c>
-      <c r="F385" s="38" t="s">
+      <c r="F385" s="37" t="s">
         <v>1045</v>
       </c>
-      <c r="G385" s="38" t="s">
+      <c r="G385" s="37" t="s">
         <v>317</v>
       </c>
-      <c r="H385" s="38" t="s">
+      <c r="H385" s="37" t="s">
         <v>1046</v>
       </c>
-      <c r="I385" s="38" t="s">
+      <c r="I385" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="J385" s="38" t="s">
+      <c r="J385" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K385" s="38" t="s">
+      <c r="K385" s="37" t="s">
         <v>945</v>
       </c>
-      <c r="L385" s="39"/>
-      <c r="M385" s="38"/>
+      <c r="L385" s="38"/>
+      <c r="M385" s="37"/>
     </row>
     <row r="386" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A386" s="35">
+      <c r="A386" s="30">
         <v>385</v>
       </c>
-      <c r="B386" s="36">
+      <c r="B386" s="35">
         <v>46179</v>
       </c>
-      <c r="C386" s="37">
+      <c r="C386" s="36">
         <v>0.6743055555555556</v>
       </c>
-      <c r="D386" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E386" s="38" t="s">
+      <c r="D386" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E386" s="37" t="s">
         <v>89</v>
       </c>
-      <c r="F386" s="38" t="s">
+      <c r="F386" s="37" t="s">
         <v>1037</v>
       </c>
-      <c r="G386" s="38" t="s">
+      <c r="G386" s="37" t="s">
         <v>754</v>
       </c>
-      <c r="H386" s="38" t="s">
+      <c r="H386" s="37" t="s">
         <v>1047</v>
       </c>
-      <c r="I386" s="38" t="s">
+      <c r="I386" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="J386" s="38" t="s">
+      <c r="J386" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K386" s="38" t="s">
+      <c r="K386" s="37" t="s">
         <v>945</v>
       </c>
-      <c r="L386" s="39"/>
-      <c r="M386" s="38"/>
+      <c r="L386" s="38"/>
+      <c r="M386" s="37"/>
     </row>
     <row r="387" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A387" s="35">
+      <c r="A387" s="22">
         <v>386</v>
       </c>
-      <c r="B387" s="36">
+      <c r="B387" s="35">
         <v>46179</v>
       </c>
-      <c r="C387" s="37">
+      <c r="C387" s="36">
         <v>0.29236111111111113</v>
       </c>
-      <c r="D387" s="38" t="s">
+      <c r="D387" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="E387" s="38" t="s">
+      <c r="E387" s="37" t="s">
         <v>993</v>
       </c>
-      <c r="F387" s="38" t="s">
+      <c r="F387" s="37" t="s">
         <v>1048</v>
       </c>
-      <c r="G387" s="38" t="s">
+      <c r="G387" s="37" t="s">
         <v>1049</v>
       </c>
-      <c r="H387" s="38" t="s">
+      <c r="H387" s="37" t="s">
         <v>1050</v>
       </c>
-      <c r="I387" s="38" t="s">
+      <c r="I387" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="J387" s="38" t="s">
+      <c r="J387" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K387" s="38"/>
-      <c r="L387" s="39"/>
-      <c r="M387" s="38"/>
+      <c r="K387" s="37"/>
+      <c r="L387" s="38"/>
+      <c r="M387" s="37"/>
     </row>
     <row r="388" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A388" s="48">
+      <c r="A388" s="39">
         <v>387</v>
       </c>
-      <c r="B388" s="45">
+      <c r="B388" s="44">
         <v>46179</v>
       </c>
-      <c r="C388" s="46">
+      <c r="C388" s="45">
         <v>0.7006944444444444</v>
       </c>
-      <c r="D388" s="44" t="s">
-        <v>15</v>
-      </c>
-      <c r="E388" s="44" t="s">
+      <c r="D388" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E388" s="43" t="s">
         <v>89</v>
       </c>
-      <c r="F388" s="44" t="s">
+      <c r="F388" s="43" t="s">
         <v>1051</v>
       </c>
-      <c r="G388" s="44" t="s">
+      <c r="G388" s="43" t="s">
         <v>754</v>
       </c>
-      <c r="H388" s="44" t="s">
+      <c r="H388" s="43" t="s">
         <v>1052</v>
       </c>
-      <c r="I388" s="44" t="s">
+      <c r="I388" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="J388" s="44" t="s">
+      <c r="J388" s="43" t="s">
         <v>791</v>
       </c>
-      <c r="K388" s="44"/>
-      <c r="L388" s="48"/>
-      <c r="M388" s="44"/>
+      <c r="K388" s="43"/>
+      <c r="L388" s="47"/>
+      <c r="M388" s="43"/>
     </row>
     <row r="389" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A389" s="35">
+      <c r="A389" s="30">
         <v>388</v>
       </c>
-      <c r="B389" s="36">
+      <c r="B389" s="35">
         <v>46181</v>
       </c>
-      <c r="C389" s="37">
+      <c r="C389" s="36">
         <v>0.29166666666666669</v>
       </c>
-      <c r="D389" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E389" s="38" t="s">
+      <c r="D389" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E389" s="37" t="s">
         <v>89</v>
       </c>
-      <c r="F389" s="38" t="s">
+      <c r="F389" s="37" t="s">
         <v>682</v>
       </c>
-      <c r="G389" s="38" t="s">
+      <c r="G389" s="37" t="s">
         <v>948</v>
       </c>
-      <c r="H389" s="38" t="s">
+      <c r="H389" s="37" t="s">
         <v>996</v>
       </c>
-      <c r="I389" s="38" t="s">
+      <c r="I389" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="J389" s="38" t="s">
+      <c r="J389" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K389" s="38" t="s">
+      <c r="K389" s="37" t="s">
         <v>945</v>
       </c>
-      <c r="L389" s="39"/>
-      <c r="M389" s="38"/>
+      <c r="L389" s="38"/>
+      <c r="M389" s="37"/>
     </row>
     <row r="390" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A390" s="35">
+      <c r="A390" s="22">
         <v>389</v>
       </c>
-      <c r="B390" s="36">
+      <c r="B390" s="35">
         <v>46181</v>
       </c>
-      <c r="C390" s="37">
+      <c r="C390" s="36">
         <v>0.29236111111111113</v>
       </c>
-      <c r="D390" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E390" s="38" t="s">
+      <c r="D390" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E390" s="37" t="s">
         <v>50</v>
       </c>
-      <c r="F390" s="38" t="s">
+      <c r="F390" s="37" t="s">
         <v>1053</v>
       </c>
-      <c r="G390" s="38" t="s">
+      <c r="G390" s="37" t="s">
         <v>948</v>
       </c>
-      <c r="H390" s="38" t="s">
+      <c r="H390" s="37" t="s">
         <v>1054</v>
       </c>
-      <c r="I390" s="38" t="s">
+      <c r="I390" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="J390" s="38" t="s">
+      <c r="J390" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K390" s="38" t="s">
+      <c r="K390" s="37" t="s">
         <v>945</v>
       </c>
-      <c r="L390" s="39"/>
-      <c r="M390" s="38"/>
+      <c r="L390" s="38"/>
+      <c r="M390" s="37"/>
     </row>
     <row r="391" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A391" s="35">
+      <c r="A391" s="39">
         <v>390</v>
       </c>
-      <c r="B391" s="36">
+      <c r="B391" s="35">
         <v>46181</v>
       </c>
-      <c r="C391" s="37">
+      <c r="C391" s="36">
         <v>0.29583333333333334</v>
       </c>
-      <c r="D391" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E391" s="38" t="s">
+      <c r="D391" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E391" s="37" t="s">
         <v>50</v>
       </c>
-      <c r="F391" s="38" t="s">
+      <c r="F391" s="37" t="s">
         <v>1055</v>
       </c>
-      <c r="G391" s="38" t="s">
+      <c r="G391" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="H391" s="38" t="s">
+      <c r="H391" s="37" t="s">
         <v>1056</v>
       </c>
-      <c r="I391" s="38" t="s">
+      <c r="I391" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="J391" s="38" t="s">
+      <c r="J391" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K391" s="38" t="s">
+      <c r="K391" s="37" t="s">
         <v>945</v>
       </c>
-      <c r="L391" s="39"/>
-      <c r="M391" s="38"/>
+      <c r="L391" s="38"/>
+      <c r="M391" s="37"/>
     </row>
     <row r="392" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A392" s="35">
+      <c r="A392" s="30">
         <v>391</v>
       </c>
-      <c r="B392" s="36">
+      <c r="B392" s="35">
         <v>46181</v>
       </c>
-      <c r="C392" s="37">
+      <c r="C392" s="36">
         <v>0.30277777777777776</v>
       </c>
-      <c r="D392" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E392" s="38" t="s">
+      <c r="D392" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E392" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="F392" s="38" t="s">
+      <c r="F392" s="37" t="s">
         <v>1057</v>
       </c>
-      <c r="G392" s="38" t="s">
+      <c r="G392" s="37" t="s">
         <v>1005</v>
       </c>
-      <c r="H392" s="38" t="s">
+      <c r="H392" s="37" t="s">
         <v>1058</v>
       </c>
-      <c r="I392" s="38" t="s">
+      <c r="I392" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="J392" s="38" t="s">
+      <c r="J392" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K392" s="38" t="s">
+      <c r="K392" s="37" t="s">
         <v>945</v>
       </c>
-      <c r="L392" s="39"/>
-      <c r="M392" s="38"/>
+      <c r="L392" s="38"/>
+      <c r="M392" s="37"/>
     </row>
     <row r="393" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A393" s="35">
+      <c r="A393" s="22">
         <v>392</v>
       </c>
-      <c r="B393" s="36">
+      <c r="B393" s="35">
         <v>46181</v>
       </c>
-      <c r="C393" s="37">
+      <c r="C393" s="36">
         <v>0.30416666666666664</v>
       </c>
-      <c r="D393" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E393" s="38" t="s">
+      <c r="D393" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E393" s="37" t="s">
         <v>232</v>
       </c>
-      <c r="F393" s="38" t="s">
+      <c r="F393" s="37" t="s">
         <v>232</v>
       </c>
-      <c r="G393" s="38" t="s">
+      <c r="G393" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="H393" s="38" t="s">
+      <c r="H393" s="37" t="s">
         <v>946</v>
       </c>
-      <c r="I393" s="38" t="s">
+      <c r="I393" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="J393" s="38" t="s">
+      <c r="J393" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K393" s="38" t="s">
+      <c r="K393" s="37" t="s">
         <v>945</v>
       </c>
-      <c r="L393" s="39"/>
-      <c r="M393" s="38"/>
+      <c r="L393" s="38"/>
+      <c r="M393" s="37"/>
     </row>
     <row r="394" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A394" s="48">
+      <c r="A394" s="39">
         <v>393</v>
       </c>
-      <c r="B394" s="45">
+      <c r="B394" s="44">
         <v>46181</v>
       </c>
-      <c r="C394" s="46">
+      <c r="C394" s="45">
         <v>0.30694444444444446</v>
       </c>
-      <c r="D394" s="44" t="s">
-        <v>15</v>
-      </c>
-      <c r="E394" s="44" t="s">
+      <c r="D394" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E394" s="43" t="s">
         <v>89</v>
       </c>
-      <c r="F394" s="44" t="s">
+      <c r="F394" s="43" t="s">
         <v>971</v>
       </c>
-      <c r="G394" s="44" t="s">
+      <c r="G394" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="H394" s="44" t="s">
+      <c r="H394" s="43" t="s">
         <v>1031</v>
       </c>
-      <c r="I394" s="44" t="s">
+      <c r="I394" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="J394" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="K394" s="44" t="s">
+      <c r="J394" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="K394" s="43" t="s">
         <v>1003</v>
       </c>
-      <c r="L394" s="47">
+      <c r="L394" s="46">
         <v>46181</v>
       </c>
-      <c r="M394" s="44"/>
+      <c r="M394" s="43"/>
     </row>
     <row r="395" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A395" s="35">
+      <c r="A395" s="30">
         <v>394</v>
       </c>
-      <c r="B395" s="36">
+      <c r="B395" s="35">
         <v>46181</v>
       </c>
-      <c r="C395" s="37">
+      <c r="C395" s="36">
         <v>0.37430555555555556</v>
       </c>
-      <c r="D395" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E395" s="38" t="s">
+      <c r="D395" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E395" s="37" t="s">
         <v>71</v>
       </c>
-      <c r="F395" s="38" t="s">
+      <c r="F395" s="37" t="s">
         <v>1059</v>
       </c>
-      <c r="G395" s="38" t="s">
+      <c r="G395" s="37" t="s">
         <v>754</v>
       </c>
-      <c r="H395" s="38" t="s">
+      <c r="H395" s="37" t="s">
         <v>1060</v>
       </c>
-      <c r="I395" s="38" t="s">
+      <c r="I395" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="J395" s="38" t="s">
+      <c r="J395" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K395" s="38" t="s">
+      <c r="K395" s="37" t="s">
         <v>945</v>
       </c>
-      <c r="L395" s="39"/>
-      <c r="M395" s="38"/>
+      <c r="L395" s="38"/>
+      <c r="M395" s="37"/>
     </row>
     <row r="396" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A396" s="48">
+      <c r="A396" s="22">
         <v>395</v>
       </c>
-      <c r="B396" s="45">
+      <c r="B396" s="44">
         <v>46181</v>
       </c>
-      <c r="C396" s="46">
+      <c r="C396" s="45">
         <v>0.375</v>
       </c>
-      <c r="D396" s="44" t="s">
-        <v>15</v>
-      </c>
-      <c r="E396" s="44" t="s">
+      <c r="D396" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E396" s="43" t="s">
         <v>71</v>
       </c>
-      <c r="F396" s="44" t="s">
+      <c r="F396" s="43" t="s">
         <v>1061</v>
       </c>
-      <c r="G396" s="44" t="s">
+      <c r="G396" s="43" t="s">
         <v>754</v>
       </c>
-      <c r="H396" s="44" t="s">
+      <c r="H396" s="43" t="s">
         <v>1062</v>
       </c>
-      <c r="I396" s="44" t="s">
+      <c r="I396" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="J396" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="K396" s="44" t="s">
+      <c r="J396" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="K396" s="43" t="s">
         <v>1003</v>
       </c>
-      <c r="L396" s="47">
+      <c r="L396" s="46">
         <v>46181</v>
       </c>
-      <c r="M396" s="44"/>
+      <c r="M396" s="43"/>
     </row>
     <row r="397" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A397" s="48">
+      <c r="A397" s="39">
         <v>396</v>
       </c>
-      <c r="B397" s="45">
+      <c r="B397" s="44">
         <v>46181</v>
       </c>
-      <c r="C397" s="46">
+      <c r="C397" s="45">
         <v>0.3923611111111111</v>
       </c>
-      <c r="D397" s="44" t="s">
-        <v>15</v>
-      </c>
-      <c r="E397" s="44" t="s">
+      <c r="D397" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E397" s="43" t="s">
         <v>43</v>
       </c>
-      <c r="F397" s="44" t="s">
+      <c r="F397" s="43" t="s">
         <v>773</v>
       </c>
-      <c r="G397" s="44" t="s">
+      <c r="G397" s="43" t="s">
         <v>1005</v>
       </c>
-      <c r="H397" s="44" t="s">
+      <c r="H397" s="43" t="s">
         <v>1063</v>
       </c>
-      <c r="I397" s="44" t="s">
+      <c r="I397" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="J397" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="K397" s="44" t="s">
+      <c r="J397" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="K397" s="43" t="s">
         <v>1003</v>
       </c>
-      <c r="L397" s="47">
+      <c r="L397" s="46">
         <v>46181</v>
       </c>
-      <c r="M397" s="44"/>
+      <c r="M397" s="43"/>
     </row>
     <row r="398" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A398" s="35">
+      <c r="A398" s="30">
         <v>397</v>
       </c>
-      <c r="B398" s="36">
+      <c r="B398" s="35">
         <v>46181</v>
       </c>
-      <c r="C398" s="37">
+      <c r="C398" s="36">
         <v>0.42083333333333334</v>
       </c>
-      <c r="D398" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E398" s="38" t="s">
+      <c r="D398" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E398" s="37" t="s">
         <v>215</v>
       </c>
-      <c r="F398" s="38" t="s">
+      <c r="F398" s="37" t="s">
         <v>1064</v>
       </c>
-      <c r="G398" s="38" t="s">
+      <c r="G398" s="37" t="s">
         <v>754</v>
       </c>
-      <c r="H398" s="38" t="s">
+      <c r="H398" s="37" t="s">
         <v>1065</v>
       </c>
-      <c r="I398" s="38" t="s">
+      <c r="I398" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="J398" s="38" t="s">
+      <c r="J398" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K398" s="38" t="s">
+      <c r="K398" s="37" t="s">
         <v>945</v>
       </c>
-      <c r="L398" s="39"/>
-      <c r="M398" s="38"/>
+      <c r="L398" s="38"/>
+      <c r="M398" s="37"/>
     </row>
     <row r="399" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A399" s="35">
+      <c r="A399" s="22">
         <v>398</v>
       </c>
-      <c r="B399" s="36">
+      <c r="B399" s="35">
         <v>46181</v>
       </c>
-      <c r="C399" s="37">
+      <c r="C399" s="36">
         <v>0.43194444444444446</v>
       </c>
-      <c r="D399" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E399" s="38" t="s">
+      <c r="D399" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E399" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="F399" s="38" t="s">
+      <c r="F399" s="37" t="s">
         <v>1066</v>
       </c>
-      <c r="G399" s="38" t="s">
+      <c r="G399" s="37" t="s">
         <v>754</v>
       </c>
-      <c r="H399" s="38" t="s">
+      <c r="H399" s="37" t="s">
         <v>1067</v>
       </c>
-      <c r="I399" s="38" t="s">
+      <c r="I399" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="J399" s="38" t="s">
+      <c r="J399" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K399" s="38" t="s">
+      <c r="K399" s="37" t="s">
         <v>945</v>
       </c>
-      <c r="L399" s="39"/>
-      <c r="M399" s="38"/>
+      <c r="L399" s="38"/>
+      <c r="M399" s="37"/>
     </row>
     <row r="400" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A400" s="35">
+      <c r="A400" s="39">
         <v>399</v>
       </c>
-      <c r="B400" s="36">
+      <c r="B400" s="35">
         <v>46181</v>
       </c>
-      <c r="C400" s="37">
+      <c r="C400" s="36">
         <v>0.43472222222222223</v>
       </c>
-      <c r="D400" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E400" s="38" t="s">
+      <c r="D400" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E400" s="37" t="s">
         <v>232</v>
       </c>
-      <c r="F400" s="38" t="s">
+      <c r="F400" s="37" t="s">
         <v>1068</v>
       </c>
-      <c r="G400" s="38" t="s">
+      <c r="G400" s="37" t="s">
         <v>948</v>
       </c>
-      <c r="H400" s="38" t="s">
+      <c r="H400" s="37" t="s">
         <v>883</v>
       </c>
-      <c r="I400" s="38" t="s">
+      <c r="I400" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="J400" s="38" t="s">
+      <c r="J400" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K400" s="38" t="s">
+      <c r="K400" s="37" t="s">
         <v>945</v>
       </c>
-      <c r="L400" s="39"/>
-      <c r="M400" s="38"/>
+      <c r="L400" s="38"/>
+      <c r="M400" s="37"/>
     </row>
     <row r="401" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A401" s="35">
+      <c r="A401" s="30">
         <v>400</v>
       </c>
-      <c r="B401" s="36">
+      <c r="B401" s="35">
         <v>46181</v>
       </c>
-      <c r="C401" s="37">
+      <c r="C401" s="36">
         <v>0.44791666666666669</v>
       </c>
-      <c r="D401" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E401" s="38" t="s">
+      <c r="D401" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E401" s="37" t="s">
         <v>232</v>
       </c>
-      <c r="F401" s="38" t="s">
+      <c r="F401" s="37" t="s">
         <v>1069</v>
       </c>
-      <c r="G401" s="38" t="s">
+      <c r="G401" s="37" t="s">
         <v>317</v>
       </c>
-      <c r="H401" s="38" t="s">
+      <c r="H401" s="37" t="s">
         <v>1070</v>
       </c>
-      <c r="I401" s="38" t="s">
+      <c r="I401" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="J401" s="38" t="s">
+      <c r="J401" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K401" s="38" t="s">
+      <c r="K401" s="37" t="s">
         <v>945</v>
       </c>
-      <c r="L401" s="39"/>
-      <c r="M401" s="38"/>
+      <c r="L401" s="38"/>
+      <c r="M401" s="37"/>
     </row>
     <row r="402" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A402" s="48">
+      <c r="A402" s="22">
         <v>401</v>
       </c>
-      <c r="B402" s="45">
+      <c r="B402" s="44">
         <v>46181</v>
       </c>
-      <c r="C402" s="46">
+      <c r="C402" s="45">
         <v>0.46666666666666667</v>
       </c>
-      <c r="D402" s="44" t="s">
-        <v>15</v>
-      </c>
-      <c r="E402" s="44" t="s">
+      <c r="D402" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E402" s="43" t="s">
         <v>80</v>
       </c>
-      <c r="F402" s="44" t="s">
+      <c r="F402" s="43" t="s">
         <v>1071</v>
       </c>
-      <c r="G402" s="44" t="s">
+      <c r="G402" s="43" t="s">
         <v>754</v>
       </c>
-      <c r="H402" s="44" t="s">
+      <c r="H402" s="43" t="s">
         <v>1072</v>
       </c>
-      <c r="I402" s="44" t="s">
+      <c r="I402" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="J402" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="K402" s="44" t="s">
+      <c r="J402" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="K402" s="43" t="s">
         <v>1003</v>
       </c>
-      <c r="L402" s="47">
+      <c r="L402" s="46">
         <v>46181</v>
       </c>
-      <c r="M402" s="44"/>
+      <c r="M402" s="43"/>
     </row>
     <row r="403" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A403" s="48">
+      <c r="A403" s="39">
         <v>402</v>
       </c>
-      <c r="B403" s="45">
+      <c r="B403" s="44">
         <v>46181</v>
       </c>
-      <c r="C403" s="46">
+      <c r="C403" s="45">
         <v>0.48819444444444443</v>
       </c>
-      <c r="D403" s="44" t="s">
-        <v>15</v>
-      </c>
-      <c r="E403" s="44" t="s">
+      <c r="D403" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E403" s="43" t="s">
         <v>80</v>
       </c>
-      <c r="F403" s="44" t="s">
+      <c r="F403" s="43" t="s">
         <v>1073</v>
       </c>
-      <c r="G403" s="44" t="s">
+      <c r="G403" s="43" t="s">
         <v>1005</v>
       </c>
-      <c r="H403" s="44" t="s">
+      <c r="H403" s="43" t="s">
         <v>1074</v>
       </c>
-      <c r="I403" s="44" t="s">
+      <c r="I403" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="J403" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="K403" s="44" t="s">
+      <c r="J403" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="K403" s="43" t="s">
         <v>1003</v>
       </c>
-      <c r="L403" s="47">
+      <c r="L403" s="46">
         <v>46181</v>
       </c>
-      <c r="M403" s="44"/>
+      <c r="M403" s="43"/>
     </row>
     <row r="404" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A404" s="48">
+      <c r="A404" s="30">
         <v>403</v>
       </c>
-      <c r="B404" s="45">
+      <c r="B404" s="44">
         <v>46181</v>
       </c>
-      <c r="C404" s="46">
+      <c r="C404" s="45">
         <v>0.49444444444444446</v>
       </c>
-      <c r="D404" s="44" t="s">
-        <v>15</v>
-      </c>
-      <c r="E404" s="44" t="s">
+      <c r="D404" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E404" s="43" t="s">
         <v>50</v>
       </c>
-      <c r="F404" s="44" t="s">
+      <c r="F404" s="43" t="s">
         <v>633</v>
       </c>
-      <c r="G404" s="44" t="s">
+      <c r="G404" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="H404" s="44" t="s">
+      <c r="H404" s="43" t="s">
         <v>1075</v>
       </c>
-      <c r="I404" s="44" t="s">
+      <c r="I404" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="J404" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="K404" s="44" t="s">
+      <c r="J404" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="K404" s="43" t="s">
         <v>945</v>
       </c>
-      <c r="L404" s="47">
+      <c r="L404" s="46">
         <v>46181</v>
       </c>
-      <c r="M404" s="44"/>
+      <c r="M404" s="43"/>
     </row>
     <row r="405" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A405" s="48">
+      <c r="A405" s="22">
         <v>404</v>
       </c>
-      <c r="B405" s="45">
+      <c r="B405" s="44">
         <v>46181</v>
       </c>
-      <c r="C405" s="46">
+      <c r="C405" s="45">
         <v>0.49722222222222223</v>
       </c>
-      <c r="D405" s="44" t="s">
-        <v>15</v>
-      </c>
-      <c r="E405" s="44" t="s">
+      <c r="D405" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E405" s="43" t="s">
         <v>43</v>
       </c>
-      <c r="F405" s="44" t="s">
+      <c r="F405" s="43" t="s">
         <v>1076</v>
       </c>
-      <c r="G405" s="44" t="s">
+      <c r="G405" s="43" t="s">
         <v>754</v>
       </c>
-      <c r="H405" s="44" t="s">
+      <c r="H405" s="43" t="s">
         <v>1077</v>
       </c>
-      <c r="I405" s="44" t="s">
+      <c r="I405" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="J405" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="K405" s="44" t="s">
+      <c r="J405" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="K405" s="43" t="s">
         <v>1003</v>
       </c>
-      <c r="L405" s="47">
+      <c r="L405" s="46">
         <v>46181</v>
       </c>
-      <c r="M405" s="44"/>
+      <c r="M405" s="43"/>
     </row>
     <row r="406" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A406" s="48">
+      <c r="A406" s="39">
         <v>405</v>
       </c>
-      <c r="B406" s="45">
+      <c r="B406" s="44">
         <v>46181</v>
       </c>
-      <c r="C406" s="46">
+      <c r="C406" s="45">
         <v>0.60555555555555551</v>
       </c>
-      <c r="D406" s="44" t="s">
-        <v>15</v>
-      </c>
-      <c r="E406" s="44" t="s">
+      <c r="D406" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E406" s="43" t="s">
         <v>278</v>
       </c>
-      <c r="F406" s="44" t="s">
+      <c r="F406" s="43" t="s">
         <v>1078</v>
       </c>
-      <c r="G406" s="44" t="s">
+      <c r="G406" s="43" t="s">
         <v>754</v>
       </c>
-      <c r="H406" s="44" t="s">
+      <c r="H406" s="43" t="s">
         <v>1079</v>
       </c>
-      <c r="I406" s="44" t="s">
+      <c r="I406" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="J406" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="K406" s="44" t="s">
+      <c r="J406" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="K406" s="43" t="s">
         <v>1003</v>
       </c>
-      <c r="L406" s="47">
+      <c r="L406" s="46">
         <v>46181</v>
       </c>
-      <c r="M406" s="44"/>
+      <c r="M406" s="43"/>
     </row>
     <row r="407" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A407" s="35">
+      <c r="A407" s="30">
         <v>406</v>
       </c>
-      <c r="B407" s="36">
+      <c r="B407" s="35">
         <v>46181</v>
       </c>
-      <c r="C407" s="37">
+      <c r="C407" s="36">
         <v>0.62291666666666667</v>
       </c>
-      <c r="D407" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E407" s="38" t="s">
+      <c r="D407" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E407" s="37" t="s">
         <v>80</v>
       </c>
-      <c r="F407" s="38" t="s">
+      <c r="F407" s="37" t="s">
         <v>1080</v>
       </c>
-      <c r="G407" s="38" t="s">
+      <c r="G407" s="37" t="s">
         <v>754</v>
       </c>
-      <c r="H407" s="38" t="s">
+      <c r="H407" s="37" t="s">
         <v>1081</v>
       </c>
-      <c r="I407" s="38" t="s">
+      <c r="I407" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="J407" s="38" t="s">
+      <c r="J407" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K407" s="38" t="s">
+      <c r="K407" s="37" t="s">
         <v>945</v>
       </c>
-      <c r="L407" s="39"/>
-      <c r="M407" s="38"/>
+      <c r="L407" s="38"/>
+      <c r="M407" s="37"/>
     </row>
     <row r="408" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A408" s="35">
+      <c r="A408" s="22">
         <v>407</v>
       </c>
-      <c r="B408" s="36">
+      <c r="B408" s="35">
         <v>46181</v>
       </c>
-      <c r="C408" s="37">
+      <c r="C408" s="36">
         <v>0.31388888888888888</v>
       </c>
-      <c r="D408" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E408" s="38" t="s">
+      <c r="D408" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E408" s="37" t="s">
         <v>984</v>
       </c>
-      <c r="F408" s="38" t="s">
+      <c r="F408" s="37" t="s">
         <v>1082</v>
       </c>
-      <c r="G408" s="38" t="s">
+      <c r="G408" s="37" t="s">
         <v>317</v>
       </c>
-      <c r="H408" s="38" t="s">
+      <c r="H408" s="37" t="s">
         <v>1083</v>
       </c>
-      <c r="I408" s="38" t="s">
+      <c r="I408" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="J408" s="38" t="s">
+      <c r="J408" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K408" s="38" t="s">
+      <c r="K408" s="37" t="s">
         <v>945</v>
       </c>
-      <c r="L408" s="39"/>
-      <c r="M408" s="38"/>
+      <c r="L408" s="38"/>
+      <c r="M408" s="37"/>
     </row>
     <row r="409" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A409" s="48">
+      <c r="A409" s="39">
         <v>408</v>
       </c>
-      <c r="B409" s="45">
+      <c r="B409" s="44">
         <v>46181</v>
       </c>
-      <c r="C409" s="46">
+      <c r="C409" s="45">
         <v>0.31805555555555554</v>
       </c>
-      <c r="D409" s="44" t="s">
-        <v>15</v>
-      </c>
-      <c r="E409" s="44" t="s">
+      <c r="D409" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E409" s="43" t="s">
         <v>50</v>
       </c>
-      <c r="F409" s="44" t="s">
+      <c r="F409" s="43" t="s">
         <v>1084</v>
       </c>
-      <c r="G409" s="44" t="s">
+      <c r="G409" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="H409" s="44" t="s">
+      <c r="H409" s="43" t="s">
         <v>1085</v>
       </c>
-      <c r="I409" s="44" t="s">
+      <c r="I409" s="43" t="s">
         <v>64</v>
       </c>
-      <c r="J409" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="K409" s="44" t="s">
+      <c r="J409" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="K409" s="43" t="s">
         <v>1086</v>
       </c>
-      <c r="L409" s="47">
+      <c r="L409" s="46">
         <v>46181</v>
       </c>
-      <c r="M409" s="44"/>
+      <c r="M409" s="43"/>
     </row>
     <row r="410" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A410" s="48">
+      <c r="A410" s="30">
         <v>409</v>
       </c>
-      <c r="B410" s="45">
+      <c r="B410" s="44">
         <v>46181</v>
       </c>
-      <c r="C410" s="46">
+      <c r="C410" s="45">
         <v>0.3576388888888889</v>
       </c>
-      <c r="D410" s="44" t="s">
-        <v>15</v>
-      </c>
-      <c r="E410" s="44" t="s">
+      <c r="D410" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E410" s="43" t="s">
         <v>71</v>
       </c>
-      <c r="F410" s="44" t="s">
+      <c r="F410" s="43" t="s">
         <v>1087</v>
       </c>
-      <c r="G410" s="44" t="s">
+      <c r="G410" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="H410" s="44" t="s">
+      <c r="H410" s="43" t="s">
         <v>1088</v>
       </c>
-      <c r="I410" s="44" t="s">
+      <c r="I410" s="43" t="s">
         <v>64</v>
       </c>
-      <c r="J410" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="K410" s="44" t="s">
+      <c r="J410" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="K410" s="43" t="s">
         <v>1086</v>
       </c>
-      <c r="L410" s="47">
+      <c r="L410" s="46">
         <v>46181</v>
       </c>
-      <c r="M410" s="44"/>
+      <c r="M410" s="43"/>
     </row>
     <row r="411" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A411" s="48">
+      <c r="A411" s="22">
         <v>410</v>
       </c>
-      <c r="B411" s="45">
+      <c r="B411" s="44">
         <v>46181</v>
       </c>
-      <c r="C411" s="46">
+      <c r="C411" s="45">
         <v>0.43611111111111112</v>
       </c>
-      <c r="D411" s="44" t="s">
-        <v>15</v>
-      </c>
-      <c r="E411" s="44" t="s">
+      <c r="D411" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E411" s="43" t="s">
         <v>278</v>
       </c>
-      <c r="F411" s="44" t="s">
+      <c r="F411" s="43" t="s">
         <v>1089</v>
       </c>
-      <c r="G411" s="44" t="s">
+      <c r="G411" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="H411" s="44" t="s">
+      <c r="H411" s="43" t="s">
         <v>1090</v>
       </c>
-      <c r="I411" s="44" t="s">
+      <c r="I411" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="J411" s="44" t="s">
+      <c r="J411" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="K411" s="44" t="s">
+      <c r="K411" s="43" t="s">
         <v>945</v>
       </c>
-      <c r="L411" s="48"/>
-      <c r="M411" s="44"/>
+      <c r="L411" s="47"/>
+      <c r="M411" s="43"/>
     </row>
     <row r="412" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A412" s="48">
+      <c r="A412" s="39">
         <v>411</v>
       </c>
-      <c r="B412" s="45">
+      <c r="B412" s="44">
         <v>46181</v>
       </c>
-      <c r="C412" s="46">
+      <c r="C412" s="45">
         <v>0.44027777777777777</v>
       </c>
-      <c r="D412" s="44" t="s">
-        <v>15</v>
-      </c>
-      <c r="E412" s="44" t="s">
+      <c r="D412" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E412" s="43" t="s">
         <v>984</v>
       </c>
-      <c r="F412" s="44" t="s">
+      <c r="F412" s="43" t="s">
         <v>985</v>
       </c>
-      <c r="G412" s="44" t="s">
+      <c r="G412" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="H412" s="44" t="s">
+      <c r="H412" s="43" t="s">
         <v>1091</v>
       </c>
-      <c r="I412" s="44" t="s">
+      <c r="I412" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="J412" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="K412" s="44" t="s">
+      <c r="J412" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="K412" s="43" t="s">
         <v>1092</v>
       </c>
-      <c r="L412" s="47">
+      <c r="L412" s="46">
         <v>46181</v>
       </c>
-      <c r="M412" s="44"/>
+      <c r="M412" s="43"/>
     </row>
     <row r="413" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A413" s="35">
+      <c r="A413" s="30">
         <v>412</v>
       </c>
-      <c r="B413" s="36">
+      <c r="B413" s="35">
         <v>46181</v>
       </c>
-      <c r="C413" s="37">
+      <c r="C413" s="36">
         <v>0.4465277777777778</v>
       </c>
-      <c r="D413" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E413" s="38" t="s">
+      <c r="D413" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E413" s="37" t="s">
         <v>215</v>
       </c>
-      <c r="F413" s="38" t="s">
+      <c r="F413" s="37" t="s">
         <v>1087</v>
       </c>
-      <c r="G413" s="38" t="s">
+      <c r="G413" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="H413" s="38" t="s">
+      <c r="H413" s="37" t="s">
         <v>1093</v>
       </c>
-      <c r="I413" s="38" t="s">
+      <c r="I413" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="J413" s="38" t="s">
+      <c r="J413" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K413" s="38" t="s">
+      <c r="K413" s="37" t="s">
         <v>945</v>
       </c>
-      <c r="L413" s="39"/>
-      <c r="M413" s="38"/>
+      <c r="L413" s="38"/>
+      <c r="M413" s="37"/>
     </row>
     <row r="414" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A414" s="35">
+      <c r="A414" s="22">
         <v>413</v>
       </c>
-      <c r="B414" s="36">
+      <c r="B414" s="35">
         <v>46181</v>
       </c>
-      <c r="C414" s="37">
+      <c r="C414" s="36">
         <v>0.49930555555555556</v>
       </c>
-      <c r="D414" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E414" s="38" t="s">
+      <c r="D414" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E414" s="37" t="s">
         <v>71</v>
       </c>
-      <c r="F414" s="38" t="s">
+      <c r="F414" s="37" t="s">
         <v>979</v>
       </c>
-      <c r="G414" s="38" t="s">
+      <c r="G414" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="H414" s="38" t="s">
+      <c r="H414" s="37" t="s">
         <v>1094</v>
       </c>
-      <c r="I414" s="38" t="s">
+      <c r="I414" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="J414" s="38" t="s">
+      <c r="J414" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K414" s="38" t="s">
+      <c r="K414" s="37" t="s">
         <v>945</v>
       </c>
-      <c r="L414" s="39"/>
-      <c r="M414" s="38"/>
+      <c r="L414" s="38"/>
+      <c r="M414" s="37"/>
     </row>
     <row r="415" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A415" s="35">
+      <c r="A415" s="39">
         <v>414</v>
       </c>
-      <c r="B415" s="36">
+      <c r="B415" s="35">
         <v>46181</v>
       </c>
-      <c r="C415" s="37">
+      <c r="C415" s="36">
         <v>0.29166666666666669</v>
       </c>
-      <c r="D415" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E415" s="38" t="s">
+      <c r="D415" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E415" s="37" t="s">
         <v>215</v>
       </c>
-      <c r="F415" s="38" t="s">
+      <c r="F415" s="37" t="s">
         <v>1095</v>
       </c>
-      <c r="G415" s="38" t="s">
+      <c r="G415" s="37" t="s">
         <v>754</v>
       </c>
-      <c r="H415" s="38" t="s">
+      <c r="H415" s="37" t="s">
         <v>1096</v>
       </c>
-      <c r="I415" s="38" t="s">
+      <c r="I415" s="37" t="s">
         <v>945</v>
       </c>
-      <c r="J415" s="38" t="s">
+      <c r="J415" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K415" s="38"/>
-      <c r="L415" s="39"/>
-      <c r="M415" s="38"/>
+      <c r="K415" s="37"/>
+      <c r="L415" s="38"/>
+      <c r="M415" s="37"/>
     </row>
     <row r="416" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A416" s="48">
+      <c r="A416" s="30">
         <v>415</v>
       </c>
-      <c r="B416" s="45">
+      <c r="B416" s="44">
         <v>46181</v>
       </c>
-      <c r="C416" s="46">
+      <c r="C416" s="45">
         <v>0.42499999999999999</v>
       </c>
-      <c r="D416" s="44" t="s">
-        <v>15</v>
-      </c>
-      <c r="E416" s="44" t="s">
+      <c r="D416" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E416" s="43" t="s">
         <v>80</v>
       </c>
-      <c r="F416" s="44" t="s">
+      <c r="F416" s="43" t="s">
         <v>1097</v>
       </c>
-      <c r="G416" s="44" t="s">
+      <c r="G416" s="43" t="s">
         <v>754</v>
       </c>
-      <c r="H416" s="44" t="s">
+      <c r="H416" s="43" t="s">
         <v>1098</v>
       </c>
-      <c r="I416" s="44" t="s">
+      <c r="I416" s="43" t="s">
         <v>1003</v>
       </c>
-      <c r="J416" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="K416" s="44"/>
-      <c r="L416" s="47">
+      <c r="J416" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="K416" s="43"/>
+      <c r="L416" s="46">
         <v>46181</v>
       </c>
-      <c r="M416" s="44"/>
+      <c r="M416" s="43"/>
     </row>
     <row r="417" spans="1:13" ht="45" x14ac:dyDescent="0.25">
-      <c r="A417" s="48">
+      <c r="A417" s="22">
         <v>416</v>
       </c>
-      <c r="B417" s="45">
+      <c r="B417" s="44">
         <v>46181</v>
       </c>
-      <c r="C417" s="46">
+      <c r="C417" s="45">
         <v>0.42638888888888887</v>
       </c>
-      <c r="D417" s="44" t="s">
-        <v>15</v>
-      </c>
-      <c r="E417" s="44" t="s">
+      <c r="D417" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E417" s="43" t="s">
         <v>215</v>
       </c>
-      <c r="F417" s="44" t="s">
+      <c r="F417" s="43" t="s">
         <v>1099</v>
       </c>
-      <c r="G417" s="44" t="s">
+      <c r="G417" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="H417" s="44" t="s">
+      <c r="H417" s="43" t="s">
         <v>1100</v>
       </c>
-      <c r="I417" s="44" t="s">
+      <c r="I417" s="43" t="s">
         <v>1101</v>
       </c>
-      <c r="J417" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="K417" s="44"/>
-      <c r="L417" s="47">
+      <c r="J417" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="K417" s="43"/>
+      <c r="L417" s="46">
         <v>46181</v>
       </c>
-      <c r="M417" s="44"/>
+      <c r="M417" s="43"/>
     </row>
     <row r="418" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A418" s="48">
+      <c r="A418" s="39">
         <v>417</v>
       </c>
-      <c r="B418" s="45">
+      <c r="B418" s="44">
         <v>46181</v>
       </c>
-      <c r="C418" s="46">
+      <c r="C418" s="45">
         <v>0.4465277777777778</v>
       </c>
-      <c r="D418" s="44" t="s">
-        <v>15</v>
-      </c>
-      <c r="E418" s="44" t="s">
+      <c r="D418" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E418" s="43" t="s">
         <v>215</v>
       </c>
-      <c r="F418" s="44" t="s">
+      <c r="F418" s="43" t="s">
         <v>1102</v>
       </c>
-      <c r="G418" s="44" t="s">
+      <c r="G418" s="43" t="s">
         <v>317</v>
       </c>
-      <c r="H418" s="44" t="s">
+      <c r="H418" s="43" t="s">
         <v>1103</v>
       </c>
-      <c r="I418" s="44" t="s">
+      <c r="I418" s="43" t="s">
         <v>1104</v>
       </c>
-      <c r="J418" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="K418" s="44"/>
-      <c r="L418" s="47">
+      <c r="J418" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="K418" s="43"/>
+      <c r="L418" s="46">
         <v>46181</v>
       </c>
-      <c r="M418" s="44"/>
+      <c r="M418" s="43"/>
     </row>
     <row r="419" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A419" s="48">
+      <c r="A419" s="30">
         <v>418</v>
       </c>
-      <c r="B419" s="45">
+      <c r="B419" s="44">
         <v>46181</v>
       </c>
-      <c r="C419" s="46">
+      <c r="C419" s="45">
         <v>0.45555555555555555</v>
       </c>
-      <c r="D419" s="44" t="s">
-        <v>15</v>
-      </c>
-      <c r="E419" s="44" t="s">
+      <c r="D419" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E419" s="43" t="s">
         <v>80</v>
       </c>
-      <c r="F419" s="44" t="s">
+      <c r="F419" s="43" t="s">
         <v>1105</v>
       </c>
-      <c r="G419" s="44" t="s">
+      <c r="G419" s="43" t="s">
         <v>317</v>
       </c>
-      <c r="H419" s="44" t="s">
+      <c r="H419" s="43" t="s">
         <v>1106</v>
       </c>
-      <c r="I419" s="44" t="s">
+      <c r="I419" s="43" t="s">
         <v>1104</v>
       </c>
-      <c r="J419" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="K419" s="44"/>
-      <c r="L419" s="48"/>
-      <c r="M419" s="44"/>
+      <c r="J419" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="K419" s="43"/>
+      <c r="L419" s="47"/>
+      <c r="M419" s="43"/>
     </row>
     <row r="420" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A420" s="35">
+      <c r="A420" s="22">
         <v>419</v>
       </c>
-      <c r="B420" s="36">
+      <c r="B420" s="35">
         <v>46181</v>
       </c>
-      <c r="C420" s="37">
+      <c r="C420" s="36">
         <v>0.46388888888888891</v>
       </c>
-      <c r="D420" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E420" s="38" t="s">
+      <c r="D420" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E420" s="37" t="s">
         <v>80</v>
       </c>
-      <c r="F420" s="38" t="s">
+      <c r="F420" s="37" t="s">
         <v>1107</v>
       </c>
-      <c r="G420" s="38" t="s">
+      <c r="G420" s="37" t="s">
         <v>317</v>
       </c>
-      <c r="H420" s="38" t="s">
+      <c r="H420" s="37" t="s">
         <v>1108</v>
       </c>
-      <c r="I420" s="38" t="s">
+      <c r="I420" s="37" t="s">
         <v>945</v>
       </c>
-      <c r="J420" s="38" t="s">
+      <c r="J420" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K420" s="38"/>
-      <c r="L420" s="39"/>
-      <c r="M420" s="38"/>
+      <c r="K420" s="37"/>
+      <c r="L420" s="38"/>
+      <c r="M420" s="37"/>
     </row>
     <row r="421" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A421" s="35">
+      <c r="A421" s="39">
         <v>420</v>
       </c>
-      <c r="B421" s="36">
+      <c r="B421" s="35">
         <v>46181</v>
       </c>
-      <c r="C421" s="37">
+      <c r="C421" s="36">
         <v>0.50486111111111109</v>
       </c>
-      <c r="D421" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E421" s="38" t="s">
+      <c r="D421" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E421" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="F421" s="38" t="s">
+      <c r="F421" s="37" t="s">
         <v>1109</v>
       </c>
-      <c r="G421" s="38" t="s">
+      <c r="G421" s="37" t="s">
         <v>754</v>
       </c>
-      <c r="H421" s="38" t="s">
+      <c r="H421" s="37" t="s">
         <v>1110</v>
       </c>
-      <c r="I421" s="38" t="s">
+      <c r="I421" s="37" t="s">
         <v>945</v>
       </c>
-      <c r="J421" s="38" t="s">
+      <c r="J421" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K421" s="38"/>
-      <c r="L421" s="39"/>
-      <c r="M421" s="38"/>
+      <c r="K421" s="37"/>
+      <c r="L421" s="38"/>
+      <c r="M421" s="37"/>
     </row>
     <row r="422" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A422" s="25">
-        <v>324</v>
+      <c r="A422" s="30">
+        <v>421</v>
       </c>
       <c r="B422" s="22" t="s">
         <v>747</v>
@@ -21036,11 +21472,11 @@
       <c r="L422" s="22" t="s">
         <v>747</v>
       </c>
-      <c r="M422" s="1"/>
+      <c r="M422" s="43"/>
     </row>
     <row r="423" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A423" s="25">
-        <v>325</v>
+      <c r="A423" s="22">
+        <v>422</v>
       </c>
       <c r="B423" s="22" t="s">
         <v>747</v>
@@ -21075,11 +21511,11 @@
       <c r="L423" s="22" t="s">
         <v>747</v>
       </c>
-      <c r="M423" s="1"/>
+      <c r="M423" s="43"/>
     </row>
     <row r="424" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A424" s="25">
-        <v>392</v>
+      <c r="A424" s="39">
+        <v>423</v>
       </c>
       <c r="B424" s="22" t="s">
         <v>905</v>
@@ -21114,46 +21550,46 @@
       <c r="L424" s="21">
         <v>46177</v>
       </c>
-      <c r="M424" s="1"/>
+      <c r="M424" s="43"/>
     </row>
     <row r="425" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A425" s="35">
-        <v>406</v>
-      </c>
-      <c r="B425" s="36" t="s">
+      <c r="A425" s="30">
+        <v>424</v>
+      </c>
+      <c r="B425" s="35" t="s">
         <v>909</v>
       </c>
-      <c r="C425" s="37" t="s">
+      <c r="C425" s="36" t="s">
         <v>910</v>
       </c>
-      <c r="D425" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E425" s="38" t="s">
+      <c r="D425" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E425" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="F425" s="38" t="s">
+      <c r="F425" s="37" t="s">
         <v>890</v>
       </c>
-      <c r="G425" s="38" t="s">
+      <c r="G425" s="37" t="s">
         <v>754</v>
       </c>
-      <c r="H425" s="38" t="s">
+      <c r="H425" s="37" t="s">
         <v>911</v>
       </c>
-      <c r="I425" s="38" t="s">
+      <c r="I425" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="J425" s="38" t="s">
+      <c r="J425" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K425" s="38"/>
-      <c r="L425" s="39"/>
-      <c r="M425" s="38"/>
+      <c r="K425" s="37"/>
+      <c r="L425" s="38"/>
+      <c r="M425" s="43"/>
     </row>
     <row r="426" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A426" s="25">
-        <v>412</v>
+      <c r="A426" s="22">
+        <v>425</v>
       </c>
       <c r="B426" s="22" t="s">
         <v>905</v>
@@ -21188,229 +21624,3345 @@
       <c r="L426" s="21">
         <v>46177</v>
       </c>
-      <c r="M426" s="1"/>
+      <c r="M426" s="43"/>
+    </row>
+    <row r="427" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A427" s="39">
+        <v>426</v>
+      </c>
+      <c r="B427" s="48">
+        <v>46182</v>
+      </c>
+      <c r="C427" s="19">
+        <v>0.3034722222222222</v>
+      </c>
+      <c r="D427" t="s">
+        <v>15</v>
+      </c>
+      <c r="E427" t="s">
+        <v>232</v>
+      </c>
+      <c r="F427" t="s">
+        <v>320</v>
+      </c>
+      <c r="G427" t="s">
+        <v>1111</v>
+      </c>
+      <c r="H427" t="s">
+        <v>1112</v>
+      </c>
+      <c r="I427" t="s">
+        <v>39</v>
+      </c>
+      <c r="J427" t="s">
+        <v>65</v>
+      </c>
+      <c r="K427" t="s">
+        <v>945</v>
+      </c>
+      <c r="M427" s="43"/>
+    </row>
+    <row r="428" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A428" s="30">
+        <v>427</v>
+      </c>
+      <c r="B428" s="48">
+        <v>46182</v>
+      </c>
+      <c r="C428" s="19">
+        <v>0.30694444444444446</v>
+      </c>
+      <c r="D428" t="s">
+        <v>15</v>
+      </c>
+      <c r="E428" t="s">
+        <v>80</v>
+      </c>
+      <c r="F428" t="s">
+        <v>1113</v>
+      </c>
+      <c r="G428" t="s">
+        <v>1114</v>
+      </c>
+      <c r="H428" t="s">
+        <v>1115</v>
+      </c>
+      <c r="I428" t="s">
+        <v>39</v>
+      </c>
+      <c r="J428" t="s">
+        <v>21</v>
+      </c>
+      <c r="K428" t="s">
+        <v>1116</v>
+      </c>
+      <c r="L428" s="49">
+        <v>46182</v>
+      </c>
+      <c r="M428" s="43"/>
+    </row>
+    <row r="429" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A429" s="22">
+        <v>428</v>
+      </c>
+      <c r="B429" s="48">
+        <v>46182</v>
+      </c>
+      <c r="C429" s="19">
+        <v>0.30902777777777779</v>
+      </c>
+      <c r="D429" t="s">
+        <v>15</v>
+      </c>
+      <c r="E429" t="s">
+        <v>71</v>
+      </c>
+      <c r="F429" t="s">
+        <v>328</v>
+      </c>
+      <c r="G429" t="s">
+        <v>1117</v>
+      </c>
+      <c r="H429" t="s">
+        <v>1118</v>
+      </c>
+      <c r="I429" t="s">
+        <v>39</v>
+      </c>
+      <c r="J429" t="s">
+        <v>65</v>
+      </c>
+      <c r="K429" t="s">
+        <v>945</v>
+      </c>
+      <c r="M429" s="43"/>
+    </row>
+    <row r="430" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A430" s="39">
+        <v>429</v>
+      </c>
+      <c r="B430" s="48">
+        <v>46182</v>
+      </c>
+      <c r="C430" s="19">
+        <v>0.31874999999999998</v>
+      </c>
+      <c r="D430" t="s">
+        <v>15</v>
+      </c>
+      <c r="E430" t="s">
+        <v>232</v>
+      </c>
+      <c r="F430" t="s">
+        <v>1119</v>
+      </c>
+      <c r="G430" t="s">
+        <v>1120</v>
+      </c>
+      <c r="H430" t="s">
+        <v>1121</v>
+      </c>
+      <c r="I430" t="s">
+        <v>64</v>
+      </c>
+      <c r="J430" t="s">
+        <v>65</v>
+      </c>
+      <c r="K430" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="431" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A431" s="30">
+        <v>430</v>
+      </c>
+      <c r="B431" s="48">
+        <v>46182</v>
+      </c>
+      <c r="C431" s="19">
+        <v>0.31805555555555554</v>
+      </c>
+      <c r="D431" t="s">
+        <v>15</v>
+      </c>
+      <c r="E431" t="s">
+        <v>71</v>
+      </c>
+      <c r="F431" t="s">
+        <v>328</v>
+      </c>
+      <c r="G431" t="s">
+        <v>1122</v>
+      </c>
+      <c r="H431" t="s">
+        <v>1123</v>
+      </c>
+      <c r="I431" t="s">
+        <v>20</v>
+      </c>
+      <c r="J431" t="s">
+        <v>21</v>
+      </c>
+      <c r="K431" t="s">
+        <v>1124</v>
+      </c>
+      <c r="L431" s="49">
+        <v>46183</v>
+      </c>
+    </row>
+    <row r="432" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A432" s="22">
+        <v>431</v>
+      </c>
+      <c r="B432" s="48">
+        <v>46182</v>
+      </c>
+      <c r="C432" s="19">
+        <v>0.33750000000000002</v>
+      </c>
+      <c r="D432" t="s">
+        <v>15</v>
+      </c>
+      <c r="E432" t="s">
+        <v>232</v>
+      </c>
+      <c r="F432" t="s">
+        <v>1125</v>
+      </c>
+      <c r="G432" t="s">
+        <v>1126</v>
+      </c>
+      <c r="H432" t="s">
+        <v>1127</v>
+      </c>
+      <c r="I432" t="s">
+        <v>64</v>
+      </c>
+      <c r="J432" t="s">
+        <v>65</v>
+      </c>
+      <c r="K432" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="433" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A433" s="39">
+        <v>432</v>
+      </c>
+      <c r="B433" s="48">
+        <v>46182</v>
+      </c>
+      <c r="C433" s="19">
+        <v>0.34305555555555556</v>
+      </c>
+      <c r="D433" t="s">
+        <v>15</v>
+      </c>
+      <c r="E433" t="s">
+        <v>232</v>
+      </c>
+      <c r="F433" t="s">
+        <v>1128</v>
+      </c>
+      <c r="G433" t="s">
+        <v>1120</v>
+      </c>
+      <c r="H433" t="s">
+        <v>1121</v>
+      </c>
+      <c r="I433" t="s">
+        <v>64</v>
+      </c>
+      <c r="J433" t="s">
+        <v>65</v>
+      </c>
+      <c r="K433" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="434" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A434" s="30">
+        <v>433</v>
+      </c>
+      <c r="B434" s="48">
+        <v>46182</v>
+      </c>
+      <c r="C434" s="19">
+        <v>0.35486111111111113</v>
+      </c>
+      <c r="D434" t="s">
+        <v>15</v>
+      </c>
+      <c r="E434" t="s">
+        <v>71</v>
+      </c>
+      <c r="F434" t="s">
+        <v>328</v>
+      </c>
+      <c r="G434" t="s">
+        <v>1126</v>
+      </c>
+      <c r="H434" t="s">
+        <v>1129</v>
+      </c>
+      <c r="I434" t="s">
+        <v>20</v>
+      </c>
+      <c r="J434" t="s">
+        <v>65</v>
+      </c>
+      <c r="K434" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="435" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A435" s="22">
+        <v>434</v>
+      </c>
+      <c r="B435" s="48">
+        <v>46182</v>
+      </c>
+      <c r="C435" s="19">
+        <v>0.36944444444444446</v>
+      </c>
+      <c r="D435" t="s">
+        <v>15</v>
+      </c>
+      <c r="E435" t="s">
+        <v>16</v>
+      </c>
+      <c r="F435" t="s">
+        <v>129</v>
+      </c>
+      <c r="G435" t="s">
+        <v>783</v>
+      </c>
+      <c r="H435" t="s">
+        <v>1130</v>
+      </c>
+      <c r="I435" t="s">
+        <v>64</v>
+      </c>
+      <c r="J435" t="s">
+        <v>21</v>
+      </c>
+      <c r="K435" t="s">
+        <v>1124</v>
+      </c>
+      <c r="L435" s="49">
+        <v>46183</v>
+      </c>
+    </row>
+    <row r="436" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A436" s="39">
+        <v>435</v>
+      </c>
+      <c r="B436" s="48">
+        <v>46182</v>
+      </c>
+      <c r="C436" s="19">
+        <v>0.38194444444444442</v>
+      </c>
+      <c r="D436" t="s">
+        <v>15</v>
+      </c>
+      <c r="E436" t="s">
+        <v>43</v>
+      </c>
+      <c r="F436" t="s">
+        <v>1131</v>
+      </c>
+      <c r="G436" t="s">
+        <v>780</v>
+      </c>
+      <c r="H436" t="s">
+        <v>1132</v>
+      </c>
+      <c r="I436" t="s">
+        <v>39</v>
+      </c>
+      <c r="J436" t="s">
+        <v>65</v>
+      </c>
+      <c r="K436" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="437" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A437" s="30">
+        <v>436</v>
+      </c>
+      <c r="B437" s="48">
+        <v>46182</v>
+      </c>
+      <c r="C437" s="19">
+        <v>0.44236111111111109</v>
+      </c>
+      <c r="D437" t="s">
+        <v>15</v>
+      </c>
+      <c r="E437" t="s">
+        <v>16</v>
+      </c>
+      <c r="F437" t="s">
+        <v>1133</v>
+      </c>
+      <c r="G437" t="s">
+        <v>1134</v>
+      </c>
+      <c r="H437" t="s">
+        <v>1135</v>
+      </c>
+      <c r="I437" t="s">
+        <v>20</v>
+      </c>
+      <c r="J437" t="s">
+        <v>21</v>
+      </c>
+      <c r="K437" t="s">
+        <v>1116</v>
+      </c>
+      <c r="L437" s="49">
+        <v>46183</v>
+      </c>
+    </row>
+    <row r="438" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A438" s="22">
+        <v>437</v>
+      </c>
+      <c r="B438" s="48">
+        <v>46182</v>
+      </c>
+      <c r="C438" s="19">
+        <v>0.53888888888888886</v>
+      </c>
+      <c r="D438" t="s">
+        <v>15</v>
+      </c>
+      <c r="E438" t="s">
+        <v>80</v>
+      </c>
+      <c r="F438" t="s">
+        <v>1136</v>
+      </c>
+      <c r="G438" t="s">
+        <v>1117</v>
+      </c>
+      <c r="H438" t="s">
+        <v>1137</v>
+      </c>
+      <c r="I438" t="s">
+        <v>20</v>
+      </c>
+      <c r="J438" t="s">
+        <v>65</v>
+      </c>
+      <c r="K438" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="439" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A439" s="39">
+        <v>438</v>
+      </c>
+      <c r="B439" s="48">
+        <v>46182</v>
+      </c>
+      <c r="C439" s="19">
+        <v>0.54236111111111107</v>
+      </c>
+      <c r="D439" t="s">
+        <v>15</v>
+      </c>
+      <c r="E439" t="s">
+        <v>71</v>
+      </c>
+      <c r="F439" t="s">
+        <v>441</v>
+      </c>
+      <c r="G439" t="s">
+        <v>1138</v>
+      </c>
+      <c r="H439" t="s">
+        <v>1139</v>
+      </c>
+      <c r="I439" t="s">
+        <v>64</v>
+      </c>
+      <c r="J439" t="s">
+        <v>65</v>
+      </c>
+      <c r="K439" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="440" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A440" s="30">
+        <v>439</v>
+      </c>
+      <c r="B440" s="48">
+        <v>46182</v>
+      </c>
+      <c r="C440" s="19">
+        <v>0.57222222222222219</v>
+      </c>
+      <c r="D440" t="s">
+        <v>15</v>
+      </c>
+      <c r="E440" t="s">
+        <v>89</v>
+      </c>
+      <c r="F440" t="s">
+        <v>1140</v>
+      </c>
+      <c r="G440" t="s">
+        <v>1117</v>
+      </c>
+      <c r="H440" t="s">
+        <v>960</v>
+      </c>
+      <c r="I440" t="s">
+        <v>20</v>
+      </c>
+      <c r="J440" t="s">
+        <v>65</v>
+      </c>
+      <c r="K440" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="441" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A441" s="22">
+        <v>440</v>
+      </c>
+      <c r="B441" s="48">
+        <v>46182</v>
+      </c>
+      <c r="C441" s="19">
+        <v>0.59513888888888888</v>
+      </c>
+      <c r="D441" t="s">
+        <v>15</v>
+      </c>
+      <c r="E441" t="s">
+        <v>89</v>
+      </c>
+      <c r="F441" t="s">
+        <v>129</v>
+      </c>
+      <c r="G441" t="s">
+        <v>780</v>
+      </c>
+      <c r="H441" t="s">
+        <v>1141</v>
+      </c>
+      <c r="I441" t="s">
+        <v>39</v>
+      </c>
+      <c r="J441" t="s">
+        <v>65</v>
+      </c>
+      <c r="K441" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="442" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A442" s="39">
+        <v>441</v>
+      </c>
+      <c r="B442" s="48">
+        <v>46182</v>
+      </c>
+      <c r="C442" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D442" t="s">
+        <v>80</v>
+      </c>
+      <c r="E442" t="s">
+        <v>415</v>
+      </c>
+      <c r="F442" t="s">
+        <v>129</v>
+      </c>
+      <c r="G442" t="s">
+        <v>1142</v>
+      </c>
+      <c r="I442" t="s">
+        <v>39</v>
+      </c>
+      <c r="J442" t="s">
+        <v>21</v>
+      </c>
+      <c r="K442" t="s">
+        <v>1143</v>
+      </c>
+      <c r="L442" s="49">
+        <v>46182</v>
+      </c>
+    </row>
+    <row r="443" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A443" s="30">
+        <v>442</v>
+      </c>
+      <c r="B443" s="48">
+        <v>46182</v>
+      </c>
+      <c r="C443" s="19" t="s">
+        <v>1144</v>
+      </c>
+      <c r="D443" t="s">
+        <v>1145</v>
+      </c>
+      <c r="E443" t="s">
+        <v>1146</v>
+      </c>
+      <c r="F443" t="s">
+        <v>1147</v>
+      </c>
+      <c r="G443" t="s">
+        <v>1148</v>
+      </c>
+      <c r="I443" t="s">
+        <v>39</v>
+      </c>
+      <c r="J443" t="s">
+        <v>65</v>
+      </c>
+      <c r="K443" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="444" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A444" s="22">
+        <v>443</v>
+      </c>
+      <c r="B444" s="48">
+        <v>46182</v>
+      </c>
+      <c r="C444" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D444" t="s">
+        <v>80</v>
+      </c>
+      <c r="E444" t="s">
+        <v>1149</v>
+      </c>
+      <c r="F444" t="s">
+        <v>1150</v>
+      </c>
+      <c r="G444" t="s">
+        <v>1151</v>
+      </c>
+      <c r="I444" t="s">
+        <v>39</v>
+      </c>
+      <c r="J444" t="s">
+        <v>21</v>
+      </c>
+      <c r="K444" t="s">
+        <v>1124</v>
+      </c>
+      <c r="L444" s="49">
+        <v>46182</v>
+      </c>
+    </row>
+    <row r="445" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A445" s="39">
+        <v>444</v>
+      </c>
+      <c r="B445" s="48">
+        <v>46182</v>
+      </c>
+      <c r="C445" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D445" t="s">
+        <v>945</v>
+      </c>
+      <c r="E445" t="s">
+        <v>1152</v>
+      </c>
+      <c r="F445" t="s">
+        <v>1152</v>
+      </c>
+      <c r="G445" t="s">
+        <v>1153</v>
+      </c>
+      <c r="I445" t="s">
+        <v>64</v>
+      </c>
+      <c r="J445" t="s">
+        <v>21</v>
+      </c>
+      <c r="K445" t="s">
+        <v>1124</v>
+      </c>
+      <c r="L445" s="49">
+        <v>46182</v>
+      </c>
+    </row>
+    <row r="446" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A446" s="30">
+        <v>445</v>
+      </c>
+      <c r="B446" s="48">
+        <v>46182</v>
+      </c>
+      <c r="C446" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D446" t="s">
+        <v>232</v>
+      </c>
+      <c r="E446" t="s">
+        <v>1149</v>
+      </c>
+      <c r="F446" t="s">
+        <v>1150</v>
+      </c>
+      <c r="G446" t="s">
+        <v>1154</v>
+      </c>
+      <c r="I446" t="s">
+        <v>20</v>
+      </c>
+      <c r="J446" t="s">
+        <v>21</v>
+      </c>
+      <c r="K446" t="s">
+        <v>1155</v>
+      </c>
+      <c r="L446" s="49">
+        <v>46182</v>
+      </c>
+    </row>
+    <row r="447" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A447" s="22">
+        <v>446</v>
+      </c>
+      <c r="B447" s="48">
+        <v>46182</v>
+      </c>
+      <c r="C447" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D447" t="s">
+        <v>16</v>
+      </c>
+      <c r="E447" t="s">
+        <v>1156</v>
+      </c>
+      <c r="F447" t="s">
+        <v>1157</v>
+      </c>
+      <c r="G447" t="s">
+        <v>1158</v>
+      </c>
+      <c r="I447" t="s">
+        <v>64</v>
+      </c>
+      <c r="J447" t="s">
+        <v>21</v>
+      </c>
+      <c r="K447" t="s">
+        <v>1155</v>
+      </c>
+      <c r="L447" s="49">
+        <v>46182</v>
+      </c>
+    </row>
+    <row r="448" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A448" s="39">
+        <v>447</v>
+      </c>
+      <c r="B448" s="48">
+        <v>46182</v>
+      </c>
+      <c r="C448" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D448" t="s">
+        <v>50</v>
+      </c>
+      <c r="E448" t="s">
+        <v>1159</v>
+      </c>
+      <c r="F448" t="s">
+        <v>1157</v>
+      </c>
+      <c r="G448" t="s">
+        <v>1160</v>
+      </c>
+      <c r="I448" t="s">
+        <v>64</v>
+      </c>
+      <c r="J448" t="s">
+        <v>21</v>
+      </c>
+      <c r="K448" t="s">
+        <v>1155</v>
+      </c>
+      <c r="L448" s="49">
+        <v>46182</v>
+      </c>
+    </row>
+    <row r="449" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A449" s="30">
+        <v>448</v>
+      </c>
+      <c r="B449" s="48">
+        <v>46182</v>
+      </c>
+      <c r="C449" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D449" t="s">
+        <v>945</v>
+      </c>
+      <c r="E449" t="s">
+        <v>1161</v>
+      </c>
+      <c r="F449" t="s">
+        <v>1161</v>
+      </c>
+      <c r="G449" t="s">
+        <v>1162</v>
+      </c>
+      <c r="I449" t="s">
+        <v>20</v>
+      </c>
+      <c r="J449" t="s">
+        <v>21</v>
+      </c>
+      <c r="K449" t="s">
+        <v>1155</v>
+      </c>
+      <c r="L449" s="49">
+        <v>46182</v>
+      </c>
+    </row>
+    <row r="450" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A450" s="22">
+        <v>449</v>
+      </c>
+      <c r="B450" s="48">
+        <v>46182</v>
+      </c>
+      <c r="C450" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D450" t="s">
+        <v>945</v>
+      </c>
+      <c r="E450" t="s">
+        <v>1163</v>
+      </c>
+      <c r="F450" t="s">
+        <v>1150</v>
+      </c>
+      <c r="G450" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I450" t="s">
+        <v>64</v>
+      </c>
+      <c r="J450" t="s">
+        <v>65</v>
+      </c>
+      <c r="K450" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="451" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A451" s="39">
+        <v>450</v>
+      </c>
+      <c r="B451" s="48">
+        <v>46182</v>
+      </c>
+      <c r="C451" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D451" t="s">
+        <v>945</v>
+      </c>
+      <c r="E451" t="s">
+        <v>1165</v>
+      </c>
+      <c r="F451" t="s">
+        <v>1150</v>
+      </c>
+      <c r="G451" t="s">
+        <v>1166</v>
+      </c>
+      <c r="I451" t="s">
+        <v>39</v>
+      </c>
+      <c r="J451" t="s">
+        <v>65</v>
+      </c>
+      <c r="K451" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="452" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A452" s="30">
+        <v>451</v>
+      </c>
+      <c r="B452" s="48">
+        <v>46182</v>
+      </c>
+      <c r="C452" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D452" t="s">
+        <v>16</v>
+      </c>
+      <c r="E452" t="s">
+        <v>1167</v>
+      </c>
+      <c r="F452" t="s">
+        <v>1150</v>
+      </c>
+      <c r="G452" t="s">
+        <v>1168</v>
+      </c>
+      <c r="I452" t="s">
+        <v>20</v>
+      </c>
+      <c r="J452" t="s">
+        <v>21</v>
+      </c>
+      <c r="K452" t="s">
+        <v>1155</v>
+      </c>
+      <c r="L452" s="49">
+        <v>46182</v>
+      </c>
+    </row>
+    <row r="453" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A453" s="22">
+        <v>452</v>
+      </c>
+      <c r="B453" s="48">
+        <v>46182</v>
+      </c>
+      <c r="C453" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D453" t="s">
+        <v>16</v>
+      </c>
+      <c r="E453" t="s">
+        <v>1133</v>
+      </c>
+      <c r="F453" t="s">
+        <v>1150</v>
+      </c>
+      <c r="G453" t="s">
+        <v>1169</v>
+      </c>
+      <c r="I453" t="s">
+        <v>20</v>
+      </c>
+      <c r="J453" t="s">
+        <v>65</v>
+      </c>
+      <c r="K453" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="454" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A454" s="39">
+        <v>453</v>
+      </c>
+      <c r="B454" s="48">
+        <v>46182</v>
+      </c>
+      <c r="C454" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D454" t="s">
+        <v>43</v>
+      </c>
+      <c r="E454" t="s">
+        <v>1170</v>
+      </c>
+      <c r="F454" t="s">
+        <v>1147</v>
+      </c>
+      <c r="G454" t="s">
+        <v>1171</v>
+      </c>
+      <c r="I454" t="s">
+        <v>64</v>
+      </c>
+      <c r="J454" t="s">
+        <v>65</v>
+      </c>
+      <c r="K454" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="455" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A455" s="30">
+        <v>454</v>
+      </c>
+      <c r="B455" s="48">
+        <v>46182</v>
+      </c>
+      <c r="C455" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D455" t="s">
+        <v>945</v>
+      </c>
+      <c r="E455" t="s">
+        <v>1172</v>
+      </c>
+      <c r="F455" t="s">
+        <v>1173</v>
+      </c>
+      <c r="G455" t="s">
+        <v>1174</v>
+      </c>
+      <c r="I455" t="s">
+        <v>20</v>
+      </c>
+      <c r="J455" t="s">
+        <v>21</v>
+      </c>
+      <c r="K455" t="s">
+        <v>1175</v>
+      </c>
+      <c r="L455" s="49">
+        <v>46183</v>
+      </c>
+    </row>
+    <row r="456" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A456" s="22">
+        <v>455</v>
+      </c>
+      <c r="B456" s="48">
+        <v>46182</v>
+      </c>
+      <c r="C456" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D456" t="s">
+        <v>43</v>
+      </c>
+      <c r="E456" t="s">
+        <v>1176</v>
+      </c>
+      <c r="F456" t="s">
+        <v>1173</v>
+      </c>
+      <c r="G456" t="s">
+        <v>1177</v>
+      </c>
+      <c r="I456" t="s">
+        <v>20</v>
+      </c>
+      <c r="J456" t="s">
+        <v>65</v>
+      </c>
+      <c r="K456" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="457" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A457" s="39">
+        <v>456</v>
+      </c>
+      <c r="B457" s="48">
+        <v>46182</v>
+      </c>
+      <c r="C457" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D457" t="s">
+        <v>43</v>
+      </c>
+      <c r="E457" t="s">
+        <v>1178</v>
+      </c>
+      <c r="F457" t="s">
+        <v>1173</v>
+      </c>
+      <c r="G457" t="s">
+        <v>1179</v>
+      </c>
+      <c r="I457" t="s">
+        <v>39</v>
+      </c>
+      <c r="J457" t="s">
+        <v>21</v>
+      </c>
+      <c r="K457" t="s">
+        <v>1175</v>
+      </c>
+      <c r="L457" s="49">
+        <v>46183</v>
+      </c>
+    </row>
+    <row r="458" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A458" s="30">
+        <v>457</v>
+      </c>
+      <c r="B458" s="48">
+        <v>46182</v>
+      </c>
+      <c r="C458" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D458" t="s">
+        <v>1180</v>
+      </c>
+      <c r="E458" t="s">
+        <v>1181</v>
+      </c>
+      <c r="F458" t="s">
+        <v>1173</v>
+      </c>
+      <c r="G458" t="s">
+        <v>1182</v>
+      </c>
+      <c r="I458" t="s">
+        <v>39</v>
+      </c>
+      <c r="J458" t="s">
+        <v>65</v>
+      </c>
+      <c r="K458" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="459" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A459" s="22">
+        <v>458</v>
+      </c>
+      <c r="B459" s="48">
+        <v>46182</v>
+      </c>
+      <c r="D459" t="s">
+        <v>16</v>
+      </c>
+      <c r="E459" t="s">
+        <v>1183</v>
+      </c>
+      <c r="F459" t="s">
+        <v>1150</v>
+      </c>
+      <c r="G459" t="s">
+        <v>1184</v>
+      </c>
+      <c r="I459" t="s">
+        <v>20</v>
+      </c>
+      <c r="J459" t="s">
+        <v>21</v>
+      </c>
+      <c r="K459" t="s">
+        <v>1155</v>
+      </c>
+      <c r="L459" s="49">
+        <v>46183</v>
+      </c>
+    </row>
+    <row r="460" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A460" s="39">
+        <v>459</v>
+      </c>
+      <c r="B460" s="48">
+        <v>46182</v>
+      </c>
+      <c r="D460" t="s">
+        <v>16</v>
+      </c>
+      <c r="E460" t="s">
+        <v>1185</v>
+      </c>
+      <c r="F460" t="s">
+        <v>1173</v>
+      </c>
+      <c r="G460" t="s">
+        <v>1186</v>
+      </c>
+      <c r="I460" t="s">
+        <v>64</v>
+      </c>
+      <c r="J460" t="s">
+        <v>21</v>
+      </c>
+      <c r="K460" t="s">
+        <v>1116</v>
+      </c>
+      <c r="L460" s="49">
+        <v>46183</v>
+      </c>
+    </row>
+    <row r="461" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A461" s="30">
+        <v>460</v>
+      </c>
+      <c r="B461" s="48">
+        <v>46182</v>
+      </c>
+      <c r="D461" t="s">
+        <v>16</v>
+      </c>
+      <c r="E461" t="s">
+        <v>1187</v>
+      </c>
+      <c r="F461" t="s">
+        <v>1150</v>
+      </c>
+      <c r="G461" t="s">
+        <v>1188</v>
+      </c>
+      <c r="I461" t="s">
+        <v>39</v>
+      </c>
+      <c r="J461" t="s">
+        <v>21</v>
+      </c>
+      <c r="K461" t="s">
+        <v>1116</v>
+      </c>
+      <c r="L461" s="49">
+        <v>46183</v>
+      </c>
+    </row>
+    <row r="462" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A462" s="22">
+        <v>461</v>
+      </c>
+      <c r="B462" s="48">
+        <v>46182</v>
+      </c>
+      <c r="D462" t="s">
+        <v>15</v>
+      </c>
+      <c r="E462" t="s">
+        <v>1189</v>
+      </c>
+      <c r="F462" t="s">
+        <v>1150</v>
+      </c>
+      <c r="G462" t="s">
+        <v>1190</v>
+      </c>
+      <c r="I462" t="s">
+        <v>20</v>
+      </c>
+      <c r="J462" t="s">
+        <v>65</v>
+      </c>
+      <c r="K462" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="463" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A463" s="39">
+        <v>462</v>
+      </c>
+      <c r="B463" s="48">
+        <v>46182</v>
+      </c>
+      <c r="D463" t="s">
+        <v>50</v>
+      </c>
+      <c r="E463" t="s">
+        <v>1191</v>
+      </c>
+      <c r="F463" t="s">
+        <v>1192</v>
+      </c>
+      <c r="G463" t="s">
+        <v>1264</v>
+      </c>
+      <c r="I463" t="s">
+        <v>20</v>
+      </c>
+      <c r="J463" t="s">
+        <v>1193</v>
+      </c>
+      <c r="K463" t="s">
+        <v>1194</v>
+      </c>
+      <c r="L463" s="49">
+        <v>46183</v>
+      </c>
+    </row>
+    <row r="464" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A464" s="30">
+        <v>463</v>
+      </c>
+      <c r="B464" s="48">
+        <v>46183</v>
+      </c>
+      <c r="C464" s="19">
+        <v>0.25972222222222224</v>
+      </c>
+      <c r="D464" t="s">
+        <v>15</v>
+      </c>
+      <c r="E464" t="s">
+        <v>80</v>
+      </c>
+      <c r="F464" t="s">
+        <v>415</v>
+      </c>
+      <c r="G464" t="s">
+        <v>1195</v>
+      </c>
+      <c r="H464" t="s">
+        <v>1196</v>
+      </c>
+      <c r="I464" t="s">
+        <v>20</v>
+      </c>
+      <c r="J464" t="s">
+        <v>21</v>
+      </c>
+      <c r="K464" t="s">
+        <v>1197</v>
+      </c>
+      <c r="L464" s="49">
+        <v>46183</v>
+      </c>
+    </row>
+    <row r="465" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A465" s="22">
+        <v>464</v>
+      </c>
+      <c r="B465" s="48">
+        <v>46183</v>
+      </c>
+      <c r="C465" s="19">
+        <v>0.33611111111111114</v>
+      </c>
+      <c r="D465" t="s">
+        <v>15</v>
+      </c>
+      <c r="E465" t="s">
+        <v>80</v>
+      </c>
+      <c r="F465" t="s">
+        <v>1149</v>
+      </c>
+      <c r="G465" t="s">
+        <v>1111</v>
+      </c>
+      <c r="H465" t="s">
+        <v>1198</v>
+      </c>
+      <c r="I465" t="s">
+        <v>39</v>
+      </c>
+      <c r="J465" t="s">
+        <v>21</v>
+      </c>
+      <c r="K465" t="s">
+        <v>1197</v>
+      </c>
+      <c r="L465" s="49">
+        <v>46183</v>
+      </c>
+      <c r="M465" s="43"/>
+    </row>
+    <row r="466" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A466" s="39">
+        <v>465</v>
+      </c>
+      <c r="B466" s="48">
+        <v>46183</v>
+      </c>
+      <c r="C466" s="19">
+        <v>0.36041666666666666</v>
+      </c>
+      <c r="D466" t="s">
+        <v>15</v>
+      </c>
+      <c r="E466" t="s">
+        <v>945</v>
+      </c>
+      <c r="F466" t="s">
+        <v>1152</v>
+      </c>
+      <c r="G466" t="s">
+        <v>1199</v>
+      </c>
+      <c r="H466" t="s">
+        <v>1200</v>
+      </c>
+      <c r="I466" t="s">
+        <v>64</v>
+      </c>
+      <c r="J466" t="s">
+        <v>21</v>
+      </c>
+      <c r="K466" t="s">
+        <v>1197</v>
+      </c>
+      <c r="L466" s="49">
+        <v>46183</v>
+      </c>
+      <c r="M466" s="43"/>
+    </row>
+    <row r="467" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A467" s="30">
+        <v>466</v>
+      </c>
+      <c r="B467" s="48">
+        <v>46183</v>
+      </c>
+      <c r="C467" s="19">
+        <v>0.40972222222222221</v>
+      </c>
+      <c r="D467" t="s">
+        <v>15</v>
+      </c>
+      <c r="E467" t="s">
+        <v>232</v>
+      </c>
+      <c r="F467" t="s">
+        <v>1149</v>
+      </c>
+      <c r="G467" t="s">
+        <v>1157</v>
+      </c>
+      <c r="H467" t="s">
+        <v>1201</v>
+      </c>
+      <c r="I467" t="s">
+        <v>20</v>
+      </c>
+      <c r="J467" t="s">
+        <v>21</v>
+      </c>
+      <c r="K467" t="s">
+        <v>1202</v>
+      </c>
+      <c r="L467" s="49">
+        <v>46183</v>
+      </c>
+      <c r="M467" s="43"/>
+    </row>
+    <row r="468" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A468" s="39">
+        <v>467</v>
+      </c>
+      <c r="B468" s="48">
+        <v>46183</v>
+      </c>
+      <c r="C468" s="19">
+        <v>0.41458333333333336</v>
+      </c>
+      <c r="D468" t="s">
+        <v>15</v>
+      </c>
+      <c r="E468" t="s">
+        <v>16</v>
+      </c>
+      <c r="F468" t="s">
+        <v>1156</v>
+      </c>
+      <c r="G468" t="s">
+        <v>1203</v>
+      </c>
+      <c r="H468" t="s">
+        <v>1204</v>
+      </c>
+      <c r="I468" t="s">
+        <v>64</v>
+      </c>
+      <c r="J468" t="s">
+        <v>21</v>
+      </c>
+      <c r="K468" t="s">
+        <v>1202</v>
+      </c>
+      <c r="L468" s="49">
+        <v>46183</v>
+      </c>
+      <c r="M468" s="43"/>
+    </row>
+    <row r="469" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A469" s="30">
+        <v>468</v>
+      </c>
+      <c r="B469" s="48">
+        <v>46183</v>
+      </c>
+      <c r="C469" s="19">
+        <v>0.45069444444444445</v>
+      </c>
+      <c r="D469" t="s">
+        <v>15</v>
+      </c>
+      <c r="E469" t="s">
+        <v>50</v>
+      </c>
+      <c r="F469" t="s">
+        <v>1159</v>
+      </c>
+      <c r="G469" t="s">
+        <v>1157</v>
+      </c>
+      <c r="H469" t="s">
+        <v>1160</v>
+      </c>
+      <c r="I469" t="s">
+        <v>64</v>
+      </c>
+      <c r="J469" t="s">
+        <v>21</v>
+      </c>
+      <c r="K469" t="s">
+        <v>1202</v>
+      </c>
+      <c r="L469" s="49">
+        <v>46183</v>
+      </c>
+      <c r="M469" s="43"/>
+    </row>
+    <row r="470" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A470" s="22">
+        <v>469</v>
+      </c>
+      <c r="B470" s="48">
+        <v>46183</v>
+      </c>
+      <c r="C470" s="19">
+        <v>0.59097222222222223</v>
+      </c>
+      <c r="D470" t="s">
+        <v>15</v>
+      </c>
+      <c r="E470" t="s">
+        <v>945</v>
+      </c>
+      <c r="F470" t="s">
+        <v>1161</v>
+      </c>
+      <c r="G470" t="s">
+        <v>1205</v>
+      </c>
+      <c r="H470" t="s">
+        <v>1206</v>
+      </c>
+      <c r="I470" t="s">
+        <v>39</v>
+      </c>
+      <c r="J470" t="s">
+        <v>21</v>
+      </c>
+      <c r="K470" t="s">
+        <v>1202</v>
+      </c>
+      <c r="L470" s="49">
+        <v>46183</v>
+      </c>
+      <c r="M470" s="43"/>
+    </row>
+    <row r="471" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A471" s="39">
+        <v>470</v>
+      </c>
+      <c r="B471" s="48">
+        <v>46183</v>
+      </c>
+      <c r="C471" s="19">
+        <v>0.59861111111111109</v>
+      </c>
+      <c r="D471" t="s">
+        <v>15</v>
+      </c>
+      <c r="E471" t="s">
+        <v>50</v>
+      </c>
+      <c r="F471" t="s">
+        <v>1163</v>
+      </c>
+      <c r="G471" t="s">
+        <v>1111</v>
+      </c>
+      <c r="H471" t="s">
+        <v>1207</v>
+      </c>
+      <c r="I471" t="s">
+        <v>39</v>
+      </c>
+      <c r="J471" t="s">
+        <v>65</v>
+      </c>
+      <c r="K471" t="s">
+        <v>945</v>
+      </c>
+      <c r="M471" s="43"/>
+    </row>
+    <row r="472" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A472" s="30">
+        <v>471</v>
+      </c>
+      <c r="B472" s="48">
+        <v>46183</v>
+      </c>
+      <c r="C472" s="19">
+        <v>0.65069444444444446</v>
+      </c>
+      <c r="D472" t="s">
+        <v>15</v>
+      </c>
+      <c r="E472" t="s">
+        <v>50</v>
+      </c>
+      <c r="F472" t="s">
+        <v>1165</v>
+      </c>
+      <c r="G472" t="s">
+        <v>1111</v>
+      </c>
+      <c r="H472" t="s">
+        <v>1208</v>
+      </c>
+      <c r="I472" t="s">
+        <v>20</v>
+      </c>
+      <c r="J472" t="s">
+        <v>65</v>
+      </c>
+      <c r="K472" t="s">
+        <v>945</v>
+      </c>
+      <c r="M472" s="43"/>
+    </row>
+    <row r="473" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A473" s="39">
+        <v>472</v>
+      </c>
+      <c r="B473" s="48">
+        <v>46183</v>
+      </c>
+      <c r="C473" s="19">
+        <v>0.66319444444444442</v>
+      </c>
+      <c r="D473" t="s">
+        <v>15</v>
+      </c>
+      <c r="E473" t="s">
+        <v>16</v>
+      </c>
+      <c r="F473" t="s">
+        <v>1167</v>
+      </c>
+      <c r="G473" t="s">
+        <v>1209</v>
+      </c>
+      <c r="H473" t="s">
+        <v>1210</v>
+      </c>
+      <c r="I473" t="s">
+        <v>20</v>
+      </c>
+      <c r="J473" t="s">
+        <v>21</v>
+      </c>
+      <c r="K473" t="s">
+        <v>1202</v>
+      </c>
+      <c r="L473" s="49">
+        <v>46183</v>
+      </c>
+      <c r="M473" s="43"/>
+    </row>
+    <row r="474" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A474" s="30">
+        <v>473</v>
+      </c>
+      <c r="B474" s="48">
+        <v>46183</v>
+      </c>
+      <c r="C474" s="19">
+        <v>0.67638888888888893</v>
+      </c>
+      <c r="D474" t="s">
+        <v>15</v>
+      </c>
+      <c r="E474" t="s">
+        <v>16</v>
+      </c>
+      <c r="F474" t="s">
+        <v>1133</v>
+      </c>
+      <c r="G474" t="s">
+        <v>1111</v>
+      </c>
+      <c r="H474" t="s">
+        <v>1211</v>
+      </c>
+      <c r="I474" t="s">
+        <v>39</v>
+      </c>
+      <c r="J474" t="s">
+        <v>65</v>
+      </c>
+      <c r="K474" t="s">
+        <v>945</v>
+      </c>
+      <c r="M474" s="43"/>
+    </row>
+    <row r="475" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A475" s="22">
+        <v>474</v>
+      </c>
+      <c r="B475" s="48">
+        <v>46183</v>
+      </c>
+      <c r="C475" s="19">
+        <v>0.71736111111111112</v>
+      </c>
+      <c r="D475" t="s">
+        <v>15</v>
+      </c>
+      <c r="E475" t="s">
+        <v>43</v>
+      </c>
+      <c r="F475" t="s">
+        <v>1170</v>
+      </c>
+      <c r="G475" t="s">
+        <v>1134</v>
+      </c>
+      <c r="H475" t="s">
+        <v>1212</v>
+      </c>
+      <c r="I475" t="s">
+        <v>20</v>
+      </c>
+      <c r="J475" t="s">
+        <v>65</v>
+      </c>
+      <c r="K475" t="s">
+        <v>945</v>
+      </c>
+      <c r="M475" s="43"/>
+    </row>
+    <row r="476" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A476" s="39">
+        <v>475</v>
+      </c>
+      <c r="B476" s="48">
+        <v>46183</v>
+      </c>
+      <c r="C476" s="19">
+        <v>0.71944444444444444</v>
+      </c>
+      <c r="D476" t="s">
+        <v>15</v>
+      </c>
+      <c r="E476" t="s">
+        <v>945</v>
+      </c>
+      <c r="F476" t="s">
+        <v>1172</v>
+      </c>
+      <c r="G476" t="s">
+        <v>1213</v>
+      </c>
+      <c r="H476" t="s">
+        <v>1214</v>
+      </c>
+      <c r="I476" t="s">
+        <v>64</v>
+      </c>
+      <c r="J476" t="s">
+        <v>21</v>
+      </c>
+      <c r="K476" t="s">
+        <v>1202</v>
+      </c>
+      <c r="L476" s="49">
+        <v>46183</v>
+      </c>
+      <c r="M476" s="43"/>
+    </row>
+    <row r="477" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A477" s="30">
+        <v>476</v>
+      </c>
+      <c r="B477" s="48">
+        <v>46183</v>
+      </c>
+      <c r="C477" s="19">
+        <v>0.35625000000000001</v>
+      </c>
+      <c r="D477" t="s">
+        <v>15</v>
+      </c>
+      <c r="E477" t="s">
+        <v>43</v>
+      </c>
+      <c r="F477" t="s">
+        <v>1176</v>
+      </c>
+      <c r="G477" t="s">
+        <v>1134</v>
+      </c>
+      <c r="H477" t="s">
+        <v>1215</v>
+      </c>
+      <c r="I477" t="s">
+        <v>20</v>
+      </c>
+      <c r="J477" t="s">
+        <v>65</v>
+      </c>
+      <c r="K477" t="s">
+        <v>945</v>
+      </c>
+      <c r="M477" s="43"/>
+    </row>
+    <row r="478" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A478" s="39">
+        <v>477</v>
+      </c>
+      <c r="B478" s="48">
+        <v>46183</v>
+      </c>
+      <c r="C478" s="19">
+        <v>0.37708333333333333</v>
+      </c>
+      <c r="D478" t="s">
+        <v>15</v>
+      </c>
+      <c r="E478" t="s">
+        <v>43</v>
+      </c>
+      <c r="F478" t="s">
+        <v>1178</v>
+      </c>
+      <c r="G478" t="s">
+        <v>1216</v>
+      </c>
+      <c r="H478" t="s">
+        <v>1217</v>
+      </c>
+      <c r="I478" t="s">
+        <v>64</v>
+      </c>
+      <c r="J478" t="s">
+        <v>21</v>
+      </c>
+      <c r="K478" t="s">
+        <v>1218</v>
+      </c>
+      <c r="L478" s="49">
+        <v>46183</v>
+      </c>
+      <c r="M478" s="43"/>
+    </row>
+    <row r="479" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A479" s="30">
+        <v>478</v>
+      </c>
+      <c r="B479" s="48">
+        <v>46183</v>
+      </c>
+      <c r="C479" s="19">
+        <v>0.6694444444444444</v>
+      </c>
+      <c r="D479" t="s">
+        <v>15</v>
+      </c>
+      <c r="E479" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F479" t="s">
+        <v>1181</v>
+      </c>
+      <c r="G479" t="s">
+        <v>1117</v>
+      </c>
+      <c r="H479" t="s">
+        <v>1220</v>
+      </c>
+      <c r="I479" t="s">
+        <v>20</v>
+      </c>
+      <c r="J479" t="s">
+        <v>65</v>
+      </c>
+      <c r="K479" t="s">
+        <v>945</v>
+      </c>
+      <c r="M479" s="43"/>
+    </row>
+    <row r="480" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A480" s="22">
+        <v>479</v>
+      </c>
+      <c r="B480" s="48">
+        <v>46183</v>
+      </c>
+      <c r="C480" s="19">
+        <v>0.37361111111111112</v>
+      </c>
+      <c r="D480" t="s">
+        <v>15</v>
+      </c>
+      <c r="E480" t="s">
+        <v>16</v>
+      </c>
+      <c r="F480" t="s">
+        <v>1183</v>
+      </c>
+      <c r="G480" t="s">
+        <v>1157</v>
+      </c>
+      <c r="H480" t="s">
+        <v>1184</v>
+      </c>
+      <c r="I480" t="s">
+        <v>20</v>
+      </c>
+      <c r="J480" t="s">
+        <v>21</v>
+      </c>
+      <c r="K480" t="s">
+        <v>1221</v>
+      </c>
+      <c r="L480" s="49">
+        <v>46183</v>
+      </c>
+      <c r="M480" s="43"/>
+    </row>
+    <row r="481" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A481" s="39">
+        <v>480</v>
+      </c>
+      <c r="B481" s="48">
+        <v>46183</v>
+      </c>
+      <c r="C481" s="19">
+        <v>0.37777777777777777</v>
+      </c>
+      <c r="D481" t="s">
+        <v>15</v>
+      </c>
+      <c r="E481" t="s">
+        <v>16</v>
+      </c>
+      <c r="F481" t="s">
+        <v>1185</v>
+      </c>
+      <c r="G481" t="s">
+        <v>1222</v>
+      </c>
+      <c r="H481" t="s">
+        <v>1223</v>
+      </c>
+      <c r="I481" t="s">
+        <v>64</v>
+      </c>
+      <c r="J481" t="s">
+        <v>21</v>
+      </c>
+      <c r="K481" t="s">
+        <v>1221</v>
+      </c>
+      <c r="L481" s="49">
+        <v>46183</v>
+      </c>
+      <c r="M481" s="43"/>
+    </row>
+    <row r="482" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A482" s="30">
+        <v>481</v>
+      </c>
+      <c r="B482" s="48">
+        <v>46183</v>
+      </c>
+      <c r="C482" s="19">
+        <v>0.36944444444444446</v>
+      </c>
+      <c r="D482" t="s">
+        <v>15</v>
+      </c>
+      <c r="E482" t="s">
+        <v>80</v>
+      </c>
+      <c r="F482" t="s">
+        <v>144</v>
+      </c>
+      <c r="G482" t="s">
+        <v>1222</v>
+      </c>
+      <c r="H482" t="s">
+        <v>1224</v>
+      </c>
+      <c r="I482" t="s">
+        <v>20</v>
+      </c>
+      <c r="J482" t="s">
+        <v>65</v>
+      </c>
+      <c r="K482" t="s">
+        <v>945</v>
+      </c>
+      <c r="M482" s="43"/>
+    </row>
+    <row r="483" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A483" s="39">
+        <v>482</v>
+      </c>
+      <c r="B483" s="48">
+        <v>46183</v>
+      </c>
+      <c r="C483" s="19">
+        <v>0.45763888888888887</v>
+      </c>
+      <c r="D483" t="s">
+        <v>15</v>
+      </c>
+      <c r="E483" t="s">
+        <v>232</v>
+      </c>
+      <c r="F483" t="s">
+        <v>1225</v>
+      </c>
+      <c r="G483" t="s">
+        <v>1150</v>
+      </c>
+      <c r="H483" t="s">
+        <v>1226</v>
+      </c>
+      <c r="I483" t="s">
+        <v>39</v>
+      </c>
+      <c r="J483" t="s">
+        <v>65</v>
+      </c>
+      <c r="K483" t="s">
+        <v>945</v>
+      </c>
+      <c r="M483" s="43"/>
+    </row>
+    <row r="484" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A484" s="30">
+        <v>483</v>
+      </c>
+      <c r="B484" s="48">
+        <v>46183</v>
+      </c>
+      <c r="C484" s="19">
+        <v>0.53263888888888888</v>
+      </c>
+      <c r="D484" t="s">
+        <v>15</v>
+      </c>
+      <c r="E484" t="s">
+        <v>50</v>
+      </c>
+      <c r="F484" t="s">
+        <v>1227</v>
+      </c>
+      <c r="G484" t="s">
+        <v>1222</v>
+      </c>
+      <c r="H484" t="s">
+        <v>1228</v>
+      </c>
+      <c r="I484" t="s">
+        <v>64</v>
+      </c>
+      <c r="J484" t="s">
+        <v>65</v>
+      </c>
+      <c r="K484" t="s">
+        <v>945</v>
+      </c>
+      <c r="M484" s="43"/>
+    </row>
+    <row r="485" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A485" s="22">
+        <v>484</v>
+      </c>
+      <c r="B485" s="48">
+        <v>46183</v>
+      </c>
+      <c r="C485" s="19">
+        <v>0.53333333333333333</v>
+      </c>
+      <c r="D485" t="s">
+        <v>15</v>
+      </c>
+      <c r="E485" t="s">
+        <v>80</v>
+      </c>
+      <c r="F485" t="s">
+        <v>1149</v>
+      </c>
+      <c r="G485" t="s">
+        <v>1150</v>
+      </c>
+      <c r="H485" t="s">
+        <v>1229</v>
+      </c>
+      <c r="I485" t="s">
+        <v>20</v>
+      </c>
+      <c r="J485" t="s">
+        <v>21</v>
+      </c>
+      <c r="K485" t="s">
+        <v>1202</v>
+      </c>
+      <c r="L485" s="49">
+        <v>46183</v>
+      </c>
+      <c r="M485" s="43"/>
+    </row>
+    <row r="486" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A486" s="39">
+        <v>485</v>
+      </c>
+      <c r="B486" s="48">
+        <v>46183</v>
+      </c>
+      <c r="C486" s="19">
+        <v>0.58472222222222225</v>
+      </c>
+      <c r="D486" t="s">
+        <v>15</v>
+      </c>
+      <c r="E486" t="s">
+        <v>139</v>
+      </c>
+      <c r="F486" t="s">
+        <v>1230</v>
+      </c>
+      <c r="G486" t="s">
+        <v>1117</v>
+      </c>
+      <c r="H486" t="s">
+        <v>1231</v>
+      </c>
+      <c r="I486" t="s">
+        <v>64</v>
+      </c>
+      <c r="J486" t="s">
+        <v>65</v>
+      </c>
+      <c r="K486" t="s">
+        <v>945</v>
+      </c>
+      <c r="M486" s="43"/>
+    </row>
+    <row r="487" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A487" s="30">
+        <v>486</v>
+      </c>
+      <c r="B487" s="48">
+        <v>46183</v>
+      </c>
+      <c r="C487" s="19">
+        <v>0.64097222222222228</v>
+      </c>
+      <c r="D487" t="s">
+        <v>15</v>
+      </c>
+      <c r="E487" t="s">
+        <v>278</v>
+      </c>
+      <c r="F487" t="s">
+        <v>1232</v>
+      </c>
+      <c r="G487" t="s">
+        <v>1150</v>
+      </c>
+      <c r="H487" t="s">
+        <v>1233</v>
+      </c>
+      <c r="I487" t="s">
+        <v>64</v>
+      </c>
+      <c r="J487" t="s">
+        <v>65</v>
+      </c>
+      <c r="K487" t="s">
+        <v>945</v>
+      </c>
+      <c r="M487" s="43"/>
+    </row>
+    <row r="488" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A488" s="39">
+        <v>487</v>
+      </c>
+      <c r="B488" s="48">
+        <v>46183</v>
+      </c>
+      <c r="C488" s="19">
+        <v>0.65</v>
+      </c>
+      <c r="D488" t="s">
+        <v>15</v>
+      </c>
+      <c r="E488" t="s">
+        <v>1145</v>
+      </c>
+      <c r="F488" t="s">
+        <v>1234</v>
+      </c>
+      <c r="G488" t="s">
+        <v>1235</v>
+      </c>
+      <c r="H488" t="s">
+        <v>1236</v>
+      </c>
+      <c r="I488" t="s">
+        <v>39</v>
+      </c>
+      <c r="J488" t="s">
+        <v>65</v>
+      </c>
+      <c r="K488" t="s">
+        <v>945</v>
+      </c>
+      <c r="M488" s="43"/>
+    </row>
+    <row r="489" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A489" s="30">
+        <v>488</v>
+      </c>
+      <c r="B489" s="48">
+        <v>46183</v>
+      </c>
+      <c r="C489" s="19">
+        <v>0.71666666666666667</v>
+      </c>
+      <c r="D489" t="s">
+        <v>15</v>
+      </c>
+      <c r="E489" t="s">
+        <v>16</v>
+      </c>
+      <c r="F489" t="s">
+        <v>1237</v>
+      </c>
+      <c r="G489" t="s">
+        <v>1150</v>
+      </c>
+      <c r="H489" t="s">
+        <v>1238</v>
+      </c>
+      <c r="I489" t="s">
+        <v>39</v>
+      </c>
+      <c r="J489" t="s">
+        <v>65</v>
+      </c>
+      <c r="K489" t="s">
+        <v>945</v>
+      </c>
+      <c r="M489" s="43"/>
+    </row>
+    <row r="490" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A490" s="22">
+        <v>489</v>
+      </c>
+      <c r="B490" s="48">
+        <v>46183</v>
+      </c>
+      <c r="C490" s="19">
+        <v>0.27361111111111114</v>
+      </c>
+      <c r="D490" t="s">
+        <v>15</v>
+      </c>
+      <c r="E490" t="s">
+        <v>25</v>
+      </c>
+      <c r="F490" t="s">
+        <v>773</v>
+      </c>
+      <c r="G490" t="s">
+        <v>1150</v>
+      </c>
+      <c r="H490" t="s">
+        <v>1239</v>
+      </c>
+      <c r="I490" t="s">
+        <v>64</v>
+      </c>
+      <c r="J490" t="s">
+        <v>65</v>
+      </c>
+      <c r="K490" t="s">
+        <v>945</v>
+      </c>
+      <c r="M490" s="43"/>
+    </row>
+    <row r="491" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A491" s="39">
+        <v>490</v>
+      </c>
+      <c r="B491" s="48">
+        <v>46183</v>
+      </c>
+      <c r="C491" s="19">
+        <v>0.35</v>
+      </c>
+      <c r="D491" t="s">
+        <v>15</v>
+      </c>
+      <c r="E491" t="s">
+        <v>43</v>
+      </c>
+      <c r="F491" t="s">
+        <v>1176</v>
+      </c>
+      <c r="G491" t="s">
+        <v>1222</v>
+      </c>
+      <c r="H491" t="s">
+        <v>1265</v>
+      </c>
+      <c r="I491" t="s">
+        <v>20</v>
+      </c>
+      <c r="J491" t="s">
+        <v>65</v>
+      </c>
+      <c r="K491" t="s">
+        <v>945</v>
+      </c>
+      <c r="M491" s="43"/>
+    </row>
+    <row r="492" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A492" s="30">
+        <v>491</v>
+      </c>
+      <c r="B492" s="48">
+        <v>46183</v>
+      </c>
+      <c r="C492" s="19">
+        <v>0.4284722222222222</v>
+      </c>
+      <c r="D492" t="s">
+        <v>15</v>
+      </c>
+      <c r="E492" t="s">
+        <v>278</v>
+      </c>
+      <c r="F492" t="s">
+        <v>1240</v>
+      </c>
+      <c r="G492" t="s">
+        <v>1222</v>
+      </c>
+      <c r="H492" t="s">
+        <v>1241</v>
+      </c>
+      <c r="I492" t="s">
+        <v>20</v>
+      </c>
+      <c r="J492" t="s">
+        <v>65</v>
+      </c>
+      <c r="K492" t="s">
+        <v>945</v>
+      </c>
+      <c r="M492" s="43"/>
+    </row>
+    <row r="493" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A493" s="39">
+        <v>492</v>
+      </c>
+      <c r="B493" s="48">
+        <v>46184</v>
+      </c>
+      <c r="C493" s="19">
+        <v>0.4236111111111111</v>
+      </c>
+      <c r="D493" t="s">
+        <v>15</v>
+      </c>
+      <c r="E493" t="s">
+        <v>16</v>
+      </c>
+      <c r="F493" t="s">
+        <v>1187</v>
+      </c>
+      <c r="G493" t="s">
+        <v>1134</v>
+      </c>
+      <c r="H493" t="s">
+        <v>1242</v>
+      </c>
+      <c r="I493" t="s">
+        <v>20</v>
+      </c>
+      <c r="J493" t="s">
+        <v>21</v>
+      </c>
+      <c r="K493" t="s">
+        <v>1243</v>
+      </c>
+      <c r="L493" s="49">
+        <v>46184</v>
+      </c>
+      <c r="M493" s="43"/>
+    </row>
+    <row r="494" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A494" s="30">
+        <v>493</v>
+      </c>
+      <c r="B494" s="48">
+        <v>46184</v>
+      </c>
+      <c r="C494" s="19">
+        <v>0.4236111111111111</v>
+      </c>
+      <c r="D494" t="s">
+        <v>15</v>
+      </c>
+      <c r="E494" t="s">
+        <v>16</v>
+      </c>
+      <c r="F494" t="s">
+        <v>1187</v>
+      </c>
+      <c r="G494" t="s">
+        <v>1134</v>
+      </c>
+      <c r="H494" t="s">
+        <v>1242</v>
+      </c>
+      <c r="I494" t="s">
+        <v>20</v>
+      </c>
+      <c r="J494" t="s">
+        <v>21</v>
+      </c>
+      <c r="K494" t="s">
+        <v>1243</v>
+      </c>
+      <c r="L494" s="49">
+        <v>46184</v>
+      </c>
+      <c r="M494" s="43"/>
+    </row>
+    <row r="495" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A495" s="22">
+        <v>494</v>
+      </c>
+      <c r="B495" s="48">
+        <v>46184</v>
+      </c>
+      <c r="C495" s="19">
+        <v>0.56944444444444442</v>
+      </c>
+      <c r="D495" t="s">
+        <v>15</v>
+      </c>
+      <c r="E495" t="s">
+        <v>50</v>
+      </c>
+      <c r="F495" t="s">
+        <v>1244</v>
+      </c>
+      <c r="G495" t="s">
+        <v>1117</v>
+      </c>
+      <c r="H495" t="s">
+        <v>1267</v>
+      </c>
+      <c r="I495" t="s">
+        <v>20</v>
+      </c>
+      <c r="J495" t="s">
+        <v>1193</v>
+      </c>
+      <c r="K495" t="s">
+        <v>1266</v>
+      </c>
+      <c r="M495" s="43"/>
+    </row>
+    <row r="496" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A496" s="39">
+        <v>495</v>
+      </c>
+      <c r="B496" s="48">
+        <v>46184</v>
+      </c>
+      <c r="C496" s="19">
+        <v>0.42916666666666664</v>
+      </c>
+      <c r="D496" t="s">
+        <v>15</v>
+      </c>
+      <c r="E496" t="s">
+        <v>43</v>
+      </c>
+      <c r="F496" t="s">
+        <v>1245</v>
+      </c>
+      <c r="G496" t="s">
+        <v>1150</v>
+      </c>
+      <c r="H496" t="s">
+        <v>1246</v>
+      </c>
+      <c r="I496" t="s">
+        <v>39</v>
+      </c>
+      <c r="J496" t="s">
+        <v>65</v>
+      </c>
+      <c r="K496" t="s">
+        <v>945</v>
+      </c>
+      <c r="M496" s="43"/>
+    </row>
+    <row r="497" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A497" s="30">
+        <v>496</v>
+      </c>
+      <c r="B497" s="48">
+        <v>46184</v>
+      </c>
+      <c r="C497" s="19">
+        <v>0.47986111111111113</v>
+      </c>
+      <c r="D497" t="s">
+        <v>15</v>
+      </c>
+      <c r="E497" t="s">
+        <v>16</v>
+      </c>
+      <c r="F497" t="s">
+        <v>1133</v>
+      </c>
+      <c r="G497" t="s">
+        <v>1150</v>
+      </c>
+      <c r="H497" t="s">
+        <v>1247</v>
+      </c>
+      <c r="I497" t="s">
+        <v>39</v>
+      </c>
+      <c r="J497" t="s">
+        <v>65</v>
+      </c>
+      <c r="K497" t="s">
+        <v>945</v>
+      </c>
+      <c r="M497" s="43"/>
+    </row>
+    <row r="498" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A498" s="39">
+        <v>497</v>
+      </c>
+      <c r="B498" s="48">
+        <v>46184</v>
+      </c>
+      <c r="C498" s="19">
+        <v>0.58680555555555558</v>
+      </c>
+      <c r="D498" t="s">
+        <v>15</v>
+      </c>
+      <c r="E498" t="s">
+        <v>43</v>
+      </c>
+      <c r="F498" t="s">
+        <v>1248</v>
+      </c>
+      <c r="G498" t="s">
+        <v>1150</v>
+      </c>
+      <c r="H498" t="s">
+        <v>1249</v>
+      </c>
+      <c r="I498" t="s">
+        <v>39</v>
+      </c>
+      <c r="J498" t="s">
+        <v>65</v>
+      </c>
+      <c r="K498" t="s">
+        <v>945</v>
+      </c>
+      <c r="M498" s="43"/>
+    </row>
+    <row r="499" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A499" s="30">
+        <v>498</v>
+      </c>
+      <c r="B499" s="48">
+        <v>46184</v>
+      </c>
+      <c r="C499" s="19">
+        <v>0.59513888888888888</v>
+      </c>
+      <c r="D499" t="s">
+        <v>15</v>
+      </c>
+      <c r="E499" t="s">
+        <v>43</v>
+      </c>
+      <c r="F499" t="s">
+        <v>1250</v>
+      </c>
+      <c r="G499" t="s">
+        <v>1251</v>
+      </c>
+      <c r="H499" t="s">
+        <v>1252</v>
+      </c>
+      <c r="I499" t="s">
+        <v>39</v>
+      </c>
+      <c r="J499" t="s">
+        <v>1193</v>
+      </c>
+      <c r="K499" t="s">
+        <v>1253</v>
+      </c>
+      <c r="M499" s="43"/>
+    </row>
+    <row r="500" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A500" s="22">
+        <v>499</v>
+      </c>
+      <c r="B500" s="48">
+        <v>46184</v>
+      </c>
+      <c r="C500" s="19">
+        <v>0.27361111111111114</v>
+      </c>
+      <c r="D500" t="s">
+        <v>15</v>
+      </c>
+      <c r="E500" t="s">
+        <v>80</v>
+      </c>
+      <c r="F500" t="s">
+        <v>1254</v>
+      </c>
+      <c r="G500" t="s">
+        <v>783</v>
+      </c>
+      <c r="H500" t="s">
+        <v>1255</v>
+      </c>
+      <c r="I500" t="s">
+        <v>20</v>
+      </c>
+      <c r="J500" t="s">
+        <v>1193</v>
+      </c>
+      <c r="K500" t="s">
+        <v>1256</v>
+      </c>
+      <c r="M500" s="43"/>
+    </row>
+    <row r="501" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A501" s="39">
+        <v>500</v>
+      </c>
+      <c r="B501" s="48">
+        <v>46184</v>
+      </c>
+      <c r="C501" s="19">
+        <v>0.43819444444444444</v>
+      </c>
+      <c r="D501" t="s">
+        <v>15</v>
+      </c>
+      <c r="E501" t="s">
+        <v>1268</v>
+      </c>
+      <c r="F501" t="s">
+        <v>1257</v>
+      </c>
+      <c r="G501" t="s">
+        <v>1258</v>
+      </c>
+      <c r="H501" t="s">
+        <v>1259</v>
+      </c>
+      <c r="I501" t="s">
+        <v>39</v>
+      </c>
+      <c r="J501" t="s">
+        <v>21</v>
+      </c>
+      <c r="K501" t="s">
+        <v>1260</v>
+      </c>
+      <c r="L501" s="49">
+        <v>46184</v>
+      </c>
+      <c r="M501" s="43"/>
+    </row>
+    <row r="502" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A502" s="30">
+        <v>501</v>
+      </c>
+      <c r="B502" s="48">
+        <v>46184</v>
+      </c>
+      <c r="C502" s="19">
+        <v>0.42916666666666664</v>
+      </c>
+      <c r="D502" t="s">
+        <v>15</v>
+      </c>
+      <c r="E502" t="s">
+        <v>1269</v>
+      </c>
+      <c r="F502" t="s">
+        <v>1261</v>
+      </c>
+      <c r="G502" t="s">
+        <v>1262</v>
+      </c>
+      <c r="H502" t="s">
+        <v>1263</v>
+      </c>
+      <c r="I502" t="s">
+        <v>20</v>
+      </c>
+      <c r="J502" t="s">
+        <v>21</v>
+      </c>
+      <c r="K502" t="s">
+        <v>1260</v>
+      </c>
+      <c r="L502" s="49">
+        <v>46184</v>
+      </c>
+      <c r="M502" s="43"/>
+    </row>
+    <row r="503" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A503" s="39">
+        <v>502</v>
+      </c>
+      <c r="B503" s="44"/>
+      <c r="C503" s="45"/>
+      <c r="D503" s="43"/>
+      <c r="E503" s="43"/>
+      <c r="F503" s="43"/>
+      <c r="G503" s="43"/>
+      <c r="H503" s="43"/>
+      <c r="I503" s="43"/>
+      <c r="J503" s="43"/>
+      <c r="K503" s="43"/>
+      <c r="L503" s="47"/>
+      <c r="M503" s="43"/>
+    </row>
+    <row r="504" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A504" s="30">
+        <v>503</v>
+      </c>
+      <c r="B504" s="44"/>
+      <c r="C504" s="45"/>
+      <c r="D504" s="43"/>
+      <c r="E504" s="43"/>
+      <c r="F504" s="43"/>
+      <c r="G504" s="43"/>
+      <c r="H504" s="43"/>
+      <c r="I504" s="43"/>
+      <c r="J504" s="43"/>
+      <c r="K504" s="43"/>
+      <c r="L504" s="47"/>
+      <c r="M504" s="43"/>
+    </row>
+    <row r="505" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A505" s="22">
+        <v>504</v>
+      </c>
+      <c r="B505" s="44"/>
+      <c r="C505" s="45"/>
+      <c r="D505" s="43"/>
+      <c r="E505" s="43"/>
+      <c r="F505" s="43"/>
+      <c r="G505" s="43"/>
+      <c r="H505" s="43"/>
+      <c r="I505" s="43"/>
+      <c r="J505" s="43"/>
+      <c r="K505" s="43"/>
+      <c r="L505" s="47"/>
+      <c r="M505" s="43"/>
+    </row>
+    <row r="506" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A506" s="39">
+        <v>505</v>
+      </c>
+      <c r="B506" s="44"/>
+      <c r="C506" s="45"/>
+      <c r="D506" s="43"/>
+      <c r="E506" s="43"/>
+      <c r="F506" s="43"/>
+      <c r="G506" s="43"/>
+      <c r="H506" s="43"/>
+      <c r="I506" s="43"/>
+      <c r="J506" s="43"/>
+      <c r="K506" s="43"/>
+      <c r="L506" s="47"/>
+      <c r="M506" s="43"/>
+    </row>
+    <row r="507" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A507" s="30">
+        <v>506</v>
+      </c>
+      <c r="B507" s="44"/>
+      <c r="C507" s="45"/>
+      <c r="D507" s="43"/>
+      <c r="E507" s="43"/>
+      <c r="F507" s="43"/>
+      <c r="G507" s="43"/>
+      <c r="H507" s="43"/>
+      <c r="I507" s="43"/>
+      <c r="J507" s="43"/>
+      <c r="K507" s="43"/>
+      <c r="L507" s="47"/>
+      <c r="M507" s="43"/>
+    </row>
+    <row r="508" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A508" s="39">
+        <v>507</v>
+      </c>
+      <c r="B508" s="44"/>
+      <c r="C508" s="45"/>
+      <c r="D508" s="43"/>
+      <c r="E508" s="43"/>
+      <c r="F508" s="43"/>
+      <c r="G508" s="43"/>
+      <c r="H508" s="43"/>
+      <c r="I508" s="43"/>
+      <c r="J508" s="43"/>
+      <c r="K508" s="43"/>
+      <c r="L508" s="47"/>
+      <c r="M508" s="43"/>
+    </row>
+    <row r="509" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A509" s="30">
+        <v>508</v>
+      </c>
+      <c r="B509" s="44"/>
+      <c r="C509" s="45"/>
+      <c r="D509" s="43"/>
+      <c r="E509" s="43"/>
+      <c r="F509" s="43"/>
+      <c r="G509" s="43"/>
+      <c r="H509" s="43"/>
+      <c r="I509" s="43"/>
+      <c r="J509" s="43"/>
+      <c r="K509" s="43"/>
+      <c r="L509" s="47"/>
+      <c r="M509" s="43"/>
+    </row>
+    <row r="510" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A510" s="22">
+        <v>509</v>
+      </c>
+      <c r="B510" s="44"/>
+      <c r="C510" s="45"/>
+      <c r="D510" s="43"/>
+      <c r="E510" s="43"/>
+      <c r="F510" s="43"/>
+      <c r="G510" s="43"/>
+      <c r="H510" s="43"/>
+      <c r="I510" s="43"/>
+      <c r="J510" s="43"/>
+      <c r="K510" s="43"/>
+      <c r="L510" s="47"/>
+      <c r="M510" s="43"/>
+    </row>
+    <row r="511" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A511" s="39">
+        <v>510</v>
+      </c>
+      <c r="B511" s="44"/>
+      <c r="C511" s="45"/>
+      <c r="D511" s="43"/>
+      <c r="E511" s="43"/>
+      <c r="F511" s="43"/>
+      <c r="G511" s="43"/>
+      <c r="H511" s="43"/>
+      <c r="I511" s="43"/>
+      <c r="J511" s="43"/>
+      <c r="K511" s="43"/>
+      <c r="L511" s="47"/>
+      <c r="M511" s="43"/>
+    </row>
+    <row r="512" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A512" s="30">
+        <v>511</v>
+      </c>
+      <c r="B512" s="44"/>
+      <c r="C512" s="45"/>
+      <c r="D512" s="43"/>
+      <c r="E512" s="43"/>
+      <c r="F512" s="43"/>
+      <c r="G512" s="43"/>
+      <c r="H512" s="43"/>
+      <c r="I512" s="43"/>
+      <c r="J512" s="43"/>
+      <c r="K512" s="43"/>
+      <c r="L512" s="47"/>
+      <c r="M512" s="43"/>
+    </row>
+    <row r="513" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A513" s="39">
+        <v>512</v>
+      </c>
+      <c r="B513" s="44"/>
+      <c r="C513" s="45"/>
+      <c r="D513" s="43"/>
+      <c r="E513" s="43"/>
+      <c r="F513" s="43"/>
+      <c r="G513" s="43"/>
+      <c r="H513" s="43"/>
+      <c r="I513" s="43"/>
+      <c r="J513" s="43"/>
+      <c r="K513" s="43"/>
+      <c r="L513" s="47"/>
+      <c r="M513" s="43"/>
+    </row>
+    <row r="514" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A514" s="30">
+        <v>513</v>
+      </c>
+      <c r="B514" s="44"/>
+      <c r="C514" s="45"/>
+      <c r="D514" s="43"/>
+      <c r="E514" s="43"/>
+      <c r="F514" s="43"/>
+      <c r="G514" s="43"/>
+      <c r="H514" s="43"/>
+      <c r="I514" s="43"/>
+      <c r="J514" s="43"/>
+      <c r="K514" s="43"/>
+      <c r="L514" s="47"/>
+      <c r="M514" s="43"/>
+    </row>
+    <row r="515" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A515" s="22">
+        <v>514</v>
+      </c>
+      <c r="B515" s="44"/>
+      <c r="C515" s="45"/>
+      <c r="D515" s="43"/>
+      <c r="E515" s="43"/>
+      <c r="F515" s="43"/>
+      <c r="G515" s="43"/>
+      <c r="H515" s="43"/>
+      <c r="I515" s="43"/>
+      <c r="J515" s="43"/>
+      <c r="K515" s="43"/>
+      <c r="L515" s="47"/>
+      <c r="M515" s="43"/>
+    </row>
+    <row r="516" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A516" s="39">
+        <v>515</v>
+      </c>
+      <c r="B516" s="44"/>
+      <c r="C516" s="45"/>
+      <c r="D516" s="43"/>
+      <c r="E516" s="43"/>
+      <c r="F516" s="43"/>
+      <c r="G516" s="43"/>
+      <c r="H516" s="43"/>
+      <c r="I516" s="43"/>
+      <c r="J516" s="43"/>
+      <c r="K516" s="43"/>
+      <c r="L516" s="47"/>
+      <c r="M516" s="43"/>
+    </row>
+    <row r="517" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A517" s="30">
+        <v>516</v>
+      </c>
+      <c r="B517" s="44"/>
+      <c r="C517" s="45"/>
+      <c r="D517" s="43"/>
+      <c r="E517" s="43"/>
+      <c r="F517" s="43"/>
+      <c r="G517" s="43"/>
+      <c r="H517" s="43"/>
+      <c r="I517" s="43"/>
+      <c r="J517" s="43"/>
+      <c r="K517" s="43"/>
+      <c r="L517" s="47"/>
+      <c r="M517" s="43"/>
+    </row>
+    <row r="518" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A518" s="39">
+        <v>517</v>
+      </c>
+      <c r="B518" s="44"/>
+      <c r="C518" s="45"/>
+      <c r="D518" s="43"/>
+      <c r="E518" s="43"/>
+      <c r="F518" s="43"/>
+      <c r="G518" s="43"/>
+      <c r="H518" s="43"/>
+      <c r="I518" s="43"/>
+      <c r="J518" s="43"/>
+      <c r="K518" s="43"/>
+      <c r="L518" s="47"/>
+      <c r="M518" s="43"/>
+    </row>
+    <row r="519" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A519" s="30">
+        <v>518</v>
+      </c>
+      <c r="B519" s="44"/>
+      <c r="C519" s="45"/>
+      <c r="D519" s="43"/>
+      <c r="E519" s="43"/>
+      <c r="F519" s="43"/>
+      <c r="G519" s="43"/>
+      <c r="H519" s="43"/>
+      <c r="I519" s="43"/>
+      <c r="J519" s="43"/>
+      <c r="K519" s="43"/>
+      <c r="L519" s="47"/>
+      <c r="M519" s="43"/>
+    </row>
+    <row r="520" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A520" s="22">
+        <v>519</v>
+      </c>
+      <c r="B520" s="44"/>
+      <c r="C520" s="45"/>
+      <c r="D520" s="43"/>
+      <c r="E520" s="43"/>
+      <c r="F520" s="43"/>
+      <c r="G520" s="43"/>
+      <c r="H520" s="43"/>
+      <c r="I520" s="43"/>
+      <c r="J520" s="43"/>
+      <c r="K520" s="43"/>
+      <c r="L520" s="47"/>
+      <c r="M520" s="43"/>
+    </row>
+    <row r="521" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A521" s="39">
+        <v>520</v>
+      </c>
+      <c r="B521" s="44"/>
+      <c r="C521" s="45"/>
+      <c r="D521" s="43"/>
+      <c r="E521" s="43"/>
+      <c r="F521" s="43"/>
+      <c r="G521" s="43"/>
+      <c r="H521" s="43"/>
+      <c r="I521" s="43"/>
+      <c r="J521" s="43"/>
+      <c r="K521" s="43"/>
+      <c r="L521" s="47"/>
+      <c r="M521" s="43"/>
+    </row>
+    <row r="522" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A522" s="30">
+        <v>521</v>
+      </c>
+      <c r="B522" s="44"/>
+      <c r="C522" s="45"/>
+      <c r="D522" s="43"/>
+      <c r="E522" s="43"/>
+      <c r="F522" s="43"/>
+      <c r="G522" s="43"/>
+      <c r="H522" s="43"/>
+      <c r="I522" s="43"/>
+      <c r="J522" s="43"/>
+      <c r="K522" s="43"/>
+      <c r="L522" s="47"/>
+      <c r="M522" s="43"/>
+    </row>
+    <row r="523" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A523" s="39">
+        <v>522</v>
+      </c>
+      <c r="B523" s="44"/>
+      <c r="C523" s="45"/>
+      <c r="D523" s="43"/>
+      <c r="E523" s="43"/>
+      <c r="F523" s="43"/>
+      <c r="G523" s="43"/>
+      <c r="H523" s="43"/>
+      <c r="I523" s="43"/>
+      <c r="J523" s="43"/>
+      <c r="K523" s="43"/>
+      <c r="L523" s="47"/>
+      <c r="M523" s="43"/>
+    </row>
+    <row r="524" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A524" s="30">
+        <v>523</v>
+      </c>
+      <c r="B524" s="44"/>
+      <c r="C524" s="45"/>
+      <c r="D524" s="43"/>
+      <c r="E524" s="43"/>
+      <c r="F524" s="43"/>
+      <c r="G524" s="43"/>
+      <c r="H524" s="43"/>
+      <c r="I524" s="43"/>
+      <c r="J524" s="43"/>
+      <c r="K524" s="43"/>
+      <c r="L524" s="47"/>
+      <c r="M524" s="43"/>
+    </row>
+    <row r="525" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A525" s="22">
+        <v>524</v>
+      </c>
+      <c r="B525" s="44"/>
+      <c r="C525" s="45"/>
+      <c r="D525" s="43"/>
+      <c r="E525" s="43"/>
+      <c r="F525" s="43"/>
+      <c r="G525" s="43"/>
+      <c r="H525" s="43"/>
+      <c r="I525" s="43"/>
+      <c r="J525" s="43"/>
+      <c r="K525" s="43"/>
+      <c r="L525" s="47"/>
+      <c r="M525" s="43"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:M15 L16:M16 A16:K18 M17:M18 A19:M60 A61:I61 K61:M61 A62:M90 A91:J91 L91:M91 A92:M110 A111:J112 L111:M112 A113:M126 A127:J129 L127:M129 A130:M162 A163:J163 L163:M163 A164:M307">
-    <cfRule type="expression" dxfId="79" priority="116">
+  <conditionalFormatting sqref="A2:M5 L16:M16 B16:K18 M17:M18 B19:M60 B61:I61 K61:M61 B62:M90 B91:J91 L91:M91 B92:M110 B111:J112 L111:M112 B113:M126 B127:J129 L127:M129 B130:M162 B163:J163 L163:M163 B164:M307 B6:M15 A6:A318 A321 A324 A327 A330 A333 A336 A339 A342 A345 A348 A351 A354 A357 A360 A363 A366 A369 A372 A375 A378 A381 A384 A387 A390 A393 A396 A399 A402 A405 A408 A411 A414 A417 A420 A423 A426 A429 A432 A435 A438 A441 A444 A447 A450 A453 A456 A459 A462 A465 A470 A475 A480 A485 A490 A495 A500 A505 A510 A515 A520 A525">
+    <cfRule type="expression" dxfId="71" priority="128">
       <formula>$J2="PENDIENTE"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="78" priority="117">
+    <cfRule type="expression" dxfId="70" priority="129">
       <formula>$J2="EN ATENCIÓN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="77" priority="118">
+    <cfRule type="expression" dxfId="69" priority="130">
       <formula>$J2="EN ATENCION"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="76" priority="119">
+    <cfRule type="expression" dxfId="68" priority="131">
       <formula>$J2="PROGRAMADO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="75" priority="120">
+    <cfRule type="expression" dxfId="67" priority="132">
       <formula>$J2="INFORMATIVO"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A19:M60 A2:M15 L16:M16 A16:K18 M17:M18 A61:I61 K61:M61 A62:M90 A91:J91 L91:M91 A92:M110 A111:J112 L111:M112 A113:M126 A127:J129 L127:M129 A130:M162 A163:J163 L163:M163 A164:M307">
-    <cfRule type="expression" dxfId="74" priority="115">
+  <conditionalFormatting sqref="B19:M60 A2:M5 L16:M16 B16:K18 M17:M18 B61:I61 K61:M61 B62:M90 B91:J91 L91:M91 B92:M110 B111:J112 L111:M112 B113:M126 B127:J129 L127:M129 B130:M162 B163:J163 L163:M163 B164:M307 B6:M15 A6:A318 A321 A324 A327 A330 A333 A336 A339 A342 A345 A348 A351 A354 A357 A360 A363 A366 A369 A372 A375 A378 A381 A384 A387 A390 A393 A396 A399 A402 A405 A408 A411 A414 A417 A420 A423 A426 A429 A432 A435 A438 A441 A444 A447 A450 A453 A456 A459 A462 A465 A470 A475 A480 A485 A490 A495 A500 A505 A510 A515 A520 A525">
+    <cfRule type="expression" dxfId="66" priority="127">
       <formula>$J2="ATENDIDO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K91">
-    <cfRule type="expression" dxfId="67" priority="7">
+    <cfRule type="expression" dxfId="65" priority="19">
       <formula>$J91="ATENDIDO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="66" priority="8">
+    <cfRule type="expression" dxfId="64" priority="20">
       <formula>$J91="PENDIENTE"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="65" priority="9">
+    <cfRule type="expression" dxfId="63" priority="21">
       <formula>$J91="EN ATENCIÓN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="64" priority="10">
+    <cfRule type="expression" dxfId="62" priority="22">
       <formula>$J91="EN ATENCION"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="63" priority="11">
+    <cfRule type="expression" dxfId="61" priority="23">
       <formula>$J91="PROGRAMADO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="62" priority="12">
+    <cfRule type="expression" dxfId="60" priority="24">
       <formula>$J91="INFORMATIVO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K111">
-    <cfRule type="expression" dxfId="61" priority="1">
+    <cfRule type="expression" dxfId="59" priority="13">
       <formula>$J111="ATENDIDO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="60" priority="2">
+    <cfRule type="expression" dxfId="58" priority="14">
       <formula>$J111="PENDIENTE"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="59" priority="3">
+    <cfRule type="expression" dxfId="57" priority="15">
       <formula>$J111="EN ATENCIÓN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="58" priority="4">
+    <cfRule type="expression" dxfId="56" priority="16">
       <formula>$J111="EN ATENCION"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="57" priority="5">
+    <cfRule type="expression" dxfId="55" priority="17">
       <formula>$J111="PROGRAMADO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="56" priority="6">
+    <cfRule type="expression" dxfId="54" priority="18">
       <formula>$J111="INFORMATIVO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K127">
-    <cfRule type="expression" dxfId="55" priority="25">
+    <cfRule type="expression" dxfId="53" priority="37">
       <formula>$J127="ATENDIDO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="54" priority="26">
+    <cfRule type="expression" dxfId="52" priority="38">
       <formula>$J127="PENDIENTE"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="53" priority="27">
+    <cfRule type="expression" dxfId="51" priority="39">
       <formula>$J127="EN ATENCIÓN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="52" priority="28">
+    <cfRule type="expression" dxfId="50" priority="40">
       <formula>$J127="EN ATENCION"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="51" priority="29">
+    <cfRule type="expression" dxfId="49" priority="41">
       <formula>$J127="PROGRAMADO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="50" priority="30">
+    <cfRule type="expression" dxfId="48" priority="42">
       <formula>$J127="INFORMATIVO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K129">
-    <cfRule type="expression" dxfId="49" priority="19">
+    <cfRule type="expression" dxfId="47" priority="31">
       <formula>$J129="ATENDIDO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="48" priority="20">
+    <cfRule type="expression" dxfId="46" priority="32">
       <formula>$J129="PENDIENTE"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="47" priority="21">
+    <cfRule type="expression" dxfId="45" priority="33">
       <formula>$J129="EN ATENCIÓN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="46" priority="22">
+    <cfRule type="expression" dxfId="44" priority="34">
       <formula>$J129="EN ATENCION"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="23">
+    <cfRule type="expression" dxfId="43" priority="35">
       <formula>$J129="PROGRAMADO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="44" priority="24">
+    <cfRule type="expression" dxfId="42" priority="36">
       <formula>$J129="INFORMATIVO"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="L17">
+    <cfRule type="expression" dxfId="41" priority="67">
+      <formula>$J17="ATENDIDO"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="40" priority="68">
+      <formula>$J17="PENDIENTE"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="39" priority="69">
+      <formula>$J17="EN ATENCIÓN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="38" priority="70">
+      <formula>$J17="EN ATENCION"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="37" priority="71">
+      <formula>$J17="PROGRAMADO"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="36" priority="72">
+      <formula>$J17="INFORMATIVO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L18">
+    <cfRule type="expression" dxfId="35" priority="139">
+      <formula>$J17="ATENDIDO"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="34" priority="140">
+      <formula>$J17="PENDIENTE"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="33" priority="141">
+      <formula>$J17="EN ATENCIÓN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="32" priority="142">
+      <formula>$J17="EN ATENCION"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="31" priority="143">
+      <formula>$J17="PROGRAMADO"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="30" priority="144">
+      <formula>$J17="INFORMATIVO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L20:L21">
+    <cfRule type="expression" dxfId="29" priority="61">
+      <formula>$J18="ATENDIDO"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="28" priority="62">
+      <formula>$J18="PENDIENTE"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="27" priority="63">
+      <formula>$J18="EN ATENCIÓN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="26" priority="64">
+      <formula>$J18="EN ATENCION"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="25" priority="65">
+      <formula>$J18="PROGRAMADO"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="24" priority="66">
+      <formula>$J18="INFORMATIVO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L26">
+    <cfRule type="expression" dxfId="23" priority="55">
+      <formula>$J24="ATENDIDO"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="56">
+      <formula>$J24="PENDIENTE"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="21" priority="57">
+      <formula>$J24="EN ATENCIÓN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="20" priority="58">
+      <formula>$J24="EN ATENCION"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="19" priority="59">
+      <formula>$J24="PROGRAMADO"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="18" priority="60">
+      <formula>$J24="INFORMATIVO"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="K424">
-    <cfRule type="expression" dxfId="43" priority="37">
+    <cfRule type="expression" dxfId="17" priority="7">
       <formula>$J424="ATENDIDO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="42" priority="38">
+    <cfRule type="expression" dxfId="16" priority="8">
       <formula>$J424="PENDIENTE"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="41" priority="39">
+    <cfRule type="expression" dxfId="15" priority="9">
       <formula>$J424="EN ATENCIÓN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="40" priority="40">
+    <cfRule type="expression" dxfId="14" priority="10">
       <formula>$J424="EN ATENCION"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="39" priority="41">
+    <cfRule type="expression" dxfId="13" priority="11">
       <formula>$J424="PROGRAMADO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="42">
+    <cfRule type="expression" dxfId="12" priority="12">
       <formula>$J424="INFORMATIVO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K426">
-    <cfRule type="expression" dxfId="37" priority="31">
+    <cfRule type="expression" dxfId="11" priority="1">
       <formula>$J426="ATENDIDO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="36" priority="32">
+    <cfRule type="expression" dxfId="10" priority="2">
       <formula>$J426="PENDIENTE"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="35" priority="33">
+    <cfRule type="expression" dxfId="9" priority="3">
       <formula>$J426="EN ATENCIÓN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="34" priority="34">
+    <cfRule type="expression" dxfId="8" priority="4">
       <formula>$J426="EN ATENCION"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="33" priority="35">
+    <cfRule type="expression" dxfId="7" priority="5">
       <formula>$J426="PROGRAMADO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="32" priority="36">
+    <cfRule type="expression" dxfId="6" priority="6">
       <formula>$J426="INFORMATIVO"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L17">
-    <cfRule type="expression" dxfId="31" priority="55">
-      <formula>$J17="ATENDIDO"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="30" priority="56">
-      <formula>$J17="PENDIENTE"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="29" priority="57">
-      <formula>$J17="EN ATENCIÓN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="28" priority="58">
-      <formula>$J17="EN ATENCION"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="27" priority="59">
-      <formula>$J17="PROGRAMADO"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="26" priority="60">
-      <formula>$J17="INFORMATIVO"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L18">
-    <cfRule type="expression" dxfId="25" priority="127">
-      <formula>$J17="ATENDIDO"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="24" priority="128">
-      <formula>$J17="PENDIENTE"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="23" priority="129">
-      <formula>$J17="EN ATENCIÓN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="22" priority="130">
-      <formula>$J17="EN ATENCION"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="21" priority="131">
-      <formula>$J17="PROGRAMADO"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="20" priority="132">
-      <formula>$J17="INFORMATIVO"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L20:L21">
-    <cfRule type="expression" dxfId="19" priority="49">
-      <formula>$J18="ATENDIDO"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="18" priority="50">
-      <formula>$J18="PENDIENTE"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="17" priority="51">
-      <formula>$J18="EN ATENCIÓN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="16" priority="52">
-      <formula>$J18="EN ATENCION"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="15" priority="53">
-      <formula>$J18="PROGRAMADO"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="14" priority="54">
-      <formula>$J18="INFORMATIVO"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L26">
-    <cfRule type="expression" dxfId="13" priority="43">
-      <formula>$J24="ATENDIDO"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="12" priority="44">
-      <formula>$J24="PENDIENTE"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="11" priority="45">
-      <formula>$J24="EN ATENCIÓN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="10" priority="46">
-      <formula>$J24="EN ATENCION"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="9" priority="47">
-      <formula>$J24="PROGRAMADO"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="8" priority="48">
-      <formula>$J24="INFORMATIVO"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -21495,22 +25047,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:F3">
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="5" priority="1">
       <formula>$J2="ATENDIDO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="2">
+    <cfRule type="expression" dxfId="4" priority="2">
       <formula>$J2="PENDIENTE"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="3">
+    <cfRule type="expression" dxfId="3" priority="3">
       <formula>$J2="EN ATENCIÓN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="4">
+    <cfRule type="expression" dxfId="2" priority="4">
       <formula>$J2="EN ATENCION"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="5">
+    <cfRule type="expression" dxfId="1" priority="5">
       <formula>$J2="PROGRAMADO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="6">
+    <cfRule type="expression" dxfId="0" priority="6">
       <formula>$J2="INFORMATIVO"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/CONSOLIDADO DASHBOARD VILLA.xlsx
+++ b/CONSOLIDADO DASHBOARD VILLA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FCHAVEZC\Desktop\KPIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D67BC2B2-8269-444E-B8AB-12CFC5C2C9E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2AB9575-EEB6-4616-9FC8-F35CCE972CCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4689" uniqueCount="1270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4711" uniqueCount="1274">
   <si>
     <t>ID</t>
   </si>
@@ -3831,6 +3831,18 @@
   </si>
   <si>
     <t>POZO TUBULAR</t>
+  </si>
+  <si>
+    <t>cerrajeria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">servicios generales </t>
+  </si>
+  <si>
+    <t>limpieza</t>
+  </si>
+  <si>
+    <t>Informativo</t>
   </si>
 </sst>
 </file>
@@ -4290,6 +4302,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFE7E6E6"/>
           <bgColor rgb="FFE7E6E6"/>
         </patternFill>
@@ -4300,6 +4320,230 @@
         <patternFill patternType="solid">
           <fgColor rgb="FFBDD7EE"/>
           <bgColor rgb="FFBDD7EE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFE699"/>
+          <bgColor rgb="FFFFE699"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFE699"/>
+          <bgColor rgb="FFFFE699"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE7E6E6"/>
+          <bgColor rgb="FFE7E6E6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFE699"/>
+          <bgColor rgb="FFFFE699"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFE699"/>
+          <bgColor rgb="FFFFE699"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBDD7EE"/>
+          <bgColor rgb="FFBDD7EE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFE699"/>
+          <bgColor rgb="FFFFE699"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE7E6E6"/>
+          <bgColor rgb="FFE7E6E6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBDD7EE"/>
+          <bgColor rgb="FFBDD7EE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFE699"/>
+          <bgColor rgb="FFFFE699"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFE699"/>
+          <bgColor rgb="FFFFE699"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFE699"/>
+          <bgColor rgb="FFFFE699"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE7E6E6"/>
+          <bgColor rgb="FFE7E6E6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBDD7EE"/>
+          <bgColor rgb="FFBDD7EE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFE699"/>
+          <bgColor rgb="FFFFE699"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBDD7EE"/>
+          <bgColor rgb="FFBDD7EE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFE699"/>
+          <bgColor rgb="FFFFE699"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE7E6E6"/>
+          <bgColor rgb="FFE7E6E6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE7E6E6"/>
+          <bgColor rgb="FFE7E6E6"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4338,240 +4582,8 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFE7E6E6"/>
-          <bgColor rgb="FFE7E6E6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
           <fgColor rgb="FFBDD7EE"/>
           <bgColor rgb="FFBDD7EE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFE699"/>
-          <bgColor rgb="FFFFE699"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFE699"/>
-          <bgColor rgb="FFFFE699"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE7E6E6"/>
-          <bgColor rgb="FFE7E6E6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBDD7EE"/>
-          <bgColor rgb="FFBDD7EE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFE699"/>
-          <bgColor rgb="FFFFE699"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFE699"/>
-          <bgColor rgb="FFFFE699"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE7E6E6"/>
-          <bgColor rgb="FFE7E6E6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBDD7EE"/>
-          <bgColor rgb="FFBDD7EE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFE699"/>
-          <bgColor rgb="FFFFE699"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFE699"/>
-          <bgColor rgb="FFFFE699"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE7E6E6"/>
-          <bgColor rgb="FFE7E6E6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBDD7EE"/>
-          <bgColor rgb="FFBDD7EE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFE699"/>
-          <bgColor rgb="FFFFE699"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFE699"/>
-          <bgColor rgb="FFFFE699"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE7E6E6"/>
-          <bgColor rgb="FFE7E6E6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBDD7EE"/>
-          <bgColor rgb="FFBDD7EE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFE699"/>
-          <bgColor rgb="FFFFE699"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFE699"/>
-          <bgColor rgb="FFFFE699"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4658,16 +4670,16 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFE699"/>
-          <bgColor rgb="FFFFE699"/>
+          <fgColor rgb="FFF4CCCC"/>
+          <bgColor rgb="FFF4CCCC"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
+          <fgColor rgb="FFFFE699"/>
+          <bgColor rgb="FFFFE699"/>
         </patternFill>
       </fill>
     </dxf>
@@ -22186,6 +22198,9 @@
         <v>129</v>
       </c>
       <c r="G442" t="s">
+        <v>1195</v>
+      </c>
+      <c r="H442" t="s">
         <v>1142</v>
       </c>
       <c r="I442" t="s">
@@ -22221,6 +22236,9 @@
         <v>1147</v>
       </c>
       <c r="G443" t="s">
+        <v>1270</v>
+      </c>
+      <c r="H443" t="s">
         <v>1148</v>
       </c>
       <c r="I443" t="s">
@@ -22253,6 +22271,9 @@
         <v>1150</v>
       </c>
       <c r="G444" t="s">
+        <v>18</v>
+      </c>
+      <c r="H444" t="s">
         <v>1151</v>
       </c>
       <c r="I444" t="s">
@@ -22288,6 +22309,9 @@
         <v>1152</v>
       </c>
       <c r="G445" t="s">
+        <v>1271</v>
+      </c>
+      <c r="H445" t="s">
         <v>1153</v>
       </c>
       <c r="I445" t="s">
@@ -22323,6 +22347,9 @@
         <v>1150</v>
       </c>
       <c r="G446" t="s">
+        <v>1272</v>
+      </c>
+      <c r="H446" t="s">
         <v>1154</v>
       </c>
       <c r="I446" t="s">
@@ -22358,6 +22385,9 @@
         <v>1157</v>
       </c>
       <c r="G447" t="s">
+        <v>1272</v>
+      </c>
+      <c r="H447" t="s">
         <v>1158</v>
       </c>
       <c r="I447" t="s">
@@ -22393,6 +22423,9 @@
         <v>1157</v>
       </c>
       <c r="G448" t="s">
+        <v>1272</v>
+      </c>
+      <c r="H448" t="s">
         <v>1160</v>
       </c>
       <c r="I448" t="s">
@@ -22428,6 +22461,9 @@
         <v>1161</v>
       </c>
       <c r="G449" t="s">
+        <v>1273</v>
+      </c>
+      <c r="H449" t="s">
         <v>1162</v>
       </c>
       <c r="I449" t="s">
@@ -22463,6 +22499,9 @@
         <v>1150</v>
       </c>
       <c r="G450" t="s">
+        <v>18</v>
+      </c>
+      <c r="H450" t="s">
         <v>1164</v>
       </c>
       <c r="I450" t="s">
@@ -22495,6 +22534,9 @@
         <v>1150</v>
       </c>
       <c r="G451" t="s">
+        <v>18</v>
+      </c>
+      <c r="H451" t="s">
         <v>1166</v>
       </c>
       <c r="I451" t="s">
@@ -22527,6 +22569,9 @@
         <v>1150</v>
       </c>
       <c r="G452" t="s">
+        <v>1273</v>
+      </c>
+      <c r="H452" t="s">
         <v>1168</v>
       </c>
       <c r="I452" t="s">
@@ -22562,6 +22607,9 @@
         <v>1150</v>
       </c>
       <c r="G453" t="s">
+        <v>18</v>
+      </c>
+      <c r="H453" t="s">
         <v>1169</v>
       </c>
       <c r="I453" t="s">
@@ -22594,6 +22642,9 @@
         <v>1147</v>
       </c>
       <c r="G454" t="s">
+        <v>1270</v>
+      </c>
+      <c r="H454" t="s">
         <v>1171</v>
       </c>
       <c r="I454" t="s">
@@ -22626,6 +22677,9 @@
         <v>1173</v>
       </c>
       <c r="G455" t="s">
+        <v>1271</v>
+      </c>
+      <c r="H455" t="s">
         <v>1174</v>
       </c>
       <c r="I455" t="s">
@@ -22661,6 +22715,9 @@
         <v>1173</v>
       </c>
       <c r="G456" t="s">
+        <v>1270</v>
+      </c>
+      <c r="H456" t="s">
         <v>1177</v>
       </c>
       <c r="I456" t="s">
@@ -22693,6 +22750,9 @@
         <v>1173</v>
       </c>
       <c r="G457" t="s">
+        <v>1273</v>
+      </c>
+      <c r="H457" t="s">
         <v>1179</v>
       </c>
       <c r="I457" t="s">
@@ -22728,6 +22788,9 @@
         <v>1173</v>
       </c>
       <c r="G458" t="s">
+        <v>1049</v>
+      </c>
+      <c r="H458" t="s">
         <v>1182</v>
       </c>
       <c r="I458" t="s">
@@ -22757,6 +22820,9 @@
         <v>1150</v>
       </c>
       <c r="G459" t="s">
+        <v>18</v>
+      </c>
+      <c r="H459" t="s">
         <v>1184</v>
       </c>
       <c r="I459" t="s">
@@ -22789,6 +22855,9 @@
         <v>1173</v>
       </c>
       <c r="G460" t="s">
+        <v>1271</v>
+      </c>
+      <c r="H460" t="s">
         <v>1186</v>
       </c>
       <c r="I460" t="s">
@@ -22821,6 +22890,9 @@
         <v>1150</v>
       </c>
       <c r="G461" t="s">
+        <v>1270</v>
+      </c>
+      <c r="H461" t="s">
         <v>1188</v>
       </c>
       <c r="I461" t="s">
@@ -22853,6 +22925,9 @@
         <v>1150</v>
       </c>
       <c r="G462" t="s">
+        <v>18</v>
+      </c>
+      <c r="H462" t="s">
         <v>1190</v>
       </c>
       <c r="I462" t="s">
@@ -22882,6 +22957,9 @@
         <v>1192</v>
       </c>
       <c r="G463" t="s">
+        <v>1049</v>
+      </c>
+      <c r="H463" t="s">
         <v>1264</v>
       </c>
       <c r="I463" t="s">
@@ -24743,12 +24821,12 @@
       <c r="M525" s="43"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:M5 L16:M16 B16:K18 M17:M18 B19:M60 B61:I61 K61:M61 B62:M90 B91:J91 L91:M91 B92:M110 B111:J112 L111:M112 B113:M126 B127:J129 L127:M129 B130:M162 B163:J163 L163:M163 B164:M307 B6:M15 A6:A318 A321 A324 A327 A330 A333 A336 A339 A342 A345 A348 A351 A354 A357 A360 A363 A366 A369 A372 A375 A378 A381 A384 A387 A390 A393 A396 A399 A402 A405 A408 A411 A414 A417 A420 A423 A426 A429 A432 A435 A438 A441 A444 A447 A450 A453 A456 A459 A462 A465 A470 A475 A480 A485 A490 A495 A500 A505 A510 A515 A520 A525">
-    <cfRule type="expression" dxfId="71" priority="128">
+  <conditionalFormatting sqref="A2:M5 B6:M15 A6:A318 L16:M16 B16:K18 M17:M18 B19:M60 B61:I61 K61:M61 B62:M90 B91:J91 L91:M91 B92:M110 B111:J112 L111:M112 B113:M126 B127:J129 L127:M129 B130:M162 B163:J163 L163:M163 B164:M307 A321 A324 A327 A330 A333 A336 A339 A342 A345 A348 A351 A354 A357 A360 A363 A366 A369 A372 A375 A378 A381 A384 A387 A390 A393 A396 A399 A402 A405 A408 A411 A414 A417 A420 A423 A426 A429 A432 A435 A438 A441 A444 A447 A450 A453 A456 A459 A462 A465 A470 A475 A480 A485 A490 A495 A500 A505 A510 A515 A520 A525">
+    <cfRule type="expression" dxfId="71" priority="129">
+      <formula>$J2="EN ATENCIÓN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="70" priority="128">
       <formula>$J2="PENDIENTE"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="70" priority="129">
-      <formula>$J2="EN ATENCIÓN"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="69" priority="130">
       <formula>$J2="EN ATENCION"</formula>
@@ -24760,7 +24838,7 @@
       <formula>$J2="INFORMATIVO"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B19:M60 A2:M5 L16:M16 B16:K18 M17:M18 B61:I61 K61:M61 B62:M90 B91:J91 L91:M91 B92:M110 B111:J112 L111:M112 B113:M126 B127:J129 L127:M129 B130:M162 B163:J163 L163:M163 B164:M307 B6:M15 A6:A318 A321 A324 A327 A330 A333 A336 A339 A342 A345 A348 A351 A354 A357 A360 A363 A366 A369 A372 A375 A378 A381 A384 A387 A390 A393 A396 A399 A402 A405 A408 A411 A414 A417 A420 A423 A426 A429 A432 A435 A438 A441 A444 A447 A450 A453 A456 A459 A462 A465 A470 A475 A480 A485 A490 A495 A500 A505 A510 A515 A520 A525">
+  <conditionalFormatting sqref="B19:M60 A2:M5 B6:M15 A6:A318 L16:M16 B16:K18 M17:M18 B61:I61 K61:M61 B62:M90 B91:J91 L91:M91 B92:M110 B111:J112 L111:M112 B113:M126 B127:J129 L127:M129 B130:M162 B163:J163 L163:M163 B164:M307 A321 A324 A327 A330 A333 A336 A339 A342 A345 A348 A351 A354 A357 A360 A363 A366 A369 A372 A375 A378 A381 A384 A387 A390 A393 A396 A399 A402 A405 A408 A411 A414 A417 A420 A423 A426 A429 A432 A435 A438 A441 A444 A447 A450 A453 A456 A459 A462 A465 A470 A475 A480 A485 A490 A495 A500 A505 A510 A515 A520 A525">
     <cfRule type="expression" dxfId="66" priority="127">
       <formula>$J2="ATENDIDO"</formula>
     </cfRule>
@@ -24786,183 +24864,183 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K111">
-    <cfRule type="expression" dxfId="59" priority="13">
+    <cfRule type="expression" dxfId="59" priority="17">
+      <formula>$J111="PROGRAMADO"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="58" priority="13">
       <formula>$J111="ATENDIDO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="58" priority="14">
+    <cfRule type="expression" dxfId="57" priority="14">
       <formula>$J111="PENDIENTE"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="57" priority="15">
+    <cfRule type="expression" dxfId="56" priority="15">
       <formula>$J111="EN ATENCIÓN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="56" priority="16">
+    <cfRule type="expression" dxfId="55" priority="16">
       <formula>$J111="EN ATENCION"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="55" priority="17">
-      <formula>$J111="PROGRAMADO"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="54" priority="18">
       <formula>$J111="INFORMATIVO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K127">
-    <cfRule type="expression" dxfId="53" priority="37">
+    <cfRule type="expression" dxfId="53" priority="42">
+      <formula>$J127="INFORMATIVO"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="52" priority="37">
       <formula>$J127="ATENDIDO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="52" priority="38">
+    <cfRule type="expression" dxfId="51" priority="38">
       <formula>$J127="PENDIENTE"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="51" priority="39">
+    <cfRule type="expression" dxfId="50" priority="39">
       <formula>$J127="EN ATENCIÓN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="50" priority="40">
-      <formula>$J127="EN ATENCION"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="49" priority="41">
       <formula>$J127="PROGRAMADO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="48" priority="42">
-      <formula>$J127="INFORMATIVO"</formula>
+    <cfRule type="expression" dxfId="48" priority="40">
+      <formula>$J127="EN ATENCION"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K129">
-    <cfRule type="expression" dxfId="47" priority="31">
+    <cfRule type="expression" dxfId="47" priority="35">
+      <formula>$J129="PROGRAMADO"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="46" priority="36">
+      <formula>$J129="INFORMATIVO"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="45" priority="32">
+      <formula>$J129="PENDIENTE"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="44" priority="31">
       <formula>$J129="ATENDIDO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="46" priority="32">
-      <formula>$J129="PENDIENTE"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="45" priority="33">
+    <cfRule type="expression" dxfId="43" priority="33">
       <formula>$J129="EN ATENCIÓN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="44" priority="34">
+    <cfRule type="expression" dxfId="42" priority="34">
       <formula>$J129="EN ATENCION"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="43" priority="35">
-      <formula>$J129="PROGRAMADO"</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K424">
+    <cfRule type="expression" dxfId="41" priority="10">
+      <formula>$J424="EN ATENCION"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="42" priority="36">
-      <formula>$J129="INFORMATIVO"</formula>
+    <cfRule type="expression" dxfId="40" priority="11">
+      <formula>$J424="PROGRAMADO"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="39" priority="12">
+      <formula>$J424="INFORMATIVO"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="38" priority="9">
+      <formula>$J424="EN ATENCIÓN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="37" priority="7">
+      <formula>$J424="ATENDIDO"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="36" priority="8">
+      <formula>$J424="PENDIENTE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K426">
+    <cfRule type="expression" dxfId="35" priority="5">
+      <formula>$J426="PROGRAMADO"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="34" priority="4">
+      <formula>$J426="EN ATENCION"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="33" priority="3">
+      <formula>$J426="EN ATENCIÓN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="32" priority="2">
+      <formula>$J426="PENDIENTE"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="31" priority="1">
+      <formula>$J426="ATENDIDO"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="30" priority="6">
+      <formula>$J426="INFORMATIVO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L17">
-    <cfRule type="expression" dxfId="41" priority="67">
+    <cfRule type="expression" dxfId="29" priority="67">
       <formula>$J17="ATENDIDO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="40" priority="68">
-      <formula>$J17="PENDIENTE"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="39" priority="69">
+    <cfRule type="expression" dxfId="28" priority="69">
       <formula>$J17="EN ATENCIÓN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="70">
+    <cfRule type="expression" dxfId="27" priority="70">
       <formula>$J17="EN ATENCION"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="37" priority="71">
+    <cfRule type="expression" dxfId="26" priority="71">
       <formula>$J17="PROGRAMADO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="36" priority="72">
+    <cfRule type="expression" dxfId="25" priority="72">
       <formula>$J17="INFORMATIVO"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="24" priority="68">
+      <formula>$J17="PENDIENTE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L18">
-    <cfRule type="expression" dxfId="35" priority="139">
+    <cfRule type="expression" dxfId="23" priority="139">
       <formula>$J17="ATENDIDO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="34" priority="140">
+    <cfRule type="expression" dxfId="22" priority="140">
       <formula>$J17="PENDIENTE"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="33" priority="141">
+    <cfRule type="expression" dxfId="21" priority="141">
       <formula>$J17="EN ATENCIÓN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="32" priority="142">
+    <cfRule type="expression" dxfId="20" priority="142">
       <formula>$J17="EN ATENCION"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="31" priority="143">
+    <cfRule type="expression" dxfId="19" priority="143">
       <formula>$J17="PROGRAMADO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="144">
+    <cfRule type="expression" dxfId="18" priority="144">
       <formula>$J17="INFORMATIVO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L20:L21">
-    <cfRule type="expression" dxfId="29" priority="61">
+    <cfRule type="expression" dxfId="17" priority="61">
       <formula>$J18="ATENDIDO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="28" priority="62">
+    <cfRule type="expression" dxfId="16" priority="62">
       <formula>$J18="PENDIENTE"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="27" priority="63">
+    <cfRule type="expression" dxfId="15" priority="63">
       <formula>$J18="EN ATENCIÓN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="26" priority="64">
+    <cfRule type="expression" dxfId="14" priority="64">
       <formula>$J18="EN ATENCION"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="65">
+    <cfRule type="expression" dxfId="13" priority="65">
       <formula>$J18="PROGRAMADO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="66">
+    <cfRule type="expression" dxfId="12" priority="66">
       <formula>$J18="INFORMATIVO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L26">
-    <cfRule type="expression" dxfId="23" priority="55">
+    <cfRule type="expression" dxfId="11" priority="55">
       <formula>$J24="ATENDIDO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="56">
+    <cfRule type="expression" dxfId="10" priority="56">
       <formula>$J24="PENDIENTE"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="57">
+    <cfRule type="expression" dxfId="9" priority="57">
       <formula>$J24="EN ATENCIÓN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="58">
+    <cfRule type="expression" dxfId="8" priority="58">
       <formula>$J24="EN ATENCION"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="19" priority="59">
+    <cfRule type="expression" dxfId="7" priority="59">
       <formula>$J24="PROGRAMADO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="60">
+    <cfRule type="expression" dxfId="6" priority="60">
       <formula>$J24="INFORMATIVO"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K424">
-    <cfRule type="expression" dxfId="17" priority="7">
-      <formula>$J424="ATENDIDO"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="16" priority="8">
-      <formula>$J424="PENDIENTE"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="15" priority="9">
-      <formula>$J424="EN ATENCIÓN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="14" priority="10">
-      <formula>$J424="EN ATENCION"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="13" priority="11">
-      <formula>$J424="PROGRAMADO"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="12" priority="12">
-      <formula>$J424="INFORMATIVO"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K426">
-    <cfRule type="expression" dxfId="11" priority="1">
-      <formula>$J426="ATENDIDO"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="10" priority="2">
-      <formula>$J426="PENDIENTE"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="9" priority="3">
-      <formula>$J426="EN ATENCIÓN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="8" priority="4">
-      <formula>$J426="EN ATENCION"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="7" priority="5">
-      <formula>$J426="PROGRAMADO"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="6" priority="6">
-      <formula>$J426="INFORMATIVO"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/CONSOLIDADO DASHBOARD VILLA.xlsx
+++ b/CONSOLIDADO DASHBOARD VILLA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FCHAVEZC\Desktop\KPIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2AB9575-EEB6-4616-9FC8-F35CCE972CCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2653A9A-2963-4492-984D-7B520B0FBE3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CONSOLIDADO" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4711" uniqueCount="1274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5942" uniqueCount="1577">
   <si>
     <t>ID</t>
   </si>
@@ -3821,18 +3821,6 @@
     <t>Reincidencia: Puerta corrediza continúa salida de su riel y pendiente de reparación.</t>
   </si>
   <si>
-    <t xml:space="preserve">francisco chavez </t>
-  </si>
-  <si>
-    <t>Reclamo de antigüedad: Solicitud del 26 de mayo para revisión de aires acon</t>
-  </si>
-  <si>
-    <t>UZIT</t>
-  </si>
-  <si>
-    <t>POZO TUBULAR</t>
-  </si>
-  <si>
     <t>cerrajeria</t>
   </si>
   <si>
@@ -3843,6 +3831,927 @@
   </si>
   <si>
     <t>Informativo</t>
+  </si>
+  <si>
+    <t>Reclamo de antigüedad: Solicitud del 26 de mayo para revisión de aires acondicionados sigue sin atención</t>
+  </si>
+  <si>
+    <t>Reportado por Ynes (Vgu). F. Chávez indica que ha solicitado el estatus del correctivo de todo el primer piso</t>
+  </si>
+  <si>
+    <t>jose rodas</t>
+  </si>
+  <si>
+    <t>Villa</t>
+  </si>
+  <si>
+    <t>2do piso, frente a consultorios</t>
+  </si>
+  <si>
+    <t>Luz de emergencia se encendió</t>
+  </si>
+  <si>
+    <t>Reportado por Liderman y confirmado como atendido por D. Magallanes</t>
+  </si>
+  <si>
+    <t>3er piso, lado de 2da escalera</t>
+  </si>
+  <si>
+    <t>Señal de salida descolgada de un lado</t>
+  </si>
+  <si>
+    <t>Confirmado como atendido por D. Magallanes</t>
+  </si>
+  <si>
+    <t>Postes que dan al comedor</t>
+  </si>
+  <si>
+    <t>No hay luz en los postes</t>
+  </si>
+  <si>
+    <t>daniel magallanes</t>
+  </si>
+  <si>
+    <t>Luminaria parpadeando</t>
+  </si>
+  <si>
+    <t>luis matos</t>
+  </si>
+  <si>
+    <t>Filtración en el techo / formación de gotas ("grumos") de agua</t>
+  </si>
+  <si>
+    <t>Reportado por Bruno (Eulen). F. Chávez acudió a revisar el lugar</t>
+  </si>
+  <si>
+    <t>Laboratorio de Biología O-204</t>
+  </si>
+  <si>
+    <t>Casillero del laboratorio averiado</t>
+  </si>
+  <si>
+    <t>Daniel (Mantenimiento)</t>
+  </si>
+  <si>
+    <t>Reportado por Dra. Danae. Reparado inmediatamente en el turno de la noche</t>
+  </si>
+  <si>
+    <t>Escalera de terraza</t>
+  </si>
+  <si>
+    <t>Luces de la escalera encendidas</t>
+  </si>
+  <si>
+    <t>Seguridad Electronica</t>
+  </si>
+  <si>
+    <t>Sensor de humo retirado del pasillo por alta fidelidad N°1</t>
+  </si>
+  <si>
+    <t>angel yataco</t>
+  </si>
+  <si>
+    <t>baustelle deja sensor malogrado</t>
+  </si>
+  <si>
+    <t>Panel de alarma emite pitido continuo</t>
+  </si>
+  <si>
+    <t>Al lado del Aula 101, 1er piso</t>
+  </si>
+  <si>
+    <t>SSHH Mujeres, 2do piso</t>
+  </si>
+  <si>
+    <t>Servicios</t>
+  </si>
+  <si>
+    <t>Dispensador de jabón inoperativo</t>
+  </si>
+  <si>
+    <t>Zona de pozos</t>
+  </si>
+  <si>
+    <t>Pozo de agua tratada lleno</t>
+  </si>
+  <si>
+    <t>Sala de reuniones, 2do piso derecho</t>
+  </si>
+  <si>
+    <t>Aire acondicionado no funciona, control en 0</t>
+  </si>
+  <si>
+    <t>SSHH Tercer piso</t>
+  </si>
+  <si>
+    <t>Baldosa suelta</t>
+  </si>
+  <si>
+    <t>Baldosa se está desprendiendo</t>
+  </si>
+  <si>
+    <t>SSHH Hombres 1er piso, cubículo centro</t>
+  </si>
+  <si>
+    <t>Fuga de agua al bajar la palanca</t>
+  </si>
+  <si>
+    <t>Pasadizos 2do piso</t>
+  </si>
+  <si>
+    <t>Pasadizos / Áreas comunes</t>
+  </si>
+  <si>
+    <t>Mallas obstruyen el paso de la alarma contra incendio</t>
+  </si>
+  <si>
+    <t>Set de radio</t>
+  </si>
+  <si>
+    <t>Llave de set de radio con una rajadura</t>
+  </si>
+  <si>
+    <t>juan hernandez</t>
+  </si>
+  <si>
+    <t>Consultorio N°5 (L-214)</t>
+  </si>
+  <si>
+    <t>Brazo de la silla salido</t>
+  </si>
+  <si>
+    <t>1er piso, cerca al cajero Interbank</t>
+  </si>
+  <si>
+    <t>Luces de emergencia por caer</t>
+  </si>
+  <si>
+    <t>Continúa saliendo agua del caño</t>
+  </si>
+  <si>
+    <t>SSHH Varones, frente a la pileta</t>
+  </si>
+  <si>
+    <t>No tiene llave para abrir la puerta</t>
+  </si>
+  <si>
+    <t>Comedor</t>
+  </si>
+  <si>
+    <t>1 aire acondicionado averiado</t>
+  </si>
+  <si>
+    <t>SSHH Hombres 3er piso</t>
+  </si>
+  <si>
+    <t>Luces de emergencia sin indicador LED</t>
+  </si>
+  <si>
+    <t>Aula 203, parte externa</t>
+  </si>
+  <si>
+    <t>Mobiliario / Apoyo</t>
+  </si>
+  <si>
+    <t>Un caballete se observa con bisagra rota</t>
+  </si>
+  <si>
+    <t>Parte externa del Lab 206</t>
+  </si>
+  <si>
+    <t>Luces de emergencia caídas</t>
+  </si>
+  <si>
+    <t>Almacén de Eulen</t>
+  </si>
+  <si>
+    <t>Filtración de agua desde tubería</t>
+  </si>
+  <si>
+    <t>Lockers</t>
+  </si>
+  <si>
+    <t>Reparación de bisagra de Lockers</t>
+  </si>
+  <si>
+    <t>Cerrajería / Infrae.</t>
+  </si>
+  <si>
+    <t>Tornillos sueltos de la manija de la puerta</t>
+  </si>
+  <si>
+    <t>Aire acondicionado se encuentra apagado</t>
+  </si>
+  <si>
+    <t>SSHH Varones 3er piso, frente a Deisto</t>
+  </si>
+  <si>
+    <t>Fuga interna en baño</t>
+  </si>
+  <si>
+    <t>Empresa H&amp;E</t>
+  </si>
+  <si>
+    <t>Entrada principal</t>
+  </si>
+  <si>
+    <t>Áreas Verdes / Limpieza</t>
+  </si>
+  <si>
+    <t>Entrada dejada en mal estado o desordenada por jardineros</t>
+  </si>
+  <si>
+    <t>Rossy Carrera</t>
+  </si>
+  <si>
+    <t>Reportado por Roxana (Eulen). R. Carrera coordinó revisión inmediata</t>
+  </si>
+  <si>
+    <t>Seguridad Elect.</t>
+  </si>
+  <si>
+    <t>Angel Yatco - Tecnico  Electricidad</t>
+  </si>
+  <si>
+    <t>Empresa Bausteli</t>
+  </si>
+  <si>
+    <t>Dejado inoperativo por la empresa externa Bausteli</t>
+  </si>
+  <si>
+    <t>TI / Soporte</t>
+  </si>
+  <si>
+    <t>Alumno derramó jugo en el teclado</t>
+  </si>
+  <si>
+    <t>Requiere cambio/limpieza de periférico</t>
+  </si>
+  <si>
+    <t>Se cambió de pila al control de AA. Operativo</t>
+  </si>
+  <si>
+    <t>Reportado por Liderman y solucionado por SSGG</t>
+  </si>
+  <si>
+    <t>Servicios / Gasfit.</t>
+  </si>
+  <si>
+    <t>Incidencia sin especificar en baño de varones</t>
+  </si>
+  <si>
+    <t>Reportado por Roxana (Eulen)</t>
+  </si>
+  <si>
+    <t>Luces de emergencia corregidas</t>
+  </si>
+  <si>
+    <t>Servicios / Admin.</t>
+  </si>
+  <si>
+    <t>Falta de acrílicos para hojas de control de limpieza</t>
+  </si>
+  <si>
+    <t>Rossy Carrera solicita apoyo con fotos como evidencia</t>
+  </si>
+  <si>
+    <t>Revisado y atendido por SSGG</t>
+  </si>
+  <si>
+    <t>Trabajo realizado correctamente</t>
+  </si>
+  <si>
+    <t>Fuga reparada y solucionada</t>
+  </si>
+  <si>
+    <t>Comunicado a SSGG para conocimiento del supervisor</t>
+  </si>
+  <si>
+    <t>Reinstalado y solucionado</t>
+  </si>
+  <si>
+    <t>Ingresó el técnico y reparó la bisagra</t>
+  </si>
+  <si>
+    <t>Puerta de uno de los cubículos se ha caído</t>
+  </si>
+  <si>
+    <t>Reportado por Angélica y Roxana (Eulen)</t>
+  </si>
+  <si>
+    <t>Todo el pabellón</t>
+  </si>
+  <si>
+    <t>Corte total de agua por filtración grave</t>
+  </si>
+  <si>
+    <t>Crítica</t>
+  </si>
+  <si>
+    <t>Proveedor por definir</t>
+  </si>
+  <si>
+    <t>Se cerró el paso de agua preventivamente en espera de un proveedor técnico</t>
+  </si>
+  <si>
+    <t>Puerta malograda en el cubículo #1</t>
+  </si>
+  <si>
+    <t>Reportado por Ana (Eulen)</t>
+  </si>
+  <si>
+    <t>Se dio la atención inmediata al equipo</t>
+  </si>
+  <si>
+    <t>Empresa externa trabajando en el lugar</t>
+  </si>
+  <si>
+    <t>Plaza 2</t>
+  </si>
+  <si>
+    <t>Incidencia en mesa de la plaza</t>
+  </si>
+  <si>
+    <t>Exterior posterior del Comedor</t>
+  </si>
+  <si>
+    <t>Adoquines salidos en el piso</t>
+  </si>
+  <si>
+    <t>Reportado al cierre del turno</t>
+  </si>
+  <si>
+    <t>Iluminación</t>
+  </si>
+  <si>
+    <t>Luces de escalera se encuentran encendidas.</t>
+  </si>
+  <si>
+    <t>Se requiere apagar/revisar sensor.</t>
+  </si>
+  <si>
+    <t>SSHH Varón administrativo - 1er piso</t>
+  </si>
+  <si>
+    <t>La baldosa del techo se cayó.</t>
+  </si>
+  <si>
+    <t>Requiere reposición de baldosa.</t>
+  </si>
+  <si>
+    <t>Se observa la pileta apagada.</t>
+  </si>
+  <si>
+    <t>Angel Yataco</t>
+  </si>
+  <si>
+    <t>Revisión del sistema de la pileta.</t>
+  </si>
+  <si>
+    <t>Se observa mallas en el área.</t>
+  </si>
+  <si>
+    <t>Mallas guardadas o acumuladas en la zona.</t>
+  </si>
+  <si>
+    <t>Seguridad (ACI)</t>
+  </si>
+  <si>
+    <t>El panel de alarma contra incendio emite un pitido.</t>
+  </si>
+  <si>
+    <t>Se procede a silenciar por Liderman de forma recurrente.</t>
+  </si>
+  <si>
+    <t>Continúa el panel de aire acondicionado apagado.</t>
+  </si>
+  <si>
+    <t>Zona crítica requiere climatización constante.</t>
+  </si>
+  <si>
+    <t>Pasillo al costado de Alta Fidelidad N°1</t>
+  </si>
+  <si>
+    <t>Continúa el sensor de humo retirado del pasillo.</t>
+  </si>
+  <si>
+    <t>Falta reinstalar sensor en su posición original.</t>
+  </si>
+  <si>
+    <t>Se observa el cartel de números de aula despegándose.</t>
+  </si>
+  <si>
+    <t>Requiere pegado o asegurar el cartel.</t>
+  </si>
+  <si>
+    <t>SSHH de Hombres - 2do piso</t>
+  </si>
+  <si>
+    <t>El urinario se encuentra rajado.</t>
+  </si>
+  <si>
+    <t>Requiere cambio de loza sanitaria.</t>
+  </si>
+  <si>
+    <t>SSHH Varones - 3er y 1er piso (frente a Listo)</t>
+  </si>
+  <si>
+    <t>Fuga interna reportada a las 15:42h del día anterior.</t>
+  </si>
+  <si>
+    <t>Solucionado</t>
+  </si>
+  <si>
+    <t>Quedó operativo y reparado a las 08:00 AM.</t>
+  </si>
+  <si>
+    <t>Panel de alarma contra incendio continúa con pitido.</t>
+  </si>
+  <si>
+    <t>Reincidencia. Se vuelve a silenciar.</t>
+  </si>
+  <si>
+    <t>Hall principal</t>
+  </si>
+  <si>
+    <t>Infraestructura / Pintura</t>
+  </si>
+  <si>
+    <t>Zócalos sueltos detrás del mueble grande y pared pelada.</t>
+  </si>
+  <si>
+    <t>Requiere trabajos de pintura y asegurar zócalo.</t>
+  </si>
+  <si>
+    <t>Laboratorio de Arquitectura 103</t>
+  </si>
+  <si>
+    <t>Vidriería / Mallas</t>
+  </si>
+  <si>
+    <t>Balón rompió la ventana (malla) desde la cancha. Está por caer.</t>
+  </si>
+  <si>
+    <t>Riesgo de caída de fragmentos. Están en clase.</t>
+  </si>
+  <si>
+    <t>Se activa pitido continuamente en panel de alarma.</t>
+  </si>
+  <si>
+    <t>Tercer reporte del estado del panel.</t>
+  </si>
+  <si>
+    <t>Pasadizos - 2do piso</t>
+  </si>
+  <si>
+    <t>Lámpara se encuentra a punto de desprenderse.</t>
+  </si>
+  <si>
+    <t>Riesgo de caída. Requiere fijación urgente.</t>
+  </si>
+  <si>
+    <t>Al costado del Lab. de Robótica</t>
+  </si>
+  <si>
+    <t>Se encuentra salida la puerta del casillero (Locker).</t>
+  </si>
+  <si>
+    <t>Requiere reparación de bisagra/puerta.</t>
+  </si>
+  <si>
+    <t>Pabellón N (PN)</t>
+  </si>
+  <si>
+    <t>SSHH Varones - 3er piso</t>
+  </si>
+  <si>
+    <t>Puerta en mal estado y no sale agua.</t>
+  </si>
+  <si>
+    <t>Requiere habilitación de agua y reparación de puerta.</t>
+  </si>
+  <si>
+    <t>Varios</t>
+  </si>
+  <si>
+    <t>Registro</t>
+  </si>
+  <si>
+    <t>Reporte de inspección general (envío de 3 fotos).</t>
+  </si>
+  <si>
+    <t>Miriam Eulen</t>
+  </si>
+  <si>
+    <t>Archivo de control visual.</t>
+  </si>
+  <si>
+    <t>SSHH Varones - 1er piso</t>
+  </si>
+  <si>
+    <t>Cúmulo de agua reventado en la parte alta del techo.</t>
+  </si>
+  <si>
+    <t>Reporte inicial de fuga alta. Bruno realiza limpieza.</t>
+  </si>
+  <si>
+    <t>Filtración activa de agua formando cúmulos por todo el techo.</t>
+  </si>
+  <si>
+    <t>Reincidencia y agravamiento de la filtración en el techo.</t>
+  </si>
+  <si>
+    <t>Lab. Farmacología - A306</t>
+  </si>
+  <si>
+    <t>Techo humedecido en varios puntos a causa de la lluvia nocturna.</t>
+  </si>
+  <si>
+    <t>Coordinado para intervenir el 14/06 entre las 13:40 y 15:20, o a partir de las 18:40.</t>
+  </si>
+  <si>
+    <t>Lab. Fisiología 2 - A304</t>
+  </si>
+  <si>
+    <t>Nueva filtración de agua por baldosa; esta vez goteó sobre equipos.</t>
+  </si>
+  <si>
+    <t>Aula ocupada el 13/06. Coordinado espacio libre para el 14/06 de 11:20 AM a 12:50 PM.</t>
+  </si>
+  <si>
+    <t>Laboratorio O308</t>
+  </si>
+  <si>
+    <t>Aire acondicionado no enfría y docente lo requiere con urgencia.</t>
+  </si>
+  <si>
+    <t>Proveedor de climatización</t>
+  </si>
+  <si>
+    <t>Inicialmente se halló el termostato mal manipulado (en ventilación). Al ser defecto del equipo, interviene proveedor en la noche (12:14 PM).</t>
+  </si>
+  <si>
+    <t>Lab. Microbiología - O310</t>
+  </si>
+  <si>
+    <t>Se solicita apoyo para la reparación/revisión de uno de los casilleros.</t>
+  </si>
+  <si>
+    <t>Reportado por personal del laboratorio.</t>
+  </si>
+  <si>
+    <t>Aula K 108</t>
+  </si>
+  <si>
+    <t>La pared se encuentra en mal estado.</t>
+  </si>
+  <si>
+    <t>Proveedor externo</t>
+  </si>
+  <si>
+    <t>Juan H. confirma que ya está mapeado con proveedor.</t>
+  </si>
+  <si>
+    <t>Almacén - 3er piso</t>
+  </si>
+  <si>
+    <t>Cerramientos</t>
+  </si>
+  <si>
+    <t>No abre la puerta con la llave; no pueden sacar pertenencias.</t>
+  </si>
+  <si>
+    <t>Juan Hernandez</t>
+  </si>
+  <si>
+    <t>Se realizó el cambio de cerradura y se entregó la llave a Bruno (09:42 AM).</t>
+  </si>
+  <si>
+    <t>Áreas Verdes</t>
+  </si>
+  <si>
+    <t>Biohuerto</t>
+  </si>
+  <si>
+    <t>Jardinería</t>
+  </si>
+  <si>
+    <t>Observaciones pendientes en la zona del biohuerto.</t>
+  </si>
+  <si>
+    <t>Bruno Eulen</t>
+  </si>
+  <si>
+    <t>Se levantaron las observaciones y se hizo limpieza (08:28 AM).</t>
+  </si>
+  <si>
+    <t>Pabellón A (PA)</t>
+  </si>
+  <si>
+    <t>Lab. Fisiología 2 - PA304</t>
+  </si>
+  <si>
+    <t>Se identifica baldosa del techo deteriorada y desprendida (reincidencia de filtración).</t>
+  </si>
+  <si>
+    <t>Personal técnico</t>
+  </si>
+  <si>
+    <t>Se aprovecha ventana de tiempo libre informada en el laboratorio hasta las 12:50 PM para su evaluación.</t>
+  </si>
+  <si>
+    <t>Inhabilitado el soporte para teclado y mouse.</t>
+  </si>
+  <si>
+    <t>Soporte dañado, requiere reparación técnica.</t>
+  </si>
+  <si>
+    <t>Sala de estudio - Pasadizo principal</t>
+  </si>
+  <si>
+    <t>Mallas de protección se encuentran en mal estado.</t>
+  </si>
+  <si>
+    <t>Requiere tensado o cambio de mallas.</t>
+  </si>
+  <si>
+    <t>Seguridad / Accesos</t>
+  </si>
+  <si>
+    <t>Mallas obstruyen el pase al tablero de alarma ACI.</t>
+  </si>
+  <si>
+    <t>Obstrucción de equipos de emergencia. Liberar área.</t>
+  </si>
+  <si>
+    <t>La llave de ingreso al set de radio está rajada por ambos lados.</t>
+  </si>
+  <si>
+    <t>Requiere cambio de llave / cerradura.</t>
+  </si>
+  <si>
+    <t>Costado del ascensor</t>
+  </si>
+  <si>
+    <t>Señalización por despegarse.</t>
+  </si>
+  <si>
+    <t>José Rodas (SS.GG)</t>
+  </si>
+  <si>
+    <t>Confirmado como solucionado a las 10:07 AM.</t>
+  </si>
+  <si>
+    <t>Consultorios 1er y 2do piso, SSHH, Farmacia</t>
+  </si>
+  <si>
+    <t>Cantidad excesiva de mosquitos en pasillos y áreas de salud.</t>
+  </si>
+  <si>
+    <t>Requiere fumigación/control de plagas en zona médica.</t>
+  </si>
+  <si>
+    <t>Oficina de Contact Center</t>
+  </si>
+  <si>
+    <t>Cerramientos / Puertas</t>
+  </si>
+  <si>
+    <t>Alumnos y personal encerrados por desperfecto en puerta de aluminio.</t>
+  </si>
+  <si>
+    <t>Puerta destrabada. Solucionado a las 10:01 AM.</t>
+  </si>
+  <si>
+    <t>Lab. Anatomía Animal 103</t>
+  </si>
+  <si>
+    <t>Limpieza / Mantenimiento</t>
+  </si>
+  <si>
+    <t>Baldosa del techo se encuentra manchada.</t>
+  </si>
+  <si>
+    <t>Limpieza / cambio efectuado a las 10:26 AM.</t>
+  </si>
+  <si>
+    <t>Baño de Damas</t>
+  </si>
+  <si>
+    <t>Objetos Perdidos</t>
+  </si>
+  <si>
+    <t>Se halló short azul de la Fed. de Wushu.</t>
+  </si>
+  <si>
+    <t>AVP K. Amezquita</t>
+  </si>
+  <si>
+    <t>Derivado al área de CCTV para seguimiento.</t>
+  </si>
+  <si>
+    <t>Aula 103</t>
+  </si>
+  <si>
+    <t>Sin energía eléctrica en tomacorrientes negros y amarillos.</t>
+  </si>
+  <si>
+    <t>Sin energía para clases; requiere revisión de llaves térmicas.</t>
+  </si>
+  <si>
+    <t>LAB-304</t>
+  </si>
+  <si>
+    <t>Mobiliario educativo</t>
+  </si>
+  <si>
+    <t>Pantalla Ecran se cayó encima de exposición. Alumno ileso.</t>
+  </si>
+  <si>
+    <t>Ingresó personal a las 11:06 AM, retiró el dañado e instaló uno nuevo.</t>
+  </si>
+  <si>
+    <t>3er piso - Lado de 2da escalera</t>
+  </si>
+  <si>
+    <t>Señal de salida descolgada de los dos lados.</t>
+  </si>
+  <si>
+    <t>Requiere ser colgada correctamente para evacuación.</t>
+  </si>
+  <si>
+    <t>Continúa con el caño inhabilitado.</t>
+  </si>
+  <si>
+    <t>Requiere reparación o cambio de grifería.</t>
+  </si>
+  <si>
+    <t>Al lado del Aula 101 - 1er piso</t>
+  </si>
+  <si>
+    <t>Luminaria encendida en horario diurno.</t>
+  </si>
+  <si>
+    <t>Revisar encendido automático o interruptor.</t>
+  </si>
+  <si>
+    <t>SSHH Damas y Varones - 3er piso</t>
+  </si>
+  <si>
+    <t>Baños se encuentran completamente inhabilitados.</t>
+  </si>
+  <si>
+    <t>Clausura temporal. Requiere atención urgente por afluencia.</t>
+  </si>
+  <si>
+    <t>Pasadizos - 1er piso</t>
+  </si>
+  <si>
+    <t>Seguridad / Señalética</t>
+  </si>
+  <si>
+    <t>Los parantes de los extintores no tienen señalética reglamentaria.</t>
+  </si>
+  <si>
+    <t>Falta colocar los carteles de extintor.</t>
+  </si>
+  <si>
+    <t>El filo de aluminio de la pizarra acrílica se desprendió.</t>
+  </si>
+  <si>
+    <t>Requiere reparación de perfil de la pizarra.</t>
+  </si>
+  <si>
+    <t>Aula 302</t>
+  </si>
+  <si>
+    <t>Se observa que el Ecran de la pizarra se despegó.</t>
+  </si>
+  <si>
+    <t>Requiere volver a pegar o fijar el ecran.</t>
+  </si>
+  <si>
+    <t>Baño de varones (Cafetería)</t>
+  </si>
+  <si>
+    <t>Chapa de la puerta se encuentra rota.</t>
+  </si>
+  <si>
+    <t>Reportado por Miriam Eulen; requiere cambio de chapa.</t>
+  </si>
+  <si>
+    <t>Sanitarios</t>
+  </si>
+  <si>
+    <t>Se encontró la tapa del inodoro salida.</t>
+  </si>
+  <si>
+    <t>Reparado y colocado en su posición a las 08:46 AM.</t>
+  </si>
+  <si>
+    <t>Pabellón K (PK)</t>
+  </si>
+  <si>
+    <t>Inodoro se encuentra sin tapa.</t>
+  </si>
+  <si>
+    <t>Repuesto / Solucionado a las 09:34 AM.</t>
+  </si>
+  <si>
+    <t>Lavado programado de la pileta.</t>
+  </si>
+  <si>
+    <t>Angelica (Eulen)</t>
+  </si>
+  <si>
+    <t>Labores de lavado culminadas con éxito a las 08:21 AM.</t>
+  </si>
+  <si>
+    <t>Pabellón J (PJ)</t>
+  </si>
+  <si>
+    <t>SSHH Damas - 3er piso</t>
+  </si>
+  <si>
+    <t>No hay suministro de agua en los servicios de damas.</t>
+  </si>
+  <si>
+    <t>Juan Hernandez toma conocimiento para su revisión en campo.</t>
+  </si>
+  <si>
+    <t>Se reporta desecho / residuo incorrecto en tacho de basura.</t>
+  </si>
+  <si>
+    <t>Evidencia registrada por Roxana Eulen.</t>
+  </si>
+  <si>
+    <t>Comedor de Villa 2</t>
+  </si>
+  <si>
+    <t>Silla rota en el área del comedor.</t>
+  </si>
+  <si>
+    <t>Retiro de la silla malograda ejecutado a las 02:14 PM.</t>
+  </si>
+  <si>
+    <t>Comedor de colaboradores</t>
+  </si>
+  <si>
+    <t>Control de Plagas</t>
+  </si>
+  <si>
+    <t>Olor demasiado intenso y proliferación crítica de moscas.</t>
+  </si>
+  <si>
+    <t>Personal de Rossy Carrera</t>
+  </si>
+  <si>
+    <t>Se aplicó aspersión ambiental para mitigar. Mañana se evalúa en campo (15:10h).</t>
+  </si>
+  <si>
+    <t>Piso 1</t>
+  </si>
+  <si>
+    <t>Gestión / Control</t>
+  </si>
+  <si>
+    <t>No están firmando la hoja de inspección obligatoria.</t>
+  </si>
+  <si>
+    <t>Juan H. observa la falta de firmas. Angélica reforzará con el personal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pabellón K </t>
+  </si>
+  <si>
+    <t>Comedor de Varones</t>
+  </si>
+  <si>
+    <t>Incidencia general / revisión del estado del comedor.</t>
+  </si>
+  <si>
+    <t>Registrado por Juan Hernandez.</t>
+  </si>
+  <si>
+    <t>Limpieza / Insumos</t>
+  </si>
+  <si>
+    <t>Baño de varones se encuentra sin cono de señalización/papel.</t>
+  </si>
+  <si>
+    <t>Observación levantada inmediatamente en campo a las 02:45 PM.</t>
+  </si>
+  <si>
+    <t>Seguridad / Mobiliario</t>
+  </si>
+  <si>
+    <t>Solicita retirar soporte de Ecran. Ocasionó golpe a alumno al jalarlo para usarlo. N° Valuekeep: 0000009818</t>
+  </si>
+  <si>
+    <t>Personal de SS.GG</t>
+  </si>
+  <si>
+    <t>(Nota: Coincide con reporte ID 27). Personal ingresó a retirar la estructura dañada e instaló un ecran nuevo a las 11:06 AM.</t>
   </si>
 </sst>
 </file>
@@ -3957,7 +4866,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -4101,6 +5010,18 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4845,8 +5766,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="REGISTRO_DIARIO" displayName="REGISTRO_DIARIO" ref="A1:M525" totalsRowShown="0" headerRowDxfId="86" dataDxfId="85">
-  <autoFilter ref="A1:M525" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="REGISTRO_DIARIO" displayName="REGISTRO_DIARIO" ref="A1:M636" totalsRowShown="0" headerRowDxfId="86" dataDxfId="85">
+  <autoFilter ref="A1:M636" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID" dataDxfId="84"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Fecha" dataDxfId="83"/>
@@ -5151,13 +6072,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M525"/>
+  <dimension ref="A1:M636"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="29" customWidth="1"/>
-    <col min="2" max="2" width="14" style="13" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" style="19" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="17.42578125" style="13" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" style="19" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" customWidth="1"/>
     <col min="5" max="5" width="26" customWidth="1"/>
     <col min="6" max="6" width="29.28515625" customWidth="1"/>
     <col min="7" max="7" width="21.28515625" customWidth="1"/>
@@ -22236,7 +23157,7 @@
         <v>1147</v>
       </c>
       <c r="G443" t="s">
-        <v>1270</v>
+        <v>1266</v>
       </c>
       <c r="H443" t="s">
         <v>1148</v>
@@ -22309,7 +23230,7 @@
         <v>1152</v>
       </c>
       <c r="G445" t="s">
-        <v>1271</v>
+        <v>1267</v>
       </c>
       <c r="H445" t="s">
         <v>1153</v>
@@ -22347,7 +23268,7 @@
         <v>1150</v>
       </c>
       <c r="G446" t="s">
-        <v>1272</v>
+        <v>1268</v>
       </c>
       <c r="H446" t="s">
         <v>1154</v>
@@ -22385,7 +23306,7 @@
         <v>1157</v>
       </c>
       <c r="G447" t="s">
-        <v>1272</v>
+        <v>1268</v>
       </c>
       <c r="H447" t="s">
         <v>1158</v>
@@ -22423,7 +23344,7 @@
         <v>1157</v>
       </c>
       <c r="G448" t="s">
-        <v>1272</v>
+        <v>1268</v>
       </c>
       <c r="H448" t="s">
         <v>1160</v>
@@ -22461,7 +23382,7 @@
         <v>1161</v>
       </c>
       <c r="G449" t="s">
-        <v>1273</v>
+        <v>1269</v>
       </c>
       <c r="H449" t="s">
         <v>1162</v>
@@ -22569,7 +23490,7 @@
         <v>1150</v>
       </c>
       <c r="G452" t="s">
-        <v>1273</v>
+        <v>1269</v>
       </c>
       <c r="H452" t="s">
         <v>1168</v>
@@ -22642,7 +23563,7 @@
         <v>1147</v>
       </c>
       <c r="G454" t="s">
-        <v>1270</v>
+        <v>1266</v>
       </c>
       <c r="H454" t="s">
         <v>1171</v>
@@ -22677,7 +23598,7 @@
         <v>1173</v>
       </c>
       <c r="G455" t="s">
-        <v>1271</v>
+        <v>1267</v>
       </c>
       <c r="H455" t="s">
         <v>1174</v>
@@ -22715,7 +23636,7 @@
         <v>1173</v>
       </c>
       <c r="G456" t="s">
-        <v>1270</v>
+        <v>1266</v>
       </c>
       <c r="H456" t="s">
         <v>1177</v>
@@ -22750,7 +23671,7 @@
         <v>1173</v>
       </c>
       <c r="G457" t="s">
-        <v>1273</v>
+        <v>1269</v>
       </c>
       <c r="H457" t="s">
         <v>1179</v>
@@ -22855,7 +23776,7 @@
         <v>1173</v>
       </c>
       <c r="G460" t="s">
-        <v>1271</v>
+        <v>1267</v>
       </c>
       <c r="H460" t="s">
         <v>1186</v>
@@ -22890,7 +23811,7 @@
         <v>1150</v>
       </c>
       <c r="G461" t="s">
-        <v>1270</v>
+        <v>1266</v>
       </c>
       <c r="H461" t="s">
         <v>1188</v>
@@ -24104,35 +25025,33 @@
         <v>46184</v>
       </c>
       <c r="C494" s="19">
-        <v>0.4236111111111111</v>
+        <v>0.56944444444444442</v>
       </c>
       <c r="D494" t="s">
         <v>15</v>
       </c>
       <c r="E494" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="F494" t="s">
-        <v>1187</v>
+        <v>1244</v>
       </c>
       <c r="G494" t="s">
-        <v>1134</v>
+        <v>1117</v>
       </c>
       <c r="H494" t="s">
-        <v>1242</v>
+        <v>1270</v>
       </c>
       <c r="I494" t="s">
         <v>20</v>
       </c>
       <c r="J494" t="s">
-        <v>21</v>
+        <v>1193</v>
       </c>
       <c r="K494" t="s">
-        <v>1243</v>
-      </c>
-      <c r="L494" s="49">
-        <v>46184</v>
-      </c>
+        <v>1271</v>
+      </c>
+      <c r="L494" s="49"/>
       <c r="M494" s="43"/>
     </row>
     <row r="495" spans="1:13" x14ac:dyDescent="0.25">
@@ -24143,31 +25062,31 @@
         <v>46184</v>
       </c>
       <c r="C495" s="19">
-        <v>0.56944444444444442</v>
+        <v>0.42916666666666664</v>
       </c>
       <c r="D495" t="s">
         <v>15</v>
       </c>
       <c r="E495" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="F495" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="G495" t="s">
-        <v>1117</v>
+        <v>1150</v>
       </c>
       <c r="H495" t="s">
-        <v>1267</v>
+        <v>1246</v>
       </c>
       <c r="I495" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="J495" t="s">
-        <v>1193</v>
+        <v>65</v>
       </c>
       <c r="K495" t="s">
-        <v>1266</v>
+        <v>945</v>
       </c>
       <c r="M495" s="43"/>
     </row>
@@ -24179,31 +25098,34 @@
         <v>46184</v>
       </c>
       <c r="C496" s="19">
-        <v>0.42916666666666664</v>
+        <v>0.47986111111111113</v>
       </c>
       <c r="D496" t="s">
         <v>15</v>
       </c>
       <c r="E496" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="F496" t="s">
-        <v>1245</v>
+        <v>1133</v>
       </c>
       <c r="G496" t="s">
         <v>1150</v>
       </c>
       <c r="H496" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="I496" t="s">
         <v>39</v>
       </c>
       <c r="J496" t="s">
-        <v>65</v>
+        <v>934</v>
       </c>
       <c r="K496" t="s">
-        <v>945</v>
+        <v>1272</v>
+      </c>
+      <c r="L496" s="49">
+        <v>46184</v>
       </c>
       <c r="M496" s="43"/>
     </row>
@@ -24215,22 +25137,22 @@
         <v>46184</v>
       </c>
       <c r="C497" s="19">
-        <v>0.47986111111111113</v>
+        <v>0.58680555555555558</v>
       </c>
       <c r="D497" t="s">
         <v>15</v>
       </c>
       <c r="E497" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="F497" t="s">
-        <v>1133</v>
+        <v>1248</v>
       </c>
       <c r="G497" t="s">
         <v>1150</v>
       </c>
       <c r="H497" t="s">
-        <v>1247</v>
+        <v>1249</v>
       </c>
       <c r="I497" t="s">
         <v>39</v>
@@ -24251,7 +25173,7 @@
         <v>46184</v>
       </c>
       <c r="C498" s="19">
-        <v>0.58680555555555558</v>
+        <v>0.59513888888888888</v>
       </c>
       <c r="D498" t="s">
         <v>15</v>
@@ -24260,22 +25182,22 @@
         <v>43</v>
       </c>
       <c r="F498" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="G498" t="s">
-        <v>1150</v>
+        <v>1251</v>
       </c>
       <c r="H498" t="s">
-        <v>1249</v>
+        <v>1252</v>
       </c>
       <c r="I498" t="s">
         <v>39</v>
       </c>
       <c r="J498" t="s">
-        <v>65</v>
+        <v>1193</v>
       </c>
       <c r="K498" t="s">
-        <v>945</v>
+        <v>1253</v>
       </c>
       <c r="M498" s="43"/>
     </row>
@@ -24287,31 +25209,31 @@
         <v>46184</v>
       </c>
       <c r="C499" s="19">
-        <v>0.59513888888888888</v>
+        <v>0.27361111111111114</v>
       </c>
       <c r="D499" t="s">
         <v>15</v>
       </c>
       <c r="E499" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="F499" t="s">
-        <v>1250</v>
+        <v>1254</v>
       </c>
       <c r="G499" t="s">
-        <v>1251</v>
+        <v>783</v>
       </c>
       <c r="H499" t="s">
-        <v>1252</v>
+        <v>1255</v>
       </c>
       <c r="I499" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="J499" t="s">
         <v>1193</v>
       </c>
       <c r="K499" t="s">
-        <v>1253</v>
+        <v>1256</v>
       </c>
       <c r="M499" s="43"/>
     </row>
@@ -24323,31 +25245,34 @@
         <v>46184</v>
       </c>
       <c r="C500" s="19">
-        <v>0.27361111111111114</v>
+        <v>0.43819444444444444</v>
       </c>
       <c r="D500" t="s">
         <v>15</v>
       </c>
       <c r="E500" t="s">
-        <v>80</v>
+        <v>945</v>
       </c>
       <c r="F500" t="s">
-        <v>1254</v>
+        <v>1257</v>
       </c>
       <c r="G500" t="s">
-        <v>783</v>
+        <v>1258</v>
       </c>
       <c r="H500" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="I500" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="J500" t="s">
-        <v>1193</v>
+        <v>21</v>
       </c>
       <c r="K500" t="s">
-        <v>1256</v>
+        <v>1260</v>
+      </c>
+      <c r="L500" s="49">
+        <v>46184</v>
       </c>
       <c r="M500" s="43"/>
     </row>
@@ -24359,25 +25284,25 @@
         <v>46184</v>
       </c>
       <c r="C501" s="19">
-        <v>0.43819444444444444</v>
+        <v>0.42916666666666664</v>
       </c>
       <c r="D501" t="s">
         <v>15</v>
       </c>
       <c r="E501" t="s">
-        <v>1268</v>
+        <v>945</v>
       </c>
       <c r="F501" t="s">
-        <v>1257</v>
+        <v>1261</v>
       </c>
       <c r="G501" t="s">
-        <v>1258</v>
+        <v>1262</v>
       </c>
       <c r="H501" t="s">
-        <v>1259</v>
+        <v>1263</v>
       </c>
       <c r="I501" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="J501" t="s">
         <v>21</v>
@@ -24390,7 +25315,7 @@
       </c>
       <c r="M501" s="43"/>
     </row>
-    <row r="502" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A502" s="30">
         <v>501</v>
       </c>
@@ -24398,22 +25323,22 @@
         <v>46184</v>
       </c>
       <c r="C502" s="19">
-        <v>0.42916666666666664</v>
+        <v>0.81944444444444442</v>
       </c>
       <c r="D502" t="s">
-        <v>15</v>
+        <v>1273</v>
       </c>
       <c r="E502" t="s">
-        <v>1269</v>
+        <v>71</v>
       </c>
       <c r="F502" t="s">
-        <v>1261</v>
+        <v>1274</v>
       </c>
       <c r="G502" t="s">
-        <v>1262</v>
+        <v>1114</v>
       </c>
       <c r="H502" t="s">
-        <v>1263</v>
+        <v>1275</v>
       </c>
       <c r="I502" t="s">
         <v>20</v>
@@ -24422,406 +25347,5457 @@
         <v>21</v>
       </c>
       <c r="K502" t="s">
-        <v>1260</v>
+        <v>945</v>
       </c>
       <c r="L502" s="49">
         <v>46184</v>
       </c>
-      <c r="M502" s="43"/>
-    </row>
-    <row r="503" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M502" s="43" t="s">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="503" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A503" s="39">
         <v>502</v>
       </c>
-      <c r="B503" s="44"/>
-      <c r="C503" s="45"/>
-      <c r="D503" s="43"/>
-      <c r="E503" s="43"/>
-      <c r="F503" s="43"/>
-      <c r="G503" s="43"/>
-      <c r="H503" s="43"/>
-      <c r="I503" s="43"/>
-      <c r="J503" s="43"/>
-      <c r="K503" s="43"/>
-      <c r="L503" s="47"/>
-      <c r="M503" s="43"/>
+      <c r="B503" s="44">
+        <v>46184</v>
+      </c>
+      <c r="C503" s="45">
+        <v>0.6166666666666667</v>
+      </c>
+      <c r="D503" s="43" t="s">
+        <v>1273</v>
+      </c>
+      <c r="E503" s="43" t="s">
+        <v>89</v>
+      </c>
+      <c r="F503" s="43" t="s">
+        <v>1277</v>
+      </c>
+      <c r="G503" s="43" t="s">
+        <v>783</v>
+      </c>
+      <c r="H503" s="43" t="s">
+        <v>1278</v>
+      </c>
+      <c r="I503" s="43" t="s">
+        <v>64</v>
+      </c>
+      <c r="J503" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="K503" s="43" t="s">
+        <v>945</v>
+      </c>
+      <c r="L503" s="46">
+        <v>46184</v>
+      </c>
+      <c r="M503" s="43" t="s">
+        <v>1279</v>
+      </c>
     </row>
     <row r="504" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A504" s="30">
         <v>503</v>
       </c>
-      <c r="B504" s="44"/>
-      <c r="C504" s="45"/>
-      <c r="D504" s="43"/>
-      <c r="E504" s="43"/>
-      <c r="F504" s="43"/>
-      <c r="G504" s="43"/>
-      <c r="H504" s="43"/>
-      <c r="I504" s="43"/>
-      <c r="J504" s="43"/>
-      <c r="K504" s="43"/>
-      <c r="L504" s="47"/>
-      <c r="M504" s="43"/>
+      <c r="B504" s="44">
+        <v>46184</v>
+      </c>
+      <c r="C504" s="45">
+        <v>0.88194444444444442</v>
+      </c>
+      <c r="D504" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E504" s="43" t="s">
+        <v>278</v>
+      </c>
+      <c r="F504" s="43" t="s">
+        <v>1280</v>
+      </c>
+      <c r="G504" s="43" t="s">
+        <v>1114</v>
+      </c>
+      <c r="H504" s="43" t="s">
+        <v>1281</v>
+      </c>
+      <c r="I504" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="J504" s="43" t="s">
+        <v>934</v>
+      </c>
+      <c r="K504" s="43" t="s">
+        <v>1282</v>
+      </c>
+      <c r="L504" s="46">
+        <v>46184</v>
+      </c>
+      <c r="M504" s="43" t="s">
+        <v>945</v>
+      </c>
     </row>
     <row r="505" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A505" s="22">
         <v>504</v>
       </c>
-      <c r="B505" s="44"/>
-      <c r="C505" s="45"/>
-      <c r="D505" s="43"/>
-      <c r="E505" s="43"/>
-      <c r="F505" s="43"/>
-      <c r="G505" s="43"/>
-      <c r="H505" s="43"/>
-      <c r="I505" s="43"/>
-      <c r="J505" s="43"/>
-      <c r="K505" s="43"/>
-      <c r="L505" s="47"/>
-      <c r="M505" s="43"/>
-    </row>
-    <row r="506" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B505" s="44">
+        <v>46184</v>
+      </c>
+      <c r="C505" s="45">
+        <v>0.90347222222222223</v>
+      </c>
+      <c r="D505" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E505" s="43" t="s">
+        <v>232</v>
+      </c>
+      <c r="F505" s="43" t="s">
+        <v>679</v>
+      </c>
+      <c r="G505" s="43" t="s">
+        <v>1114</v>
+      </c>
+      <c r="H505" s="43" t="s">
+        <v>1283</v>
+      </c>
+      <c r="I505" s="43" t="s">
+        <v>64</v>
+      </c>
+      <c r="J505" s="43" t="s">
+        <v>934</v>
+      </c>
+      <c r="K505" s="43" t="s">
+        <v>1284</v>
+      </c>
+      <c r="L505" s="46">
+        <v>46184</v>
+      </c>
+      <c r="M505" s="43" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="506" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A506" s="39">
         <v>505</v>
       </c>
-      <c r="B506" s="44"/>
-      <c r="C506" s="45"/>
-      <c r="D506" s="43"/>
-      <c r="E506" s="43"/>
-      <c r="F506" s="43"/>
-      <c r="G506" s="43"/>
-      <c r="H506" s="43"/>
-      <c r="I506" s="43"/>
-      <c r="J506" s="43"/>
-      <c r="K506" s="43"/>
-      <c r="L506" s="47"/>
-      <c r="M506" s="43"/>
-    </row>
-    <row r="507" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B506" s="44">
+        <v>46184</v>
+      </c>
+      <c r="C506" s="45">
+        <v>0.72013888888888888</v>
+      </c>
+      <c r="D506" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E506" s="43" t="s">
+        <v>232</v>
+      </c>
+      <c r="F506" s="43" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G506" s="43" t="s">
+        <v>789</v>
+      </c>
+      <c r="H506" s="43" t="s">
+        <v>1285</v>
+      </c>
+      <c r="I506" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="J506" s="43" t="s">
+        <v>1193</v>
+      </c>
+      <c r="K506" s="43" t="s">
+        <v>862</v>
+      </c>
+      <c r="L506" s="47" t="s">
+        <v>945</v>
+      </c>
+      <c r="M506" s="43" t="s">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="507" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A507" s="30">
         <v>506</v>
       </c>
-      <c r="B507" s="44"/>
-      <c r="C507" s="45"/>
-      <c r="D507" s="43"/>
-      <c r="E507" s="43"/>
-      <c r="F507" s="43"/>
-      <c r="G507" s="43"/>
-      <c r="H507" s="43"/>
-      <c r="I507" s="43"/>
-      <c r="J507" s="43"/>
-      <c r="K507" s="43"/>
-      <c r="L507" s="47"/>
-      <c r="M507" s="43"/>
-    </row>
-    <row r="508" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B507" s="44">
+        <v>46184</v>
+      </c>
+      <c r="C507" s="45">
+        <v>0.81944444444444442</v>
+      </c>
+      <c r="D507" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E507" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="F507" s="43" t="s">
+        <v>1274</v>
+      </c>
+      <c r="G507" s="43" t="s">
+        <v>1114</v>
+      </c>
+      <c r="H507" s="43" t="s">
+        <v>1275</v>
+      </c>
+      <c r="I507" s="43" t="s">
+        <v>20</v>
+      </c>
+      <c r="J507" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="K507" s="43" t="s">
+        <v>945</v>
+      </c>
+      <c r="L507" s="46">
+        <v>46184</v>
+      </c>
+      <c r="M507" s="43" t="s">
+        <v>1279</v>
+      </c>
+    </row>
+    <row r="508" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A508" s="39">
         <v>507</v>
       </c>
-      <c r="B508" s="44"/>
-      <c r="C508" s="45"/>
-      <c r="D508" s="43"/>
-      <c r="E508" s="43"/>
-      <c r="F508" s="43"/>
-      <c r="G508" s="43"/>
-      <c r="H508" s="43"/>
-      <c r="I508" s="43"/>
-      <c r="J508" s="43"/>
-      <c r="K508" s="43"/>
-      <c r="L508" s="47"/>
-      <c r="M508" s="43"/>
-    </row>
-    <row r="509" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B508" s="44">
+        <v>46184</v>
+      </c>
+      <c r="C508" s="45">
+        <v>0.6166666666666667</v>
+      </c>
+      <c r="D508" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E508" s="43" t="s">
+        <v>89</v>
+      </c>
+      <c r="F508" s="43" t="s">
+        <v>1277</v>
+      </c>
+      <c r="G508" s="43" t="s">
+        <v>783</v>
+      </c>
+      <c r="H508" s="43" t="s">
+        <v>1278</v>
+      </c>
+      <c r="I508" s="43" t="s">
+        <v>64</v>
+      </c>
+      <c r="J508" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="K508" s="43" t="s">
+        <v>945</v>
+      </c>
+      <c r="L508" s="46">
+        <v>46184</v>
+      </c>
+      <c r="M508" s="43" t="s">
+        <v>1279</v>
+      </c>
+    </row>
+    <row r="509" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A509" s="30">
         <v>508</v>
       </c>
-      <c r="B509" s="44"/>
-      <c r="C509" s="45"/>
-      <c r="D509" s="43"/>
-      <c r="E509" s="43"/>
-      <c r="F509" s="43"/>
-      <c r="G509" s="43"/>
-      <c r="H509" s="43"/>
-      <c r="I509" s="43"/>
-      <c r="J509" s="43"/>
-      <c r="K509" s="43"/>
-      <c r="L509" s="47"/>
-      <c r="M509" s="43"/>
+      <c r="B509" s="44">
+        <v>46184</v>
+      </c>
+      <c r="C509" s="45">
+        <v>0.86736111111111114</v>
+      </c>
+      <c r="D509" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E509" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="F509" s="43" t="s">
+        <v>1287</v>
+      </c>
+      <c r="G509" s="43" t="s">
+        <v>802</v>
+      </c>
+      <c r="H509" s="43" t="s">
+        <v>1288</v>
+      </c>
+      <c r="I509" s="43" t="s">
+        <v>20</v>
+      </c>
+      <c r="J509" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="K509" s="43" t="s">
+        <v>1289</v>
+      </c>
+      <c r="L509" s="46">
+        <v>46184</v>
+      </c>
+      <c r="M509" s="43" t="s">
+        <v>1290</v>
+      </c>
     </row>
     <row r="510" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A510" s="22">
         <v>509</v>
       </c>
-      <c r="B510" s="44"/>
-      <c r="C510" s="45"/>
-      <c r="D510" s="43"/>
-      <c r="E510" s="43"/>
-      <c r="F510" s="43"/>
-      <c r="G510" s="43"/>
-      <c r="H510" s="43"/>
-      <c r="I510" s="43"/>
-      <c r="J510" s="43"/>
-      <c r="K510" s="43"/>
-      <c r="L510" s="47"/>
-      <c r="M510" s="43"/>
+      <c r="B510" s="44">
+        <v>46184</v>
+      </c>
+      <c r="C510" s="45">
+        <v>0.88194444444444442</v>
+      </c>
+      <c r="D510" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E510" s="43" t="s">
+        <v>278</v>
+      </c>
+      <c r="F510" s="43" t="s">
+        <v>1280</v>
+      </c>
+      <c r="G510" s="43" t="s">
+        <v>1114</v>
+      </c>
+      <c r="H510" s="43" t="s">
+        <v>1281</v>
+      </c>
+      <c r="I510" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="J510" s="43" t="s">
+        <v>934</v>
+      </c>
+      <c r="K510" s="43" t="s">
+        <v>1282</v>
+      </c>
+      <c r="L510" s="46">
+        <v>46184</v>
+      </c>
+      <c r="M510" s="43" t="s">
+        <v>945</v>
+      </c>
     </row>
     <row r="511" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A511" s="39">
         <v>510</v>
       </c>
-      <c r="B511" s="44"/>
-      <c r="C511" s="45"/>
-      <c r="D511" s="43"/>
-      <c r="E511" s="43"/>
-      <c r="F511" s="43"/>
-      <c r="G511" s="43"/>
-      <c r="H511" s="43"/>
-      <c r="I511" s="43"/>
-      <c r="J511" s="43"/>
-      <c r="K511" s="43"/>
-      <c r="L511" s="47"/>
-      <c r="M511" s="43"/>
+      <c r="B511" s="44">
+        <v>46184</v>
+      </c>
+      <c r="C511" s="45">
+        <v>0.90347222222222223</v>
+      </c>
+      <c r="D511" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E511" s="43" t="s">
+        <v>232</v>
+      </c>
+      <c r="F511" s="43" t="s">
+        <v>679</v>
+      </c>
+      <c r="G511" s="43" t="s">
+        <v>1114</v>
+      </c>
+      <c r="H511" s="43" t="s">
+        <v>1283</v>
+      </c>
+      <c r="I511" s="43" t="s">
+        <v>64</v>
+      </c>
+      <c r="J511" s="43" t="s">
+        <v>934</v>
+      </c>
+      <c r="K511" s="43" t="s">
+        <v>1284</v>
+      </c>
+      <c r="L511" s="46">
+        <v>46184</v>
+      </c>
+      <c r="M511" s="43" t="s">
+        <v>945</v>
+      </c>
     </row>
     <row r="512" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A512" s="30">
         <v>511</v>
       </c>
-      <c r="B512" s="44"/>
-      <c r="C512" s="45"/>
-      <c r="D512" s="43"/>
-      <c r="E512" s="43"/>
-      <c r="F512" s="43"/>
-      <c r="G512" s="43"/>
-      <c r="H512" s="43"/>
-      <c r="I512" s="43"/>
-      <c r="J512" s="43"/>
-      <c r="K512" s="43"/>
-      <c r="L512" s="47"/>
+      <c r="B512" s="44">
+        <v>46185</v>
+      </c>
+      <c r="C512" s="45">
+        <v>0.28888888888888886</v>
+      </c>
+      <c r="D512" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E512" s="43" t="s">
+        <v>50</v>
+      </c>
+      <c r="F512" s="43" t="s">
+        <v>1291</v>
+      </c>
+      <c r="G512" s="43" t="s">
+        <v>1114</v>
+      </c>
+      <c r="H512" s="43" t="s">
+        <v>1292</v>
+      </c>
+      <c r="I512" s="43" t="s">
+        <v>64</v>
+      </c>
+      <c r="J512" s="43" t="s">
+        <v>934</v>
+      </c>
+      <c r="K512" s="43" t="s">
+        <v>1272</v>
+      </c>
+      <c r="L512" s="46">
+        <v>46185</v>
+      </c>
       <c r="M512" s="43"/>
     </row>
     <row r="513" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A513" s="39">
         <v>512</v>
       </c>
-      <c r="B513" s="44"/>
-      <c r="C513" s="45"/>
-      <c r="D513" s="43"/>
-      <c r="E513" s="43"/>
-      <c r="F513" s="43"/>
-      <c r="G513" s="43"/>
-      <c r="H513" s="43"/>
-      <c r="I513" s="43"/>
-      <c r="J513" s="43"/>
-      <c r="K513" s="43"/>
-      <c r="L513" s="47"/>
-      <c r="M513" s="43"/>
+      <c r="B513" s="44">
+        <v>46185</v>
+      </c>
+      <c r="C513" s="45">
+        <v>0.30694444444444446</v>
+      </c>
+      <c r="D513" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E513" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="F513" s="43" t="s">
+        <v>328</v>
+      </c>
+      <c r="G513" s="43" t="s">
+        <v>1293</v>
+      </c>
+      <c r="H513" s="43" t="s">
+        <v>1294</v>
+      </c>
+      <c r="I513" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="J513" s="43" t="s">
+        <v>934</v>
+      </c>
+      <c r="K513" s="43" t="s">
+        <v>1295</v>
+      </c>
+      <c r="L513" s="46">
+        <v>46185</v>
+      </c>
+      <c r="M513" s="43" t="s">
+        <v>1296</v>
+      </c>
     </row>
     <row r="514" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A514" s="30">
         <v>513</v>
       </c>
-      <c r="B514" s="44"/>
-      <c r="C514" s="45"/>
-      <c r="D514" s="43"/>
-      <c r="E514" s="43"/>
-      <c r="F514" s="43"/>
-      <c r="G514" s="43"/>
-      <c r="H514" s="43"/>
-      <c r="I514" s="43"/>
-      <c r="J514" s="43"/>
-      <c r="K514" s="43"/>
-      <c r="L514" s="47"/>
+      <c r="B514" s="44">
+        <v>46185</v>
+      </c>
+      <c r="C514" s="45">
+        <v>0.30625000000000002</v>
+      </c>
+      <c r="D514" s="43" t="s">
+        <v>1273</v>
+      </c>
+      <c r="E514" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="F514" s="43" t="s">
+        <v>328</v>
+      </c>
+      <c r="G514" s="43" t="s">
+        <v>1293</v>
+      </c>
+      <c r="H514" s="43" t="s">
+        <v>1297</v>
+      </c>
+      <c r="I514" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="J514" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="K514" s="43" t="s">
+        <v>945</v>
+      </c>
+      <c r="L514" s="46">
+        <v>46185</v>
+      </c>
       <c r="M514" s="43"/>
     </row>
     <row r="515" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A515" s="22">
         <v>514</v>
       </c>
-      <c r="B515" s="44"/>
-      <c r="C515" s="45"/>
-      <c r="D515" s="43"/>
-      <c r="E515" s="43"/>
-      <c r="F515" s="43"/>
-      <c r="G515" s="43"/>
-      <c r="H515" s="43"/>
-      <c r="I515" s="43"/>
-      <c r="J515" s="43"/>
-      <c r="K515" s="43"/>
-      <c r="L515" s="47"/>
+      <c r="B515" s="44">
+        <v>46185</v>
+      </c>
+      <c r="C515" s="45">
+        <v>0.31111111111111112</v>
+      </c>
+      <c r="D515" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E515" s="43" t="s">
+        <v>232</v>
+      </c>
+      <c r="F515" s="43" t="s">
+        <v>1298</v>
+      </c>
+      <c r="G515" s="43" t="s">
+        <v>1114</v>
+      </c>
+      <c r="H515" s="43" t="s">
+        <v>949</v>
+      </c>
+      <c r="I515" s="43" t="s">
+        <v>64</v>
+      </c>
+      <c r="J515" s="43" t="s">
+        <v>934</v>
+      </c>
+      <c r="K515" s="43" t="s">
+        <v>1295</v>
+      </c>
+      <c r="L515" s="46">
+        <v>46186</v>
+      </c>
       <c r="M515" s="43"/>
     </row>
     <row r="516" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A516" s="39">
         <v>515</v>
       </c>
-      <c r="B516" s="44"/>
-      <c r="C516" s="45"/>
-      <c r="D516" s="43"/>
-      <c r="E516" s="43"/>
-      <c r="F516" s="43"/>
-      <c r="G516" s="43"/>
-      <c r="H516" s="43"/>
-      <c r="I516" s="43"/>
-      <c r="J516" s="43"/>
-      <c r="K516" s="43"/>
-      <c r="L516" s="47"/>
+      <c r="B516" s="44">
+        <v>46185</v>
+      </c>
+      <c r="C516" s="45">
+        <v>0.31041666666666667</v>
+      </c>
+      <c r="D516" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E516" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="F516" s="43" t="s">
+        <v>1299</v>
+      </c>
+      <c r="G516" s="43" t="s">
+        <v>1300</v>
+      </c>
+      <c r="H516" s="43" t="s">
+        <v>1301</v>
+      </c>
+      <c r="I516" s="43" t="s">
+        <v>64</v>
+      </c>
+      <c r="J516" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="K516" s="43" t="s">
+        <v>945</v>
+      </c>
+      <c r="L516" s="47" t="s">
+        <v>945</v>
+      </c>
       <c r="M516" s="43"/>
     </row>
     <row r="517" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A517" s="30">
         <v>516</v>
       </c>
-      <c r="B517" s="44"/>
-      <c r="C517" s="45"/>
-      <c r="D517" s="43"/>
-      <c r="E517" s="43"/>
-      <c r="F517" s="43"/>
-      <c r="G517" s="43"/>
-      <c r="H517" s="43"/>
-      <c r="I517" s="43"/>
-      <c r="J517" s="43"/>
-      <c r="K517" s="43"/>
-      <c r="L517" s="47"/>
-      <c r="M517" s="43"/>
-    </row>
-    <row r="518" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B517" s="44">
+        <v>46185</v>
+      </c>
+      <c r="C517" s="45">
+        <v>0.31319444444444444</v>
+      </c>
+      <c r="D517" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E517" s="43" t="s">
+        <v>232</v>
+      </c>
+      <c r="F517" s="43" t="s">
+        <v>1302</v>
+      </c>
+      <c r="G517" s="43" t="s">
+        <v>1300</v>
+      </c>
+      <c r="H517" s="43" t="s">
+        <v>1303</v>
+      </c>
+      <c r="I517" s="43" t="s">
+        <v>20</v>
+      </c>
+      <c r="J517" s="43" t="s">
+        <v>934</v>
+      </c>
+      <c r="K517" s="43" t="s">
+        <v>1295</v>
+      </c>
+      <c r="L517" s="46">
+        <v>46185</v>
+      </c>
+      <c r="M517" s="43" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="518" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A518" s="39">
         <v>517</v>
       </c>
-      <c r="B518" s="44"/>
-      <c r="C518" s="45"/>
-      <c r="D518" s="43"/>
-      <c r="E518" s="43"/>
-      <c r="F518" s="43"/>
-      <c r="G518" s="43"/>
-      <c r="H518" s="43"/>
-      <c r="I518" s="43"/>
-      <c r="J518" s="43"/>
-      <c r="K518" s="43"/>
-      <c r="L518" s="47"/>
+      <c r="B518" s="44">
+        <v>46185</v>
+      </c>
+      <c r="C518" s="45">
+        <v>0.31944444444444442</v>
+      </c>
+      <c r="D518" s="43" t="s">
+        <v>1273</v>
+      </c>
+      <c r="E518" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="F518" s="43" t="s">
+        <v>1304</v>
+      </c>
+      <c r="G518" s="43" t="s">
+        <v>1117</v>
+      </c>
+      <c r="H518" s="43" t="s">
+        <v>1305</v>
+      </c>
+      <c r="I518" s="43" t="s">
+        <v>20</v>
+      </c>
+      <c r="J518" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="K518" s="43" t="s">
+        <v>1003</v>
+      </c>
+      <c r="L518" s="46">
+        <v>46185</v>
+      </c>
       <c r="M518" s="43"/>
     </row>
     <row r="519" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A519" s="30">
         <v>518</v>
       </c>
-      <c r="B519" s="44"/>
-      <c r="C519" s="45"/>
-      <c r="D519" s="43"/>
-      <c r="E519" s="43"/>
-      <c r="F519" s="43"/>
-      <c r="G519" s="43"/>
-      <c r="H519" s="43"/>
-      <c r="I519" s="43"/>
-      <c r="J519" s="43"/>
-      <c r="K519" s="43"/>
-      <c r="L519" s="47"/>
+      <c r="B519" s="44">
+        <v>46185</v>
+      </c>
+      <c r="C519" s="45">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="D519" s="43" t="s">
+        <v>1273</v>
+      </c>
+      <c r="E519" s="43" t="s">
+        <v>16</v>
+      </c>
+      <c r="F519" s="43" t="s">
+        <v>1306</v>
+      </c>
+      <c r="G519" s="43" t="s">
+        <v>783</v>
+      </c>
+      <c r="H519" s="43" t="s">
+        <v>1307</v>
+      </c>
+      <c r="I519" s="43" t="s">
+        <v>20</v>
+      </c>
+      <c r="J519" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="K519" s="43" t="s">
+        <v>1003</v>
+      </c>
+      <c r="L519" s="46">
+        <v>46185</v>
+      </c>
       <c r="M519" s="43"/>
     </row>
     <row r="520" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A520" s="22">
         <v>519</v>
       </c>
-      <c r="B520" s="44"/>
-      <c r="C520" s="45"/>
-      <c r="D520" s="43"/>
-      <c r="E520" s="43"/>
-      <c r="F520" s="43"/>
-      <c r="G520" s="43"/>
-      <c r="H520" s="43"/>
-      <c r="I520" s="43"/>
-      <c r="J520" s="43"/>
-      <c r="K520" s="43"/>
-      <c r="L520" s="47"/>
+      <c r="B520" s="44">
+        <v>46185</v>
+      </c>
+      <c r="C520" s="45">
+        <v>0.32569444444444445</v>
+      </c>
+      <c r="D520" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E520" s="43" t="s">
+        <v>232</v>
+      </c>
+      <c r="F520" s="43" t="s">
+        <v>332</v>
+      </c>
+      <c r="G520" s="43" t="s">
+        <v>783</v>
+      </c>
+      <c r="H520" s="43" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I520" s="43" t="s">
+        <v>20</v>
+      </c>
+      <c r="J520" s="43" t="s">
+        <v>934</v>
+      </c>
+      <c r="K520" s="43" t="s">
+        <v>1272</v>
+      </c>
+      <c r="L520" s="46">
+        <v>46186</v>
+      </c>
       <c r="M520" s="43"/>
     </row>
     <row r="521" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A521" s="39">
         <v>520</v>
       </c>
-      <c r="B521" s="44"/>
-      <c r="C521" s="45"/>
-      <c r="D521" s="43"/>
-      <c r="E521" s="43"/>
-      <c r="F521" s="43"/>
-      <c r="G521" s="43"/>
-      <c r="H521" s="43"/>
-      <c r="I521" s="43"/>
-      <c r="J521" s="43"/>
-      <c r="K521" s="43"/>
-      <c r="L521" s="47"/>
+      <c r="B521" s="44">
+        <v>46185</v>
+      </c>
+      <c r="C521" s="45">
+        <v>0.32777777777777778</v>
+      </c>
+      <c r="D521" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E521" s="43" t="s">
+        <v>232</v>
+      </c>
+      <c r="F521" s="43" t="s">
+        <v>832</v>
+      </c>
+      <c r="G521" s="43" t="s">
+        <v>780</v>
+      </c>
+      <c r="H521" s="43" t="s">
+        <v>885</v>
+      </c>
+      <c r="I521" s="43" t="s">
+        <v>64</v>
+      </c>
+      <c r="J521" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="K521" s="43" t="s">
+        <v>945</v>
+      </c>
+      <c r="L521" s="47" t="s">
+        <v>945</v>
+      </c>
       <c r="M521" s="43"/>
     </row>
-    <row r="522" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A522" s="30">
         <v>521</v>
       </c>
-      <c r="B522" s="44"/>
-      <c r="C522" s="45"/>
-      <c r="D522" s="43"/>
-      <c r="E522" s="43"/>
-      <c r="F522" s="43"/>
-      <c r="G522" s="43"/>
-      <c r="H522" s="43"/>
-      <c r="I522" s="43"/>
-      <c r="J522" s="43"/>
-      <c r="K522" s="43"/>
-      <c r="L522" s="47"/>
+      <c r="B522" s="44">
+        <v>46185</v>
+      </c>
+      <c r="C522" s="45">
+        <v>0.34444444444444444</v>
+      </c>
+      <c r="D522" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E522" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="F522" s="43" t="s">
+        <v>1309</v>
+      </c>
+      <c r="G522" s="43" t="s">
+        <v>789</v>
+      </c>
+      <c r="H522" s="43" t="s">
+        <v>1310</v>
+      </c>
+      <c r="I522" s="43" t="s">
+        <v>20</v>
+      </c>
+      <c r="J522" s="43" t="s">
+        <v>934</v>
+      </c>
+      <c r="K522" s="43" t="s">
+        <v>1295</v>
+      </c>
+      <c r="L522" s="46">
+        <v>46185</v>
+      </c>
       <c r="M522" s="43"/>
     </row>
     <row r="523" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A523" s="39">
         <v>522</v>
       </c>
-      <c r="B523" s="44"/>
-      <c r="C523" s="45"/>
-      <c r="D523" s="43"/>
-      <c r="E523" s="43"/>
-      <c r="F523" s="43"/>
-      <c r="G523" s="43"/>
-      <c r="H523" s="43"/>
-      <c r="I523" s="43"/>
-      <c r="J523" s="43"/>
-      <c r="K523" s="43"/>
-      <c r="L523" s="47"/>
+      <c r="B523" s="44">
+        <v>46185</v>
+      </c>
+      <c r="C523" s="45">
+        <v>0.34652777777777777</v>
+      </c>
+      <c r="D523" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E523" s="43" t="s">
+        <v>232</v>
+      </c>
+      <c r="F523" s="43" t="s">
+        <v>1311</v>
+      </c>
+      <c r="G523" s="43" t="s">
+        <v>780</v>
+      </c>
+      <c r="H523" s="43" t="s">
+        <v>1070</v>
+      </c>
+      <c r="I523" s="43" t="s">
+        <v>64</v>
+      </c>
+      <c r="J523" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="K523" s="43" t="s">
+        <v>945</v>
+      </c>
+      <c r="L523" s="47" t="s">
+        <v>945</v>
+      </c>
       <c r="M523" s="43"/>
     </row>
     <row r="524" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A524" s="30">
         <v>523</v>
       </c>
-      <c r="B524" s="44"/>
-      <c r="C524" s="45"/>
-      <c r="D524" s="43"/>
-      <c r="E524" s="43"/>
-      <c r="F524" s="43"/>
-      <c r="G524" s="43"/>
-      <c r="H524" s="43"/>
-      <c r="I524" s="43"/>
-      <c r="J524" s="43"/>
-      <c r="K524" s="43"/>
-      <c r="L524" s="47"/>
+      <c r="B524" s="44">
+        <v>46185</v>
+      </c>
+      <c r="C524" s="45">
+        <v>0.35069444444444442</v>
+      </c>
+      <c r="D524" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E524" s="43" t="s">
+        <v>232</v>
+      </c>
+      <c r="F524" s="43" t="s">
+        <v>1312</v>
+      </c>
+      <c r="G524" s="43" t="s">
+        <v>780</v>
+      </c>
+      <c r="H524" s="43" t="s">
+        <v>1313</v>
+      </c>
+      <c r="I524" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="J524" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="K524" s="43" t="s">
+        <v>945</v>
+      </c>
+      <c r="L524" s="47" t="s">
+        <v>945</v>
+      </c>
       <c r="M524" s="43"/>
     </row>
     <row r="525" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A525" s="22">
         <v>524</v>
       </c>
-      <c r="B525" s="44"/>
-      <c r="C525" s="45"/>
-      <c r="D525" s="43"/>
-      <c r="E525" s="43"/>
-      <c r="F525" s="43"/>
-      <c r="G525" s="43"/>
-      <c r="H525" s="43"/>
-      <c r="I525" s="43"/>
-      <c r="J525" s="43"/>
-      <c r="K525" s="43"/>
-      <c r="L525" s="47"/>
+      <c r="B525" s="44">
+        <v>46185</v>
+      </c>
+      <c r="C525" s="45">
+        <v>0.3611111111111111</v>
+      </c>
+      <c r="D525" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E525" s="43" t="s">
+        <v>232</v>
+      </c>
+      <c r="F525" s="43" t="s">
+        <v>1314</v>
+      </c>
+      <c r="G525" s="43" t="s">
+        <v>802</v>
+      </c>
+      <c r="H525" s="43" t="s">
+        <v>1315</v>
+      </c>
+      <c r="I525" s="43" t="s">
+        <v>64</v>
+      </c>
+      <c r="J525" s="43" t="s">
+        <v>934</v>
+      </c>
+      <c r="K525" s="43" t="s">
+        <v>1316</v>
+      </c>
+      <c r="L525" s="46">
+        <v>46186</v>
+      </c>
       <c r="M525" s="43"/>
     </row>
+    <row r="526" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A526" s="30">
+        <v>525</v>
+      </c>
+      <c r="B526" s="51">
+        <v>46185</v>
+      </c>
+      <c r="C526" s="52">
+        <v>0.37569444444444444</v>
+      </c>
+      <c r="D526" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E526" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="F526" s="20" t="s">
+        <v>1317</v>
+      </c>
+      <c r="G526" s="20" t="s">
+        <v>802</v>
+      </c>
+      <c r="H526" s="20" t="s">
+        <v>1318</v>
+      </c>
+      <c r="I526" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="J526" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="K526" s="20" t="s">
+        <v>945</v>
+      </c>
+      <c r="L526" s="50" t="s">
+        <v>945</v>
+      </c>
+      <c r="M526" s="20"/>
+    </row>
+    <row r="527" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A527" s="39">
+        <v>526</v>
+      </c>
+      <c r="B527" s="51">
+        <v>46185</v>
+      </c>
+      <c r="C527" s="52">
+        <v>0.40416666666666667</v>
+      </c>
+      <c r="D527" s="20" t="s">
+        <v>1273</v>
+      </c>
+      <c r="E527" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="F527" s="20" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G527" s="20" t="s">
+        <v>1114</v>
+      </c>
+      <c r="H527" s="20" t="s">
+        <v>1320</v>
+      </c>
+      <c r="I527" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="J527" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K527" s="20" t="s">
+        <v>1003</v>
+      </c>
+      <c r="L527" s="53">
+        <v>46185</v>
+      </c>
+      <c r="M527" s="20"/>
+    </row>
+    <row r="528" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A528" s="30">
+        <v>527</v>
+      </c>
+      <c r="B528" s="51">
+        <v>46185</v>
+      </c>
+      <c r="C528" s="52">
+        <v>0.4201388888888889</v>
+      </c>
+      <c r="D528" s="20" t="s">
+        <v>1273</v>
+      </c>
+      <c r="E528" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="F528" s="20" t="s">
+        <v>1299</v>
+      </c>
+      <c r="G528" s="20" t="s">
+        <v>789</v>
+      </c>
+      <c r="H528" s="20" t="s">
+        <v>1321</v>
+      </c>
+      <c r="I528" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="J528" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K528" s="20" t="s">
+        <v>1003</v>
+      </c>
+      <c r="L528" s="53">
+        <v>46185</v>
+      </c>
+      <c r="M528" s="20"/>
+    </row>
+    <row r="529" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A529" s="22">
+        <v>528</v>
+      </c>
+      <c r="B529" s="51">
+        <v>46185</v>
+      </c>
+      <c r="C529" s="52">
+        <v>0.42291666666666666</v>
+      </c>
+      <c r="D529" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E529" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="F529" s="20" t="s">
+        <v>1322</v>
+      </c>
+      <c r="G529" s="20" t="s">
+        <v>797</v>
+      </c>
+      <c r="H529" s="20" t="s">
+        <v>1323</v>
+      </c>
+      <c r="I529" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="J529" s="20" t="s">
+        <v>934</v>
+      </c>
+      <c r="K529" s="20" t="s">
+        <v>955</v>
+      </c>
+      <c r="L529" s="53">
+        <v>46186</v>
+      </c>
+      <c r="M529" s="20"/>
+    </row>
+    <row r="530" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A530" s="30">
+        <v>529</v>
+      </c>
+      <c r="B530" s="51">
+        <v>46185</v>
+      </c>
+      <c r="C530" s="52">
+        <v>0.44166666666666665</v>
+      </c>
+      <c r="D530" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E530" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="F530" s="20" t="s">
+        <v>1324</v>
+      </c>
+      <c r="G530" s="20" t="s">
+        <v>1117</v>
+      </c>
+      <c r="H530" s="20" t="s">
+        <v>1325</v>
+      </c>
+      <c r="I530" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="J530" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="K530" s="20" t="s">
+        <v>945</v>
+      </c>
+      <c r="L530" s="50" t="s">
+        <v>945</v>
+      </c>
+      <c r="M530" s="20"/>
+    </row>
+    <row r="531" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A531" s="39">
+        <v>530</v>
+      </c>
+      <c r="B531" s="51">
+        <v>46185</v>
+      </c>
+      <c r="C531" s="52">
+        <v>0.46388888888888891</v>
+      </c>
+      <c r="D531" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E531" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="F531" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="G531" s="20" t="s">
+        <v>789</v>
+      </c>
+      <c r="H531" s="20" t="s">
+        <v>968</v>
+      </c>
+      <c r="I531" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="J531" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="K531" s="20" t="s">
+        <v>945</v>
+      </c>
+      <c r="L531" s="50" t="s">
+        <v>945</v>
+      </c>
+      <c r="M531" s="20"/>
+    </row>
+    <row r="532" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A532" s="30">
+        <v>531</v>
+      </c>
+      <c r="B532" s="51">
+        <v>46185</v>
+      </c>
+      <c r="C532" s="52">
+        <v>0.37916666666666665</v>
+      </c>
+      <c r="D532" s="20" t="s">
+        <v>1273</v>
+      </c>
+      <c r="E532" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="F532" s="20" t="s">
+        <v>1326</v>
+      </c>
+      <c r="G532" s="20" t="s">
+        <v>1114</v>
+      </c>
+      <c r="H532" s="20" t="s">
+        <v>1327</v>
+      </c>
+      <c r="I532" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="J532" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K532" s="20" t="s">
+        <v>1003</v>
+      </c>
+      <c r="L532" s="53">
+        <v>46185</v>
+      </c>
+      <c r="M532" s="20"/>
+    </row>
+    <row r="533" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A533" s="22">
+        <v>532</v>
+      </c>
+      <c r="B533" s="51">
+        <v>46185</v>
+      </c>
+      <c r="C533" s="52">
+        <v>0.3923611111111111</v>
+      </c>
+      <c r="D533" s="20" t="s">
+        <v>1273</v>
+      </c>
+      <c r="E533" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="F533" s="20" t="s">
+        <v>1328</v>
+      </c>
+      <c r="G533" s="20" t="s">
+        <v>1114</v>
+      </c>
+      <c r="H533" s="20" t="s">
+        <v>1327</v>
+      </c>
+      <c r="I533" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="J533" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K533" s="20" t="s">
+        <v>1003</v>
+      </c>
+      <c r="L533" s="53">
+        <v>46185</v>
+      </c>
+      <c r="M533" s="20"/>
+    </row>
+    <row r="534" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A534" s="30">
+        <v>533</v>
+      </c>
+      <c r="B534" s="51">
+        <v>46185</v>
+      </c>
+      <c r="C534" s="52">
+        <v>0.4826388888888889</v>
+      </c>
+      <c r="D534" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E534" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="F534" s="20" t="s">
+        <v>945</v>
+      </c>
+      <c r="G534" s="20" t="s">
+        <v>1329</v>
+      </c>
+      <c r="H534" s="20" t="s">
+        <v>1330</v>
+      </c>
+      <c r="I534" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="J534" s="20" t="s">
+        <v>934</v>
+      </c>
+      <c r="K534" s="20" t="s">
+        <v>1272</v>
+      </c>
+      <c r="L534" s="53">
+        <v>46185</v>
+      </c>
+      <c r="M534" s="20"/>
+    </row>
+    <row r="535" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A535" s="39">
+        <v>534</v>
+      </c>
+      <c r="B535" s="51">
+        <v>46185</v>
+      </c>
+      <c r="C535" s="52">
+        <v>0.4861111111111111</v>
+      </c>
+      <c r="D535" s="20" t="s">
+        <v>1273</v>
+      </c>
+      <c r="E535" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="F535" s="20" t="s">
+        <v>1331</v>
+      </c>
+      <c r="G535" s="20" t="s">
+        <v>1114</v>
+      </c>
+      <c r="H535" s="20" t="s">
+        <v>1332</v>
+      </c>
+      <c r="I535" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="J535" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K535" s="20" t="s">
+        <v>1003</v>
+      </c>
+      <c r="L535" s="53">
+        <v>46185</v>
+      </c>
+      <c r="M535" s="20"/>
+    </row>
+    <row r="536" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A536" s="30">
+        <v>535</v>
+      </c>
+      <c r="B536" s="51">
+        <v>46185</v>
+      </c>
+      <c r="C536" s="52">
+        <v>0.49236111111111114</v>
+      </c>
+      <c r="D536" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E536" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="F536" s="20" t="s">
+        <v>1333</v>
+      </c>
+      <c r="G536" s="20" t="s">
+        <v>789</v>
+      </c>
+      <c r="H536" s="20" t="s">
+        <v>1334</v>
+      </c>
+      <c r="I536" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="J536" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="K536" s="20" t="s">
+        <v>945</v>
+      </c>
+      <c r="L536" s="50" t="s">
+        <v>945</v>
+      </c>
+      <c r="M536" s="20"/>
+    </row>
+    <row r="537" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A537" s="22">
+        <v>536</v>
+      </c>
+      <c r="B537" s="51">
+        <v>46185</v>
+      </c>
+      <c r="C537" s="52">
+        <v>0.52152777777777781</v>
+      </c>
+      <c r="D537" s="20" t="s">
+        <v>1273</v>
+      </c>
+      <c r="E537" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="F537" s="20" t="s">
+        <v>1335</v>
+      </c>
+      <c r="G537" s="20" t="s">
+        <v>797</v>
+      </c>
+      <c r="H537" s="20" t="s">
+        <v>1336</v>
+      </c>
+      <c r="I537" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="J537" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K537" s="20" t="s">
+        <v>1003</v>
+      </c>
+      <c r="L537" s="53">
+        <v>46185</v>
+      </c>
+      <c r="M537" s="20"/>
+    </row>
+    <row r="538" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A538" s="30">
+        <v>537</v>
+      </c>
+      <c r="B538" s="51">
+        <v>46185</v>
+      </c>
+      <c r="C538" s="52">
+        <v>0.58194444444444449</v>
+      </c>
+      <c r="D538" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E538" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="F538" s="20" t="s">
+        <v>220</v>
+      </c>
+      <c r="G538" s="20" t="s">
+        <v>1337</v>
+      </c>
+      <c r="H538" s="20" t="s">
+        <v>1338</v>
+      </c>
+      <c r="I538" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="J538" s="20" t="s">
+        <v>934</v>
+      </c>
+      <c r="K538" s="20" t="s">
+        <v>1295</v>
+      </c>
+      <c r="L538" s="53">
+        <v>46185</v>
+      </c>
+      <c r="M538" s="20"/>
+    </row>
+    <row r="539" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A539" s="39">
+        <v>538</v>
+      </c>
+      <c r="B539" s="51">
+        <v>46185</v>
+      </c>
+      <c r="C539" s="52">
+        <v>0.6430555555555556</v>
+      </c>
+      <c r="D539" s="20" t="s">
+        <v>1273</v>
+      </c>
+      <c r="E539" s="20" t="s">
+        <v>278</v>
+      </c>
+      <c r="F539" s="20" t="s">
+        <v>328</v>
+      </c>
+      <c r="G539" s="20" t="s">
+        <v>1117</v>
+      </c>
+      <c r="H539" s="20" t="s">
+        <v>1339</v>
+      </c>
+      <c r="I539" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="J539" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K539" s="20" t="s">
+        <v>955</v>
+      </c>
+      <c r="L539" s="53">
+        <v>46185</v>
+      </c>
+      <c r="M539" s="20"/>
+    </row>
+    <row r="540" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A540" s="30">
+        <v>539</v>
+      </c>
+      <c r="B540" s="51">
+        <v>46185</v>
+      </c>
+      <c r="C540" s="52">
+        <v>0.65416666666666667</v>
+      </c>
+      <c r="D540" s="20" t="s">
+        <v>1273</v>
+      </c>
+      <c r="E540" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="F540" s="20" t="s">
+        <v>1340</v>
+      </c>
+      <c r="G540" s="20" t="s">
+        <v>789</v>
+      </c>
+      <c r="H540" s="20" t="s">
+        <v>1341</v>
+      </c>
+      <c r="I540" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="J540" s="20" t="s">
+        <v>1193</v>
+      </c>
+      <c r="K540" s="20" t="s">
+        <v>1342</v>
+      </c>
+      <c r="L540" s="50" t="s">
+        <v>945</v>
+      </c>
+      <c r="M540" s="20"/>
+    </row>
+    <row r="541" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A541" s="22">
+        <v>540</v>
+      </c>
+      <c r="B541" s="51">
+        <v>46185</v>
+      </c>
+      <c r="C541" s="52">
+        <v>0.28888888888888886</v>
+      </c>
+      <c r="D541" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E541" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="F541" s="20" t="s">
+        <v>1291</v>
+      </c>
+      <c r="G541" s="20" t="s">
+        <v>1114</v>
+      </c>
+      <c r="H541" s="20" t="s">
+        <v>1292</v>
+      </c>
+      <c r="I541" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="J541" s="20" t="s">
+        <v>934</v>
+      </c>
+      <c r="K541" s="20" t="s">
+        <v>1272</v>
+      </c>
+      <c r="L541" s="53">
+        <v>46185</v>
+      </c>
+      <c r="M541" s="20" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="542" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A542" s="30">
+        <v>541</v>
+      </c>
+      <c r="B542" s="51">
+        <v>46185</v>
+      </c>
+      <c r="C542" s="52">
+        <v>0.30486111111111114</v>
+      </c>
+      <c r="D542" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E542" s="20" t="s">
+        <v>945</v>
+      </c>
+      <c r="F542" s="20" t="s">
+        <v>1343</v>
+      </c>
+      <c r="G542" s="20" t="s">
+        <v>1344</v>
+      </c>
+      <c r="H542" s="20" t="s">
+        <v>1345</v>
+      </c>
+      <c r="I542" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="J542" s="20" t="s">
+        <v>1193</v>
+      </c>
+      <c r="K542" s="20" t="s">
+        <v>1346</v>
+      </c>
+      <c r="L542" s="50" t="s">
+        <v>945</v>
+      </c>
+      <c r="M542" s="20" t="s">
+        <v>1347</v>
+      </c>
+    </row>
+    <row r="543" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A543" s="39">
+        <v>542</v>
+      </c>
+      <c r="B543" s="51">
+        <v>46185</v>
+      </c>
+      <c r="C543" s="52">
+        <v>0.30625000000000002</v>
+      </c>
+      <c r="D543" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E543" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="F543" s="20" t="s">
+        <v>328</v>
+      </c>
+      <c r="G543" s="20" t="s">
+        <v>1348</v>
+      </c>
+      <c r="H543" s="20" t="s">
+        <v>1297</v>
+      </c>
+      <c r="I543" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="J543" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K543" s="20" t="s">
+        <v>945</v>
+      </c>
+      <c r="L543" s="53">
+        <v>46185</v>
+      </c>
+      <c r="M543" s="20" t="s">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="544" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A544" s="30">
+        <v>543</v>
+      </c>
+      <c r="B544" s="51">
+        <v>46185</v>
+      </c>
+      <c r="C544" s="52">
+        <v>0.30694444444444446</v>
+      </c>
+      <c r="D544" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E544" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="F544" s="20" t="s">
+        <v>328</v>
+      </c>
+      <c r="G544" s="20" t="s">
+        <v>1348</v>
+      </c>
+      <c r="H544" s="20" t="s">
+        <v>1294</v>
+      </c>
+      <c r="I544" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="J544" s="20" t="s">
+        <v>934</v>
+      </c>
+      <c r="K544" s="20" t="s">
+        <v>1350</v>
+      </c>
+      <c r="L544" s="50" t="s">
+        <v>945</v>
+      </c>
+      <c r="M544" s="20" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="545" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A545" s="22">
+        <v>544</v>
+      </c>
+      <c r="B545" s="51">
+        <v>46185</v>
+      </c>
+      <c r="C545" s="52">
+        <v>0.31041666666666667</v>
+      </c>
+      <c r="D545" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E545" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="F545" s="20" t="s">
+        <v>1299</v>
+      </c>
+      <c r="G545" s="20" t="s">
+        <v>1300</v>
+      </c>
+      <c r="H545" s="20" t="s">
+        <v>1301</v>
+      </c>
+      <c r="I545" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="J545" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="K545" s="20" t="s">
+        <v>945</v>
+      </c>
+      <c r="L545" s="50" t="s">
+        <v>945</v>
+      </c>
+      <c r="M545" s="20" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="546" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A546" s="30">
+        <v>545</v>
+      </c>
+      <c r="B546" s="51">
+        <v>46185</v>
+      </c>
+      <c r="C546" s="52">
+        <v>0.31111111111111112</v>
+      </c>
+      <c r="D546" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E546" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="F546" s="20" t="s">
+        <v>1298</v>
+      </c>
+      <c r="G546" s="20" t="s">
+        <v>1114</v>
+      </c>
+      <c r="H546" s="20" t="s">
+        <v>949</v>
+      </c>
+      <c r="I546" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="J546" s="20" t="s">
+        <v>934</v>
+      </c>
+      <c r="K546" s="20" t="s">
+        <v>1295</v>
+      </c>
+      <c r="L546" s="53">
+        <v>46185</v>
+      </c>
+      <c r="M546" s="20" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="547" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A547" s="39">
+        <v>546</v>
+      </c>
+      <c r="B547" s="51">
+        <v>46185</v>
+      </c>
+      <c r="C547" s="52">
+        <v>0.31111111111111112</v>
+      </c>
+      <c r="D547" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E547" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="F547" s="20" t="s">
+        <v>182</v>
+      </c>
+      <c r="G547" s="20" t="s">
+        <v>1352</v>
+      </c>
+      <c r="H547" s="20" t="s">
+        <v>1353</v>
+      </c>
+      <c r="I547" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="J547" s="20" t="s">
+        <v>934</v>
+      </c>
+      <c r="K547" s="20" t="s">
+        <v>1295</v>
+      </c>
+      <c r="L547" s="53">
+        <v>46185</v>
+      </c>
+      <c r="M547" s="20" t="s">
+        <v>1354</v>
+      </c>
+    </row>
+    <row r="548" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A548" s="30">
+        <v>547</v>
+      </c>
+      <c r="B548" s="51">
+        <v>46185</v>
+      </c>
+      <c r="C548" s="52">
+        <v>0.31319444444444444</v>
+      </c>
+      <c r="D548" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E548" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="F548" s="20" t="s">
+        <v>1302</v>
+      </c>
+      <c r="G548" s="20" t="s">
+        <v>1300</v>
+      </c>
+      <c r="H548" s="20" t="s">
+        <v>1303</v>
+      </c>
+      <c r="I548" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="J548" s="20" t="s">
+        <v>934</v>
+      </c>
+      <c r="K548" s="20" t="s">
+        <v>1272</v>
+      </c>
+      <c r="L548" s="53">
+        <v>46185</v>
+      </c>
+      <c r="M548" s="20" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="549" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A549" s="22">
+        <v>548</v>
+      </c>
+      <c r="B549" s="51">
+        <v>46185</v>
+      </c>
+      <c r="C549" s="52">
+        <v>0.31944444444444442</v>
+      </c>
+      <c r="D549" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E549" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="F549" s="20" t="s">
+        <v>1304</v>
+      </c>
+      <c r="G549" s="20" t="s">
+        <v>1117</v>
+      </c>
+      <c r="H549" s="20" t="s">
+        <v>1305</v>
+      </c>
+      <c r="I549" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="J549" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K549" s="20" t="s">
+        <v>1003</v>
+      </c>
+      <c r="L549" s="53">
+        <v>46185</v>
+      </c>
+      <c r="M549" s="20" t="s">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="550" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A550" s="30">
+        <v>549</v>
+      </c>
+      <c r="B550" s="51">
+        <v>46185</v>
+      </c>
+      <c r="C550" s="52">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="D550" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E550" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="F550" s="20" t="s">
+        <v>1306</v>
+      </c>
+      <c r="G550" s="20" t="s">
+        <v>783</v>
+      </c>
+      <c r="H550" s="20" t="s">
+        <v>1307</v>
+      </c>
+      <c r="I550" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="J550" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K550" s="20" t="s">
+        <v>1003</v>
+      </c>
+      <c r="L550" s="53">
+        <v>46185</v>
+      </c>
+      <c r="M550" s="20" t="s">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="551" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A551" s="39">
+        <v>550</v>
+      </c>
+      <c r="B551" s="51">
+        <v>46185</v>
+      </c>
+      <c r="C551" s="52">
+        <v>0.32569444444444445</v>
+      </c>
+      <c r="D551" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E551" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="F551" s="20" t="s">
+        <v>332</v>
+      </c>
+      <c r="G551" s="20" t="s">
+        <v>783</v>
+      </c>
+      <c r="H551" s="20" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I551" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="J551" s="20" t="s">
+        <v>934</v>
+      </c>
+      <c r="K551" s="20" t="s">
+        <v>1272</v>
+      </c>
+      <c r="L551" s="53">
+        <v>46185</v>
+      </c>
+      <c r="M551" s="20" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="552" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A552" s="30">
+        <v>551</v>
+      </c>
+      <c r="B552" s="51">
+        <v>46185</v>
+      </c>
+      <c r="C552" s="52">
+        <v>0.32777777777777778</v>
+      </c>
+      <c r="D552" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E552" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="F552" s="20" t="s">
+        <v>832</v>
+      </c>
+      <c r="G552" s="20" t="s">
+        <v>780</v>
+      </c>
+      <c r="H552" s="20" t="s">
+        <v>885</v>
+      </c>
+      <c r="I552" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="J552" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="K552" s="20" t="s">
+        <v>945</v>
+      </c>
+      <c r="L552" s="50" t="s">
+        <v>945</v>
+      </c>
+      <c r="M552" s="20" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="553" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A553" s="22">
+        <v>552</v>
+      </c>
+      <c r="B553" s="51">
+        <v>46185</v>
+      </c>
+      <c r="C553" s="52">
+        <v>0.34444444444444444</v>
+      </c>
+      <c r="D553" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E553" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="F553" s="20" t="s">
+        <v>1309</v>
+      </c>
+      <c r="G553" s="20" t="s">
+        <v>789</v>
+      </c>
+      <c r="H553" s="20" t="s">
+        <v>1310</v>
+      </c>
+      <c r="I553" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="J553" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="K553" s="20" t="s">
+        <v>1272</v>
+      </c>
+      <c r="L553" s="53">
+        <v>46185</v>
+      </c>
+      <c r="M553" s="20" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="554" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A554" s="30">
+        <v>553</v>
+      </c>
+      <c r="B554" s="51">
+        <v>46185</v>
+      </c>
+      <c r="C554" s="52">
+        <v>0.34652777777777777</v>
+      </c>
+      <c r="D554" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E554" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="F554" s="20" t="s">
+        <v>1311</v>
+      </c>
+      <c r="G554" s="20" t="s">
+        <v>780</v>
+      </c>
+      <c r="H554" s="20" t="s">
+        <v>1070</v>
+      </c>
+      <c r="I554" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="J554" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="K554" s="20" t="s">
+        <v>945</v>
+      </c>
+      <c r="L554" s="50" t="s">
+        <v>945</v>
+      </c>
+      <c r="M554" s="20" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="555" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A555" s="39">
+        <v>554</v>
+      </c>
+      <c r="B555" s="51">
+        <v>46185</v>
+      </c>
+      <c r="C555" s="52">
+        <v>0.35069444444444442</v>
+      </c>
+      <c r="D555" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E555" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="F555" s="20" t="s">
+        <v>1312</v>
+      </c>
+      <c r="G555" s="20" t="s">
+        <v>780</v>
+      </c>
+      <c r="H555" s="20" t="s">
+        <v>1313</v>
+      </c>
+      <c r="I555" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="J555" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="K555" s="20" t="s">
+        <v>945</v>
+      </c>
+      <c r="L555" s="50" t="s">
+        <v>945</v>
+      </c>
+      <c r="M555" s="20" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="556" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A556" s="30">
+        <v>555</v>
+      </c>
+      <c r="B556" s="51">
+        <v>46185</v>
+      </c>
+      <c r="C556" s="52">
+        <v>0.35486111111111113</v>
+      </c>
+      <c r="D556" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E556" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="F556" s="20" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G556" s="20" t="s">
+        <v>1357</v>
+      </c>
+      <c r="H556" s="20" t="s">
+        <v>1358</v>
+      </c>
+      <c r="I556" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="J556" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="K556" s="20" t="s">
+        <v>945</v>
+      </c>
+      <c r="L556" s="50" t="s">
+        <v>945</v>
+      </c>
+      <c r="M556" s="20" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="557" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A557" s="22">
+        <v>556</v>
+      </c>
+      <c r="B557" s="51">
+        <v>46185</v>
+      </c>
+      <c r="C557" s="52">
+        <v>0.3611111111111111</v>
+      </c>
+      <c r="D557" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E557" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="F557" s="20" t="s">
+        <v>1314</v>
+      </c>
+      <c r="G557" s="20" t="s">
+        <v>802</v>
+      </c>
+      <c r="H557" s="20" t="s">
+        <v>1315</v>
+      </c>
+      <c r="I557" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="J557" s="20" t="s">
+        <v>934</v>
+      </c>
+      <c r="K557" s="20" t="s">
+        <v>1316</v>
+      </c>
+      <c r="L557" s="53">
+        <v>46186</v>
+      </c>
+      <c r="M557" s="20" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="558" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A558" s="30">
+        <v>557</v>
+      </c>
+      <c r="B558" s="51">
+        <v>46185</v>
+      </c>
+      <c r="C558" s="52">
+        <v>0.37569444444444444</v>
+      </c>
+      <c r="D558" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E558" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="F558" s="20" t="s">
+        <v>1317</v>
+      </c>
+      <c r="G558" s="20" t="s">
+        <v>802</v>
+      </c>
+      <c r="H558" s="20" t="s">
+        <v>1318</v>
+      </c>
+      <c r="I558" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="J558" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="K558" s="20" t="s">
+        <v>945</v>
+      </c>
+      <c r="L558" s="50" t="s">
+        <v>945</v>
+      </c>
+      <c r="M558" s="20" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="559" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A559" s="39">
+        <v>558</v>
+      </c>
+      <c r="B559" s="51">
+        <v>46185</v>
+      </c>
+      <c r="C559" s="52">
+        <v>0.37916666666666665</v>
+      </c>
+      <c r="D559" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E559" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="F559" s="20" t="s">
+        <v>1326</v>
+      </c>
+      <c r="G559" s="20" t="s">
+        <v>1114</v>
+      </c>
+      <c r="H559" s="20" t="s">
+        <v>1327</v>
+      </c>
+      <c r="I559" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="J559" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K559" s="20" t="s">
+        <v>1003</v>
+      </c>
+      <c r="L559" s="53">
+        <v>46185</v>
+      </c>
+      <c r="M559" s="20" t="s">
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="560" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A560" s="30">
+        <v>559</v>
+      </c>
+      <c r="B560" s="51">
+        <v>46185</v>
+      </c>
+      <c r="C560" s="52">
+        <v>0.38124999999999998</v>
+      </c>
+      <c r="D560" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E560" s="20" t="s">
+        <v>945</v>
+      </c>
+      <c r="F560" s="20" t="s">
+        <v>945</v>
+      </c>
+      <c r="G560" s="20" t="s">
+        <v>1361</v>
+      </c>
+      <c r="H560" s="20" t="s">
+        <v>1362</v>
+      </c>
+      <c r="I560" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="J560" s="20" t="s">
+        <v>1193</v>
+      </c>
+      <c r="K560" s="20" t="s">
+        <v>862</v>
+      </c>
+      <c r="L560" s="50" t="s">
+        <v>945</v>
+      </c>
+      <c r="M560" s="20" t="s">
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="561" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A561" s="22">
+        <v>560</v>
+      </c>
+      <c r="B561" s="51">
+        <v>46185</v>
+      </c>
+      <c r="C561" s="52">
+        <v>0.3923611111111111</v>
+      </c>
+      <c r="D561" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E561" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="F561" s="20" t="s">
+        <v>1328</v>
+      </c>
+      <c r="G561" s="20" t="s">
+        <v>1114</v>
+      </c>
+      <c r="H561" s="20" t="s">
+        <v>1327</v>
+      </c>
+      <c r="I561" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="J561" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K561" s="20" t="s">
+        <v>1003</v>
+      </c>
+      <c r="L561" s="53">
+        <v>46185</v>
+      </c>
+      <c r="M561" s="20" t="s">
+        <v>1364</v>
+      </c>
+    </row>
+    <row r="562" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A562" s="30">
+        <v>561</v>
+      </c>
+      <c r="B562" s="51">
+        <v>46185</v>
+      </c>
+      <c r="C562" s="52">
+        <v>0.40416666666666667</v>
+      </c>
+      <c r="D562" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E562" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="F562" s="20" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G562" s="20" t="s">
+        <v>1114</v>
+      </c>
+      <c r="H562" s="20" t="s">
+        <v>1320</v>
+      </c>
+      <c r="I562" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="J562" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K562" s="20" t="s">
+        <v>1003</v>
+      </c>
+      <c r="L562" s="53">
+        <v>46185</v>
+      </c>
+      <c r="M562" s="20" t="s">
+        <v>1365</v>
+      </c>
+    </row>
+    <row r="563" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A563" s="39">
+        <v>562</v>
+      </c>
+      <c r="B563" s="51">
+        <v>46185</v>
+      </c>
+      <c r="C563" s="52">
+        <v>0.4201388888888889</v>
+      </c>
+      <c r="D563" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E563" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="F563" s="20" t="s">
+        <v>1299</v>
+      </c>
+      <c r="G563" s="20" t="s">
+        <v>789</v>
+      </c>
+      <c r="H563" s="20" t="s">
+        <v>1321</v>
+      </c>
+      <c r="I563" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="J563" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K563" s="20" t="s">
+        <v>1003</v>
+      </c>
+      <c r="L563" s="53">
+        <v>46185</v>
+      </c>
+      <c r="M563" s="20" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="564" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A564" s="30">
+        <v>563</v>
+      </c>
+      <c r="B564" s="51">
+        <v>46185</v>
+      </c>
+      <c r="C564" s="52">
+        <v>0.42291666666666666</v>
+      </c>
+      <c r="D564" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E564" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="F564" s="20" t="s">
+        <v>1322</v>
+      </c>
+      <c r="G564" s="20" t="s">
+        <v>797</v>
+      </c>
+      <c r="H564" s="20" t="s">
+        <v>1323</v>
+      </c>
+      <c r="I564" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="J564" s="20" t="s">
+        <v>934</v>
+      </c>
+      <c r="K564" s="20" t="s">
+        <v>955</v>
+      </c>
+      <c r="L564" s="53">
+        <v>46186</v>
+      </c>
+      <c r="M564" s="20" t="s">
+        <v>1367</v>
+      </c>
+    </row>
+    <row r="565" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A565" s="22">
+        <v>564</v>
+      </c>
+      <c r="B565" s="51">
+        <v>46185</v>
+      </c>
+      <c r="C565" s="52">
+        <v>0.44166666666666665</v>
+      </c>
+      <c r="D565" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E565" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="F565" s="20" t="s">
+        <v>1324</v>
+      </c>
+      <c r="G565" s="20" t="s">
+        <v>1117</v>
+      </c>
+      <c r="H565" s="20" t="s">
+        <v>1325</v>
+      </c>
+      <c r="I565" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="J565" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="K565" s="20" t="s">
+        <v>945</v>
+      </c>
+      <c r="L565" s="50" t="s">
+        <v>945</v>
+      </c>
+      <c r="M565" s="20" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="566" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A566" s="30">
+        <v>565</v>
+      </c>
+      <c r="B566" s="51">
+        <v>46185</v>
+      </c>
+      <c r="C566" s="52">
+        <v>0.46388888888888891</v>
+      </c>
+      <c r="D566" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E566" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="F566" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="G566" s="20" t="s">
+        <v>789</v>
+      </c>
+      <c r="H566" s="20" t="s">
+        <v>968</v>
+      </c>
+      <c r="I566" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="J566" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="K566" s="20" t="s">
+        <v>945</v>
+      </c>
+      <c r="L566" s="50" t="s">
+        <v>945</v>
+      </c>
+      <c r="M566" s="20" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="567" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A567" s="39">
+        <v>566</v>
+      </c>
+      <c r="B567" s="51">
+        <v>46185</v>
+      </c>
+      <c r="C567" s="52">
+        <v>0.4826388888888889</v>
+      </c>
+      <c r="D567" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E567" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="F567" s="20" t="s">
+        <v>945</v>
+      </c>
+      <c r="G567" s="20" t="s">
+        <v>802</v>
+      </c>
+      <c r="H567" s="20" t="s">
+        <v>1330</v>
+      </c>
+      <c r="I567" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="J567" s="20" t="s">
+        <v>934</v>
+      </c>
+      <c r="K567" s="20" t="s">
+        <v>1272</v>
+      </c>
+      <c r="L567" s="53">
+        <v>46186</v>
+      </c>
+      <c r="M567" s="20" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="568" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A568" s="30">
+        <v>567</v>
+      </c>
+      <c r="B568" s="51">
+        <v>46185</v>
+      </c>
+      <c r="C568" s="52">
+        <v>0.4861111111111111</v>
+      </c>
+      <c r="D568" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E568" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="F568" s="20" t="s">
+        <v>1331</v>
+      </c>
+      <c r="G568" s="20" t="s">
+        <v>1114</v>
+      </c>
+      <c r="H568" s="20" t="s">
+        <v>1332</v>
+      </c>
+      <c r="I568" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="J568" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K568" s="20" t="s">
+        <v>1003</v>
+      </c>
+      <c r="L568" s="53">
+        <v>46185</v>
+      </c>
+      <c r="M568" s="20" t="s">
+        <v>1368</v>
+      </c>
+    </row>
+    <row r="569" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A569" s="22">
+        <v>568</v>
+      </c>
+      <c r="B569" s="51">
+        <v>46185</v>
+      </c>
+      <c r="C569" s="52">
+        <v>0.49236111111111114</v>
+      </c>
+      <c r="D569" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E569" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="F569" s="20" t="s">
+        <v>1333</v>
+      </c>
+      <c r="G569" s="20" t="s">
+        <v>789</v>
+      </c>
+      <c r="H569" s="20" t="s">
+        <v>1334</v>
+      </c>
+      <c r="I569" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="J569" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="K569" s="20" t="s">
+        <v>945</v>
+      </c>
+      <c r="L569" s="50" t="s">
+        <v>945</v>
+      </c>
+      <c r="M569" s="20" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="570" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A570" s="30">
+        <v>569</v>
+      </c>
+      <c r="B570" s="51">
+        <v>46185</v>
+      </c>
+      <c r="C570" s="52">
+        <v>0.52152777777777781</v>
+      </c>
+      <c r="D570" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E570" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="F570" s="20" t="s">
+        <v>1335</v>
+      </c>
+      <c r="G570" s="20" t="s">
+        <v>797</v>
+      </c>
+      <c r="H570" s="20" t="s">
+        <v>1336</v>
+      </c>
+      <c r="I570" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="J570" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K570" s="20" t="s">
+        <v>1003</v>
+      </c>
+      <c r="L570" s="53">
+        <v>46185</v>
+      </c>
+      <c r="M570" s="20" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="571" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A571" s="39">
+        <v>570</v>
+      </c>
+      <c r="B571" s="51">
+        <v>46185</v>
+      </c>
+      <c r="C571" s="52">
+        <v>0.54027777777777775</v>
+      </c>
+      <c r="D571" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E571" s="20" t="s">
+        <v>984</v>
+      </c>
+      <c r="F571" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="G571" s="20" t="s">
+        <v>783</v>
+      </c>
+      <c r="H571" s="20" t="s">
+        <v>1370</v>
+      </c>
+      <c r="I571" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="J571" s="20" t="s">
+        <v>934</v>
+      </c>
+      <c r="K571" s="20" t="s">
+        <v>1284</v>
+      </c>
+      <c r="L571" s="53">
+        <v>46185</v>
+      </c>
+      <c r="M571" s="20" t="s">
+        <v>1371</v>
+      </c>
+    </row>
+    <row r="572" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A572" s="30">
+        <v>571</v>
+      </c>
+      <c r="B572" s="51">
+        <v>46185</v>
+      </c>
+      <c r="C572" s="52">
+        <v>0.58194444444444449</v>
+      </c>
+      <c r="D572" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E572" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="F572" s="20" t="s">
+        <v>220</v>
+      </c>
+      <c r="G572" s="20" t="s">
+        <v>797</v>
+      </c>
+      <c r="H572" s="20" t="s">
+        <v>1338</v>
+      </c>
+      <c r="I572" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="J572" s="20" t="s">
+        <v>934</v>
+      </c>
+      <c r="K572" s="20" t="s">
+        <v>1282</v>
+      </c>
+      <c r="L572" s="53">
+        <v>46185</v>
+      </c>
+      <c r="M572" s="20" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="573" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A573" s="22">
+        <v>572</v>
+      </c>
+      <c r="B573" s="51">
+        <v>46185</v>
+      </c>
+      <c r="C573" s="52">
+        <v>0.61250000000000004</v>
+      </c>
+      <c r="D573" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E573" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="F573" s="20" t="s">
+        <v>1372</v>
+      </c>
+      <c r="G573" s="20" t="s">
+        <v>1357</v>
+      </c>
+      <c r="H573" s="20" t="s">
+        <v>1373</v>
+      </c>
+      <c r="I573" s="20" t="s">
+        <v>1374</v>
+      </c>
+      <c r="J573" s="20" t="s">
+        <v>1193</v>
+      </c>
+      <c r="K573" s="20" t="s">
+        <v>1375</v>
+      </c>
+      <c r="L573" s="50" t="s">
+        <v>945</v>
+      </c>
+      <c r="M573" s="20" t="s">
+        <v>1376</v>
+      </c>
+    </row>
+    <row r="574" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A574" s="30">
+        <v>573</v>
+      </c>
+      <c r="B574" s="51">
+        <v>46185</v>
+      </c>
+      <c r="C574" s="52">
+        <v>0.63749999999999996</v>
+      </c>
+      <c r="D574" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E574" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="F574" s="20" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G574" s="20" t="s">
+        <v>797</v>
+      </c>
+      <c r="H574" s="20" t="s">
+        <v>1377</v>
+      </c>
+      <c r="I574" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="J574" s="20" t="s">
+        <v>934</v>
+      </c>
+      <c r="K574" s="20" t="s">
+        <v>1282</v>
+      </c>
+      <c r="L574" s="53">
+        <v>46185</v>
+      </c>
+      <c r="M574" s="20" t="s">
+        <v>1378</v>
+      </c>
+    </row>
+    <row r="575" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A575" s="39">
+        <v>574</v>
+      </c>
+      <c r="B575" s="51">
+        <v>46185</v>
+      </c>
+      <c r="C575" s="52">
+        <v>0.6430555555555556</v>
+      </c>
+      <c r="D575" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E575" s="20" t="s">
+        <v>278</v>
+      </c>
+      <c r="F575" s="20" t="s">
+        <v>328</v>
+      </c>
+      <c r="G575" s="20" t="s">
+        <v>1117</v>
+      </c>
+      <c r="H575" s="20" t="s">
+        <v>1339</v>
+      </c>
+      <c r="I575" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="J575" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K575" s="20" t="s">
+        <v>955</v>
+      </c>
+      <c r="L575" s="53">
+        <v>46185</v>
+      </c>
+      <c r="M575" s="20" t="s">
+        <v>1379</v>
+      </c>
+    </row>
+    <row r="576" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A576" s="30">
+        <v>575</v>
+      </c>
+      <c r="B576" s="51">
+        <v>46185</v>
+      </c>
+      <c r="C576" s="52">
+        <v>0.65416666666666667</v>
+      </c>
+      <c r="D576" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E576" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="F576" s="20" t="s">
+        <v>1340</v>
+      </c>
+      <c r="G576" s="20" t="s">
+        <v>789</v>
+      </c>
+      <c r="H576" s="20" t="s">
+        <v>1341</v>
+      </c>
+      <c r="I576" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="J576" s="20" t="s">
+        <v>1193</v>
+      </c>
+      <c r="K576" s="20" t="s">
+        <v>1342</v>
+      </c>
+      <c r="L576" s="50" t="s">
+        <v>945</v>
+      </c>
+      <c r="M576" s="20" t="s">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="577" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A577" s="22">
+        <v>576</v>
+      </c>
+      <c r="B577" s="51">
+        <v>46185</v>
+      </c>
+      <c r="C577" s="52">
+        <v>0.66041666666666665</v>
+      </c>
+      <c r="D577" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E577" s="20" t="s">
+        <v>945</v>
+      </c>
+      <c r="F577" s="20" t="s">
+        <v>1381</v>
+      </c>
+      <c r="G577" s="20" t="s">
+        <v>802</v>
+      </c>
+      <c r="H577" s="20" t="s">
+        <v>1382</v>
+      </c>
+      <c r="I577" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="J577" s="20" t="s">
+        <v>934</v>
+      </c>
+      <c r="K577" s="20" t="s">
+        <v>1284</v>
+      </c>
+      <c r="L577" s="53">
+        <v>46185</v>
+      </c>
+      <c r="M577" s="20" t="s">
+        <v>1378</v>
+      </c>
+    </row>
+    <row r="578" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A578" s="30">
+        <v>577</v>
+      </c>
+      <c r="B578" s="51">
+        <v>46185</v>
+      </c>
+      <c r="C578" s="52" t="s">
+        <v>945</v>
+      </c>
+      <c r="D578" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E578" s="20" t="s">
+        <v>945</v>
+      </c>
+      <c r="F578" s="20" t="s">
+        <v>1383</v>
+      </c>
+      <c r="G578" s="20" t="s">
+        <v>783</v>
+      </c>
+      <c r="H578" s="20" t="s">
+        <v>1384</v>
+      </c>
+      <c r="I578" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="J578" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="K578" s="20" t="s">
+        <v>945</v>
+      </c>
+      <c r="L578" s="50" t="s">
+        <v>945</v>
+      </c>
+      <c r="M578" s="20" t="s">
+        <v>1385</v>
+      </c>
+    </row>
+    <row r="579" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A579" s="39">
+        <v>578</v>
+      </c>
+      <c r="B579" s="51">
+        <v>46186</v>
+      </c>
+      <c r="C579" s="52">
+        <v>0.28749999999999998</v>
+      </c>
+      <c r="D579" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E579" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="F579" s="20" t="s">
+        <v>1291</v>
+      </c>
+      <c r="G579" s="20" t="s">
+        <v>1386</v>
+      </c>
+      <c r="H579" s="20" t="s">
+        <v>1387</v>
+      </c>
+      <c r="I579" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="J579" s="20" t="s">
+        <v>934</v>
+      </c>
+      <c r="K579" s="20" t="s">
+        <v>1272</v>
+      </c>
+      <c r="L579" s="53">
+        <v>46186</v>
+      </c>
+      <c r="M579" s="20" t="s">
+        <v>1388</v>
+      </c>
+    </row>
+    <row r="580" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A580" s="30">
+        <v>579</v>
+      </c>
+      <c r="B580" s="51">
+        <v>46186</v>
+      </c>
+      <c r="C580" s="52">
+        <v>0.29583333333333334</v>
+      </c>
+      <c r="D580" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E580" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="F580" s="20" t="s">
+        <v>1389</v>
+      </c>
+      <c r="G580" s="20" t="s">
+        <v>783</v>
+      </c>
+      <c r="H580" s="20" t="s">
+        <v>1390</v>
+      </c>
+      <c r="I580" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="J580" s="20" t="s">
+        <v>934</v>
+      </c>
+      <c r="K580" s="20" t="s">
+        <v>1272</v>
+      </c>
+      <c r="L580" s="53">
+        <v>46186</v>
+      </c>
+      <c r="M580" s="20" t="s">
+        <v>1391</v>
+      </c>
+    </row>
+    <row r="581" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A581" s="22">
+        <v>580</v>
+      </c>
+      <c r="B581" s="51">
+        <v>46186</v>
+      </c>
+      <c r="C581" s="52">
+        <v>0.29930555555555555</v>
+      </c>
+      <c r="D581" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E581" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="F581" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="G581" s="20" t="s">
+        <v>783</v>
+      </c>
+      <c r="H581" s="20" t="s">
+        <v>1392</v>
+      </c>
+      <c r="I581" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="J581" s="20" t="s">
+        <v>934</v>
+      </c>
+      <c r="K581" s="20" t="s">
+        <v>1393</v>
+      </c>
+      <c r="L581" s="53">
+        <v>46186</v>
+      </c>
+      <c r="M581" s="20" t="s">
+        <v>1394</v>
+      </c>
+    </row>
+    <row r="582" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A582" s="30">
+        <v>581</v>
+      </c>
+      <c r="B582" s="51">
+        <v>46186</v>
+      </c>
+      <c r="C582" s="52">
+        <v>0.3034722222222222</v>
+      </c>
+      <c r="D582" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E582" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="F582" s="20" t="s">
+        <v>328</v>
+      </c>
+      <c r="G582" s="20" t="s">
+        <v>783</v>
+      </c>
+      <c r="H582" s="20" t="s">
+        <v>1395</v>
+      </c>
+      <c r="I582" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="J582" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="K582" s="20" t="s">
+        <v>945</v>
+      </c>
+      <c r="L582" s="50" t="s">
+        <v>945</v>
+      </c>
+      <c r="M582" s="20" t="s">
+        <v>1396</v>
+      </c>
+    </row>
+    <row r="583" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A583" s="39">
+        <v>582</v>
+      </c>
+      <c r="B583" s="51">
+        <v>46186</v>
+      </c>
+      <c r="C583" s="52">
+        <v>0.30416666666666664</v>
+      </c>
+      <c r="D583" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E583" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="F583" s="20" t="s">
+        <v>328</v>
+      </c>
+      <c r="G583" s="20" t="s">
+        <v>1397</v>
+      </c>
+      <c r="H583" s="20" t="s">
+        <v>1398</v>
+      </c>
+      <c r="I583" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="J583" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="K583" s="20" t="s">
+        <v>945</v>
+      </c>
+      <c r="L583" s="50" t="s">
+        <v>945</v>
+      </c>
+      <c r="M583" s="20" t="s">
+        <v>1399</v>
+      </c>
+    </row>
+    <row r="584" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A584" s="30">
+        <v>583</v>
+      </c>
+      <c r="B584" s="51">
+        <v>46186</v>
+      </c>
+      <c r="C584" s="52">
+        <v>0.30625000000000002</v>
+      </c>
+      <c r="D584" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E584" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="F584" s="20" t="s">
+        <v>328</v>
+      </c>
+      <c r="G584" s="20" t="s">
+        <v>1117</v>
+      </c>
+      <c r="H584" s="20" t="s">
+        <v>1400</v>
+      </c>
+      <c r="I584" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="J584" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="K584" s="20" t="s">
+        <v>945</v>
+      </c>
+      <c r="L584" s="50" t="s">
+        <v>945</v>
+      </c>
+      <c r="M584" s="20" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="585" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A585" s="22">
+        <v>584</v>
+      </c>
+      <c r="B585" s="51">
+        <v>46186</v>
+      </c>
+      <c r="C585" s="52">
+        <v>0.30833333333333335</v>
+      </c>
+      <c r="D585" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E585" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="F585" s="20" t="s">
+        <v>1402</v>
+      </c>
+      <c r="G585" s="20" t="s">
+        <v>1397</v>
+      </c>
+      <c r="H585" s="20" t="s">
+        <v>1403</v>
+      </c>
+      <c r="I585" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="J585" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="K585" s="20" t="s">
+        <v>945</v>
+      </c>
+      <c r="L585" s="50" t="s">
+        <v>945</v>
+      </c>
+      <c r="M585" s="20" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="586" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A586" s="30">
+        <v>585</v>
+      </c>
+      <c r="B586" s="51">
+        <v>46186</v>
+      </c>
+      <c r="C586" s="52">
+        <v>0.31458333333333333</v>
+      </c>
+      <c r="D586" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E586" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="F586" s="20" t="s">
+        <v>1076</v>
+      </c>
+      <c r="G586" s="20" t="s">
+        <v>777</v>
+      </c>
+      <c r="H586" s="20" t="s">
+        <v>1405</v>
+      </c>
+      <c r="I586" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="J586" s="20" t="s">
+        <v>934</v>
+      </c>
+      <c r="K586" s="20" t="s">
+        <v>1393</v>
+      </c>
+      <c r="L586" s="53">
+        <v>46186</v>
+      </c>
+      <c r="M586" s="20" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="587" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A587" s="39">
+        <v>586</v>
+      </c>
+      <c r="B587" s="51">
+        <v>46186</v>
+      </c>
+      <c r="C587" s="52">
+        <v>0.32083333333333336</v>
+      </c>
+      <c r="D587" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E587" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="F587" s="20" t="s">
+        <v>1407</v>
+      </c>
+      <c r="G587" s="20" t="s">
+        <v>1111</v>
+      </c>
+      <c r="H587" s="20" t="s">
+        <v>1408</v>
+      </c>
+      <c r="I587" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="J587" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="K587" s="20" t="s">
+        <v>945</v>
+      </c>
+      <c r="L587" s="50" t="s">
+        <v>945</v>
+      </c>
+      <c r="M587" s="20" t="s">
+        <v>1409</v>
+      </c>
+    </row>
+    <row r="588" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A588" s="30">
+        <v>587</v>
+      </c>
+      <c r="B588" s="51">
+        <v>46186</v>
+      </c>
+      <c r="C588" s="52">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D588" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E588" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="F588" s="20" t="s">
+        <v>1410</v>
+      </c>
+      <c r="G588" s="20" t="s">
+        <v>1111</v>
+      </c>
+      <c r="H588" s="20" t="s">
+        <v>1411</v>
+      </c>
+      <c r="I588" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="J588" s="20" t="s">
+        <v>1412</v>
+      </c>
+      <c r="K588" s="20" t="s">
+        <v>1342</v>
+      </c>
+      <c r="L588" s="53">
+        <v>46186</v>
+      </c>
+      <c r="M588" s="20" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="589" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A589" s="22">
+        <v>588</v>
+      </c>
+      <c r="B589" s="51">
+        <v>46186</v>
+      </c>
+      <c r="C589" s="52">
+        <v>0.34097222222222223</v>
+      </c>
+      <c r="D589" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E589" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="F589" s="20" t="s">
+        <v>328</v>
+      </c>
+      <c r="G589" s="20" t="s">
+        <v>1397</v>
+      </c>
+      <c r="H589" s="20" t="s">
+        <v>1414</v>
+      </c>
+      <c r="I589" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="J589" s="20" t="s">
+        <v>934</v>
+      </c>
+      <c r="K589" s="20" t="s">
+        <v>1295</v>
+      </c>
+      <c r="L589" s="53">
+        <v>46186</v>
+      </c>
+      <c r="M589" s="20" t="s">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="590" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A590" s="30">
+        <v>589</v>
+      </c>
+      <c r="B590" s="51">
+        <v>46186</v>
+      </c>
+      <c r="C590" s="52">
+        <v>0.36458333333333331</v>
+      </c>
+      <c r="D590" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E590" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="F590" s="20" t="s">
+        <v>1416</v>
+      </c>
+      <c r="G590" s="20" t="s">
+        <v>1417</v>
+      </c>
+      <c r="H590" s="20" t="s">
+        <v>1418</v>
+      </c>
+      <c r="I590" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="J590" s="20" t="s">
+        <v>934</v>
+      </c>
+      <c r="K590" s="20" t="s">
+        <v>1272</v>
+      </c>
+      <c r="L590" s="53">
+        <v>46186</v>
+      </c>
+      <c r="M590" s="20" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="591" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A591" s="39">
+        <v>590</v>
+      </c>
+      <c r="B591" s="51">
+        <v>46186</v>
+      </c>
+      <c r="C591" s="52">
+        <v>0.39305555555555555</v>
+      </c>
+      <c r="D591" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E591" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="F591" s="20" t="s">
+        <v>1420</v>
+      </c>
+      <c r="G591" s="20" t="s">
+        <v>1421</v>
+      </c>
+      <c r="H591" s="20" t="s">
+        <v>1422</v>
+      </c>
+      <c r="I591" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="J591" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="K591" s="20" t="s">
+        <v>945</v>
+      </c>
+      <c r="L591" s="50" t="s">
+        <v>945</v>
+      </c>
+      <c r="M591" s="20" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="592" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A592" s="30">
+        <v>591</v>
+      </c>
+      <c r="B592" s="51">
+        <v>46186</v>
+      </c>
+      <c r="C592" s="52">
+        <v>0.39930555555555558</v>
+      </c>
+      <c r="D592" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E592" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="F592" s="20" t="s">
+        <v>328</v>
+      </c>
+      <c r="G592" s="20" t="s">
+        <v>1397</v>
+      </c>
+      <c r="H592" s="20" t="s">
+        <v>1424</v>
+      </c>
+      <c r="I592" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="J592" s="20" t="s">
+        <v>934</v>
+      </c>
+      <c r="K592" s="20" t="s">
+        <v>1295</v>
+      </c>
+      <c r="L592" s="53">
+        <v>46186</v>
+      </c>
+      <c r="M592" s="20" t="s">
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="593" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A593" s="22">
+        <v>592</v>
+      </c>
+      <c r="B593" s="51">
+        <v>46186</v>
+      </c>
+      <c r="C593" s="52">
+        <v>0.42638888888888887</v>
+      </c>
+      <c r="D593" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E593" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="F593" s="20" t="s">
+        <v>1426</v>
+      </c>
+      <c r="G593" s="20" t="s">
+        <v>1386</v>
+      </c>
+      <c r="H593" s="20" t="s">
+        <v>1427</v>
+      </c>
+      <c r="I593" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="J593" s="20" t="s">
+        <v>934</v>
+      </c>
+      <c r="K593" s="20" t="s">
+        <v>1272</v>
+      </c>
+      <c r="L593" s="53">
+        <v>46186</v>
+      </c>
+      <c r="M593" s="20" t="s">
+        <v>1428</v>
+      </c>
+    </row>
+    <row r="594" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A594" s="30">
+        <v>593</v>
+      </c>
+      <c r="B594" s="51">
+        <v>46186</v>
+      </c>
+      <c r="C594" s="52">
+        <v>0.44236111111111109</v>
+      </c>
+      <c r="D594" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E594" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="F594" s="20" t="s">
+        <v>1429</v>
+      </c>
+      <c r="G594" s="20" t="s">
+        <v>802</v>
+      </c>
+      <c r="H594" s="20" t="s">
+        <v>1430</v>
+      </c>
+      <c r="I594" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="J594" s="20" t="s">
+        <v>934</v>
+      </c>
+      <c r="K594" s="20" t="s">
+        <v>1295</v>
+      </c>
+      <c r="L594" s="53">
+        <v>46186</v>
+      </c>
+      <c r="M594" s="20" t="s">
+        <v>1431</v>
+      </c>
+    </row>
+    <row r="595" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A595" s="39">
+        <v>594</v>
+      </c>
+      <c r="B595" s="51">
+        <v>46186</v>
+      </c>
+      <c r="C595" s="52">
+        <v>0.33194444444444443</v>
+      </c>
+      <c r="D595" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E595" s="20" t="s">
+        <v>1432</v>
+      </c>
+      <c r="F595" s="20" t="s">
+        <v>1433</v>
+      </c>
+      <c r="G595" s="20" t="s">
+        <v>789</v>
+      </c>
+      <c r="H595" s="20" t="s">
+        <v>1434</v>
+      </c>
+      <c r="I595" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="J595" s="20" t="s">
+        <v>934</v>
+      </c>
+      <c r="K595" s="20" t="s">
+        <v>1284</v>
+      </c>
+      <c r="L595" s="53">
+        <v>46187</v>
+      </c>
+      <c r="M595" s="20" t="s">
+        <v>1435</v>
+      </c>
+    </row>
+    <row r="596" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A596" s="30">
+        <v>595</v>
+      </c>
+      <c r="B596" s="51">
+        <v>46186</v>
+      </c>
+      <c r="C596" s="52">
+        <v>0.48055555555555557</v>
+      </c>
+      <c r="D596" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="E596" s="20" t="s">
+        <v>1436</v>
+      </c>
+      <c r="F596" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="G596" s="20" t="s">
+        <v>1437</v>
+      </c>
+      <c r="H596" s="20" t="s">
+        <v>1438</v>
+      </c>
+      <c r="I596" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="J596" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="K596" s="20" t="s">
+        <v>1439</v>
+      </c>
+      <c r="L596" s="50" t="s">
+        <v>945</v>
+      </c>
+      <c r="M596" s="20" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="597" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A597" s="22">
+        <v>596</v>
+      </c>
+      <c r="B597" s="51">
+        <v>46186</v>
+      </c>
+      <c r="C597" s="52">
+        <v>0.6743055555555556</v>
+      </c>
+      <c r="D597" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E597" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="F597" s="20" t="s">
+        <v>1441</v>
+      </c>
+      <c r="G597" s="20" t="s">
+        <v>789</v>
+      </c>
+      <c r="H597" s="20" t="s">
+        <v>1442</v>
+      </c>
+      <c r="I597" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="J597" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="K597" s="20" t="s">
+        <v>945</v>
+      </c>
+      <c r="L597" s="50" t="s">
+        <v>945</v>
+      </c>
+      <c r="M597" s="20" t="s">
+        <v>1443</v>
+      </c>
+    </row>
+    <row r="598" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A598" s="30">
+        <v>597</v>
+      </c>
+      <c r="B598" s="51">
+        <v>46186</v>
+      </c>
+      <c r="C598" s="52">
+        <v>0.71805555555555556</v>
+      </c>
+      <c r="D598" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E598" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="F598" s="20" t="s">
+        <v>1441</v>
+      </c>
+      <c r="G598" s="20" t="s">
+        <v>789</v>
+      </c>
+      <c r="H598" s="20" t="s">
+        <v>1444</v>
+      </c>
+      <c r="I598" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="J598" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="K598" s="20" t="s">
+        <v>945</v>
+      </c>
+      <c r="L598" s="50" t="s">
+        <v>945</v>
+      </c>
+      <c r="M598" s="20" t="s">
+        <v>1445</v>
+      </c>
+    </row>
+    <row r="599" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A599" s="39">
+        <v>598</v>
+      </c>
+      <c r="B599" s="51">
+        <v>46186</v>
+      </c>
+      <c r="C599" s="52">
+        <v>0.28472222222222221</v>
+      </c>
+      <c r="D599" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="E599" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="F599" s="20" t="s">
+        <v>1446</v>
+      </c>
+      <c r="G599" s="20" t="s">
+        <v>783</v>
+      </c>
+      <c r="H599" s="20" t="s">
+        <v>1447</v>
+      </c>
+      <c r="I599" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="J599" s="20" t="s">
+        <v>934</v>
+      </c>
+      <c r="K599" s="20" t="s">
+        <v>1295</v>
+      </c>
+      <c r="L599" s="53">
+        <v>46186</v>
+      </c>
+      <c r="M599" s="20" t="s">
+        <v>1448</v>
+      </c>
+    </row>
+    <row r="600" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A600" s="30">
+        <v>599</v>
+      </c>
+      <c r="B600" s="51">
+        <v>46186</v>
+      </c>
+      <c r="C600" s="52">
+        <v>0.29097222222222224</v>
+      </c>
+      <c r="D600" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="E600" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="F600" s="20" t="s">
+        <v>1449</v>
+      </c>
+      <c r="G600" s="20" t="s">
+        <v>783</v>
+      </c>
+      <c r="H600" s="20" t="s">
+        <v>1450</v>
+      </c>
+      <c r="I600" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="J600" s="20" t="s">
+        <v>934</v>
+      </c>
+      <c r="K600" s="20" t="s">
+        <v>1295</v>
+      </c>
+      <c r="L600" s="53">
+        <v>46186</v>
+      </c>
+      <c r="M600" s="20" t="s">
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="601" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="A601" s="22">
+        <v>600</v>
+      </c>
+      <c r="B601" s="51">
+        <v>46186</v>
+      </c>
+      <c r="C601" s="52">
+        <v>0.48125000000000001</v>
+      </c>
+      <c r="D601" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E601" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="F601" s="20" t="s">
+        <v>1452</v>
+      </c>
+      <c r="G601" s="20" t="s">
+        <v>1117</v>
+      </c>
+      <c r="H601" s="20" t="s">
+        <v>1453</v>
+      </c>
+      <c r="I601" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="J601" s="20" t="s">
+        <v>791</v>
+      </c>
+      <c r="K601" s="20" t="s">
+        <v>1454</v>
+      </c>
+      <c r="L601" s="50" t="s">
+        <v>945</v>
+      </c>
+      <c r="M601" s="20" t="s">
+        <v>1455</v>
+      </c>
+    </row>
+    <row r="602" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A602" s="30">
+        <v>601</v>
+      </c>
+      <c r="B602" s="51">
+        <v>46186</v>
+      </c>
+      <c r="C602" s="52">
+        <v>0.64236111111111116</v>
+      </c>
+      <c r="D602" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E602" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="F602" s="20" t="s">
+        <v>1456</v>
+      </c>
+      <c r="G602" s="20" t="s">
+        <v>802</v>
+      </c>
+      <c r="H602" s="20" t="s">
+        <v>1457</v>
+      </c>
+      <c r="I602" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="J602" s="20" t="s">
+        <v>934</v>
+      </c>
+      <c r="K602" s="20" t="s">
+        <v>1393</v>
+      </c>
+      <c r="L602" s="53">
+        <v>46186</v>
+      </c>
+      <c r="M602" s="20" t="s">
+        <v>1458</v>
+      </c>
+    </row>
+    <row r="603" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A603" s="39">
+        <v>602</v>
+      </c>
+      <c r="B603" s="51">
+        <v>46187</v>
+      </c>
+      <c r="C603" s="52">
+        <v>0.29236111111111113</v>
+      </c>
+      <c r="D603" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E603" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="F603" s="20" t="s">
+        <v>1459</v>
+      </c>
+      <c r="G603" s="20" t="s">
+        <v>783</v>
+      </c>
+      <c r="H603" s="20" t="s">
+        <v>1460</v>
+      </c>
+      <c r="I603" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="J603" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="K603" s="20" t="s">
+        <v>1461</v>
+      </c>
+      <c r="L603" s="50" t="s">
+        <v>945</v>
+      </c>
+      <c r="M603" s="20" t="s">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="604" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A604" s="30">
+        <v>603</v>
+      </c>
+      <c r="B604" s="51">
+        <v>46187</v>
+      </c>
+      <c r="C604" s="52">
+        <v>0.32361111111111113</v>
+      </c>
+      <c r="D604" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E604" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="F604" s="20" t="s">
+        <v>1463</v>
+      </c>
+      <c r="G604" s="20" t="s">
+        <v>1464</v>
+      </c>
+      <c r="H604" s="20" t="s">
+        <v>1465</v>
+      </c>
+      <c r="I604" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="J604" s="20" t="s">
+        <v>1412</v>
+      </c>
+      <c r="K604" s="20" t="s">
+        <v>1466</v>
+      </c>
+      <c r="L604" s="53">
+        <v>46187</v>
+      </c>
+      <c r="M604" s="20" t="s">
+        <v>1467</v>
+      </c>
+    </row>
+    <row r="605" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A605" s="22">
+        <v>604</v>
+      </c>
+      <c r="B605" s="51">
+        <v>46187</v>
+      </c>
+      <c r="C605" s="52">
+        <v>0.34027777777777779</v>
+      </c>
+      <c r="D605" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E605" s="20" t="s">
+        <v>1468</v>
+      </c>
+      <c r="F605" s="20" t="s">
+        <v>1469</v>
+      </c>
+      <c r="G605" s="20" t="s">
+        <v>1470</v>
+      </c>
+      <c r="H605" s="20" t="s">
+        <v>1471</v>
+      </c>
+      <c r="I605" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="J605" s="20" t="s">
+        <v>1412</v>
+      </c>
+      <c r="K605" s="20" t="s">
+        <v>1472</v>
+      </c>
+      <c r="L605" s="53">
+        <v>46187</v>
+      </c>
+      <c r="M605" s="20" t="s">
+        <v>1473</v>
+      </c>
+    </row>
+    <row r="606" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A606" s="30">
+        <v>605</v>
+      </c>
+      <c r="B606" s="51">
+        <v>46187</v>
+      </c>
+      <c r="C606" s="52">
+        <v>0.47222222222222221</v>
+      </c>
+      <c r="D606" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E606" s="20" t="s">
+        <v>1474</v>
+      </c>
+      <c r="F606" s="20" t="s">
+        <v>1475</v>
+      </c>
+      <c r="G606" s="20" t="s">
+        <v>783</v>
+      </c>
+      <c r="H606" s="20" t="s">
+        <v>1476</v>
+      </c>
+      <c r="I606" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="J606" s="20" t="s">
+        <v>791</v>
+      </c>
+      <c r="K606" s="20" t="s">
+        <v>1477</v>
+      </c>
+      <c r="L606" s="50" t="s">
+        <v>945</v>
+      </c>
+      <c r="M606" s="20" t="s">
+        <v>1478</v>
+      </c>
+    </row>
+    <row r="607" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A607" s="39">
+        <v>606</v>
+      </c>
+      <c r="B607" s="51">
+        <v>46188</v>
+      </c>
+      <c r="C607" s="52">
+        <v>0.35902777777777778</v>
+      </c>
+      <c r="D607" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E607" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="F607" s="20" t="s">
+        <v>220</v>
+      </c>
+      <c r="G607" s="20" t="s">
+        <v>802</v>
+      </c>
+      <c r="H607" s="20" t="s">
+        <v>1479</v>
+      </c>
+      <c r="I607" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="J607" s="20" t="s">
+        <v>934</v>
+      </c>
+      <c r="K607" s="20" t="s">
+        <v>1393</v>
+      </c>
+      <c r="L607" s="53">
+        <v>46188</v>
+      </c>
+      <c r="M607" s="20" t="s">
+        <v>1480</v>
+      </c>
+    </row>
+    <row r="608" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A608" s="30">
+        <v>607</v>
+      </c>
+      <c r="B608" s="51">
+        <v>46188</v>
+      </c>
+      <c r="C608" s="52">
+        <v>0.3659722222222222</v>
+      </c>
+      <c r="D608" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E608" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="F608" s="20" t="s">
+        <v>1481</v>
+      </c>
+      <c r="G608" s="20" t="s">
+        <v>783</v>
+      </c>
+      <c r="H608" s="20" t="s">
+        <v>1482</v>
+      </c>
+      <c r="I608" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="J608" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="K608" s="20" t="s">
+        <v>945</v>
+      </c>
+      <c r="L608" s="50" t="s">
+        <v>945</v>
+      </c>
+      <c r="M608" s="20" t="s">
+        <v>1483</v>
+      </c>
+    </row>
+    <row r="609" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A609" s="22">
+        <v>608</v>
+      </c>
+      <c r="B609" s="51">
+        <v>46188</v>
+      </c>
+      <c r="C609" s="52">
+        <v>0.37361111111111112</v>
+      </c>
+      <c r="D609" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E609" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="F609" s="20" t="s">
+        <v>328</v>
+      </c>
+      <c r="G609" s="20" t="s">
+        <v>1484</v>
+      </c>
+      <c r="H609" s="20" t="s">
+        <v>1485</v>
+      </c>
+      <c r="I609" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="J609" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="K609" s="20" t="s">
+        <v>945</v>
+      </c>
+      <c r="L609" s="50" t="s">
+        <v>945</v>
+      </c>
+      <c r="M609" s="20" t="s">
+        <v>1486</v>
+      </c>
+    </row>
+    <row r="610" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A610" s="30">
+        <v>609</v>
+      </c>
+      <c r="B610" s="51">
+        <v>46188</v>
+      </c>
+      <c r="C610" s="52">
+        <v>0.37986111111111109</v>
+      </c>
+      <c r="D610" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E610" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="F610" s="20" t="s">
+        <v>1314</v>
+      </c>
+      <c r="G610" s="20" t="s">
+        <v>783</v>
+      </c>
+      <c r="H610" s="20" t="s">
+        <v>1487</v>
+      </c>
+      <c r="I610" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="J610" s="20" t="s">
+        <v>934</v>
+      </c>
+      <c r="K610" s="20" t="s">
+        <v>1393</v>
+      </c>
+      <c r="L610" s="53">
+        <v>46188</v>
+      </c>
+      <c r="M610" s="20" t="s">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="611" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A611" s="39">
+        <v>610</v>
+      </c>
+      <c r="B611" s="51">
+        <v>46188</v>
+      </c>
+      <c r="C611" s="52">
+        <v>0.38680555555555557</v>
+      </c>
+      <c r="D611" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E611" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="F611" s="20" t="s">
+        <v>1489</v>
+      </c>
+      <c r="G611" s="20" t="s">
+        <v>777</v>
+      </c>
+      <c r="H611" s="20" t="s">
+        <v>1490</v>
+      </c>
+      <c r="I611" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="J611" s="20" t="s">
+        <v>934</v>
+      </c>
+      <c r="K611" s="20" t="s">
+        <v>1491</v>
+      </c>
+      <c r="L611" s="53">
+        <v>46188</v>
+      </c>
+      <c r="M611" s="20" t="s">
+        <v>1492</v>
+      </c>
+    </row>
+    <row r="612" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A612" s="30">
+        <v>611</v>
+      </c>
+      <c r="B612" s="51">
+        <v>46188</v>
+      </c>
+      <c r="C612" s="52">
+        <v>0.39097222222222222</v>
+      </c>
+      <c r="D612" s="20" t="s">
+        <v>1273</v>
+      </c>
+      <c r="E612" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="F612" s="20" t="s">
+        <v>1493</v>
+      </c>
+      <c r="G612" s="20" t="s">
+        <v>794</v>
+      </c>
+      <c r="H612" s="20" t="s">
+        <v>1494</v>
+      </c>
+      <c r="I612" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="J612" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="K612" s="20" t="s">
+        <v>945</v>
+      </c>
+      <c r="L612" s="50" t="s">
+        <v>945</v>
+      </c>
+      <c r="M612" s="20" t="s">
+        <v>1495</v>
+      </c>
+    </row>
+    <row r="613" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A613" s="22">
+        <v>612</v>
+      </c>
+      <c r="B613" s="51">
+        <v>46188</v>
+      </c>
+      <c r="C613" s="52">
+        <v>0.40138888888888891</v>
+      </c>
+      <c r="D613" s="20" t="s">
+        <v>1273</v>
+      </c>
+      <c r="E613" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="F613" s="20" t="s">
+        <v>1496</v>
+      </c>
+      <c r="G613" s="20" t="s">
+        <v>1497</v>
+      </c>
+      <c r="H613" s="20" t="s">
+        <v>1498</v>
+      </c>
+      <c r="I613" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="J613" s="20" t="s">
+        <v>934</v>
+      </c>
+      <c r="K613" s="20" t="s">
+        <v>1491</v>
+      </c>
+      <c r="L613" s="53">
+        <v>46188</v>
+      </c>
+      <c r="M613" s="20" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="614" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A614" s="30">
+        <v>613</v>
+      </c>
+      <c r="B614" s="51">
+        <v>46188</v>
+      </c>
+      <c r="C614" s="52">
+        <v>0.4236111111111111</v>
+      </c>
+      <c r="D614" s="20" t="s">
+        <v>1273</v>
+      </c>
+      <c r="E614" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="F614" s="20" t="s">
+        <v>1500</v>
+      </c>
+      <c r="G614" s="20" t="s">
+        <v>1501</v>
+      </c>
+      <c r="H614" s="20" t="s">
+        <v>1502</v>
+      </c>
+      <c r="I614" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="J614" s="20" t="s">
+        <v>934</v>
+      </c>
+      <c r="K614" s="20" t="s">
+        <v>1491</v>
+      </c>
+      <c r="L614" s="53">
+        <v>46188</v>
+      </c>
+      <c r="M614" s="20" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="615" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A615" s="39">
+        <v>614</v>
+      </c>
+      <c r="B615" s="51">
+        <v>46188</v>
+      </c>
+      <c r="C615" s="52">
+        <v>0.43055555555555558</v>
+      </c>
+      <c r="D615" s="20" t="s">
+        <v>1273</v>
+      </c>
+      <c r="E615" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="F615" s="20" t="s">
+        <v>1504</v>
+      </c>
+      <c r="G615" s="20" t="s">
+        <v>1505</v>
+      </c>
+      <c r="H615" s="20" t="s">
+        <v>1506</v>
+      </c>
+      <c r="I615" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="J615" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="K615" s="20" t="s">
+        <v>1507</v>
+      </c>
+      <c r="L615" s="50" t="s">
+        <v>945</v>
+      </c>
+      <c r="M615" s="20" t="s">
+        <v>1508</v>
+      </c>
+    </row>
+    <row r="616" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A616" s="30">
+        <v>615</v>
+      </c>
+      <c r="B616" s="51">
+        <v>46188</v>
+      </c>
+      <c r="C616" s="52">
+        <v>0.44097222222222221</v>
+      </c>
+      <c r="D616" s="20" t="s">
+        <v>1273</v>
+      </c>
+      <c r="E616" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="F616" s="20" t="s">
+        <v>1509</v>
+      </c>
+      <c r="G616" s="20" t="s">
+        <v>1114</v>
+      </c>
+      <c r="H616" s="20" t="s">
+        <v>1510</v>
+      </c>
+      <c r="I616" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="J616" s="20" t="s">
+        <v>934</v>
+      </c>
+      <c r="K616" s="20" t="s">
+        <v>1272</v>
+      </c>
+      <c r="L616" s="53">
+        <v>46188</v>
+      </c>
+      <c r="M616" s="20" t="s">
+        <v>1511</v>
+      </c>
+    </row>
+    <row r="617" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A617" s="22">
+        <v>616</v>
+      </c>
+      <c r="B617" s="51">
+        <v>46188</v>
+      </c>
+      <c r="C617" s="52">
+        <v>0.45416666666666666</v>
+      </c>
+      <c r="D617" s="20" t="s">
+        <v>1273</v>
+      </c>
+      <c r="E617" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="F617" s="20" t="s">
+        <v>1512</v>
+      </c>
+      <c r="G617" s="20" t="s">
+        <v>1513</v>
+      </c>
+      <c r="H617" s="20" t="s">
+        <v>1514</v>
+      </c>
+      <c r="I617" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="J617" s="20" t="s">
+        <v>934</v>
+      </c>
+      <c r="K617" s="20" t="s">
+        <v>1295</v>
+      </c>
+      <c r="L617" s="53">
+        <v>46188</v>
+      </c>
+      <c r="M617" s="20" t="s">
+        <v>1515</v>
+      </c>
+    </row>
+    <row r="618" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A618" s="30">
+        <v>617</v>
+      </c>
+      <c r="B618" s="51">
+        <v>46188</v>
+      </c>
+      <c r="C618" s="52">
+        <v>0.4597222222222222</v>
+      </c>
+      <c r="D618" s="20" t="s">
+        <v>1273</v>
+      </c>
+      <c r="E618" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="F618" s="20" t="s">
+        <v>1516</v>
+      </c>
+      <c r="G618" s="20" t="s">
+        <v>777</v>
+      </c>
+      <c r="H618" s="20" t="s">
+        <v>1517</v>
+      </c>
+      <c r="I618" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="J618" s="20" t="s">
+        <v>934</v>
+      </c>
+      <c r="K618" s="20" t="s">
+        <v>1272</v>
+      </c>
+      <c r="L618" s="53">
+        <v>46188</v>
+      </c>
+      <c r="M618" s="20" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="619" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A619" s="39">
+        <v>618</v>
+      </c>
+      <c r="B619" s="51">
+        <v>46188</v>
+      </c>
+      <c r="C619" s="52">
+        <v>0.51388888888888884</v>
+      </c>
+      <c r="D619" s="20" t="s">
+        <v>1273</v>
+      </c>
+      <c r="E619" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="F619" s="20" t="s">
+        <v>1333</v>
+      </c>
+      <c r="G619" s="20" t="s">
+        <v>789</v>
+      </c>
+      <c r="H619" s="20" t="s">
+        <v>1519</v>
+      </c>
+      <c r="I619" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="J619" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="K619" s="20" t="s">
+        <v>945</v>
+      </c>
+      <c r="L619" s="50" t="s">
+        <v>945</v>
+      </c>
+      <c r="M619" s="20" t="s">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="620" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A620" s="30">
+        <v>619</v>
+      </c>
+      <c r="B620" s="51">
+        <v>46188</v>
+      </c>
+      <c r="C620" s="52">
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="D620" s="20" t="s">
+        <v>1273</v>
+      </c>
+      <c r="E620" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="F620" s="20" t="s">
+        <v>1521</v>
+      </c>
+      <c r="G620" s="20" t="s">
+        <v>1386</v>
+      </c>
+      <c r="H620" s="20" t="s">
+        <v>1522</v>
+      </c>
+      <c r="I620" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="J620" s="20" t="s">
+        <v>934</v>
+      </c>
+      <c r="K620" s="20" t="s">
+        <v>1295</v>
+      </c>
+      <c r="L620" s="53">
+        <v>46188</v>
+      </c>
+      <c r="M620" s="20" t="s">
+        <v>1523</v>
+      </c>
+    </row>
+    <row r="621" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A621" s="22">
+        <v>620</v>
+      </c>
+      <c r="B621" s="51">
+        <v>46188</v>
+      </c>
+      <c r="C621" s="52">
+        <v>0.55833333333333335</v>
+      </c>
+      <c r="D621" s="20" t="s">
+        <v>1273</v>
+      </c>
+      <c r="E621" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="F621" s="20" t="s">
+        <v>1524</v>
+      </c>
+      <c r="G621" s="20" t="s">
+        <v>1111</v>
+      </c>
+      <c r="H621" s="20" t="s">
+        <v>1525</v>
+      </c>
+      <c r="I621" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="J621" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="K621" s="20" t="s">
+        <v>945</v>
+      </c>
+      <c r="L621" s="50" t="s">
+        <v>945</v>
+      </c>
+      <c r="M621" s="20" t="s">
+        <v>1526</v>
+      </c>
+    </row>
+    <row r="622" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A622" s="30">
+        <v>621</v>
+      </c>
+      <c r="B622" s="51">
+        <v>46188</v>
+      </c>
+      <c r="C622" s="52">
+        <v>0.56597222222222221</v>
+      </c>
+      <c r="D622" s="20" t="s">
+        <v>1273</v>
+      </c>
+      <c r="E622" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="F622" s="20" t="s">
+        <v>1527</v>
+      </c>
+      <c r="G622" s="20" t="s">
+        <v>1528</v>
+      </c>
+      <c r="H622" s="20" t="s">
+        <v>1529</v>
+      </c>
+      <c r="I622" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="J622" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="K622" s="20" t="s">
+        <v>945</v>
+      </c>
+      <c r="L622" s="50" t="s">
+        <v>945</v>
+      </c>
+      <c r="M622" s="20" t="s">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="623" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A623" s="39">
+        <v>622</v>
+      </c>
+      <c r="B623" s="51">
+        <v>46188</v>
+      </c>
+      <c r="C623" s="52">
+        <v>0.56944444444444442</v>
+      </c>
+      <c r="D623" s="20" t="s">
+        <v>1273</v>
+      </c>
+      <c r="E623" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="F623" s="20" t="s">
+        <v>1500</v>
+      </c>
+      <c r="G623" s="20" t="s">
+        <v>1513</v>
+      </c>
+      <c r="H623" s="20" t="s">
+        <v>1531</v>
+      </c>
+      <c r="I623" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="J623" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="K623" s="20" t="s">
+        <v>945</v>
+      </c>
+      <c r="L623" s="50" t="s">
+        <v>945</v>
+      </c>
+      <c r="M623" s="20" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="624" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A624" s="30">
+        <v>623</v>
+      </c>
+      <c r="B624" s="51">
+        <v>46188</v>
+      </c>
+      <c r="C624" s="52">
+        <v>0.59097222222222223</v>
+      </c>
+      <c r="D624" s="20" t="s">
+        <v>1273</v>
+      </c>
+      <c r="E624" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="F624" s="20" t="s">
+        <v>1533</v>
+      </c>
+      <c r="G624" s="20" t="s">
+        <v>1513</v>
+      </c>
+      <c r="H624" s="20" t="s">
+        <v>1534</v>
+      </c>
+      <c r="I624" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="J624" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="K624" s="20" t="s">
+        <v>945</v>
+      </c>
+      <c r="L624" s="50" t="s">
+        <v>945</v>
+      </c>
+      <c r="M624" s="20" t="s">
+        <v>1535</v>
+      </c>
+    </row>
+    <row r="625" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A625" s="22">
+        <v>624</v>
+      </c>
+      <c r="B625" s="51">
+        <v>46188</v>
+      </c>
+      <c r="C625" s="52">
+        <v>0.28263888888888888</v>
+      </c>
+      <c r="D625" s="20" t="s">
+        <v>1273</v>
+      </c>
+      <c r="E625" s="20" t="s">
+        <v>984</v>
+      </c>
+      <c r="F625" s="20" t="s">
+        <v>1536</v>
+      </c>
+      <c r="G625" s="20" t="s">
+        <v>1464</v>
+      </c>
+      <c r="H625" s="20" t="s">
+        <v>1537</v>
+      </c>
+      <c r="I625" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="J625" s="20" t="s">
+        <v>934</v>
+      </c>
+      <c r="K625" s="20" t="s">
+        <v>1295</v>
+      </c>
+      <c r="L625" s="53">
+        <v>46188</v>
+      </c>
+      <c r="M625" s="20" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="626" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A626" s="30">
+        <v>625</v>
+      </c>
+      <c r="B626" s="51">
+        <v>46188</v>
+      </c>
+      <c r="C626" s="52">
+        <v>0.28333333333333333</v>
+      </c>
+      <c r="D626" s="20" t="s">
+        <v>1273</v>
+      </c>
+      <c r="E626" s="20" t="s">
+        <v>984</v>
+      </c>
+      <c r="F626" s="20" t="s">
+        <v>1536</v>
+      </c>
+      <c r="G626" s="20" t="s">
+        <v>1539</v>
+      </c>
+      <c r="H626" s="20" t="s">
+        <v>1540</v>
+      </c>
+      <c r="I626" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="J626" s="20" t="s">
+        <v>934</v>
+      </c>
+      <c r="K626" s="20" t="s">
+        <v>1491</v>
+      </c>
+      <c r="L626" s="53">
+        <v>46188</v>
+      </c>
+      <c r="M626" s="20" t="s">
+        <v>1541</v>
+      </c>
+    </row>
+    <row r="627" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A627" s="39">
+        <v>626</v>
+      </c>
+      <c r="B627" s="51">
+        <v>46188</v>
+      </c>
+      <c r="C627" s="52">
+        <v>0.28749999999999998</v>
+      </c>
+      <c r="D627" s="20" t="s">
+        <v>1273</v>
+      </c>
+      <c r="E627" s="20" t="s">
+        <v>1542</v>
+      </c>
+      <c r="F627" s="20" t="s">
+        <v>1441</v>
+      </c>
+      <c r="G627" s="20" t="s">
+        <v>1539</v>
+      </c>
+      <c r="H627" s="20" t="s">
+        <v>1543</v>
+      </c>
+      <c r="I627" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="J627" s="20" t="s">
+        <v>934</v>
+      </c>
+      <c r="K627" s="20" t="s">
+        <v>1491</v>
+      </c>
+      <c r="L627" s="53">
+        <v>46188</v>
+      </c>
+      <c r="M627" s="20" t="s">
+        <v>1544</v>
+      </c>
+    </row>
+    <row r="628" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A628" s="30">
+        <v>627</v>
+      </c>
+      <c r="B628" s="51">
+        <v>46188</v>
+      </c>
+      <c r="C628" s="52">
+        <v>0.32083333333333336</v>
+      </c>
+      <c r="D628" s="20" t="s">
+        <v>1273</v>
+      </c>
+      <c r="E628" s="20" t="s">
+        <v>1542</v>
+      </c>
+      <c r="F628" s="20" t="s">
+        <v>309</v>
+      </c>
+      <c r="G628" s="20" t="s">
+        <v>1157</v>
+      </c>
+      <c r="H628" s="20" t="s">
+        <v>1545</v>
+      </c>
+      <c r="I628" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="J628" s="20" t="s">
+        <v>934</v>
+      </c>
+      <c r="K628" s="20" t="s">
+        <v>1546</v>
+      </c>
+      <c r="L628" s="53">
+        <v>46188</v>
+      </c>
+      <c r="M628" s="20" t="s">
+        <v>1547</v>
+      </c>
+    </row>
+    <row r="629" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A629" s="22">
+        <v>628</v>
+      </c>
+      <c r="B629" s="51">
+        <v>46188</v>
+      </c>
+      <c r="C629" s="52">
+        <v>0.3215277777777778</v>
+      </c>
+      <c r="D629" s="20" t="s">
+        <v>1273</v>
+      </c>
+      <c r="E629" s="20" t="s">
+        <v>1548</v>
+      </c>
+      <c r="F629" s="20" t="s">
+        <v>1549</v>
+      </c>
+      <c r="G629" s="20" t="s">
+        <v>789</v>
+      </c>
+      <c r="H629" s="20" t="s">
+        <v>1550</v>
+      </c>
+      <c r="I629" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="J629" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="K629" s="20" t="s">
+        <v>1466</v>
+      </c>
+      <c r="L629" s="50" t="s">
+        <v>945</v>
+      </c>
+      <c r="M629" s="20" t="s">
+        <v>1551</v>
+      </c>
+    </row>
+    <row r="630" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A630" s="30">
+        <v>629</v>
+      </c>
+      <c r="B630" s="51">
+        <v>46188</v>
+      </c>
+      <c r="C630" s="52">
+        <v>0.36527777777777776</v>
+      </c>
+      <c r="D630" s="20" t="s">
+        <v>1273</v>
+      </c>
+      <c r="E630" s="20" t="s">
+        <v>1152</v>
+      </c>
+      <c r="F630" s="20" t="s">
+        <v>1324</v>
+      </c>
+      <c r="G630" s="20" t="s">
+        <v>1157</v>
+      </c>
+      <c r="H630" s="20" t="s">
+        <v>1552</v>
+      </c>
+      <c r="I630" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="J630" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="K630" s="20" t="s">
+        <v>945</v>
+      </c>
+      <c r="L630" s="50" t="s">
+        <v>945</v>
+      </c>
+      <c r="M630" s="20" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="631" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A631" s="39">
+        <v>630</v>
+      </c>
+      <c r="B631" s="51">
+        <v>46188</v>
+      </c>
+      <c r="C631" s="52">
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="D631" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E631" s="20" t="s">
+        <v>1324</v>
+      </c>
+      <c r="F631" s="20" t="s">
+        <v>1554</v>
+      </c>
+      <c r="G631" s="20" t="s">
+        <v>802</v>
+      </c>
+      <c r="H631" s="20" t="s">
+        <v>1555</v>
+      </c>
+      <c r="I631" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="J631" s="20" t="s">
+        <v>934</v>
+      </c>
+      <c r="K631" s="20" t="s">
+        <v>1546</v>
+      </c>
+      <c r="L631" s="53">
+        <v>46188</v>
+      </c>
+      <c r="M631" s="20" t="s">
+        <v>1556</v>
+      </c>
+    </row>
+    <row r="632" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A632" s="30">
+        <v>631</v>
+      </c>
+      <c r="B632" s="51">
+        <v>46188</v>
+      </c>
+      <c r="C632" s="52">
+        <v>0.57013888888888886</v>
+      </c>
+      <c r="D632" s="20" t="s">
+        <v>1273</v>
+      </c>
+      <c r="E632" s="20" t="s">
+        <v>1152</v>
+      </c>
+      <c r="F632" s="20" t="s">
+        <v>1557</v>
+      </c>
+      <c r="G632" s="20" t="s">
+        <v>1558</v>
+      </c>
+      <c r="H632" s="20" t="s">
+        <v>1559</v>
+      </c>
+      <c r="I632" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="J632" s="20" t="s">
+        <v>791</v>
+      </c>
+      <c r="K632" s="20" t="s">
+        <v>1560</v>
+      </c>
+      <c r="L632" s="53">
+        <v>46188</v>
+      </c>
+      <c r="M632" s="20" t="s">
+        <v>1561</v>
+      </c>
+    </row>
+    <row r="633" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A633" s="22">
+        <v>632</v>
+      </c>
+      <c r="B633" s="51">
+        <v>46188</v>
+      </c>
+      <c r="C633" s="52">
+        <v>0.60833333333333328</v>
+      </c>
+      <c r="D633" s="20" t="s">
+        <v>1273</v>
+      </c>
+      <c r="E633" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="F633" s="20" t="s">
+        <v>1562</v>
+      </c>
+      <c r="G633" s="20" t="s">
+        <v>1563</v>
+      </c>
+      <c r="H633" s="20" t="s">
+        <v>1564</v>
+      </c>
+      <c r="I633" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="J633" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="K633" s="20" t="s">
+        <v>1546</v>
+      </c>
+      <c r="L633" s="50" t="s">
+        <v>945</v>
+      </c>
+      <c r="M633" s="20" t="s">
+        <v>1565</v>
+      </c>
+    </row>
+    <row r="634" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A634" s="30">
+        <v>633</v>
+      </c>
+      <c r="B634" s="51">
+        <v>46188</v>
+      </c>
+      <c r="C634" s="52">
+        <v>0.60833333333333328</v>
+      </c>
+      <c r="D634" s="20" t="s">
+        <v>1273</v>
+      </c>
+      <c r="E634" s="20" t="s">
+        <v>1566</v>
+      </c>
+      <c r="F634" s="20" t="s">
+        <v>1567</v>
+      </c>
+      <c r="G634" s="20" t="s">
+        <v>1157</v>
+      </c>
+      <c r="H634" s="20" t="s">
+        <v>1568</v>
+      </c>
+      <c r="I634" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="J634" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="K634" s="20" t="s">
+        <v>945</v>
+      </c>
+      <c r="L634" s="50" t="s">
+        <v>945</v>
+      </c>
+      <c r="M634" s="20" t="s">
+        <v>1569</v>
+      </c>
+    </row>
+    <row r="635" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A635" s="39">
+        <v>634</v>
+      </c>
+      <c r="B635" s="51">
+        <v>46188</v>
+      </c>
+      <c r="C635" s="52">
+        <v>0.60833333333333328</v>
+      </c>
+      <c r="D635" s="20" t="s">
+        <v>1273</v>
+      </c>
+      <c r="E635" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="F635" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="G635" s="20" t="s">
+        <v>1570</v>
+      </c>
+      <c r="H635" s="20" t="s">
+        <v>1571</v>
+      </c>
+      <c r="I635" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="J635" s="20" t="s">
+        <v>934</v>
+      </c>
+      <c r="K635" s="20" t="s">
+        <v>1472</v>
+      </c>
+      <c r="L635" s="53">
+        <v>46188</v>
+      </c>
+      <c r="M635" s="20" t="s">
+        <v>1572</v>
+      </c>
+    </row>
+    <row r="636" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A636" s="30">
+        <v>635</v>
+      </c>
+      <c r="B636" s="51">
+        <v>46188</v>
+      </c>
+      <c r="C636" s="52">
+        <v>0.4597222222222222</v>
+      </c>
+      <c r="D636" s="20" t="s">
+        <v>1273</v>
+      </c>
+      <c r="E636" s="20" t="s">
+        <v>1474</v>
+      </c>
+      <c r="F636" s="20" t="s">
+        <v>1475</v>
+      </c>
+      <c r="G636" s="20" t="s">
+        <v>1573</v>
+      </c>
+      <c r="H636" s="20" t="s">
+        <v>1574</v>
+      </c>
+      <c r="I636" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="J636" s="20" t="s">
+        <v>934</v>
+      </c>
+      <c r="K636" s="20" t="s">
+        <v>1575</v>
+      </c>
+      <c r="L636" s="53">
+        <v>46188</v>
+      </c>
+      <c r="M636" s="20" t="s">
+        <v>1576</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:M5 B6:M15 A6:A318 L16:M16 B16:K18 M17:M18 B19:M60 B61:I61 K61:M61 B62:M90 B91:J91 L91:M91 B92:M110 B111:J112 L111:M112 B113:M126 B127:J129 L127:M129 B130:M162 B163:J163 L163:M163 B164:M307 A321 A324 A327 A330 A333 A336 A339 A342 A345 A348 A351 A354 A357 A360 A363 A366 A369 A372 A375 A378 A381 A384 A387 A390 A393 A396 A399 A402 A405 A408 A411 A414 A417 A420 A423 A426 A429 A432 A435 A438 A441 A444 A447 A450 A453 A456 A459 A462 A465 A470 A475 A480 A485 A490 A495 A500 A505 A510 A515 A520 A525">
+  <conditionalFormatting sqref="A2:M5 B6:M15 A6:A318 L16:M16 B16:K18 M17:M18 B19:M60 B61:I61 K61:M61 B62:M90 B91:J91 L91:M91 B92:M110 B111:J112 L111:M112 B113:M126 B127:J129 L127:M129 B130:M162 B163:J163 L163:M163 B164:M307 A321 A324 A327 A330 A333 A336 A339 A342 A345 A348 A351 A354 A357 A360 A363 A366 A369 A372 A375 A378 A381 A384 A387 A390 A393 A396 A399 A402 A405 A408 A411 A414 A417 A420 A423 A426 A429 A432 A435 A438 A441 A444 A447 A450 A453 A456 A459 A462 A465 A470 A475 A480 A485 A490 A495 A500 A505 A510 A515 A520 A525 A529 A533 A537 A541 A545 A549 A553 A557 A561 A565 A569 A573 A577 A581 A585 A589 A593 A597 A601 A605 A609 A613 A617 A621 A625 A629 A633">
     <cfRule type="expression" dxfId="71" priority="129">
       <formula>$J2="EN ATENCIÓN"</formula>
     </cfRule>
@@ -24838,7 +30814,7 @@
       <formula>$J2="INFORMATIVO"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B19:M60 A2:M5 B6:M15 A6:A318 L16:M16 B16:K18 M17:M18 B61:I61 K61:M61 B62:M90 B91:J91 L91:M91 B92:M110 B111:J112 L111:M112 B113:M126 B127:J129 L127:M129 B130:M162 B163:J163 L163:M163 B164:M307 A321 A324 A327 A330 A333 A336 A339 A342 A345 A348 A351 A354 A357 A360 A363 A366 A369 A372 A375 A378 A381 A384 A387 A390 A393 A396 A399 A402 A405 A408 A411 A414 A417 A420 A423 A426 A429 A432 A435 A438 A441 A444 A447 A450 A453 A456 A459 A462 A465 A470 A475 A480 A485 A490 A495 A500 A505 A510 A515 A520 A525">
+  <conditionalFormatting sqref="B19:M60 A2:M5 B6:M15 A6:A318 L16:M16 B16:K18 M17:M18 B61:I61 K61:M61 B62:M90 B91:J91 L91:M91 B92:M110 B111:J112 L111:M112 B113:M126 B127:J129 L127:M129 B130:M162 B163:J163 L163:M163 B164:M307 A321 A324 A327 A330 A333 A336 A339 A342 A345 A348 A351 A354 A357 A360 A363 A366 A369 A372 A375 A378 A381 A384 A387 A390 A393 A396 A399 A402 A405 A408 A411 A414 A417 A420 A423 A426 A429 A432 A435 A438 A441 A444 A447 A450 A453 A456 A459 A462 A465 A470 A475 A480 A485 A490 A495 A500 A505 A510 A515 A520 A525 A529 A533 A537 A541 A545 A549 A553 A557 A561 A565 A569 A573 A577 A581 A585 A589 A593 A597 A601 A605 A609 A613 A617 A621 A625 A629 A633">
     <cfRule type="expression" dxfId="66" priority="127">
       <formula>$J2="ATENDIDO"</formula>
     </cfRule>
